--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
@@ -1,30 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC07230B-F1E4-4381-A817-EDF841EAF34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7B0858-41A2-464C-80C7-AE5C0E209F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="1770" windowWidth="33090" windowHeight="18225" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
-    <sheet name="【テストターゲット名】_クラス単体" sheetId="23" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体" sheetId="24" r:id="rId4"/>
-    <sheet name="取引単体" sheetId="17" r:id="rId5"/>
+    <sheet name="【リクエストID】_クラス単体テスト" sheetId="23" r:id="rId3"/>
+    <sheet name="【リクエストID】_リクエスト単体テスト" sheetId="24" r:id="rId4"/>
+    <sheet name="取引単体テスト" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体!$A$10:$R$311</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$296</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体!$A$1:$R$311</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【リクエストID】_クラス単体テスト!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体テスト!$A$10:$R$311</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">【リクエストID】_クラス単体テスト!$A$1:$R$296</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$O$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">【リクエストID】_クラス単体テスト!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体テスト!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -65,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="541">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="540">
   <si>
     <t>システム機能設計書</t>
     <rPh sb="4" eb="6">
@@ -6170,10 +6169,6 @@
       <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>リクエストID：XXX</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>バリデーション</t>
@@ -8639,8 +8634,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7953375" y="285750"/>
-          <a:ext cx="1400175" cy="590550"/>
+          <a:off x="7905750" y="285750"/>
+          <a:ext cx="1390650" cy="590550"/>
           <a:chOff x="591" y="61"/>
           <a:chExt cx="147" cy="62"/>
         </a:xfrm>
@@ -10167,8 +10162,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15497175" y="1781175"/>
-          <a:ext cx="4914900" cy="2733675"/>
+          <a:off x="15462250" y="1749425"/>
+          <a:ext cx="4899025" cy="2670175"/>
           <a:chOff x="16335375" y="4752975"/>
           <a:chExt cx="4914900" cy="2733675"/>
         </a:xfrm>
@@ -11788,9 +11783,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -11828,9 +11823,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -11863,26 +11858,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -11915,26 +11893,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -12112,9 +12073,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K513"/>
-  <sheetFormatPr defaultColWidth="6.625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="6.58203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="16384" width="6.625" style="1"/>
+    <col min="1" max="16384" width="6.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="13.5" customHeight="1">
@@ -12200,18 +12161,18 @@
       <c r="G31" s="8"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="6:11" ht="18.75">
+    <row r="32" spans="6:11" ht="19">
       <c r="F32" s="5"/>
       <c r="G32" s="8"/>
       <c r="H32" s="5"/>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="6:10" ht="18.75">
+    <row r="33" spans="6:10" ht="19">
       <c r="F33" s="5"/>
       <c r="H33" s="5"/>
       <c r="J33" s="10"/>
     </row>
-    <row r="34" spans="6:10" ht="18.75">
+    <row r="34" spans="6:10" ht="19">
       <c r="F34" s="5"/>
       <c r="H34" s="5"/>
       <c r="J34" s="9"/>
@@ -12714,9 +12675,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN34"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="11.25"/>
+  <sheetFormatPr defaultColWidth="3.58203125" defaultRowHeight="11"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="22"/>
+    <col min="1" max="16384" width="3.58203125" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
@@ -12745,7 +12706,7 @@
       <c r="Q1" s="217"/>
       <c r="R1" s="218"/>
       <c r="S1" s="225" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T1" s="226"/>
       <c r="U1" s="226"/>
@@ -13944,7 +13905,7 @@
       <c r="AH33" s="265"/>
       <c r="AI33" s="266"/>
     </row>
-    <row r="34" spans="1:35" ht="14.25">
+    <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
@@ -14143,18 +14104,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R296"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="2" width="8.625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="29" customWidth="1"/>
-    <col min="4" max="5" width="8.625" style="28" customWidth="1"/>
-    <col min="6" max="6" width="40.625" style="28" customWidth="1"/>
-    <col min="7" max="7" width="28.125" style="28" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="16.375" style="28" customWidth="1"/>
-    <col min="10" max="11" width="25.625" style="28" customWidth="1"/>
+    <col min="1" max="2" width="8.58203125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="8.58203125" style="29" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="28" customWidth="1"/>
+    <col min="6" max="6" width="40.58203125" style="28" customWidth="1"/>
+    <col min="7" max="7" width="28.08203125" style="28" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="16.33203125" style="28" customWidth="1"/>
+    <col min="10" max="11" width="25.58203125" style="28" customWidth="1"/>
     <col min="12" max="12" width="19.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.625" style="28" customWidth="1"/>
-    <col min="14" max="18" width="8.625" style="28" customWidth="1"/>
+    <col min="13" max="13" width="12.58203125" style="28" customWidth="1"/>
+    <col min="14" max="18" width="8.58203125" style="28" customWidth="1"/>
     <col min="19" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
@@ -14200,7 +14161,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12" thickBot="1">
+    <row r="8" spans="1:18" ht="11.5" thickBot="1">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="31"/>
@@ -14277,7 +14238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5">
+    <row r="11" spans="1:18" ht="22">
       <c r="A11" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E11),
@@ -14320,7 +14281,7 @@
       <c r="Q11" s="51"/>
       <c r="R11" s="53"/>
     </row>
-    <row r="12" spans="1:18" ht="22.5">
+    <row r="12" spans="1:18" ht="22">
       <c r="A12" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E12),
@@ -14357,7 +14318,7 @@
       <c r="Q12" s="57"/>
       <c r="R12" s="59"/>
     </row>
-    <row r="13" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="13" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A13" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E13),
@@ -14396,7 +14357,7 @@
       <c r="Q13" s="58"/>
       <c r="R13" s="57"/>
     </row>
-    <row r="14" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="14" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A14" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E14),
@@ -14431,7 +14392,7 @@
       <c r="Q14" s="58"/>
       <c r="R14" s="57"/>
     </row>
-    <row r="15" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="15" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A15" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E15),
@@ -14466,7 +14427,7 @@
       <c r="Q15" s="58"/>
       <c r="R15" s="57"/>
     </row>
-    <row r="16" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="16" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A16" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E16),
@@ -14501,7 +14462,7 @@
       <c r="Q16" s="57"/>
       <c r="R16" s="59"/>
     </row>
-    <row r="17" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="17" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A17" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E17),
@@ -14536,7 +14497,7 @@
       <c r="Q17" s="57"/>
       <c r="R17" s="59"/>
     </row>
-    <row r="18" spans="1:18" ht="22.5">
+    <row r="18" spans="1:18" ht="22">
       <c r="A18" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E18),
@@ -14575,7 +14536,7 @@
       <c r="Q18" s="57"/>
       <c r="R18" s="59"/>
     </row>
-    <row r="19" spans="1:18" ht="22.5">
+    <row r="19" spans="1:18" ht="22">
       <c r="A19" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E19),
@@ -14610,7 +14571,7 @@
       <c r="Q19" s="57"/>
       <c r="R19" s="59"/>
     </row>
-    <row r="20" spans="1:18" ht="22.5">
+    <row r="20" spans="1:18" ht="22">
       <c r="A20" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E20),
@@ -14645,7 +14606,7 @@
       <c r="Q20" s="57"/>
       <c r="R20" s="59"/>
     </row>
-    <row r="21" spans="1:18" ht="22.5">
+    <row r="21" spans="1:18" ht="22">
       <c r="A21" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E21),
@@ -14682,7 +14643,7 @@
       <c r="Q21" s="57"/>
       <c r="R21" s="59"/>
     </row>
-    <row r="22" spans="1:18" ht="22.5">
+    <row r="22" spans="1:18" ht="22">
       <c r="A22" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A22" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E22),
@@ -14717,7 +14678,7 @@
       <c r="Q22" s="57"/>
       <c r="R22" s="59"/>
     </row>
-    <row r="23" spans="1:18" ht="22.5">
+    <row r="23" spans="1:18" ht="22">
       <c r="A23" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A23" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E23),
@@ -14752,7 +14713,7 @@
       <c r="Q23" s="57"/>
       <c r="R23" s="59"/>
     </row>
-    <row r="24" spans="1:18" ht="22.5">
+    <row r="24" spans="1:18" ht="22">
       <c r="A24" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E24),
@@ -14787,7 +14748,7 @@
       <c r="Q24" s="57"/>
       <c r="R24" s="59"/>
     </row>
-    <row r="25" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="25" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A25" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E25),
@@ -14826,7 +14787,7 @@
       <c r="Q25" s="58"/>
       <c r="R25" s="57"/>
     </row>
-    <row r="26" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="26" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A26" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A26" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E26),
@@ -14861,7 +14822,7 @@
       <c r="Q26" s="58"/>
       <c r="R26" s="57"/>
     </row>
-    <row r="27" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="27" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A27" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E27),
@@ -14900,7 +14861,7 @@
       <c r="Q27" s="58"/>
       <c r="R27" s="57"/>
     </row>
-    <row r="28" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="28" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A28" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E28),
@@ -14935,7 +14896,7 @@
       <c r="Q28" s="58"/>
       <c r="R28" s="57"/>
     </row>
-    <row r="29" spans="1:18" ht="22.5">
+    <row r="29" spans="1:18" ht="22">
       <c r="A29" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E29),
@@ -14972,7 +14933,7 @@
       <c r="Q29" s="59"/>
       <c r="R29" s="59"/>
     </row>
-    <row r="30" spans="1:18" ht="22.5">
+    <row r="30" spans="1:18" ht="22">
       <c r="A30" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E30),
@@ -15007,7 +14968,7 @@
       <c r="Q30" s="59"/>
       <c r="R30" s="59"/>
     </row>
-    <row r="31" spans="1:18" ht="22.5">
+    <row r="31" spans="1:18" ht="22">
       <c r="A31" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A31" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E31),
@@ -15042,7 +15003,7 @@
       <c r="Q31" s="59"/>
       <c r="R31" s="59"/>
     </row>
-    <row r="32" spans="1:18" ht="22.5">
+    <row r="32" spans="1:18" ht="22">
       <c r="A32" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A32" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E32),
@@ -15077,7 +15038,7 @@
       <c r="Q32" s="59"/>
       <c r="R32" s="59"/>
     </row>
-    <row r="33" spans="1:18" ht="22.5">
+    <row r="33" spans="1:18" ht="22">
       <c r="A33" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A33" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E33),
@@ -15114,7 +15075,7 @@
       <c r="Q33" s="59"/>
       <c r="R33" s="59"/>
     </row>
-    <row r="34" spans="1:18" ht="22.5">
+    <row r="34" spans="1:18" ht="22">
       <c r="A34" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A34" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E34),
@@ -15149,7 +15110,7 @@
       <c r="Q34" s="59"/>
       <c r="R34" s="59"/>
     </row>
-    <row r="35" spans="1:18" ht="45">
+    <row r="35" spans="1:18" ht="44">
       <c r="A35" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A35" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E35),
@@ -15186,7 +15147,7 @@
       <c r="Q35" s="59"/>
       <c r="R35" s="59"/>
     </row>
-    <row r="36" spans="1:18" ht="33.75">
+    <row r="36" spans="1:18" ht="33">
       <c r="A36" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A36" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E36),
@@ -15227,7 +15188,7 @@
       <c r="Q36" s="53"/>
       <c r="R36" s="53"/>
     </row>
-    <row r="37" spans="1:18" ht="33.75">
+    <row r="37" spans="1:18" ht="33">
       <c r="A37" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A37" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E37),
@@ -15262,7 +15223,7 @@
       <c r="Q37" s="53"/>
       <c r="R37" s="53"/>
     </row>
-    <row r="38" spans="1:18" ht="22.5">
+    <row r="38" spans="1:18" ht="22">
       <c r="A38" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A38" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E38),
@@ -15297,7 +15258,7 @@
       <c r="Q38" s="53"/>
       <c r="R38" s="53"/>
     </row>
-    <row r="39" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="39" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A39" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E39),
@@ -15332,7 +15293,7 @@
       <c r="Q39" s="51"/>
       <c r="R39" s="53"/>
     </row>
-    <row r="40" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="40" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A40" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E40),
@@ -15371,7 +15332,7 @@
       <c r="Q40" s="51"/>
       <c r="R40" s="53"/>
     </row>
-    <row r="41" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="41" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A41" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A41" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E41),
@@ -15406,7 +15367,7 @@
       <c r="Q41" s="51"/>
       <c r="R41" s="53"/>
     </row>
-    <row r="42" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="42" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A42" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A42" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E42),
@@ -15439,13 +15400,13 @@
         <v>59</v>
       </c>
       <c r="I42" s="170" t="s">
+        <v>533</v>
+      </c>
+      <c r="J42" s="37" t="s">
         <v>534</v>
       </c>
-      <c r="J42" s="37" t="s">
-        <v>535</v>
-      </c>
       <c r="K42" s="37" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L42" s="190" t="s">
         <v>173</v>
@@ -15459,7 +15420,7 @@
       <c r="Q42" s="192"/>
       <c r="R42" s="159"/>
     </row>
-    <row r="43" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="43" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A43" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A43" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E43),
@@ -15480,7 +15441,7 @@
         <v>133</v>
       </c>
       <c r="G43" s="48" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H43" s="48"/>
       <c r="I43" s="48"/>
@@ -15494,7 +15455,7 @@
       <c r="Q43" s="51"/>
       <c r="R43" s="53"/>
     </row>
-    <row r="44" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="44" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A44" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A44" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E44),
@@ -15529,7 +15490,7 @@
       <c r="Q44" s="51"/>
       <c r="R44" s="53"/>
     </row>
-    <row r="45" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="45" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A45" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A45" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E45),
@@ -15566,7 +15527,7 @@
       <c r="Q45" s="51"/>
       <c r="R45" s="53"/>
     </row>
-    <row r="46" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="46" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A46" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A46" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E46),
@@ -15601,7 +15562,7 @@
       <c r="Q46" s="51"/>
       <c r="R46" s="53"/>
     </row>
-    <row r="47" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="47" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A47" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A47" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E47),
@@ -15636,7 +15597,7 @@
       <c r="Q47" s="51"/>
       <c r="R47" s="53"/>
     </row>
-    <row r="48" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="48" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A48" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A48" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E48),
@@ -15659,7 +15620,7 @@
         <v>140</v>
       </c>
       <c r="G48" s="48" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H48" s="48"/>
       <c r="I48" s="48"/>
@@ -15673,7 +15634,7 @@
       <c r="Q48" s="51"/>
       <c r="R48" s="53"/>
     </row>
-    <row r="49" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="49" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A49" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A49" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E49),
@@ -15694,7 +15655,7 @@
         <v>141</v>
       </c>
       <c r="G49" s="48" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H49" s="48"/>
       <c r="I49" s="48"/>
@@ -15708,7 +15669,7 @@
       <c r="Q49" s="51"/>
       <c r="R49" s="53"/>
     </row>
-    <row r="50" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="50" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A50" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A50" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E50),
@@ -15745,7 +15706,7 @@
       <c r="Q50" s="57"/>
       <c r="R50" s="59"/>
     </row>
-    <row r="51" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="51" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A51" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A51" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E51),
@@ -15780,7 +15741,7 @@
       <c r="Q51" s="57"/>
       <c r="R51" s="59"/>
     </row>
-    <row r="52" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="52" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A52" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A52" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E52),
@@ -15815,7 +15776,7 @@
       <c r="Q52" s="57"/>
       <c r="R52" s="59"/>
     </row>
-    <row r="53" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="53" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A53" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A53" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E53),
@@ -15850,7 +15811,7 @@
       <c r="Q53" s="57"/>
       <c r="R53" s="59"/>
     </row>
-    <row r="54" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="54" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A54" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A54" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E54),
@@ -15885,7 +15846,7 @@
       <c r="Q54" s="57"/>
       <c r="R54" s="59"/>
     </row>
-    <row r="55" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="55" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A55" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A55" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E55),
@@ -15920,7 +15881,7 @@
       <c r="Q55" s="57"/>
       <c r="R55" s="59"/>
     </row>
-    <row r="56" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="56" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A56" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A56" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E56),
@@ -15957,7 +15918,7 @@
       <c r="Q56" s="57"/>
       <c r="R56" s="59"/>
     </row>
-    <row r="57" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="57" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A57" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A57" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E57),
@@ -15994,7 +15955,7 @@
       <c r="Q57" s="57"/>
       <c r="R57" s="59"/>
     </row>
-    <row r="58" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="58" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A58" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A58" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E58),
@@ -16031,7 +15992,7 @@
       <c r="Q58" s="57"/>
       <c r="R58" s="59"/>
     </row>
-    <row r="59" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="59" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A59" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A59" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E59),
@@ -16070,7 +16031,7 @@
       <c r="Q59" s="51"/>
       <c r="R59" s="53"/>
     </row>
-    <row r="60" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="60" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A60" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A60" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E60),
@@ -16105,7 +16066,7 @@
       <c r="Q60" s="51"/>
       <c r="R60" s="53"/>
     </row>
-    <row r="61" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="61" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A61" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A61" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E61),
@@ -16140,7 +16101,7 @@
       <c r="Q61" s="51"/>
       <c r="R61" s="53"/>
     </row>
-    <row r="62" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="62" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A62" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A62" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E62),
@@ -16175,7 +16136,7 @@
       <c r="Q62" s="51"/>
       <c r="R62" s="53"/>
     </row>
-    <row r="63" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="63" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A63" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A63" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E63),
@@ -16210,7 +16171,7 @@
       <c r="Q63" s="51"/>
       <c r="R63" s="53"/>
     </row>
-    <row r="64" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="64" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A64" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A64" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E64),
@@ -16247,7 +16208,7 @@
       <c r="Q64" s="51"/>
       <c r="R64" s="53"/>
     </row>
-    <row r="65" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="65" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A65" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A65" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E65),
@@ -16282,7 +16243,7 @@
       <c r="Q65" s="51"/>
       <c r="R65" s="53"/>
     </row>
-    <row r="66" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="66" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A66" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A66" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E66),
@@ -16317,7 +16278,7 @@
       <c r="Q66" s="51"/>
       <c r="R66" s="53"/>
     </row>
-    <row r="67" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="67" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A67" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A67" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E67),
@@ -16352,7 +16313,7 @@
       <c r="Q67" s="51"/>
       <c r="R67" s="53"/>
     </row>
-    <row r="68" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="68" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A68" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A68" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E68),
@@ -16387,7 +16348,7 @@
       <c r="Q68" s="51"/>
       <c r="R68" s="53"/>
     </row>
-    <row r="69" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="69" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A69" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A69" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E69),
@@ -16422,7 +16383,7 @@
       <c r="Q69" s="51"/>
       <c r="R69" s="53"/>
     </row>
-    <row r="70" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="70" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A70" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A70" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E70),
@@ -16457,7 +16418,7 @@
       <c r="Q70" s="51"/>
       <c r="R70" s="53"/>
     </row>
-    <row r="71" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="71" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A71" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A71" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E71),
@@ -16492,7 +16453,7 @@
       <c r="Q71" s="85"/>
       <c r="R71" s="86"/>
     </row>
-    <row r="72" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="72" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A72" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A72" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E72),
@@ -16671,7 +16632,7 @@
       <c r="Q76" s="53"/>
       <c r="R76" s="53"/>
     </row>
-    <row r="77" spans="1:18" ht="22.5">
+    <row r="77" spans="1:18" ht="22">
       <c r="A77" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A77" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E77),
@@ -16706,7 +16667,7 @@
       <c r="Q77" s="53"/>
       <c r="R77" s="53"/>
     </row>
-    <row r="78" spans="1:18" ht="22.5">
+    <row r="78" spans="1:18" ht="22">
       <c r="A78" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A78" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E78),
@@ -16737,13 +16698,13 @@
         <v>59</v>
       </c>
       <c r="I78" s="170" t="s">
+        <v>533</v>
+      </c>
+      <c r="J78" s="37" t="s">
+        <v>535</v>
+      </c>
+      <c r="K78" s="37" t="s">
         <v>534</v>
-      </c>
-      <c r="J78" s="37" t="s">
-        <v>536</v>
-      </c>
-      <c r="K78" s="37" t="s">
-        <v>535</v>
       </c>
       <c r="L78" s="190" t="s">
         <v>173</v>
@@ -16757,7 +16718,7 @@
       <c r="Q78" s="159"/>
       <c r="R78" s="159"/>
     </row>
-    <row r="79" spans="1:18" ht="67.5">
+    <row r="79" spans="1:18" ht="66">
       <c r="A79" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A79" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E79),
@@ -16782,16 +16743,16 @@
         <v>59</v>
       </c>
       <c r="I79" s="170" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J79" s="37" t="s">
+        <v>536</v>
+      </c>
+      <c r="K79" s="37" t="s">
         <v>537</v>
       </c>
-      <c r="K79" s="37" t="s">
-        <v>538</v>
-      </c>
       <c r="L79" s="190" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M79" s="190" t="s">
         <v>32</v>
@@ -16825,7 +16786,7 @@
         <v>184</v>
       </c>
       <c r="G80" s="48" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H80" s="48"/>
       <c r="I80" s="48"/>
@@ -16839,7 +16800,7 @@
       <c r="Q80" s="53"/>
       <c r="R80" s="53"/>
     </row>
-    <row r="81" spans="1:18" ht="33.75">
+    <row r="81" spans="1:18" ht="33">
       <c r="A81" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A81" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E81),
@@ -16876,7 +16837,7 @@
       <c r="Q81" s="53"/>
       <c r="R81" s="53"/>
     </row>
-    <row r="82" spans="1:18" ht="33.75">
+    <row r="82" spans="1:18" ht="33">
       <c r="A82" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A82" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E82),
@@ -16911,7 +16872,7 @@
       <c r="Q82" s="53"/>
       <c r="R82" s="53"/>
     </row>
-    <row r="83" spans="1:18" ht="22.5">
+    <row r="83" spans="1:18" ht="22">
       <c r="A83" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A83" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E83),
@@ -16948,7 +16909,7 @@
       <c r="Q83" s="53"/>
       <c r="R83" s="53"/>
     </row>
-    <row r="84" spans="1:18" ht="22.5">
+    <row r="84" spans="1:18" ht="22">
       <c r="A84" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A84" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E84),
@@ -16985,7 +16946,7 @@
       <c r="Q84" s="53"/>
       <c r="R84" s="53"/>
     </row>
-    <row r="85" spans="1:18" ht="22.5">
+    <row r="85" spans="1:18" ht="22">
       <c r="A85" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A85" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E85),
@@ -17063,7 +17024,7 @@
       <c r="Q86" s="53"/>
       <c r="R86" s="53"/>
     </row>
-    <row r="87" spans="1:18" ht="33.75">
+    <row r="87" spans="1:18" ht="33">
       <c r="A87" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A87" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E87),
@@ -17100,7 +17061,7 @@
       <c r="Q87" s="53"/>
       <c r="R87" s="53"/>
     </row>
-    <row r="88" spans="1:18" ht="22.5">
+    <row r="88" spans="1:18" ht="22">
       <c r="A88" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A88" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E88),
@@ -17174,7 +17135,7 @@
       <c r="Q89" s="53"/>
       <c r="R89" s="53"/>
     </row>
-    <row r="90" spans="1:18" ht="33.75">
+    <row r="90" spans="1:18" ht="33">
       <c r="A90" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A90" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E90),
@@ -17246,7 +17207,7 @@
       <c r="Q91" s="53"/>
       <c r="R91" s="53"/>
     </row>
-    <row r="92" spans="1:18" ht="33.75">
+    <row r="92" spans="1:18" ht="33">
       <c r="A92" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A92" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E92),
@@ -17283,7 +17244,7 @@
       <c r="Q92" s="53"/>
       <c r="R92" s="53"/>
     </row>
-    <row r="93" spans="1:18" ht="33.75">
+    <row r="93" spans="1:18" ht="33">
       <c r="A93" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A93" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E93),
@@ -17318,7 +17279,7 @@
       <c r="Q93" s="53"/>
       <c r="R93" s="53"/>
     </row>
-    <row r="94" spans="1:18" ht="33.75">
+    <row r="94" spans="1:18" ht="33">
       <c r="A94" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A94" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E94),
@@ -17355,7 +17316,7 @@
       <c r="Q94" s="53"/>
       <c r="R94" s="53"/>
     </row>
-    <row r="95" spans="1:18" ht="22.5">
+    <row r="95" spans="1:18" ht="22">
       <c r="A95" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A95" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E95),
@@ -17396,7 +17357,7 @@
       <c r="Q95" s="53"/>
       <c r="R95" s="53"/>
     </row>
-    <row r="96" spans="1:18" ht="33.75">
+    <row r="96" spans="1:18" ht="33">
       <c r="A96" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A96" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E96),
@@ -17466,7 +17427,7 @@
       <c r="Q97" s="53"/>
       <c r="R97" s="53"/>
     </row>
-    <row r="98" spans="1:18" ht="33.75">
+    <row r="98" spans="1:18" ht="33">
       <c r="A98" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A98" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E98),
@@ -17501,7 +17462,7 @@
       <c r="Q98" s="53"/>
       <c r="R98" s="53"/>
     </row>
-    <row r="99" spans="1:18" ht="33.75">
+    <row r="99" spans="1:18" ht="33">
       <c r="A99" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A99" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E99),
@@ -17536,7 +17497,7 @@
       <c r="Q99" s="53"/>
       <c r="R99" s="53"/>
     </row>
-    <row r="100" spans="1:18" ht="22.5">
+    <row r="100" spans="1:18" ht="22">
       <c r="A100" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A100" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E100),
@@ -17573,7 +17534,7 @@
       <c r="Q100" s="53"/>
       <c r="R100" s="53"/>
     </row>
-    <row r="101" spans="1:18" ht="33.75">
+    <row r="101" spans="1:18" ht="33">
       <c r="A101" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A101" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E101),
@@ -17643,7 +17604,7 @@
       <c r="Q102" s="53"/>
       <c r="R102" s="53"/>
     </row>
-    <row r="103" spans="1:18" ht="33.75">
+    <row r="103" spans="1:18" ht="33">
       <c r="A103" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A103" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E103),
@@ -17678,7 +17639,7 @@
       <c r="Q103" s="53"/>
       <c r="R103" s="53"/>
     </row>
-    <row r="104" spans="1:18" ht="33.75">
+    <row r="104" spans="1:18" ht="33">
       <c r="A104" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A104" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E104),
@@ -17713,7 +17674,7 @@
       <c r="Q104" s="86"/>
       <c r="R104" s="86"/>
     </row>
-    <row r="105" spans="1:18" ht="33.75">
+    <row r="105" spans="1:18" ht="33">
       <c r="A105" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A105" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E105),
@@ -17750,7 +17711,7 @@
       <c r="Q105" s="53"/>
       <c r="R105" s="53"/>
     </row>
-    <row r="106" spans="1:18" ht="33.75">
+    <row r="106" spans="1:18" ht="33">
       <c r="A106" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A106" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E106),
@@ -17869,7 +17830,7 @@
       <c r="Q108" s="59"/>
       <c r="R108" s="59"/>
     </row>
-    <row r="109" spans="1:18" ht="22.5">
+    <row r="109" spans="1:18" ht="22">
       <c r="A109" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A109" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E109),
@@ -17910,7 +17871,7 @@
       <c r="Q109" s="59"/>
       <c r="R109" s="59"/>
     </row>
-    <row r="110" spans="1:18" ht="22.5">
+    <row r="110" spans="1:18" ht="22">
       <c r="A110" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A110" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E110),
@@ -17986,7 +17947,7 @@
       <c r="Q111" s="59"/>
       <c r="R111" s="59"/>
     </row>
-    <row r="112" spans="1:18" ht="22.5">
+    <row r="112" spans="1:18" ht="22">
       <c r="A112" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A112" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E112),
@@ -18029,7 +17990,7 @@
       <c r="Q112" s="53"/>
       <c r="R112" s="53"/>
     </row>
-    <row r="113" spans="1:18" ht="22.5">
+    <row r="113" spans="1:18" ht="22">
       <c r="A113" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A113" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E113),
@@ -18066,7 +18027,7 @@
       <c r="Q113" s="53"/>
       <c r="R113" s="53"/>
     </row>
-    <row r="114" spans="1:18" ht="22.5">
+    <row r="114" spans="1:18" ht="22">
       <c r="A114" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A114" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E114),
@@ -18101,7 +18062,7 @@
       <c r="Q114" s="53"/>
       <c r="R114" s="53"/>
     </row>
-    <row r="115" spans="1:18" ht="22.5">
+    <row r="115" spans="1:18" ht="22">
       <c r="A115" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A115" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E115),
@@ -18136,7 +18097,7 @@
       <c r="Q115" s="53"/>
       <c r="R115" s="53"/>
     </row>
-    <row r="116" spans="1:18" ht="22.5">
+    <row r="116" spans="1:18" ht="22">
       <c r="A116" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A116" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E116),
@@ -18173,7 +18134,7 @@
       <c r="Q116" s="53"/>
       <c r="R116" s="53"/>
     </row>
-    <row r="117" spans="1:18" ht="22.5">
+    <row r="117" spans="1:18" ht="22">
       <c r="A117" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A117" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E117),
@@ -18208,7 +18169,7 @@
       <c r="Q117" s="53"/>
       <c r="R117" s="53"/>
     </row>
-    <row r="118" spans="1:18" ht="22.5">
+    <row r="118" spans="1:18" ht="22">
       <c r="A118" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A118" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E118),
@@ -18243,7 +18204,7 @@
       <c r="Q118" s="53"/>
       <c r="R118" s="53"/>
     </row>
-    <row r="119" spans="1:18" ht="22.5">
+    <row r="119" spans="1:18" ht="22">
       <c r="A119" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A119" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E119),
@@ -18278,7 +18239,7 @@
       <c r="Q119" s="53"/>
       <c r="R119" s="53"/>
     </row>
-    <row r="120" spans="1:18" ht="33.75">
+    <row r="120" spans="1:18" ht="33">
       <c r="A120" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A120" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E120),
@@ -18313,7 +18274,7 @@
       <c r="Q120" s="53"/>
       <c r="R120" s="53"/>
     </row>
-    <row r="121" spans="1:18" ht="33.75">
+    <row r="121" spans="1:18" ht="33">
       <c r="A121" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A121" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E121),
@@ -18350,7 +18311,7 @@
       <c r="Q121" s="53"/>
       <c r="R121" s="53"/>
     </row>
-    <row r="122" spans="1:18" ht="33.75">
+    <row r="122" spans="1:18" ht="33">
       <c r="A122" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A122" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E122),
@@ -18385,7 +18346,7 @@
       <c r="Q122" s="53"/>
       <c r="R122" s="53"/>
     </row>
-    <row r="123" spans="1:18" ht="45">
+    <row r="123" spans="1:18" ht="44">
       <c r="A123" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A123" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E123),
@@ -18420,7 +18381,7 @@
       <c r="Q123" s="53"/>
       <c r="R123" s="53"/>
     </row>
-    <row r="124" spans="1:18" ht="45">
+    <row r="124" spans="1:18" ht="44">
       <c r="A124" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A124" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E124),
@@ -18455,7 +18416,7 @@
       <c r="Q124" s="53"/>
       <c r="R124" s="53"/>
     </row>
-    <row r="125" spans="1:18" ht="33.75">
+    <row r="125" spans="1:18" ht="33">
       <c r="A125" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A125" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E125),
@@ -18490,7 +18451,7 @@
       <c r="Q125" s="53"/>
       <c r="R125" s="53"/>
     </row>
-    <row r="126" spans="1:18" ht="33.75">
+    <row r="126" spans="1:18" ht="33">
       <c r="A126" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A126" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E126),
@@ -18527,7 +18488,7 @@
       <c r="Q126" s="53"/>
       <c r="R126" s="53"/>
     </row>
-    <row r="127" spans="1:18" ht="33.75">
+    <row r="127" spans="1:18" ht="33">
       <c r="A127" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A127" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E127),
@@ -18566,7 +18527,7 @@
       <c r="Q127" s="53"/>
       <c r="R127" s="53"/>
     </row>
-    <row r="128" spans="1:18" ht="33.75">
+    <row r="128" spans="1:18" ht="33">
       <c r="A128" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A128" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E128),
@@ -18607,7 +18568,7 @@
       <c r="Q128" s="53"/>
       <c r="R128" s="53"/>
     </row>
-    <row r="129" spans="1:18" ht="22.5">
+    <row r="129" spans="1:18" ht="22">
       <c r="A129" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A129" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E129),
@@ -18644,7 +18605,7 @@
       <c r="Q129" s="53"/>
       <c r="R129" s="53"/>
     </row>
-    <row r="130" spans="1:18" ht="22.5">
+    <row r="130" spans="1:18" ht="22">
       <c r="A130" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A130" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E130),
@@ -18679,7 +18640,7 @@
       <c r="Q130" s="53"/>
       <c r="R130" s="53"/>
     </row>
-    <row r="131" spans="1:18" ht="45">
+    <row r="131" spans="1:18" ht="44">
       <c r="A131" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A131" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E131),
@@ -18714,7 +18675,7 @@
       <c r="Q131" s="53"/>
       <c r="R131" s="53"/>
     </row>
-    <row r="132" spans="1:18" ht="22.5">
+    <row r="132" spans="1:18" ht="22">
       <c r="A132" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A132" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E132),
@@ -18757,7 +18718,7 @@
       <c r="Q132" s="53"/>
       <c r="R132" s="53"/>
     </row>
-    <row r="133" spans="1:18" ht="22.5">
+    <row r="133" spans="1:18" ht="22">
       <c r="A133" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A133" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E133),
@@ -18794,7 +18755,7 @@
       <c r="Q133" s="53"/>
       <c r="R133" s="53"/>
     </row>
-    <row r="134" spans="1:18" ht="22.5">
+    <row r="134" spans="1:18" ht="22">
       <c r="A134" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A134" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E134),
@@ -18829,7 +18790,7 @@
       <c r="Q134" s="53"/>
       <c r="R134" s="53"/>
     </row>
-    <row r="135" spans="1:18" ht="22.5">
+    <row r="135" spans="1:18" ht="22">
       <c r="A135" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A135" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E135),
@@ -18864,7 +18825,7 @@
       <c r="Q135" s="53"/>
       <c r="R135" s="53"/>
     </row>
-    <row r="136" spans="1:18" ht="22.5">
+    <row r="136" spans="1:18" ht="22">
       <c r="A136" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A136" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E136),
@@ -18901,7 +18862,7 @@
       <c r="Q136" s="53"/>
       <c r="R136" s="53"/>
     </row>
-    <row r="137" spans="1:18" ht="33.75">
+    <row r="137" spans="1:18" ht="33">
       <c r="A137" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A137" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E137),
@@ -18936,7 +18897,7 @@
       <c r="Q137" s="53"/>
       <c r="R137" s="53"/>
     </row>
-    <row r="138" spans="1:18" ht="33.75">
+    <row r="138" spans="1:18" ht="33">
       <c r="A138" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A138" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E138),
@@ -18975,7 +18936,7 @@
       <c r="Q138" s="53"/>
       <c r="R138" s="53"/>
     </row>
-    <row r="139" spans="1:18" ht="33.75">
+    <row r="139" spans="1:18" ht="33">
       <c r="A139" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A139" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E139),
@@ -19016,7 +18977,7 @@
       <c r="Q139" s="53"/>
       <c r="R139" s="53"/>
     </row>
-    <row r="140" spans="1:18" ht="33.75">
+    <row r="140" spans="1:18" ht="33">
       <c r="A140" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A140" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E140),
@@ -19053,7 +19014,7 @@
       <c r="Q140" s="53"/>
       <c r="R140" s="53"/>
     </row>
-    <row r="141" spans="1:18" ht="33.75">
+    <row r="141" spans="1:18" ht="33">
       <c r="A141" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A141" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E141),
@@ -19090,7 +19051,7 @@
       <c r="Q141" s="53"/>
       <c r="R141" s="53"/>
     </row>
-    <row r="142" spans="1:18" ht="33.75">
+    <row r="142" spans="1:18" ht="33">
       <c r="A142" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A142" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E142),
@@ -19127,7 +19088,7 @@
       <c r="Q142" s="53"/>
       <c r="R142" s="53"/>
     </row>
-    <row r="143" spans="1:18" ht="33.75">
+    <row r="143" spans="1:18" ht="33">
       <c r="A143" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A143" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E143),
@@ -19164,7 +19125,7 @@
       <c r="Q143" s="53"/>
       <c r="R143" s="53"/>
     </row>
-    <row r="144" spans="1:18" ht="22.5">
+    <row r="144" spans="1:18" ht="22">
       <c r="A144" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A144" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E144),
@@ -19201,7 +19162,7 @@
       <c r="Q144" s="53"/>
       <c r="R144" s="53"/>
     </row>
-    <row r="145" spans="1:18" ht="22.5">
+    <row r="145" spans="1:18" ht="22">
       <c r="A145" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A145" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E145),
@@ -19236,7 +19197,7 @@
       <c r="Q145" s="53"/>
       <c r="R145" s="53"/>
     </row>
-    <row r="146" spans="1:18" ht="22.5">
+    <row r="146" spans="1:18" ht="22">
       <c r="A146" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A146" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E146),
@@ -19271,7 +19232,7 @@
       <c r="Q146" s="53"/>
       <c r="R146" s="53"/>
     </row>
-    <row r="147" spans="1:18" ht="22.5">
+    <row r="147" spans="1:18" ht="22">
       <c r="A147" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A147" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E147),
@@ -19306,7 +19267,7 @@
       <c r="Q147" s="53"/>
       <c r="R147" s="53"/>
     </row>
-    <row r="148" spans="1:18" ht="22.5">
+    <row r="148" spans="1:18" ht="22">
       <c r="A148" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A148" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E148),
@@ -19341,7 +19302,7 @@
       <c r="Q148" s="53"/>
       <c r="R148" s="53"/>
     </row>
-    <row r="149" spans="1:18" ht="22.5">
+    <row r="149" spans="1:18" ht="22">
       <c r="A149" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A149" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E149),
@@ -19376,7 +19337,7 @@
       <c r="Q149" s="53"/>
       <c r="R149" s="53"/>
     </row>
-    <row r="150" spans="1:18" ht="22.5">
+    <row r="150" spans="1:18" ht="22">
       <c r="A150" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A150" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E150),
@@ -19415,7 +19376,7 @@
       <c r="Q150" s="53"/>
       <c r="R150" s="53"/>
     </row>
-    <row r="151" spans="1:18" ht="22.5">
+    <row r="151" spans="1:18" ht="22">
       <c r="A151" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A151" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E151),
@@ -19450,7 +19411,7 @@
       <c r="Q151" s="53"/>
       <c r="R151" s="53"/>
     </row>
-    <row r="152" spans="1:18" ht="33.75">
+    <row r="152" spans="1:18" ht="33">
       <c r="A152" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A152" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E152),
@@ -19487,7 +19448,7 @@
       <c r="Q152" s="53"/>
       <c r="R152" s="53"/>
     </row>
-    <row r="153" spans="1:18" ht="33.75">
+    <row r="153" spans="1:18" ht="33">
       <c r="A153" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A153" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E153),
@@ -19522,7 +19483,7 @@
       <c r="Q153" s="53"/>
       <c r="R153" s="53"/>
     </row>
-    <row r="154" spans="1:18" ht="33.75">
+    <row r="154" spans="1:18" ht="33">
       <c r="A154" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A154" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E154),
@@ -19557,7 +19518,7 @@
       <c r="Q154" s="53"/>
       <c r="R154" s="53"/>
     </row>
-    <row r="155" spans="1:18" ht="33.75">
+    <row r="155" spans="1:18" ht="33">
       <c r="A155" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A155" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E155),
@@ -19592,7 +19553,7 @@
       <c r="Q155" s="53"/>
       <c r="R155" s="53"/>
     </row>
-    <row r="156" spans="1:18" ht="33.75">
+    <row r="156" spans="1:18" ht="33">
       <c r="A156" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A156" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E156),
@@ -19627,7 +19588,7 @@
       <c r="Q156" s="53"/>
       <c r="R156" s="53"/>
     </row>
-    <row r="157" spans="1:18" ht="22.5">
+    <row r="157" spans="1:18" ht="22">
       <c r="A157" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A157" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E157),
@@ -19662,7 +19623,7 @@
       <c r="Q157" s="53"/>
       <c r="R157" s="53"/>
     </row>
-    <row r="158" spans="1:18" ht="22.5">
+    <row r="158" spans="1:18" ht="22">
       <c r="A158" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A158" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E158),
@@ -19697,7 +19658,7 @@
       <c r="Q158" s="53"/>
       <c r="R158" s="53"/>
     </row>
-    <row r="159" spans="1:18" ht="33.75">
+    <row r="159" spans="1:18" ht="33">
       <c r="A159" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A159" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E159),
@@ -19732,7 +19693,7 @@
       <c r="Q159" s="53"/>
       <c r="R159" s="53"/>
     </row>
-    <row r="160" spans="1:18" ht="33.75">
+    <row r="160" spans="1:18" ht="33">
       <c r="A160" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A160" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E160),
@@ -19767,7 +19728,7 @@
       <c r="Q160" s="53"/>
       <c r="R160" s="53"/>
     </row>
-    <row r="161" spans="1:18" ht="33.75">
+    <row r="161" spans="1:18" ht="33">
       <c r="A161" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A161" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E161),
@@ -19802,7 +19763,7 @@
       <c r="Q161" s="53"/>
       <c r="R161" s="53"/>
     </row>
-    <row r="162" spans="1:18" ht="33.75">
+    <row r="162" spans="1:18" ht="33">
       <c r="A162" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A162" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E162),
@@ -19909,7 +19870,7 @@
       <c r="Q164" s="53"/>
       <c r="R164" s="53"/>
     </row>
-    <row r="165" spans="1:18" ht="22.5">
+    <row r="165" spans="1:18" ht="22">
       <c r="A165" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A165" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E165),
@@ -19944,7 +19905,7 @@
       <c r="Q165" s="53"/>
       <c r="R165" s="53"/>
     </row>
-    <row r="166" spans="1:18" ht="22.5">
+    <row r="166" spans="1:18" ht="22">
       <c r="A166" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A166" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E166),
@@ -19979,7 +19940,7 @@
       <c r="Q166" s="53"/>
       <c r="R166" s="53"/>
     </row>
-    <row r="167" spans="1:18" ht="22.5">
+    <row r="167" spans="1:18" ht="22">
       <c r="A167" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A167" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E167),
@@ -20014,7 +19975,7 @@
       <c r="Q167" s="53"/>
       <c r="R167" s="53"/>
     </row>
-    <row r="168" spans="1:18" ht="33.75">
+    <row r="168" spans="1:18" ht="33">
       <c r="A168" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A168" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E168),
@@ -20049,7 +20010,7 @@
       <c r="Q168" s="53"/>
       <c r="R168" s="53"/>
     </row>
-    <row r="169" spans="1:18" ht="22.5">
+    <row r="169" spans="1:18" ht="22">
       <c r="A169" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A169" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E169),
@@ -20084,7 +20045,7 @@
       <c r="Q169" s="53"/>
       <c r="R169" s="53"/>
     </row>
-    <row r="170" spans="1:18" ht="22.5">
+    <row r="170" spans="1:18" ht="22">
       <c r="A170" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A170" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E170),
@@ -20121,7 +20082,7 @@
       <c r="Q170" s="53"/>
       <c r="R170" s="53"/>
     </row>
-    <row r="171" spans="1:18" ht="33.75">
+    <row r="171" spans="1:18" ht="33">
       <c r="A171" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A171" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E171),
@@ -20156,7 +20117,7 @@
       <c r="Q171" s="53"/>
       <c r="R171" s="53"/>
     </row>
-    <row r="172" spans="1:18" ht="33.75">
+    <row r="172" spans="1:18" ht="33">
       <c r="A172" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A172" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E172),
@@ -20191,7 +20152,7 @@
       <c r="Q172" s="53"/>
       <c r="R172" s="53"/>
     </row>
-    <row r="173" spans="1:18" ht="45">
+    <row r="173" spans="1:18" ht="44">
       <c r="A173" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A173" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E173),
@@ -20226,7 +20187,7 @@
       <c r="Q173" s="53"/>
       <c r="R173" s="53"/>
     </row>
-    <row r="174" spans="1:18" ht="45">
+    <row r="174" spans="1:18" ht="44">
       <c r="A174" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A174" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E174),
@@ -20261,7 +20222,7 @@
       <c r="Q174" s="53"/>
       <c r="R174" s="53"/>
     </row>
-    <row r="175" spans="1:18" ht="33.75">
+    <row r="175" spans="1:18" ht="33">
       <c r="A175" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A175" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E175),
@@ -20296,7 +20257,7 @@
       <c r="Q175" s="53"/>
       <c r="R175" s="53"/>
     </row>
-    <row r="176" spans="1:18" ht="45">
+    <row r="176" spans="1:18" ht="44">
       <c r="A176" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A176" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E176),
@@ -20331,7 +20292,7 @@
       <c r="Q176" s="53"/>
       <c r="R176" s="53"/>
     </row>
-    <row r="177" spans="1:18" ht="45">
+    <row r="177" spans="1:18" ht="44">
       <c r="A177" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A177" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E177),
@@ -20366,7 +20327,7 @@
       <c r="Q177" s="53"/>
       <c r="R177" s="53"/>
     </row>
-    <row r="178" spans="1:18" ht="22.5">
+    <row r="178" spans="1:18" ht="22">
       <c r="A178" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A178" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E178),
@@ -20401,7 +20362,7 @@
       <c r="Q178" s="53"/>
       <c r="R178" s="53"/>
     </row>
-    <row r="179" spans="1:18" ht="33.75">
+    <row r="179" spans="1:18" ht="33">
       <c r="A179" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A179" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E179),
@@ -20438,7 +20399,7 @@
       <c r="Q179" s="53"/>
       <c r="R179" s="53"/>
     </row>
-    <row r="180" spans="1:18" ht="22.5">
+    <row r="180" spans="1:18" ht="22">
       <c r="A180" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A180" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E180),
@@ -20475,7 +20436,7 @@
       <c r="Q180" s="53"/>
       <c r="R180" s="53"/>
     </row>
-    <row r="181" spans="1:18" ht="22.5">
+    <row r="181" spans="1:18" ht="22">
       <c r="A181" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A181" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E181),
@@ -20518,7 +20479,7 @@
       <c r="Q181" s="59"/>
       <c r="R181" s="59"/>
     </row>
-    <row r="182" spans="1:18" ht="22.5">
+    <row r="182" spans="1:18" ht="22">
       <c r="A182" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A182" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E182),
@@ -20596,7 +20557,7 @@
       <c r="Q183" s="59"/>
       <c r="R183" s="59"/>
     </row>
-    <row r="184" spans="1:18" ht="22.5">
+    <row r="184" spans="1:18" ht="22">
       <c r="A184" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A184" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E184),
@@ -20639,7 +20600,7 @@
       <c r="Q184" s="59"/>
       <c r="R184" s="59"/>
     </row>
-    <row r="185" spans="1:18" ht="22.5">
+    <row r="185" spans="1:18" ht="22">
       <c r="A185" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A185" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E185),
@@ -20676,7 +20637,7 @@
       <c r="Q185" s="59"/>
       <c r="R185" s="59"/>
     </row>
-    <row r="186" spans="1:18" ht="22.5">
+    <row r="186" spans="1:18" ht="22">
       <c r="A186" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A186" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E186),
@@ -20711,7 +20672,7 @@
       <c r="Q186" s="59"/>
       <c r="R186" s="59"/>
     </row>
-    <row r="187" spans="1:18" ht="22.5">
+    <row r="187" spans="1:18" ht="22">
       <c r="A187" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A187" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E187),
@@ -20748,7 +20709,7 @@
       <c r="Q187" s="59"/>
       <c r="R187" s="59"/>
     </row>
-    <row r="188" spans="1:18" ht="22.5">
+    <row r="188" spans="1:18" ht="22">
       <c r="A188" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A188" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E188),
@@ -20783,7 +20744,7 @@
       <c r="Q188" s="59"/>
       <c r="R188" s="59"/>
     </row>
-    <row r="189" spans="1:18" ht="33.75">
+    <row r="189" spans="1:18" ht="33">
       <c r="A189" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A189" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E189),
@@ -20822,7 +20783,7 @@
       <c r="Q189" s="59"/>
       <c r="R189" s="59"/>
     </row>
-    <row r="190" spans="1:18" ht="22.5">
+    <row r="190" spans="1:18" ht="22">
       <c r="A190" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A190" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E190),
@@ -20863,7 +20824,7 @@
       <c r="Q190" s="59"/>
       <c r="R190" s="59"/>
     </row>
-    <row r="191" spans="1:18" ht="22.5">
+    <row r="191" spans="1:18" ht="22">
       <c r="A191" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A191" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E191),
@@ -20898,7 +20859,7 @@
       <c r="Q191" s="59"/>
       <c r="R191" s="59"/>
     </row>
-    <row r="192" spans="1:18" ht="22.5">
+    <row r="192" spans="1:18" ht="22">
       <c r="A192" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A192" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E192),
@@ -20933,7 +20894,7 @@
       <c r="Q192" s="59"/>
       <c r="R192" s="59"/>
     </row>
-    <row r="193" spans="1:18" ht="22.5">
+    <row r="193" spans="1:18" ht="22">
       <c r="A193" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A193" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E193),
@@ -20968,7 +20929,7 @@
       <c r="Q193" s="59"/>
       <c r="R193" s="59"/>
     </row>
-    <row r="194" spans="1:18" ht="22.5">
+    <row r="194" spans="1:18" ht="22">
       <c r="A194" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A194" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E194),
@@ -21003,7 +20964,7 @@
       <c r="Q194" s="59"/>
       <c r="R194" s="59"/>
     </row>
-    <row r="195" spans="1:18" ht="22.5">
+    <row r="195" spans="1:18" ht="22">
       <c r="A195" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A195" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E195),
@@ -21038,7 +20999,7 @@
       <c r="Q195" s="59"/>
       <c r="R195" s="59"/>
     </row>
-    <row r="196" spans="1:18" ht="22.5">
+    <row r="196" spans="1:18" ht="22">
       <c r="A196" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A196" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E196),
@@ -21073,7 +21034,7 @@
       <c r="Q196" s="59"/>
       <c r="R196" s="59"/>
     </row>
-    <row r="197" spans="1:18" ht="22.5">
+    <row r="197" spans="1:18" ht="22">
       <c r="A197" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A197" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E197),
@@ -21110,7 +21071,7 @@
       <c r="Q197" s="59"/>
       <c r="R197" s="59"/>
     </row>
-    <row r="198" spans="1:18" ht="22.5">
+    <row r="198" spans="1:18" ht="22">
       <c r="A198" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A198" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E198),
@@ -21149,7 +21110,7 @@
       <c r="Q198" s="59"/>
       <c r="R198" s="59"/>
     </row>
-    <row r="199" spans="1:18" ht="22.5">
+    <row r="199" spans="1:18" ht="22">
       <c r="A199" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A199" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E199),
@@ -21219,7 +21180,7 @@
       <c r="Q200" s="59"/>
       <c r="R200" s="59"/>
     </row>
-    <row r="201" spans="1:18" ht="22.5">
+    <row r="201" spans="1:18" ht="22">
       <c r="A201" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A201" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E201),
@@ -21254,7 +21215,7 @@
       <c r="Q201" s="59"/>
       <c r="R201" s="59"/>
     </row>
-    <row r="202" spans="1:18" ht="33.75">
+    <row r="202" spans="1:18" ht="33">
       <c r="A202" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A202" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E202),
@@ -21289,7 +21250,7 @@
       <c r="Q202" s="59"/>
       <c r="R202" s="59"/>
     </row>
-    <row r="203" spans="1:18" ht="33.75">
+    <row r="203" spans="1:18" ht="33">
       <c r="A203" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A203" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E203),
@@ -21324,7 +21285,7 @@
       <c r="Q203" s="59"/>
       <c r="R203" s="59"/>
     </row>
-    <row r="204" spans="1:18" ht="45">
+    <row r="204" spans="1:18" ht="44">
       <c r="A204" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A204" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E204),
@@ -21359,7 +21320,7 @@
       <c r="Q204" s="59"/>
       <c r="R204" s="59"/>
     </row>
-    <row r="205" spans="1:18" ht="33.75">
+    <row r="205" spans="1:18" ht="33">
       <c r="A205" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A205" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E205),
@@ -21394,7 +21355,7 @@
       <c r="Q205" s="59"/>
       <c r="R205" s="59"/>
     </row>
-    <row r="206" spans="1:18" ht="33.75">
+    <row r="206" spans="1:18" ht="33">
       <c r="A206" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A206" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E206),
@@ -21429,7 +21390,7 @@
       <c r="Q206" s="59"/>
       <c r="R206" s="59"/>
     </row>
-    <row r="207" spans="1:18" ht="22.5">
+    <row r="207" spans="1:18" ht="22">
       <c r="A207" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A207" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E207),
@@ -21464,7 +21425,7 @@
       <c r="Q207" s="59"/>
       <c r="R207" s="59"/>
     </row>
-    <row r="208" spans="1:18" ht="22.5">
+    <row r="208" spans="1:18" ht="22">
       <c r="A208" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A208" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E208),
@@ -21499,7 +21460,7 @@
       <c r="Q208" s="59"/>
       <c r="R208" s="59"/>
     </row>
-    <row r="209" spans="1:18" ht="33.75">
+    <row r="209" spans="1:18" ht="33">
       <c r="A209" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A209" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E209),
@@ -21534,7 +21495,7 @@
       <c r="Q209" s="59"/>
       <c r="R209" s="59"/>
     </row>
-    <row r="210" spans="1:18" ht="22.5">
+    <row r="210" spans="1:18" ht="22">
       <c r="A210" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A210" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E210),
@@ -21569,7 +21530,7 @@
       <c r="Q210" s="59"/>
       <c r="R210" s="59"/>
     </row>
-    <row r="211" spans="1:18" ht="22.5">
+    <row r="211" spans="1:18" ht="22">
       <c r="A211" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A211" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E211),
@@ -21608,7 +21569,7 @@
       <c r="Q211" s="59"/>
       <c r="R211" s="59"/>
     </row>
-    <row r="212" spans="1:18" ht="22.5">
+    <row r="212" spans="1:18" ht="22">
       <c r="A212" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A212" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E212),
@@ -21643,7 +21604,7 @@
       <c r="Q212" s="59"/>
       <c r="R212" s="59"/>
     </row>
-    <row r="213" spans="1:18" ht="22.5">
+    <row r="213" spans="1:18" ht="22">
       <c r="A213" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A213" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E213),
@@ -21713,7 +21674,7 @@
       <c r="Q214" s="59"/>
       <c r="R214" s="59"/>
     </row>
-    <row r="215" spans="1:18" ht="22.5">
+    <row r="215" spans="1:18" ht="22">
       <c r="A215" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A215" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E215),
@@ -21748,7 +21709,7 @@
       <c r="Q215" s="59"/>
       <c r="R215" s="59"/>
     </row>
-    <row r="216" spans="1:18" ht="45">
+    <row r="216" spans="1:18" ht="44">
       <c r="A216" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A216" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E216),
@@ -21783,7 +21744,7 @@
       <c r="Q216" s="59"/>
       <c r="R216" s="59"/>
     </row>
-    <row r="217" spans="1:18" ht="33.75">
+    <row r="217" spans="1:18" ht="33">
       <c r="A217" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A217" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E217),
@@ -21818,7 +21779,7 @@
       <c r="Q217" s="59"/>
       <c r="R217" s="59"/>
     </row>
-    <row r="218" spans="1:18" ht="33.75">
+    <row r="218" spans="1:18" ht="33">
       <c r="A218" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A218" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E218),
@@ -21853,7 +21814,7 @@
       <c r="Q218" s="59"/>
       <c r="R218" s="59"/>
     </row>
-    <row r="219" spans="1:18" ht="45">
+    <row r="219" spans="1:18" ht="44">
       <c r="A219" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A219" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E219),
@@ -21888,7 +21849,7 @@
       <c r="Q219" s="59"/>
       <c r="R219" s="59"/>
     </row>
-    <row r="220" spans="1:18" ht="33.75">
+    <row r="220" spans="1:18" ht="33">
       <c r="A220" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A220" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E220),
@@ -21923,7 +21884,7 @@
       <c r="Q220" s="59"/>
       <c r="R220" s="59"/>
     </row>
-    <row r="221" spans="1:18" ht="33.75">
+    <row r="221" spans="1:18" ht="33">
       <c r="A221" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A221" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E221),
@@ -21958,7 +21919,7 @@
       <c r="Q221" s="59"/>
       <c r="R221" s="59"/>
     </row>
-    <row r="222" spans="1:18" ht="22.5">
+    <row r="222" spans="1:18" ht="22">
       <c r="A222" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A222" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E222),
@@ -21993,7 +21954,7 @@
       <c r="Q222" s="59"/>
       <c r="R222" s="59"/>
     </row>
-    <row r="223" spans="1:18" ht="22.5">
+    <row r="223" spans="1:18" ht="22">
       <c r="A223" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A223" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E223),
@@ -22028,7 +21989,7 @@
       <c r="Q223" s="59"/>
       <c r="R223" s="59"/>
     </row>
-    <row r="224" spans="1:18" ht="33.75">
+    <row r="224" spans="1:18" ht="33">
       <c r="A224" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A224" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E224),
@@ -22063,7 +22024,7 @@
       <c r="Q224" s="59"/>
       <c r="R224" s="59"/>
     </row>
-    <row r="225" spans="1:18" ht="22.5">
+    <row r="225" spans="1:18" ht="22">
       <c r="A225" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A225" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E225),
@@ -22098,7 +22059,7 @@
       <c r="Q225" s="59"/>
       <c r="R225" s="59"/>
     </row>
-    <row r="226" spans="1:18" ht="45">
+    <row r="226" spans="1:18" ht="44">
       <c r="A226" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A226" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E226),
@@ -22135,7 +22096,7 @@
       <c r="Q226" s="59"/>
       <c r="R226" s="59"/>
     </row>
-    <row r="227" spans="1:18" ht="45">
+    <row r="227" spans="1:18" ht="44">
       <c r="A227" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A227" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E227),
@@ -22170,7 +22131,7 @@
       <c r="Q227" s="59"/>
       <c r="R227" s="59"/>
     </row>
-    <row r="228" spans="1:18" ht="33.75">
+    <row r="228" spans="1:18" ht="33">
       <c r="A228" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A228" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E228),
@@ -22205,7 +22166,7 @@
       <c r="Q228" s="59"/>
       <c r="R228" s="59"/>
     </row>
-    <row r="229" spans="1:18" ht="33.75">
+    <row r="229" spans="1:18" ht="33">
       <c r="A229" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A229" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E229),
@@ -22242,7 +22203,7 @@
       <c r="Q229" s="59"/>
       <c r="R229" s="59"/>
     </row>
-    <row r="230" spans="1:18" ht="22.5">
+    <row r="230" spans="1:18" ht="22">
       <c r="A230" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A230" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E230),
@@ -22279,7 +22240,7 @@
       <c r="Q230" s="59"/>
       <c r="R230" s="59"/>
     </row>
-    <row r="231" spans="1:18" ht="22.5">
+    <row r="231" spans="1:18" ht="22">
       <c r="A231" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A231" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E231),
@@ -22322,7 +22283,7 @@
       <c r="Q231" s="59"/>
       <c r="R231" s="59"/>
     </row>
-    <row r="232" spans="1:18" ht="22.5">
+    <row r="232" spans="1:18" ht="22">
       <c r="A232" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A232" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E232),
@@ -22359,7 +22320,7 @@
       <c r="Q232" s="59"/>
       <c r="R232" s="59"/>
     </row>
-    <row r="233" spans="1:18" ht="22.5">
+    <row r="233" spans="1:18" ht="22">
       <c r="A233" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A233" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E233),
@@ -22394,7 +22355,7 @@
       <c r="Q233" s="59"/>
       <c r="R233" s="59"/>
     </row>
-    <row r="234" spans="1:18" ht="22.5">
+    <row r="234" spans="1:18" ht="22">
       <c r="A234" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A234" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E234),
@@ -22429,7 +22390,7 @@
       <c r="Q234" s="59"/>
       <c r="R234" s="59"/>
     </row>
-    <row r="235" spans="1:18" ht="22.5">
+    <row r="235" spans="1:18" ht="22">
       <c r="A235" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A235" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E235),
@@ -22464,7 +22425,7 @@
       <c r="Q235" s="59"/>
       <c r="R235" s="59"/>
     </row>
-    <row r="236" spans="1:18" ht="33.75">
+    <row r="236" spans="1:18" ht="33">
       <c r="A236" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A236" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E236),
@@ -22499,7 +22460,7 @@
       <c r="Q236" s="59"/>
       <c r="R236" s="59"/>
     </row>
-    <row r="237" spans="1:18" ht="33.75">
+    <row r="237" spans="1:18" ht="33">
       <c r="A237" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A237" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E237),
@@ -22536,7 +22497,7 @@
       <c r="Q237" s="59"/>
       <c r="R237" s="59"/>
     </row>
-    <row r="238" spans="1:18" ht="33.75">
+    <row r="238" spans="1:18" ht="33">
       <c r="A238" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A238" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E238),
@@ -22571,7 +22532,7 @@
       <c r="Q238" s="59"/>
       <c r="R238" s="59"/>
     </row>
-    <row r="239" spans="1:18" ht="45">
+    <row r="239" spans="1:18" ht="44">
       <c r="A239" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A239" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E239),
@@ -22606,7 +22567,7 @@
       <c r="Q239" s="59"/>
       <c r="R239" s="59"/>
     </row>
-    <row r="240" spans="1:18" ht="45">
+    <row r="240" spans="1:18" ht="44">
       <c r="A240" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A240" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E240),
@@ -22641,7 +22602,7 @@
       <c r="Q240" s="59"/>
       <c r="R240" s="59"/>
     </row>
-    <row r="241" spans="1:18" ht="33.75">
+    <row r="241" spans="1:18" ht="33">
       <c r="A241" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A241" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E241),
@@ -22676,7 +22637,7 @@
       <c r="Q241" s="59"/>
       <c r="R241" s="59"/>
     </row>
-    <row r="242" spans="1:18" ht="33.75">
+    <row r="242" spans="1:18" ht="33">
       <c r="A242" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A242" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E242),
@@ -22713,7 +22674,7 @@
       <c r="Q242" s="59"/>
       <c r="R242" s="59"/>
     </row>
-    <row r="243" spans="1:18" ht="33.75">
+    <row r="243" spans="1:18" ht="33">
       <c r="A243" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A243" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E243),
@@ -22754,7 +22715,7 @@
       <c r="Q243" s="59"/>
       <c r="R243" s="59"/>
     </row>
-    <row r="244" spans="1:18" ht="22.5">
+    <row r="244" spans="1:18" ht="22">
       <c r="A244" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A244" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E244),
@@ -22797,7 +22758,7 @@
       <c r="Q244" s="59"/>
       <c r="R244" s="59"/>
     </row>
-    <row r="245" spans="1:18" ht="22.5">
+    <row r="245" spans="1:18" ht="22">
       <c r="A245" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A245" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E245),
@@ -22832,7 +22793,7 @@
       <c r="Q245" s="59"/>
       <c r="R245" s="59"/>
     </row>
-    <row r="246" spans="1:18" ht="33.75">
+    <row r="246" spans="1:18" ht="33">
       <c r="A246" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A246" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E246),
@@ -22871,7 +22832,7 @@
       <c r="Q246" s="59"/>
       <c r="R246" s="59"/>
     </row>
-    <row r="247" spans="1:18" ht="33.75">
+    <row r="247" spans="1:18" ht="33">
       <c r="A247" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A247" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E247),
@@ -22906,7 +22867,7 @@
       <c r="Q247" s="59"/>
       <c r="R247" s="59"/>
     </row>
-    <row r="248" spans="1:18" ht="33.75">
+    <row r="248" spans="1:18" ht="33">
       <c r="A248" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A248" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E248),
@@ -22947,7 +22908,7 @@
       <c r="Q248" s="59"/>
       <c r="R248" s="59"/>
     </row>
-    <row r="249" spans="1:18" ht="33.75">
+    <row r="249" spans="1:18" ht="33">
       <c r="A249" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A249" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E249),
@@ -22984,7 +22945,7 @@
       <c r="Q249" s="59"/>
       <c r="R249" s="59"/>
     </row>
-    <row r="250" spans="1:18" ht="33.75">
+    <row r="250" spans="1:18" ht="33">
       <c r="A250" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A250" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E250),
@@ -23021,7 +22982,7 @@
       <c r="Q250" s="59"/>
       <c r="R250" s="59"/>
     </row>
-    <row r="251" spans="1:18" ht="33.75">
+    <row r="251" spans="1:18" ht="33">
       <c r="A251" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A251" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E251),
@@ -23058,7 +23019,7 @@
       <c r="Q251" s="59"/>
       <c r="R251" s="59"/>
     </row>
-    <row r="252" spans="1:18" ht="22.5">
+    <row r="252" spans="1:18" ht="22">
       <c r="A252" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A252" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E252),
@@ -23097,7 +23058,7 @@
       <c r="Q252" s="59"/>
       <c r="R252" s="59"/>
     </row>
-    <row r="253" spans="1:18" ht="22.5">
+    <row r="253" spans="1:18" ht="22">
       <c r="A253" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A253" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E253),
@@ -23132,7 +23093,7 @@
       <c r="Q253" s="59"/>
       <c r="R253" s="59"/>
     </row>
-    <row r="254" spans="1:18" ht="33.75">
+    <row r="254" spans="1:18" ht="33">
       <c r="A254" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A254" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E254),
@@ -23169,7 +23130,7 @@
       <c r="Q254" s="59"/>
       <c r="R254" s="59"/>
     </row>
-    <row r="255" spans="1:18" ht="33.75">
+    <row r="255" spans="1:18" ht="33">
       <c r="A255" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A255" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E255),
@@ -23204,7 +23165,7 @@
       <c r="Q255" s="59"/>
       <c r="R255" s="59"/>
     </row>
-    <row r="256" spans="1:18" ht="33.75">
+    <row r="256" spans="1:18" ht="33">
       <c r="A256" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A256" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E256),
@@ -23239,7 +23200,7 @@
       <c r="Q256" s="59"/>
       <c r="R256" s="59"/>
     </row>
-    <row r="257" spans="1:18" ht="33.75">
+    <row r="257" spans="1:18" ht="33">
       <c r="A257" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A257" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E257),
@@ -23274,7 +23235,7 @@
       <c r="Q257" s="59"/>
       <c r="R257" s="59"/>
     </row>
-    <row r="258" spans="1:18" ht="33.75">
+    <row r="258" spans="1:18" ht="33">
       <c r="A258" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A258" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E258),
@@ -23309,7 +23270,7 @@
       <c r="Q258" s="59"/>
       <c r="R258" s="59"/>
     </row>
-    <row r="259" spans="1:18" ht="22.5">
+    <row r="259" spans="1:18" ht="22">
       <c r="A259" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A259" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E259),
@@ -23344,7 +23305,7 @@
       <c r="Q259" s="59"/>
       <c r="R259" s="59"/>
     </row>
-    <row r="260" spans="1:18" ht="22.5">
+    <row r="260" spans="1:18" ht="22">
       <c r="A260" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A260" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E260),
@@ -23379,7 +23340,7 @@
       <c r="Q260" s="59"/>
       <c r="R260" s="59"/>
     </row>
-    <row r="261" spans="1:18" ht="33.75">
+    <row r="261" spans="1:18" ht="33">
       <c r="A261" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A261" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E261),
@@ -23414,7 +23375,7 @@
       <c r="Q261" s="59"/>
       <c r="R261" s="59"/>
     </row>
-    <row r="262" spans="1:18" ht="33.75">
+    <row r="262" spans="1:18" ht="33">
       <c r="A262" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A262" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E262),
@@ -23449,7 +23410,7 @@
       <c r="Q262" s="59"/>
       <c r="R262" s="59"/>
     </row>
-    <row r="263" spans="1:18" ht="33.75">
+    <row r="263" spans="1:18" ht="33">
       <c r="A263" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A263" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E263),
@@ -23484,7 +23445,7 @@
       <c r="Q263" s="59"/>
       <c r="R263" s="59"/>
     </row>
-    <row r="264" spans="1:18" ht="33.75">
+    <row r="264" spans="1:18" ht="33">
       <c r="A264" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A264" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E264),
@@ -23591,7 +23552,7 @@
       <c r="Q266" s="59"/>
       <c r="R266" s="59"/>
     </row>
-    <row r="267" spans="1:18" ht="22.5">
+    <row r="267" spans="1:18" ht="22">
       <c r="A267" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A267" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E267),
@@ -23626,7 +23587,7 @@
       <c r="Q267" s="59"/>
       <c r="R267" s="59"/>
     </row>
-    <row r="268" spans="1:18" ht="22.5">
+    <row r="268" spans="1:18" ht="22">
       <c r="A268" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A268" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E268),
@@ -23661,7 +23622,7 @@
       <c r="Q268" s="59"/>
       <c r="R268" s="59"/>
     </row>
-    <row r="269" spans="1:18" ht="22.5">
+    <row r="269" spans="1:18" ht="22">
       <c r="A269" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A269" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E269),
@@ -23696,7 +23657,7 @@
       <c r="Q269" s="59"/>
       <c r="R269" s="59"/>
     </row>
-    <row r="270" spans="1:18" ht="33.75">
+    <row r="270" spans="1:18" ht="33">
       <c r="A270" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A270" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E270),
@@ -23731,7 +23692,7 @@
       <c r="Q270" s="59"/>
       <c r="R270" s="59"/>
     </row>
-    <row r="271" spans="1:18" ht="22.5">
+    <row r="271" spans="1:18" ht="22">
       <c r="A271" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A271" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E271),
@@ -23768,7 +23729,7 @@
       <c r="Q271" s="59"/>
       <c r="R271" s="59"/>
     </row>
-    <row r="272" spans="1:18" ht="33.75">
+    <row r="272" spans="1:18" ht="33">
       <c r="A272" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A272" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E272),
@@ -23803,7 +23764,7 @@
       <c r="Q272" s="59"/>
       <c r="R272" s="59"/>
     </row>
-    <row r="273" spans="1:18" ht="45">
+    <row r="273" spans="1:18" ht="44">
       <c r="A273" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A273" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E273),
@@ -23838,7 +23799,7 @@
       <c r="Q273" s="59"/>
       <c r="R273" s="59"/>
     </row>
-    <row r="274" spans="1:18" ht="45">
+    <row r="274" spans="1:18" ht="44">
       <c r="A274" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A274" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E274),
@@ -23873,7 +23834,7 @@
       <c r="Q274" s="59"/>
       <c r="R274" s="59"/>
     </row>
-    <row r="275" spans="1:18" ht="22.5">
+    <row r="275" spans="1:18" ht="22">
       <c r="A275" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A275" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E275),
@@ -23908,7 +23869,7 @@
       <c r="Q275" s="59"/>
       <c r="R275" s="59"/>
     </row>
-    <row r="276" spans="1:18" ht="45">
+    <row r="276" spans="1:18" ht="44">
       <c r="A276" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A276" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E276),
@@ -23943,7 +23904,7 @@
       <c r="Q276" s="59"/>
       <c r="R276" s="59"/>
     </row>
-    <row r="277" spans="1:18" ht="45">
+    <row r="277" spans="1:18" ht="44">
       <c r="A277" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A277" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E277),
@@ -23978,7 +23939,7 @@
       <c r="Q277" s="59"/>
       <c r="R277" s="59"/>
     </row>
-    <row r="278" spans="1:18" ht="22.5">
+    <row r="278" spans="1:18" ht="22">
       <c r="A278" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A278" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E278),
@@ -24013,7 +23974,7 @@
       <c r="Q278" s="59"/>
       <c r="R278" s="59"/>
     </row>
-    <row r="279" spans="1:18" ht="22.5">
+    <row r="279" spans="1:18" ht="22">
       <c r="A279" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A279" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E279),
@@ -24050,7 +24011,7 @@
       <c r="Q279" s="59"/>
       <c r="R279" s="59"/>
     </row>
-    <row r="280" spans="1:18" ht="22.5">
+    <row r="280" spans="1:18" ht="22">
       <c r="A280" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A280" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E280),
@@ -24093,7 +24054,7 @@
       <c r="Q280" s="53"/>
       <c r="R280" s="53"/>
     </row>
-    <row r="281" spans="1:18" ht="22.5">
+    <row r="281" spans="1:18" ht="22">
       <c r="A281" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A281" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E281),
@@ -24128,7 +24089,7 @@
       <c r="Q281" s="53"/>
       <c r="R281" s="53"/>
     </row>
-    <row r="282" spans="1:18" ht="22.5">
+    <row r="282" spans="1:18" ht="22">
       <c r="A282" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A282" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E282),
@@ -24163,7 +24124,7 @@
       <c r="Q282" s="53"/>
       <c r="R282" s="53"/>
     </row>
-    <row r="283" spans="1:18" ht="22.5">
+    <row r="283" spans="1:18" ht="22">
       <c r="A283" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A283" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E283),
@@ -24198,7 +24159,7 @@
       <c r="Q283" s="53"/>
       <c r="R283" s="53"/>
     </row>
-    <row r="284" spans="1:18" ht="22.5">
+    <row r="284" spans="1:18" ht="22">
       <c r="A284" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A284" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E284),
@@ -24239,7 +24200,7 @@
       <c r="Q284" s="53"/>
       <c r="R284" s="53"/>
     </row>
-    <row r="285" spans="1:18" ht="22.5">
+    <row r="285" spans="1:18" ht="22">
       <c r="A285" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A285" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E285),
@@ -24276,7 +24237,7 @@
       <c r="Q285" s="53"/>
       <c r="R285" s="53"/>
     </row>
-    <row r="286" spans="1:18" ht="22.5">
+    <row r="286" spans="1:18" ht="22">
       <c r="A286" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A286" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E286),
@@ -24313,7 +24274,7 @@
       <c r="Q286" s="53"/>
       <c r="R286" s="53"/>
     </row>
-    <row r="287" spans="1:18" ht="22.5">
+    <row r="287" spans="1:18" ht="22">
       <c r="A287" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A287" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E287),
@@ -24350,7 +24311,7 @@
       <c r="Q287" s="53"/>
       <c r="R287" s="53"/>
     </row>
-    <row r="288" spans="1:18" ht="22.5">
+    <row r="288" spans="1:18" ht="22">
       <c r="A288" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A288" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E288),
@@ -24389,7 +24350,7 @@
       <c r="Q288" s="53"/>
       <c r="R288" s="53"/>
     </row>
-    <row r="289" spans="1:18" ht="22.5">
+    <row r="289" spans="1:18" ht="22">
       <c r="A289" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A289" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E289),
@@ -24424,7 +24385,7 @@
       <c r="Q289" s="53"/>
       <c r="R289" s="53"/>
     </row>
-    <row r="290" spans="1:18" ht="33.75">
+    <row r="290" spans="1:18" ht="33">
       <c r="A290" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A290" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E290),
@@ -24459,7 +24420,7 @@
       <c r="Q290" s="53"/>
       <c r="R290" s="53"/>
     </row>
-    <row r="291" spans="1:18" ht="33.75">
+    <row r="291" spans="1:18" ht="33">
       <c r="A291" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A291" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E291),
@@ -24494,7 +24455,7 @@
       <c r="Q291" s="53"/>
       <c r="R291" s="53"/>
     </row>
-    <row r="292" spans="1:18" ht="33.75">
+    <row r="292" spans="1:18" ht="33">
       <c r="A292" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A292" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E292),
@@ -24529,7 +24490,7 @@
       <c r="Q292" s="53"/>
       <c r="R292" s="53"/>
     </row>
-    <row r="293" spans="1:18" ht="33.75">
+    <row r="293" spans="1:18" ht="33">
       <c r="A293" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A293" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E293),
@@ -24564,7 +24525,7 @@
       <c r="Q293" s="53"/>
       <c r="R293" s="53"/>
     </row>
-    <row r="294" spans="1:18" ht="33.75">
+    <row r="294" spans="1:18" ht="33">
       <c r="A294" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A294" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E294),
@@ -24599,7 +24560,7 @@
       <c r="Q294" s="53"/>
       <c r="R294" s="53"/>
     </row>
-    <row r="295" spans="1:18" ht="22.5">
+    <row r="295" spans="1:18" ht="22">
       <c r="A295" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A295" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E295),
@@ -24634,7 +24595,7 @@
       <c r="Q295" s="53"/>
       <c r="R295" s="53"/>
     </row>
-    <row r="296" spans="1:18" ht="22.5">
+    <row r="296" spans="1:18" ht="22">
       <c r="A296" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A296" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E296),
@@ -24706,16 +24667,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R311"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="3" width="8.625" style="28" customWidth="1"/>
-    <col min="4" max="5" width="8.625" style="29" customWidth="1"/>
+    <col min="1" max="3" width="8.58203125" style="28" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="29" customWidth="1"/>
     <col min="6" max="6" width="42.25" style="29" customWidth="1"/>
-    <col min="7" max="7" width="28.125" style="110" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="16.375" style="28" customWidth="1"/>
+    <col min="7" max="7" width="28.08203125" style="110" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="16.33203125" style="28" customWidth="1"/>
     <col min="10" max="11" width="27.25" style="28" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="28" customWidth="1"/>
-    <col min="13" max="18" width="8.625" style="28" customWidth="1"/>
+    <col min="12" max="12" width="15.58203125" style="28" customWidth="1"/>
+    <col min="13" max="18" width="8.58203125" style="28" customWidth="1"/>
     <col min="19" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
@@ -24761,10 +24722,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12" thickBot="1">
-      <c r="A8" s="30" t="s">
-        <v>457</v>
-      </c>
+    <row r="8" spans="1:18" ht="11.5" thickBot="1">
+      <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
       <c r="D8" s="31"/>
@@ -24840,7 +24799,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5">
+    <row r="11" spans="1:18" ht="22">
       <c r="A11" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E11),
@@ -24854,7 +24813,7 @@
         <v>1-1-1</v>
       </c>
       <c r="B11" s="113" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C11" s="113" t="s">
         <v>78</v>
@@ -24869,7 +24828,7 @@
         <v>81</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H11" s="53"/>
       <c r="I11" s="53"/>
@@ -24883,7 +24842,7 @@
       <c r="Q11" s="116"/>
       <c r="R11" s="50"/>
     </row>
-    <row r="12" spans="1:18" ht="22.5">
+    <row r="12" spans="1:18" ht="22">
       <c r="A12" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E12),
@@ -24906,7 +24865,7 @@
         <v>84</v>
       </c>
       <c r="G12" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H12" s="53"/>
       <c r="I12" s="53"/>
@@ -24920,7 +24879,7 @@
       <c r="Q12" s="116"/>
       <c r="R12" s="50"/>
     </row>
-    <row r="13" spans="1:18" ht="33.75">
+    <row r="13" spans="1:18" ht="33">
       <c r="A13" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E13),
@@ -24945,7 +24904,7 @@
         <v>87</v>
       </c>
       <c r="G13" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H13" s="53"/>
       <c r="I13" s="53"/>
@@ -24959,7 +24918,7 @@
       <c r="Q13" s="116"/>
       <c r="R13" s="50"/>
     </row>
-    <row r="14" spans="1:18" ht="22.5">
+    <row r="14" spans="1:18" ht="22">
       <c r="A14" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E14),
@@ -24980,7 +24939,7 @@
         <v>88</v>
       </c>
       <c r="G14" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
@@ -24994,7 +24953,7 @@
       <c r="Q14" s="116"/>
       <c r="R14" s="50"/>
     </row>
-    <row r="15" spans="1:18" ht="22.5">
+    <row r="15" spans="1:18" ht="22">
       <c r="A15" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E15),
@@ -25015,7 +24974,7 @@
         <v>89</v>
       </c>
       <c r="G15" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H15" s="53"/>
       <c r="I15" s="53"/>
@@ -25029,7 +24988,7 @@
       <c r="Q15" s="116"/>
       <c r="R15" s="50"/>
     </row>
-    <row r="16" spans="1:18" ht="22.5">
+    <row r="16" spans="1:18" ht="22">
       <c r="A16" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E16),
@@ -25050,7 +25009,7 @@
         <v>90</v>
       </c>
       <c r="G16" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H16" s="53"/>
       <c r="I16" s="53"/>
@@ -25064,7 +25023,7 @@
       <c r="Q16" s="116"/>
       <c r="R16" s="50"/>
     </row>
-    <row r="17" spans="1:18" ht="33.75">
+    <row r="17" spans="1:18" ht="33">
       <c r="A17" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E17),
@@ -25085,7 +25044,7 @@
         <v>91</v>
       </c>
       <c r="G17" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H17" s="53"/>
       <c r="I17" s="53"/>
@@ -25099,7 +25058,7 @@
       <c r="Q17" s="116"/>
       <c r="R17" s="50"/>
     </row>
-    <row r="18" spans="1:18" ht="22.5">
+    <row r="18" spans="1:18" ht="22">
       <c r="A18" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E18),
@@ -25124,7 +25083,7 @@
         <v>94</v>
       </c>
       <c r="G18" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H18" s="53"/>
       <c r="I18" s="53"/>
@@ -25138,7 +25097,7 @@
       <c r="Q18" s="116"/>
       <c r="R18" s="50"/>
     </row>
-    <row r="19" spans="1:18" ht="22.5">
+    <row r="19" spans="1:18" ht="22">
       <c r="A19" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E19),
@@ -25159,7 +25118,7 @@
         <v>95</v>
       </c>
       <c r="G19" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H19" s="53"/>
       <c r="I19" s="53"/>
@@ -25173,7 +25132,7 @@
       <c r="Q19" s="116"/>
       <c r="R19" s="50"/>
     </row>
-    <row r="20" spans="1:18" ht="22.5">
+    <row r="20" spans="1:18" ht="22">
       <c r="A20" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E20),
@@ -25194,7 +25153,7 @@
         <v>96</v>
       </c>
       <c r="G20" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H20" s="53"/>
       <c r="I20" s="53"/>
@@ -25208,7 +25167,7 @@
       <c r="Q20" s="116"/>
       <c r="R20" s="50"/>
     </row>
-    <row r="21" spans="1:18" ht="22.5">
+    <row r="21" spans="1:18" ht="22">
       <c r="A21" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E21),
@@ -25231,7 +25190,7 @@
         <v>98</v>
       </c>
       <c r="G21" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H21" s="53"/>
       <c r="I21" s="53"/>
@@ -25245,7 +25204,7 @@
       <c r="Q21" s="116"/>
       <c r="R21" s="50"/>
     </row>
-    <row r="22" spans="1:18" ht="22.5">
+    <row r="22" spans="1:18" ht="22">
       <c r="A22" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A22" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E22),
@@ -25266,7 +25225,7 @@
         <v>99</v>
       </c>
       <c r="G22" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H22" s="53"/>
       <c r="I22" s="53"/>
@@ -25280,7 +25239,7 @@
       <c r="Q22" s="116"/>
       <c r="R22" s="50"/>
     </row>
-    <row r="23" spans="1:18" ht="22.5">
+    <row r="23" spans="1:18" ht="22">
       <c r="A23" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A23" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E23),
@@ -25298,10 +25257,10 @@
       <c r="D23" s="119"/>
       <c r="E23" s="119"/>
       <c r="F23" s="115" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G23" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
@@ -25315,7 +25274,7 @@
       <c r="Q23" s="116"/>
       <c r="R23" s="50"/>
     </row>
-    <row r="24" spans="1:18" ht="22.5">
+    <row r="24" spans="1:18" ht="22">
       <c r="A24" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E24),
@@ -25333,10 +25292,10 @@
       <c r="D24" s="120"/>
       <c r="E24" s="118"/>
       <c r="F24" s="115" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G24" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H24" s="53"/>
       <c r="I24" s="53"/>
@@ -25350,7 +25309,7 @@
       <c r="Q24" s="116"/>
       <c r="R24" s="50"/>
     </row>
-    <row r="25" spans="1:18" ht="22.5">
+    <row r="25" spans="1:18" ht="22">
       <c r="A25" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E25),
@@ -25375,7 +25334,7 @@
         <v>103</v>
       </c>
       <c r="G25" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H25" s="53"/>
       <c r="I25" s="53"/>
@@ -25410,7 +25369,7 @@
         <v>104</v>
       </c>
       <c r="G26" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H26" s="53"/>
       <c r="I26" s="53"/>
@@ -25424,7 +25383,7 @@
       <c r="Q26" s="116"/>
       <c r="R26" s="50"/>
     </row>
-    <row r="27" spans="1:18" ht="33.75">
+    <row r="27" spans="1:18" ht="33">
       <c r="A27" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E27),
@@ -25449,7 +25408,7 @@
         <v>107</v>
       </c>
       <c r="G27" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H27" s="53"/>
       <c r="I27" s="53"/>
@@ -25463,7 +25422,7 @@
       <c r="Q27" s="116"/>
       <c r="R27" s="50"/>
     </row>
-    <row r="28" spans="1:18" ht="22.5">
+    <row r="28" spans="1:18" ht="22">
       <c r="A28" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E28),
@@ -25484,7 +25443,7 @@
         <v>108</v>
       </c>
       <c r="G28" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H28" s="53"/>
       <c r="I28" s="53"/>
@@ -25498,7 +25457,7 @@
       <c r="Q28" s="116"/>
       <c r="R28" s="50"/>
     </row>
-    <row r="29" spans="1:18" ht="22.5">
+    <row r="29" spans="1:18" ht="22">
       <c r="A29" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E29),
@@ -25521,7 +25480,7 @@
         <v>110</v>
       </c>
       <c r="G29" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
@@ -25535,7 +25494,7 @@
       <c r="Q29" s="116"/>
       <c r="R29" s="50"/>
     </row>
-    <row r="30" spans="1:18" ht="22.5">
+    <row r="30" spans="1:18" ht="22">
       <c r="A30" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E30),
@@ -25556,7 +25515,7 @@
         <v>111</v>
       </c>
       <c r="G30" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H30" s="53"/>
       <c r="I30" s="53"/>
@@ -25570,7 +25529,7 @@
       <c r="Q30" s="116"/>
       <c r="R30" s="50"/>
     </row>
-    <row r="31" spans="1:18" ht="22.5">
+    <row r="31" spans="1:18" ht="22">
       <c r="A31" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A31" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E31),
@@ -25591,7 +25550,7 @@
         <v>112</v>
       </c>
       <c r="G31" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H31" s="53"/>
       <c r="I31" s="53"/>
@@ -25605,7 +25564,7 @@
       <c r="Q31" s="116"/>
       <c r="R31" s="50"/>
     </row>
-    <row r="32" spans="1:18" ht="22.5">
+    <row r="32" spans="1:18" ht="22">
       <c r="A32" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A32" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E32),
@@ -25626,7 +25585,7 @@
         <v>113</v>
       </c>
       <c r="G32" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H32" s="53"/>
       <c r="I32" s="53"/>
@@ -25640,7 +25599,7 @@
       <c r="Q32" s="116"/>
       <c r="R32" s="50"/>
     </row>
-    <row r="33" spans="1:18" ht="22.5">
+    <row r="33" spans="1:18" ht="22">
       <c r="A33" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A33" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E33),
@@ -25657,13 +25616,13 @@
       <c r="C33" s="117"/>
       <c r="D33" s="119"/>
       <c r="E33" s="119" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F33" s="115" t="s">
         <v>115</v>
       </c>
       <c r="G33" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H33" s="53"/>
       <c r="I33" s="53"/>
@@ -25677,7 +25636,7 @@
       <c r="Q33" s="116"/>
       <c r="R33" s="50"/>
     </row>
-    <row r="34" spans="1:18" ht="22.5">
+    <row r="34" spans="1:18" ht="22">
       <c r="A34" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A34" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E34),
@@ -25698,7 +25657,7 @@
         <v>116</v>
       </c>
       <c r="G34" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H34" s="53"/>
       <c r="I34" s="53"/>
@@ -25712,7 +25671,7 @@
       <c r="Q34" s="116"/>
       <c r="R34" s="50"/>
     </row>
-    <row r="35" spans="1:18" ht="45">
+    <row r="35" spans="1:18" ht="44">
       <c r="A35" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A35" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E35),
@@ -25732,10 +25691,10 @@
         <v>117</v>
       </c>
       <c r="F35" s="115" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G35" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H35" s="48"/>
       <c r="I35" s="48"/>
@@ -25749,7 +25708,7 @@
       <c r="Q35" s="116"/>
       <c r="R35" s="50"/>
     </row>
-    <row r="36" spans="1:18" ht="33.75">
+    <row r="36" spans="1:18" ht="33">
       <c r="A36" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A36" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E36),
@@ -25767,16 +25726,16 @@
         <v>119</v>
       </c>
       <c r="D36" s="121" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E36" s="113" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F36" s="118" t="s">
         <v>121</v>
       </c>
       <c r="G36" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H36" s="53"/>
       <c r="I36" s="53"/>
@@ -25790,7 +25749,7 @@
       <c r="Q36" s="116"/>
       <c r="R36" s="50"/>
     </row>
-    <row r="37" spans="1:18" ht="33.75">
+    <row r="37" spans="1:18" ht="33">
       <c r="A37" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A37" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E37),
@@ -25808,10 +25767,10 @@
       <c r="D37" s="119"/>
       <c r="E37" s="114"/>
       <c r="F37" s="115" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G37" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H37" s="53"/>
       <c r="I37" s="53"/>
@@ -25825,7 +25784,7 @@
       <c r="Q37" s="116"/>
       <c r="R37" s="50"/>
     </row>
-    <row r="38" spans="1:18" ht="22.5">
+    <row r="38" spans="1:18" ht="22">
       <c r="A38" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A38" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E38),
@@ -25846,7 +25805,7 @@
         <v>123</v>
       </c>
       <c r="G38" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H38" s="53"/>
       <c r="I38" s="53"/>
@@ -25860,7 +25819,7 @@
       <c r="Q38" s="116"/>
       <c r="R38" s="50"/>
     </row>
-    <row r="39" spans="1:18" ht="22.5">
+    <row r="39" spans="1:18" ht="22">
       <c r="A39" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E39),
@@ -25881,7 +25840,7 @@
         <v>124</v>
       </c>
       <c r="G39" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H39" s="53"/>
       <c r="I39" s="53"/>
@@ -25895,7 +25854,7 @@
       <c r="Q39" s="116"/>
       <c r="R39" s="50"/>
     </row>
-    <row r="40" spans="1:18" ht="33.75">
+    <row r="40" spans="1:18" ht="33">
       <c r="A40" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E40),
@@ -25917,10 +25876,10 @@
         <v>86</v>
       </c>
       <c r="F40" s="115" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G40" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H40" s="53"/>
       <c r="I40" s="53"/>
@@ -25952,10 +25911,10 @@
       <c r="D41" s="120"/>
       <c r="E41" s="118"/>
       <c r="F41" s="115" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G41" s="50" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H41" s="53"/>
       <c r="I41" s="53"/>
@@ -25969,7 +25928,7 @@
       <c r="Q41" s="116"/>
       <c r="R41" s="50"/>
     </row>
-    <row r="42" spans="1:18" ht="22.5">
+    <row r="42" spans="1:18" ht="22">
       <c r="A42" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A42" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E42),
@@ -26012,7 +25971,7 @@
       <c r="Q42" s="116"/>
       <c r="R42" s="50"/>
     </row>
-    <row r="43" spans="1:18" ht="22.5">
+    <row r="43" spans="1:18" ht="22">
       <c r="A43" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A43" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E43),
@@ -26047,7 +26006,7 @@
       <c r="Q43" s="116"/>
       <c r="R43" s="50"/>
     </row>
-    <row r="44" spans="1:18" ht="22.5">
+    <row r="44" spans="1:18" ht="22">
       <c r="A44" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A44" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E44),
@@ -26082,7 +26041,7 @@
       <c r="Q44" s="116"/>
       <c r="R44" s="50"/>
     </row>
-    <row r="45" spans="1:18" ht="22.5">
+    <row r="45" spans="1:18" ht="22">
       <c r="A45" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A45" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E45),
@@ -26119,7 +26078,7 @@
       <c r="Q45" s="116"/>
       <c r="R45" s="50"/>
     </row>
-    <row r="46" spans="1:18" ht="22.5">
+    <row r="46" spans="1:18" ht="22">
       <c r="A46" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A46" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E46),
@@ -26154,7 +26113,7 @@
       <c r="Q46" s="116"/>
       <c r="R46" s="50"/>
     </row>
-    <row r="47" spans="1:18" ht="22.5">
+    <row r="47" spans="1:18" ht="22">
       <c r="A47" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A47" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E47),
@@ -26189,7 +26148,7 @@
       <c r="Q47" s="116"/>
       <c r="R47" s="50"/>
     </row>
-    <row r="48" spans="1:18" ht="22.5">
+    <row r="48" spans="1:18" ht="22">
       <c r="A48" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A48" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E48),
@@ -26226,7 +26185,7 @@
       <c r="Q48" s="116"/>
       <c r="R48" s="50"/>
     </row>
-    <row r="49" spans="1:18" ht="22.5">
+    <row r="49" spans="1:18" ht="22">
       <c r="A49" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A49" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E49),
@@ -26261,7 +26220,7 @@
       <c r="Q49" s="116"/>
       <c r="R49" s="50"/>
     </row>
-    <row r="50" spans="1:18" ht="22.5">
+    <row r="50" spans="1:18" ht="22">
       <c r="A50" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A50" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E50),
@@ -26298,7 +26257,7 @@
       <c r="Q50" s="116"/>
       <c r="R50" s="50"/>
     </row>
-    <row r="51" spans="1:18" ht="22.5">
+    <row r="51" spans="1:18" ht="22">
       <c r="A51" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A51" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E51),
@@ -26333,7 +26292,7 @@
       <c r="Q51" s="116"/>
       <c r="R51" s="50"/>
     </row>
-    <row r="52" spans="1:18" ht="22.5">
+    <row r="52" spans="1:18" ht="22">
       <c r="A52" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A52" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E52),
@@ -26368,7 +26327,7 @@
       <c r="Q52" s="116"/>
       <c r="R52" s="50"/>
     </row>
-    <row r="53" spans="1:18" ht="22.5">
+    <row r="53" spans="1:18" ht="22">
       <c r="A53" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A53" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E53),
@@ -26403,7 +26362,7 @@
       <c r="Q53" s="116"/>
       <c r="R53" s="50"/>
     </row>
-    <row r="54" spans="1:18" ht="22.5">
+    <row r="54" spans="1:18" ht="22">
       <c r="A54" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A54" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E54),
@@ -26438,7 +26397,7 @@
       <c r="Q54" s="116"/>
       <c r="R54" s="50"/>
     </row>
-    <row r="55" spans="1:18" ht="22.5">
+    <row r="55" spans="1:18" ht="22">
       <c r="A55" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A55" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E55),
@@ -26473,7 +26432,7 @@
       <c r="Q55" s="116"/>
       <c r="R55" s="50"/>
     </row>
-    <row r="56" spans="1:18" ht="33.75">
+    <row r="56" spans="1:18" ht="33">
       <c r="A56" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A56" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E56),
@@ -26510,7 +26469,7 @@
       <c r="Q56" s="116"/>
       <c r="R56" s="50"/>
     </row>
-    <row r="57" spans="1:18" ht="22.5">
+    <row r="57" spans="1:18" ht="22">
       <c r="A57" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A57" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E57),
@@ -26527,7 +26486,7 @@
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="115" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F57" s="115" t="s">
         <v>152</v>
@@ -26547,7 +26506,7 @@
       <c r="Q57" s="116"/>
       <c r="R57" s="50"/>
     </row>
-    <row r="58" spans="1:18" ht="22.5">
+    <row r="58" spans="1:18" ht="22">
       <c r="A58" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A58" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E58),
@@ -26584,7 +26543,7 @@
       <c r="Q58" s="116"/>
       <c r="R58" s="50"/>
     </row>
-    <row r="59" spans="1:18" ht="22.5">
+    <row r="59" spans="1:18" ht="22">
       <c r="A59" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A59" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E59),
@@ -26603,10 +26562,10 @@
         <v>155</v>
       </c>
       <c r="E59" s="119" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F59" s="115" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G59" s="50" t="s">
         <v>157</v>
@@ -26623,7 +26582,7 @@
       <c r="Q59" s="116"/>
       <c r="R59" s="50"/>
     </row>
-    <row r="60" spans="1:18" ht="22.5">
+    <row r="60" spans="1:18" ht="22">
       <c r="A60" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A60" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E60),
@@ -26641,7 +26600,7 @@
       <c r="D60" s="114"/>
       <c r="E60" s="119"/>
       <c r="F60" s="113" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G60" s="50" t="s">
         <v>157</v>
@@ -26658,7 +26617,7 @@
       <c r="Q60" s="116"/>
       <c r="R60" s="50"/>
     </row>
-    <row r="61" spans="1:18" ht="22.5">
+    <row r="61" spans="1:18" ht="22">
       <c r="A61" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A61" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E61),
@@ -26676,7 +26635,7 @@
       <c r="D61" s="114"/>
       <c r="E61" s="119"/>
       <c r="F61" s="115" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G61" s="50" t="s">
         <v>157</v>
@@ -26693,7 +26652,7 @@
       <c r="Q61" s="116"/>
       <c r="R61" s="50"/>
     </row>
-    <row r="62" spans="1:18" ht="22.5">
+    <row r="62" spans="1:18" ht="22">
       <c r="A62" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A62" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E62),
@@ -26711,7 +26670,7 @@
       <c r="D62" s="114"/>
       <c r="E62" s="119"/>
       <c r="F62" s="115" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G62" s="50" t="s">
         <v>157</v>
@@ -26728,7 +26687,7 @@
       <c r="Q62" s="116"/>
       <c r="R62" s="50"/>
     </row>
-    <row r="63" spans="1:18" ht="22.5">
+    <row r="63" spans="1:18" ht="22">
       <c r="A63" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A63" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E63),
@@ -26763,7 +26722,7 @@
       <c r="Q63" s="116"/>
       <c r="R63" s="50"/>
     </row>
-    <row r="64" spans="1:18" ht="33.75">
+    <row r="64" spans="1:18" ht="33">
       <c r="A64" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A64" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E64),
@@ -26800,7 +26759,7 @@
       <c r="Q64" s="116"/>
       <c r="R64" s="50"/>
     </row>
-    <row r="65" spans="1:18" ht="33.75">
+    <row r="65" spans="1:18" ht="33">
       <c r="A65" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A65" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E65),
@@ -26835,7 +26794,7 @@
       <c r="Q65" s="116"/>
       <c r="R65" s="50"/>
     </row>
-    <row r="66" spans="1:18" ht="33.75">
+    <row r="66" spans="1:18" ht="33">
       <c r="A66" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A66" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E66),
@@ -26870,7 +26829,7 @@
       <c r="Q66" s="116"/>
       <c r="R66" s="50"/>
     </row>
-    <row r="67" spans="1:18" ht="33.75">
+    <row r="67" spans="1:18" ht="33">
       <c r="A67" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A67" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E67),
@@ -26905,7 +26864,7 @@
       <c r="Q67" s="116"/>
       <c r="R67" s="50"/>
     </row>
-    <row r="68" spans="1:18" ht="33.75">
+    <row r="68" spans="1:18" ht="33">
       <c r="A68" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A68" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E68),
@@ -26940,7 +26899,7 @@
       <c r="Q68" s="116"/>
       <c r="R68" s="50"/>
     </row>
-    <row r="69" spans="1:18" ht="22.5">
+    <row r="69" spans="1:18" ht="22">
       <c r="A69" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A69" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E69),
@@ -26975,7 +26934,7 @@
       <c r="Q69" s="116"/>
       <c r="R69" s="50"/>
     </row>
-    <row r="70" spans="1:18" ht="22.5">
+    <row r="70" spans="1:18" ht="22">
       <c r="A70" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A70" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E70),
@@ -27010,7 +26969,7 @@
       <c r="Q70" s="116"/>
       <c r="R70" s="50"/>
     </row>
-    <row r="71" spans="1:18" ht="33.75">
+    <row r="71" spans="1:18" ht="33">
       <c r="A71" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A71" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E71),
@@ -27045,7 +27004,7 @@
       <c r="Q71" s="116"/>
       <c r="R71" s="50"/>
     </row>
-    <row r="72" spans="1:18" ht="22.5">
+    <row r="72" spans="1:18" ht="22">
       <c r="A72" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A72" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E72),
@@ -27224,7 +27183,7 @@
       <c r="Q76" s="116"/>
       <c r="R76" s="50"/>
     </row>
-    <row r="77" spans="1:18" ht="22.5">
+    <row r="77" spans="1:18" ht="22">
       <c r="A77" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A77" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E77),
@@ -27259,7 +27218,7 @@
       <c r="Q77" s="116"/>
       <c r="R77" s="50"/>
     </row>
-    <row r="78" spans="1:18" ht="22.5">
+    <row r="78" spans="1:18" ht="22">
       <c r="A78" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A78" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E78),
@@ -27300,7 +27259,7 @@
       <c r="Q78" s="116"/>
       <c r="R78" s="50"/>
     </row>
-    <row r="79" spans="1:18" ht="33.75">
+    <row r="79" spans="1:18" ht="33">
       <c r="A79" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A79" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E79),
@@ -27372,7 +27331,7 @@
       <c r="Q80" s="116"/>
       <c r="R80" s="50"/>
     </row>
-    <row r="81" spans="1:18" ht="33.75">
+    <row r="81" spans="1:18" ht="33">
       <c r="A81" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A81" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E81),
@@ -27409,7 +27368,7 @@
       <c r="Q81" s="116"/>
       <c r="R81" s="50"/>
     </row>
-    <row r="82" spans="1:18" ht="33.75">
+    <row r="82" spans="1:18" ht="33">
       <c r="A82" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A82" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E82),
@@ -27444,7 +27403,7 @@
       <c r="Q82" s="116"/>
       <c r="R82" s="50"/>
     </row>
-    <row r="83" spans="1:18" ht="22.5">
+    <row r="83" spans="1:18" ht="22">
       <c r="A83" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A83" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E83),
@@ -27481,7 +27440,7 @@
       <c r="Q83" s="116"/>
       <c r="R83" s="50"/>
     </row>
-    <row r="84" spans="1:18" ht="22.5">
+    <row r="84" spans="1:18" ht="22">
       <c r="A84" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A84" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E84),
@@ -27539,7 +27498,7 @@
         <v>60</v>
       </c>
       <c r="E85" s="115" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F85" s="115" t="s">
         <v>193</v>
@@ -27596,7 +27555,7 @@
       <c r="Q86" s="116"/>
       <c r="R86" s="50"/>
     </row>
-    <row r="87" spans="1:18" ht="33.75">
+    <row r="87" spans="1:18" ht="33">
       <c r="A87" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A87" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E87),
@@ -27613,7 +27572,7 @@
       <c r="C87" s="118"/>
       <c r="D87" s="118"/>
       <c r="E87" s="118" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F87" s="115" t="s">
         <v>196</v>
@@ -27633,7 +27592,7 @@
       <c r="Q87" s="116"/>
       <c r="R87" s="50"/>
     </row>
-    <row r="88" spans="1:18" ht="22.5">
+    <row r="88" spans="1:18" ht="22">
       <c r="A88" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A88" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E88),
@@ -27654,13 +27613,13 @@
         <v>60</v>
       </c>
       <c r="E88" s="119" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F88" s="113" t="s">
         <v>198</v>
       </c>
       <c r="G88" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H88" s="48"/>
       <c r="I88" s="48"/>
@@ -27674,7 +27633,7 @@
       <c r="Q88" s="116"/>
       <c r="R88" s="50"/>
     </row>
-    <row r="89" spans="1:18" ht="33.75">
+    <row r="89" spans="1:18" ht="33">
       <c r="A89" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A89" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E89),
@@ -27695,7 +27654,7 @@
         <v>199</v>
       </c>
       <c r="G89" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
@@ -27732,7 +27691,7 @@
         <v>200</v>
       </c>
       <c r="G90" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
@@ -27746,7 +27705,7 @@
       <c r="Q90" s="116"/>
       <c r="R90" s="50"/>
     </row>
-    <row r="91" spans="1:18" ht="33.75">
+    <row r="91" spans="1:18" ht="33">
       <c r="A91" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A91" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E91),
@@ -27769,7 +27728,7 @@
         <v>201</v>
       </c>
       <c r="G91" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
@@ -27783,7 +27742,7 @@
       <c r="Q91" s="116"/>
       <c r="R91" s="50"/>
     </row>
-    <row r="92" spans="1:18" ht="33.75">
+    <row r="92" spans="1:18" ht="33">
       <c r="A92" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A92" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E92),
@@ -27804,7 +27763,7 @@
         <v>202</v>
       </c>
       <c r="G92" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
@@ -27818,7 +27777,7 @@
       <c r="Q92" s="116"/>
       <c r="R92" s="50"/>
     </row>
-    <row r="93" spans="1:18" ht="33.75">
+    <row r="93" spans="1:18" ht="33">
       <c r="A93" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A93" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E93),
@@ -27835,13 +27794,13 @@
       <c r="C93" s="118"/>
       <c r="D93" s="118"/>
       <c r="E93" s="118" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F93" s="115" t="s">
         <v>203</v>
       </c>
       <c r="G93" s="50" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
@@ -27855,7 +27814,7 @@
       <c r="Q93" s="116"/>
       <c r="R93" s="50"/>
     </row>
-    <row r="94" spans="1:18" ht="22.5">
+    <row r="94" spans="1:18" ht="22">
       <c r="A94" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A94" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E94),
@@ -27882,7 +27841,7 @@
         <v>206</v>
       </c>
       <c r="G94" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
@@ -27896,7 +27855,7 @@
       <c r="Q94" s="116"/>
       <c r="R94" s="50"/>
     </row>
-    <row r="95" spans="1:18" ht="33.75">
+    <row r="95" spans="1:18" ht="33">
       <c r="A95" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A95" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E95),
@@ -27917,7 +27876,7 @@
         <v>207</v>
       </c>
       <c r="G95" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
@@ -27952,7 +27911,7 @@
         <v>208</v>
       </c>
       <c r="G96" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
@@ -27966,7 +27925,7 @@
       <c r="Q96" s="116"/>
       <c r="R96" s="50"/>
     </row>
-    <row r="97" spans="1:18" ht="33.75">
+    <row r="97" spans="1:18" ht="33">
       <c r="A97" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A97" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E97),
@@ -27987,7 +27946,7 @@
         <v>209</v>
       </c>
       <c r="G97" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H97" s="53"/>
       <c r="I97" s="53"/>
@@ -28001,7 +27960,7 @@
       <c r="Q97" s="116"/>
       <c r="R97" s="50"/>
     </row>
-    <row r="98" spans="1:18" ht="33.75">
+    <row r="98" spans="1:18" ht="33">
       <c r="A98" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A98" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E98),
@@ -28022,7 +27981,7 @@
         <v>210</v>
       </c>
       <c r="G98" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H98" s="53"/>
       <c r="I98" s="53"/>
@@ -28036,7 +27995,7 @@
       <c r="Q98" s="116"/>
       <c r="R98" s="50"/>
     </row>
-    <row r="99" spans="1:18" ht="22.5">
+    <row r="99" spans="1:18" ht="22">
       <c r="A99" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A99" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E99),
@@ -28059,7 +28018,7 @@
         <v>212</v>
       </c>
       <c r="G99" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H99" s="53"/>
       <c r="I99" s="53"/>
@@ -28073,7 +28032,7 @@
       <c r="Q99" s="116"/>
       <c r="R99" s="50"/>
     </row>
-    <row r="100" spans="1:18" ht="33.75">
+    <row r="100" spans="1:18" ht="33">
       <c r="A100" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A100" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E100),
@@ -28094,7 +28053,7 @@
         <v>213</v>
       </c>
       <c r="G100" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H100" s="53"/>
       <c r="I100" s="53"/>
@@ -28129,7 +28088,7 @@
         <v>214</v>
       </c>
       <c r="G101" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H101" s="53"/>
       <c r="I101" s="53"/>
@@ -28143,7 +28102,7 @@
       <c r="Q101" s="116"/>
       <c r="R101" s="50"/>
     </row>
-    <row r="102" spans="1:18" ht="33.75">
+    <row r="102" spans="1:18" ht="33">
       <c r="A102" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A102" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E102),
@@ -28164,7 +28123,7 @@
         <v>215</v>
       </c>
       <c r="G102" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H102" s="53"/>
       <c r="I102" s="53"/>
@@ -28178,7 +28137,7 @@
       <c r="Q102" s="116"/>
       <c r="R102" s="50"/>
     </row>
-    <row r="103" spans="1:18" ht="33.75">
+    <row r="103" spans="1:18" ht="33">
       <c r="A103" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A103" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E103),
@@ -28199,7 +28158,7 @@
         <v>216</v>
       </c>
       <c r="G103" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H103" s="53"/>
       <c r="I103" s="53"/>
@@ -28213,7 +28172,7 @@
       <c r="Q103" s="116"/>
       <c r="R103" s="50"/>
     </row>
-    <row r="104" spans="1:18" ht="33.75">
+    <row r="104" spans="1:18" ht="33">
       <c r="A104" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A104" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E104),
@@ -28230,13 +28189,13 @@
       <c r="C104" s="118"/>
       <c r="D104" s="114"/>
       <c r="E104" s="120" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F104" s="115" t="s">
         <v>217</v>
       </c>
       <c r="G104" s="50" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H104" s="53"/>
       <c r="I104" s="53"/>
@@ -28250,7 +28209,7 @@
       <c r="Q104" s="116"/>
       <c r="R104" s="50"/>
     </row>
-    <row r="105" spans="1:18" ht="33.75">
+    <row r="105" spans="1:18" ht="33">
       <c r="A105" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A105" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E105),
@@ -28369,7 +28328,7 @@
       <c r="Q107" s="116"/>
       <c r="R107" s="50"/>
     </row>
-    <row r="108" spans="1:18" ht="22.5">
+    <row r="108" spans="1:18" ht="22">
       <c r="A108" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A108" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E108),
@@ -28384,7 +28343,7 @@
       </c>
       <c r="B108" s="114"/>
       <c r="C108" s="115" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D108" s="115" t="s">
         <v>86</v>
@@ -28410,7 +28369,7 @@
       <c r="Q108" s="116"/>
       <c r="R108" s="50"/>
     </row>
-    <row r="109" spans="1:18" ht="22.5">
+    <row r="109" spans="1:18" ht="22">
       <c r="A109" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A109" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E109),
@@ -28425,7 +28384,7 @@
       </c>
       <c r="B109" s="114"/>
       <c r="C109" s="114" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D109" s="114" t="s">
         <v>86</v>
@@ -28486,7 +28445,7 @@
       <c r="Q110" s="116"/>
       <c r="R110" s="50"/>
     </row>
-    <row r="111" spans="1:18" ht="22.5">
+    <row r="111" spans="1:18" ht="22">
       <c r="A111" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A111" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E111),
@@ -28506,10 +28465,10 @@
         <v>230</v>
       </c>
       <c r="D111" s="113" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E111" s="129" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F111" s="115" t="s">
         <v>231</v>
@@ -28529,7 +28488,7 @@
       <c r="Q111" s="116"/>
       <c r="R111" s="50"/>
     </row>
-    <row r="112" spans="1:18" ht="22.5">
+    <row r="112" spans="1:18" ht="22">
       <c r="A112" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A112" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E112),
@@ -28543,7 +28502,7 @@
         <v>43-2-1</v>
       </c>
       <c r="B112" s="272" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C112" s="119"/>
       <c r="D112" s="114"/>
@@ -28566,7 +28525,7 @@
       <c r="Q112" s="116"/>
       <c r="R112" s="50"/>
     </row>
-    <row r="113" spans="1:18" ht="22.5">
+    <row r="113" spans="1:18" ht="22">
       <c r="A113" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A113" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E113),
@@ -28601,7 +28560,7 @@
       <c r="Q113" s="116"/>
       <c r="R113" s="50"/>
     </row>
-    <row r="114" spans="1:18" ht="22.5">
+    <row r="114" spans="1:18" ht="22">
       <c r="A114" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A114" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E114),
@@ -28636,7 +28595,7 @@
       <c r="Q114" s="116"/>
       <c r="R114" s="50"/>
     </row>
-    <row r="115" spans="1:18" ht="22.5">
+    <row r="115" spans="1:18" ht="22">
       <c r="A115" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A115" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E115),
@@ -28673,7 +28632,7 @@
       <c r="Q115" s="116"/>
       <c r="R115" s="50"/>
     </row>
-    <row r="116" spans="1:18" ht="22.5">
+    <row r="116" spans="1:18" ht="22">
       <c r="A116" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A116" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E116),
@@ -28708,7 +28667,7 @@
       <c r="Q116" s="116"/>
       <c r="R116" s="50"/>
     </row>
-    <row r="117" spans="1:18" ht="22.5">
+    <row r="117" spans="1:18" ht="22">
       <c r="A117" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A117" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E117),
@@ -28743,7 +28702,7 @@
       <c r="Q117" s="116"/>
       <c r="R117" s="50"/>
     </row>
-    <row r="118" spans="1:18" ht="22.5">
+    <row r="118" spans="1:18" ht="22">
       <c r="A118" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A118" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E118),
@@ -28778,7 +28737,7 @@
       <c r="Q118" s="116"/>
       <c r="R118" s="50"/>
     </row>
-    <row r="119" spans="1:18" ht="33.75">
+    <row r="119" spans="1:18" ht="33">
       <c r="A119" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A119" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E119),
@@ -28813,7 +28772,7 @@
       <c r="Q119" s="116"/>
       <c r="R119" s="50"/>
     </row>
-    <row r="120" spans="1:18" ht="33.75">
+    <row r="120" spans="1:18" ht="33">
       <c r="A120" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A120" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E120),
@@ -28850,7 +28809,7 @@
       <c r="Q120" s="116"/>
       <c r="R120" s="50"/>
     </row>
-    <row r="121" spans="1:18" ht="33.75">
+    <row r="121" spans="1:18" ht="33">
       <c r="A121" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A121" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E121),
@@ -28885,7 +28844,7 @@
       <c r="Q121" s="116"/>
       <c r="R121" s="50"/>
     </row>
-    <row r="122" spans="1:18" ht="45">
+    <row r="122" spans="1:18" ht="44">
       <c r="A122" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A122" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E122),
@@ -28920,7 +28879,7 @@
       <c r="Q122" s="116"/>
       <c r="R122" s="50"/>
     </row>
-    <row r="123" spans="1:18" ht="45">
+    <row r="123" spans="1:18" ht="44">
       <c r="A123" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A123" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E123),
@@ -28955,7 +28914,7 @@
       <c r="Q123" s="116"/>
       <c r="R123" s="50"/>
     </row>
-    <row r="124" spans="1:18" ht="33.75">
+    <row r="124" spans="1:18" ht="33">
       <c r="A124" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A124" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E124),
@@ -28990,7 +28949,7 @@
       <c r="Q124" s="116"/>
       <c r="R124" s="50"/>
     </row>
-    <row r="125" spans="1:18" ht="33.75">
+    <row r="125" spans="1:18" ht="33">
       <c r="A125" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A125" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E125),
@@ -29007,7 +28966,7 @@
       <c r="C125" s="119"/>
       <c r="D125" s="118"/>
       <c r="E125" s="118" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F125" s="115" t="s">
         <v>249</v>
@@ -29027,7 +28986,7 @@
       <c r="Q125" s="116"/>
       <c r="R125" s="50"/>
     </row>
-    <row r="126" spans="1:18" ht="33.75">
+    <row r="126" spans="1:18" ht="33">
       <c r="A126" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A126" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E126),
@@ -29043,10 +29002,10 @@
       <c r="B126" s="114"/>
       <c r="C126" s="120"/>
       <c r="D126" s="118" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E126" s="118" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F126" s="115" t="s">
         <v>250</v>
@@ -29066,7 +29025,7 @@
       <c r="Q126" s="116"/>
       <c r="R126" s="50"/>
     </row>
-    <row r="127" spans="1:18" ht="33.75">
+    <row r="127" spans="1:18" ht="33">
       <c r="A127" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A127" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E127),
@@ -29081,7 +29040,7 @@
       </c>
       <c r="B127" s="114"/>
       <c r="C127" s="114" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D127" s="114" t="s">
         <v>251</v>
@@ -29107,7 +29066,7 @@
       <c r="Q127" s="116"/>
       <c r="R127" s="50"/>
     </row>
-    <row r="128" spans="1:18" ht="22.5">
+    <row r="128" spans="1:18" ht="22">
       <c r="A128" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A128" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E128),
@@ -29124,7 +29083,7 @@
       <c r="C128" s="114"/>
       <c r="D128" s="114"/>
       <c r="E128" s="119" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F128" s="115" t="s">
         <v>255</v>
@@ -29144,7 +29103,7 @@
       <c r="Q128" s="116"/>
       <c r="R128" s="50"/>
     </row>
-    <row r="129" spans="1:18" ht="22.5">
+    <row r="129" spans="1:18" ht="22">
       <c r="A129" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A129" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E129),
@@ -29179,7 +29138,7 @@
       <c r="Q129" s="116"/>
       <c r="R129" s="50"/>
     </row>
-    <row r="130" spans="1:18" ht="33.75">
+    <row r="130" spans="1:18" ht="33">
       <c r="A130" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A130" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E130),
@@ -29214,7 +29173,7 @@
       <c r="Q130" s="116"/>
       <c r="R130" s="50"/>
     </row>
-    <row r="131" spans="1:18" ht="22.5">
+    <row r="131" spans="1:18" ht="22">
       <c r="A131" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A131" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E131),
@@ -29234,10 +29193,10 @@
         <v>230</v>
       </c>
       <c r="D131" s="113" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E131" s="129" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F131" s="115" t="s">
         <v>259</v>
@@ -29257,7 +29216,7 @@
       <c r="Q131" s="116"/>
       <c r="R131" s="50"/>
     </row>
-    <row r="132" spans="1:18" ht="22.5">
+    <row r="132" spans="1:18" ht="22">
       <c r="A132" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A132" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E132),
@@ -29294,7 +29253,7 @@
       <c r="Q132" s="116"/>
       <c r="R132" s="50"/>
     </row>
-    <row r="133" spans="1:18" ht="22.5">
+    <row r="133" spans="1:18" ht="22">
       <c r="A133" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A133" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E133),
@@ -29329,7 +29288,7 @@
       <c r="Q133" s="116"/>
       <c r="R133" s="50"/>
     </row>
-    <row r="134" spans="1:18" ht="22.5">
+    <row r="134" spans="1:18" ht="22">
       <c r="A134" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A134" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E134),
@@ -29364,7 +29323,7 @@
       <c r="Q134" s="116"/>
       <c r="R134" s="50"/>
     </row>
-    <row r="135" spans="1:18" ht="22.5">
+    <row r="135" spans="1:18" ht="22">
       <c r="A135" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A135" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E135),
@@ -29401,7 +29360,7 @@
       <c r="Q135" s="116"/>
       <c r="R135" s="50"/>
     </row>
-    <row r="136" spans="1:18" ht="33.75">
+    <row r="136" spans="1:18" ht="33">
       <c r="A136" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A136" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E136),
@@ -29436,7 +29395,7 @@
       <c r="Q136" s="116"/>
       <c r="R136" s="50"/>
     </row>
-    <row r="137" spans="1:18" ht="33.75">
+    <row r="137" spans="1:18" ht="33">
       <c r="A137" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A137" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E137),
@@ -29452,10 +29411,10 @@
       <c r="B137" s="114"/>
       <c r="C137" s="120"/>
       <c r="D137" s="118" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E137" s="118" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F137" s="115" t="s">
         <v>268</v>
@@ -29475,7 +29434,7 @@
       <c r="Q137" s="116"/>
       <c r="R137" s="50"/>
     </row>
-    <row r="138" spans="1:18" ht="33.75">
+    <row r="138" spans="1:18" ht="33">
       <c r="A138" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A138" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E138),
@@ -29516,7 +29475,7 @@
       <c r="Q138" s="116"/>
       <c r="R138" s="50"/>
     </row>
-    <row r="139" spans="1:18" ht="33.75">
+    <row r="139" spans="1:18" ht="33">
       <c r="A139" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A139" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E139),
@@ -29553,7 +29512,7 @@
       <c r="Q139" s="116"/>
       <c r="R139" s="50"/>
     </row>
-    <row r="140" spans="1:18" ht="33.75">
+    <row r="140" spans="1:18" ht="33">
       <c r="A140" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A140" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E140),
@@ -29590,7 +29549,7 @@
       <c r="Q140" s="116"/>
       <c r="R140" s="50"/>
     </row>
-    <row r="141" spans="1:18" ht="33.75">
+    <row r="141" spans="1:18" ht="33">
       <c r="A141" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A141" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E141),
@@ -29627,7 +29586,7 @@
       <c r="Q141" s="116"/>
       <c r="R141" s="50"/>
     </row>
-    <row r="142" spans="1:18" ht="33.75">
+    <row r="142" spans="1:18" ht="33">
       <c r="A142" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A142" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E142),
@@ -29644,7 +29603,7 @@
       <c r="C142" s="119"/>
       <c r="D142" s="114"/>
       <c r="E142" s="115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F142" s="115" t="s">
         <v>278</v>
@@ -29664,7 +29623,7 @@
       <c r="Q142" s="116"/>
       <c r="R142" s="50"/>
     </row>
-    <row r="143" spans="1:18" ht="22.5">
+    <row r="143" spans="1:18" ht="22">
       <c r="A143" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A143" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E143),
@@ -29681,7 +29640,7 @@
       <c r="C143" s="119"/>
       <c r="D143" s="114"/>
       <c r="E143" s="127" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F143" s="115" t="s">
         <v>280</v>
@@ -29701,7 +29660,7 @@
       <c r="Q143" s="116"/>
       <c r="R143" s="50"/>
     </row>
-    <row r="144" spans="1:18" ht="22.5">
+    <row r="144" spans="1:18" ht="22">
       <c r="A144" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A144" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E144),
@@ -29736,7 +29695,7 @@
       <c r="Q144" s="116"/>
       <c r="R144" s="50"/>
     </row>
-    <row r="145" spans="1:18" ht="22.5">
+    <row r="145" spans="1:18" ht="22">
       <c r="A145" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A145" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E145),
@@ -29771,7 +29730,7 @@
       <c r="Q145" s="116"/>
       <c r="R145" s="50"/>
     </row>
-    <row r="146" spans="1:18" ht="22.5">
+    <row r="146" spans="1:18" ht="22">
       <c r="A146" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A146" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E146),
@@ -29806,7 +29765,7 @@
       <c r="Q146" s="116"/>
       <c r="R146" s="50"/>
     </row>
-    <row r="147" spans="1:18" ht="22.5">
+    <row r="147" spans="1:18" ht="22">
       <c r="A147" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A147" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E147),
@@ -29841,7 +29800,7 @@
       <c r="Q147" s="116"/>
       <c r="R147" s="50"/>
     </row>
-    <row r="148" spans="1:18" ht="22.5">
+    <row r="148" spans="1:18" ht="22">
       <c r="A148" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A148" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E148),
@@ -29876,7 +29835,7 @@
       <c r="Q148" s="116"/>
       <c r="R148" s="50"/>
     </row>
-    <row r="149" spans="1:18" ht="22.5">
+    <row r="149" spans="1:18" ht="22">
       <c r="A149" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A149" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E149),
@@ -29895,7 +29854,7 @@
         <v>286</v>
       </c>
       <c r="E149" s="113" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F149" s="115" t="s">
         <v>287</v>
@@ -29915,7 +29874,7 @@
       <c r="Q149" s="116"/>
       <c r="R149" s="50"/>
     </row>
-    <row r="150" spans="1:18" ht="22.5">
+    <row r="150" spans="1:18" ht="22">
       <c r="A150" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A150" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E150),
@@ -29950,7 +29909,7 @@
       <c r="Q150" s="116"/>
       <c r="R150" s="50"/>
     </row>
-    <row r="151" spans="1:18" ht="33.75">
+    <row r="151" spans="1:18" ht="33">
       <c r="A151" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A151" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E151),
@@ -29987,7 +29946,7 @@
       <c r="Q151" s="116"/>
       <c r="R151" s="50"/>
     </row>
-    <row r="152" spans="1:18" ht="33.75">
+    <row r="152" spans="1:18" ht="33">
       <c r="A152" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A152" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E152),
@@ -30022,7 +29981,7 @@
       <c r="Q152" s="116"/>
       <c r="R152" s="50"/>
     </row>
-    <row r="153" spans="1:18" ht="33.75">
+    <row r="153" spans="1:18" ht="33">
       <c r="A153" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A153" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E153),
@@ -30040,7 +29999,7 @@
       <c r="D153" s="114"/>
       <c r="E153" s="127"/>
       <c r="F153" s="115" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G153" s="48" t="s">
         <v>260</v>
@@ -30057,7 +30016,7 @@
       <c r="Q153" s="116"/>
       <c r="R153" s="50"/>
     </row>
-    <row r="154" spans="1:18" ht="33.75">
+    <row r="154" spans="1:18" ht="33">
       <c r="A154" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A154" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E154),
@@ -30075,7 +30034,7 @@
       <c r="D154" s="114"/>
       <c r="E154" s="127"/>
       <c r="F154" s="115" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G154" s="48" t="s">
         <v>260</v>
@@ -30092,7 +30051,7 @@
       <c r="Q154" s="116"/>
       <c r="R154" s="50"/>
     </row>
-    <row r="155" spans="1:18" ht="33.75">
+    <row r="155" spans="1:18" ht="33">
       <c r="A155" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A155" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E155),
@@ -30127,7 +30086,7 @@
       <c r="Q155" s="116"/>
       <c r="R155" s="50"/>
     </row>
-    <row r="156" spans="1:18" ht="22.5">
+    <row r="156" spans="1:18" ht="22">
       <c r="A156" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A156" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E156),
@@ -30162,7 +30121,7 @@
       <c r="Q156" s="116"/>
       <c r="R156" s="50"/>
     </row>
-    <row r="157" spans="1:18" ht="22.5">
+    <row r="157" spans="1:18" ht="22">
       <c r="A157" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A157" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E157),
@@ -30197,7 +30156,7 @@
       <c r="Q157" s="116"/>
       <c r="R157" s="50"/>
     </row>
-    <row r="158" spans="1:18" ht="33.75">
+    <row r="158" spans="1:18" ht="33">
       <c r="A158" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A158" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E158),
@@ -30232,7 +30191,7 @@
       <c r="Q158" s="116"/>
       <c r="R158" s="50"/>
     </row>
-    <row r="159" spans="1:18" ht="33.75">
+    <row r="159" spans="1:18" ht="33">
       <c r="A159" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A159" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E159),
@@ -30267,7 +30226,7 @@
       <c r="Q159" s="116"/>
       <c r="R159" s="50"/>
     </row>
-    <row r="160" spans="1:18" ht="33.75">
+    <row r="160" spans="1:18" ht="33">
       <c r="A160" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A160" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E160),
@@ -30302,7 +30261,7 @@
       <c r="Q160" s="116"/>
       <c r="R160" s="50"/>
     </row>
-    <row r="161" spans="1:18" ht="33.75">
+    <row r="161" spans="1:18" ht="33">
       <c r="A161" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A161" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E161),
@@ -30409,7 +30368,7 @@
       <c r="Q163" s="116"/>
       <c r="R163" s="50"/>
     </row>
-    <row r="164" spans="1:18" ht="22.5">
+    <row r="164" spans="1:18" ht="22">
       <c r="A164" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A164" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E164),
@@ -30444,7 +30403,7 @@
       <c r="Q164" s="116"/>
       <c r="R164" s="50"/>
     </row>
-    <row r="165" spans="1:18" ht="22.5">
+    <row r="165" spans="1:18" ht="22">
       <c r="A165" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A165" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E165),
@@ -30479,7 +30438,7 @@
       <c r="Q165" s="116"/>
       <c r="R165" s="50"/>
     </row>
-    <row r="166" spans="1:18" ht="22.5">
+    <row r="166" spans="1:18" ht="22">
       <c r="A166" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A166" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E166),
@@ -30514,7 +30473,7 @@
       <c r="Q166" s="116"/>
       <c r="R166" s="50"/>
     </row>
-    <row r="167" spans="1:18" ht="33.75">
+    <row r="167" spans="1:18" ht="33">
       <c r="A167" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A167" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E167),
@@ -30549,7 +30508,7 @@
       <c r="Q167" s="116"/>
       <c r="R167" s="50"/>
     </row>
-    <row r="168" spans="1:18" ht="22.5">
+    <row r="168" spans="1:18" ht="22">
       <c r="A168" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A168" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E168),
@@ -30584,7 +30543,7 @@
       <c r="Q168" s="116"/>
       <c r="R168" s="50"/>
     </row>
-    <row r="169" spans="1:18" ht="22.5">
+    <row r="169" spans="1:18" ht="22">
       <c r="A169" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A169" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E169),
@@ -30621,7 +30580,7 @@
       <c r="Q169" s="116"/>
       <c r="R169" s="50"/>
     </row>
-    <row r="170" spans="1:18" ht="33.75">
+    <row r="170" spans="1:18" ht="33">
       <c r="A170" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A170" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E170),
@@ -30656,7 +30615,7 @@
       <c r="Q170" s="116"/>
       <c r="R170" s="50"/>
     </row>
-    <row r="171" spans="1:18" ht="33.75">
+    <row r="171" spans="1:18" ht="33">
       <c r="A171" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A171" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E171),
@@ -30691,7 +30650,7 @@
       <c r="Q171" s="116"/>
       <c r="R171" s="50"/>
     </row>
-    <row r="172" spans="1:18" ht="33.75">
+    <row r="172" spans="1:18" ht="33">
       <c r="A172" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A172" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E172),
@@ -30726,7 +30685,7 @@
       <c r="Q172" s="116"/>
       <c r="R172" s="50"/>
     </row>
-    <row r="173" spans="1:18" ht="45">
+    <row r="173" spans="1:18" ht="44">
       <c r="A173" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A173" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E173),
@@ -30761,7 +30720,7 @@
       <c r="Q173" s="116"/>
       <c r="R173" s="50"/>
     </row>
-    <row r="174" spans="1:18" ht="33.75">
+    <row r="174" spans="1:18" ht="33">
       <c r="A174" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A174" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E174),
@@ -30796,7 +30755,7 @@
       <c r="Q174" s="116"/>
       <c r="R174" s="50"/>
     </row>
-    <row r="175" spans="1:18" ht="33.75">
+    <row r="175" spans="1:18" ht="33">
       <c r="A175" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A175" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E175),
@@ -30831,7 +30790,7 @@
       <c r="Q175" s="116"/>
       <c r="R175" s="50"/>
     </row>
-    <row r="176" spans="1:18" ht="45">
+    <row r="176" spans="1:18" ht="44">
       <c r="A176" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A176" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E176),
@@ -30866,7 +30825,7 @@
       <c r="Q176" s="116"/>
       <c r="R176" s="50"/>
     </row>
-    <row r="177" spans="1:18" ht="22.5">
+    <row r="177" spans="1:18" ht="22">
       <c r="A177" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A177" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E177),
@@ -30901,7 +30860,7 @@
       <c r="Q177" s="116"/>
       <c r="R177" s="50"/>
     </row>
-    <row r="178" spans="1:18" ht="22.5">
+    <row r="178" spans="1:18" ht="22">
       <c r="A178" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A178" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E178),
@@ -30938,7 +30897,7 @@
       <c r="Q178" s="116"/>
       <c r="R178" s="50"/>
     </row>
-    <row r="179" spans="1:18" ht="22.5">
+    <row r="179" spans="1:18" ht="22">
       <c r="A179" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A179" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E179),
@@ -30975,7 +30934,7 @@
       <c r="Q179" s="116"/>
       <c r="R179" s="50"/>
     </row>
-    <row r="180" spans="1:18" ht="22.5">
+    <row r="180" spans="1:18" ht="22">
       <c r="A180" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A180" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E180),
@@ -31018,7 +30977,7 @@
       <c r="Q180" s="116"/>
       <c r="R180" s="50"/>
     </row>
-    <row r="181" spans="1:18" ht="22.5">
+    <row r="181" spans="1:18" ht="22">
       <c r="A181" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A181" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E181),
@@ -31073,7 +31032,7 @@
       <c r="B182" s="118"/>
       <c r="C182" s="120"/>
       <c r="D182" s="120" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E182" s="120" t="s">
         <v>86</v>
@@ -31096,7 +31055,7 @@
       <c r="Q182" s="116"/>
       <c r="R182" s="50"/>
     </row>
-    <row r="183" spans="1:18" ht="22.5">
+    <row r="183" spans="1:18" ht="22">
       <c r="A183" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A183" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E183),
@@ -31116,7 +31075,7 @@
         <v>230</v>
       </c>
       <c r="D183" s="113" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E183" s="115" t="s">
         <v>328</v>
@@ -31139,7 +31098,7 @@
       <c r="Q183" s="116"/>
       <c r="R183" s="50"/>
     </row>
-    <row r="184" spans="1:18" ht="22.5">
+    <row r="184" spans="1:18" ht="22">
       <c r="A184" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A184" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E184),
@@ -31176,7 +31135,7 @@
       <c r="Q184" s="116"/>
       <c r="R184" s="50"/>
     </row>
-    <row r="185" spans="1:18" ht="22.5">
+    <row r="185" spans="1:18" ht="22">
       <c r="A185" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A185" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E185),
@@ -31211,7 +31170,7 @@
       <c r="Q185" s="116"/>
       <c r="R185" s="50"/>
     </row>
-    <row r="186" spans="1:18" ht="22.5">
+    <row r="186" spans="1:18" ht="22">
       <c r="A186" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A186" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E186),
@@ -31248,7 +31207,7 @@
       <c r="Q186" s="116"/>
       <c r="R186" s="50"/>
     </row>
-    <row r="187" spans="1:18" ht="22.5">
+    <row r="187" spans="1:18" ht="22">
       <c r="A187" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A187" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E187),
@@ -31283,7 +31242,7 @@
       <c r="Q187" s="116"/>
       <c r="R187" s="50"/>
     </row>
-    <row r="188" spans="1:18" ht="22.5">
+    <row r="188" spans="1:18" ht="22">
       <c r="A188" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A188" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E188),
@@ -31299,10 +31258,10 @@
       <c r="B188" s="114"/>
       <c r="C188" s="118"/>
       <c r="D188" s="118" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E188" s="118" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F188" s="115" t="s">
         <v>336</v>
@@ -31322,7 +31281,7 @@
       <c r="Q188" s="116"/>
       <c r="R188" s="50"/>
     </row>
-    <row r="189" spans="1:18" ht="22.5">
+    <row r="189" spans="1:18" ht="22">
       <c r="A189" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A189" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E189),
@@ -31340,7 +31299,7 @@
         <v>337</v>
       </c>
       <c r="D189" s="114" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E189" s="119" t="s">
         <v>339</v>
@@ -31363,7 +31322,7 @@
       <c r="Q189" s="116"/>
       <c r="R189" s="50"/>
     </row>
-    <row r="190" spans="1:18" ht="22.5">
+    <row r="190" spans="1:18" ht="22">
       <c r="A190" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A190" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E190),
@@ -31398,7 +31357,7 @@
       <c r="Q190" s="116"/>
       <c r="R190" s="50"/>
     </row>
-    <row r="191" spans="1:18" ht="22.5">
+    <row r="191" spans="1:18" ht="22">
       <c r="A191" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A191" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E191),
@@ -31433,7 +31392,7 @@
       <c r="Q191" s="116"/>
       <c r="R191" s="50"/>
     </row>
-    <row r="192" spans="1:18" ht="22.5">
+    <row r="192" spans="1:18" ht="22">
       <c r="A192" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A192" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E192),
@@ -31468,7 +31427,7 @@
       <c r="Q192" s="116"/>
       <c r="R192" s="50"/>
     </row>
-    <row r="193" spans="1:18" ht="22.5">
+    <row r="193" spans="1:18" ht="22">
       <c r="A193" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A193" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E193),
@@ -31503,7 +31462,7 @@
       <c r="Q193" s="116"/>
       <c r="R193" s="50"/>
     </row>
-    <row r="194" spans="1:18" ht="22.5">
+    <row r="194" spans="1:18" ht="22">
       <c r="A194" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A194" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E194),
@@ -31538,7 +31497,7 @@
       <c r="Q194" s="116"/>
       <c r="R194" s="50"/>
     </row>
-    <row r="195" spans="1:18" ht="22.5">
+    <row r="195" spans="1:18" ht="22">
       <c r="A195" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A195" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E195),
@@ -31573,7 +31532,7 @@
       <c r="Q195" s="116"/>
       <c r="R195" s="50"/>
     </row>
-    <row r="196" spans="1:18" ht="22.5">
+    <row r="196" spans="1:18" ht="22">
       <c r="A196" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A196" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E196),
@@ -31593,7 +31552,7 @@
         <v>347</v>
       </c>
       <c r="F196" s="115" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G196" s="48" t="s">
         <v>330</v>
@@ -31610,7 +31569,7 @@
       <c r="Q196" s="116"/>
       <c r="R196" s="50"/>
     </row>
-    <row r="197" spans="1:18" ht="22.5">
+    <row r="197" spans="1:18" ht="22">
       <c r="A197" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A197" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E197),
@@ -31649,7 +31608,7 @@
       <c r="Q197" s="116"/>
       <c r="R197" s="50"/>
     </row>
-    <row r="198" spans="1:18" ht="22.5">
+    <row r="198" spans="1:18" ht="22">
       <c r="A198" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A198" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E198),
@@ -31754,7 +31713,7 @@
       <c r="Q200" s="116"/>
       <c r="R200" s="50"/>
     </row>
-    <row r="201" spans="1:18" ht="33.75">
+    <row r="201" spans="1:18" ht="33">
       <c r="A201" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A201" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E201),
@@ -31789,7 +31748,7 @@
       <c r="Q201" s="116"/>
       <c r="R201" s="50"/>
     </row>
-    <row r="202" spans="1:18" ht="33.75">
+    <row r="202" spans="1:18" ht="33">
       <c r="A202" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A202" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E202),
@@ -31824,7 +31783,7 @@
       <c r="Q202" s="116"/>
       <c r="R202" s="50"/>
     </row>
-    <row r="203" spans="1:18" ht="45">
+    <row r="203" spans="1:18" ht="44">
       <c r="A203" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A203" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E203),
@@ -31842,7 +31801,7 @@
       <c r="D203" s="114"/>
       <c r="E203" s="119"/>
       <c r="F203" s="115" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G203" s="48" t="s">
         <v>330</v>
@@ -31859,7 +31818,7 @@
       <c r="Q203" s="116"/>
       <c r="R203" s="50"/>
     </row>
-    <row r="204" spans="1:18" ht="33.75">
+    <row r="204" spans="1:18" ht="33">
       <c r="A204" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A204" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E204),
@@ -31894,7 +31853,7 @@
       <c r="Q204" s="116"/>
       <c r="R204" s="50"/>
     </row>
-    <row r="205" spans="1:18" ht="33.75">
+    <row r="205" spans="1:18" ht="33">
       <c r="A205" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A205" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E205),
@@ -31929,7 +31888,7 @@
       <c r="Q205" s="116"/>
       <c r="R205" s="50"/>
     </row>
-    <row r="206" spans="1:18" ht="22.5">
+    <row r="206" spans="1:18" ht="22">
       <c r="A206" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A206" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E206),
@@ -31964,7 +31923,7 @@
       <c r="Q206" s="116"/>
       <c r="R206" s="50"/>
     </row>
-    <row r="207" spans="1:18" ht="22.5">
+    <row r="207" spans="1:18" ht="22">
       <c r="A207" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A207" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E207),
@@ -31999,7 +31958,7 @@
       <c r="Q207" s="116"/>
       <c r="R207" s="50"/>
     </row>
-    <row r="208" spans="1:18" ht="33.75">
+    <row r="208" spans="1:18" ht="33">
       <c r="A208" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A208" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E208),
@@ -32034,7 +31993,7 @@
       <c r="Q208" s="116"/>
       <c r="R208" s="50"/>
     </row>
-    <row r="209" spans="1:18" ht="22.5">
+    <row r="209" spans="1:18" ht="22">
       <c r="A209" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A209" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E209),
@@ -32069,7 +32028,7 @@
       <c r="Q209" s="116"/>
       <c r="R209" s="50"/>
     </row>
-    <row r="210" spans="1:18" ht="22.5">
+    <row r="210" spans="1:18" ht="22">
       <c r="A210" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A210" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E210),
@@ -32085,7 +32044,7 @@
       <c r="B210" s="114"/>
       <c r="C210" s="117"/>
       <c r="D210" s="113" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E210" s="121" t="s">
         <v>162</v>
@@ -32108,7 +32067,7 @@
       <c r="Q210" s="116"/>
       <c r="R210" s="50"/>
     </row>
-    <row r="211" spans="1:18" ht="22.5">
+    <row r="211" spans="1:18" ht="22">
       <c r="A211" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A211" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E211),
@@ -32248,7 +32207,7 @@
       <c r="Q214" s="116"/>
       <c r="R214" s="50"/>
     </row>
-    <row r="215" spans="1:18" ht="45">
+    <row r="215" spans="1:18" ht="44">
       <c r="A215" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A215" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E215),
@@ -32283,7 +32242,7 @@
       <c r="Q215" s="116"/>
       <c r="R215" s="50"/>
     </row>
-    <row r="216" spans="1:18" ht="33.75">
+    <row r="216" spans="1:18" ht="33">
       <c r="A216" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A216" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E216),
@@ -32318,7 +32277,7 @@
       <c r="Q216" s="116"/>
       <c r="R216" s="50"/>
     </row>
-    <row r="217" spans="1:18" ht="33.75">
+    <row r="217" spans="1:18" ht="33">
       <c r="A217" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A217" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E217),
@@ -32336,7 +32295,7 @@
       <c r="D217" s="114"/>
       <c r="E217" s="119"/>
       <c r="F217" s="115" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G217" s="48" t="s">
         <v>330</v>
@@ -32353,7 +32312,7 @@
       <c r="Q217" s="116"/>
       <c r="R217" s="50"/>
     </row>
-    <row r="218" spans="1:18" ht="45">
+    <row r="218" spans="1:18" ht="44">
       <c r="A218" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A218" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E218),
@@ -32371,7 +32330,7 @@
       <c r="D218" s="114"/>
       <c r="E218" s="119"/>
       <c r="F218" s="115" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G218" s="48" t="s">
         <v>330</v>
@@ -32388,7 +32347,7 @@
       <c r="Q218" s="116"/>
       <c r="R218" s="50"/>
     </row>
-    <row r="219" spans="1:18" ht="33.75">
+    <row r="219" spans="1:18" ht="33">
       <c r="A219" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A219" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E219),
@@ -32423,7 +32382,7 @@
       <c r="Q219" s="116"/>
       <c r="R219" s="50"/>
     </row>
-    <row r="220" spans="1:18" ht="33.75">
+    <row r="220" spans="1:18" ht="33">
       <c r="A220" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A220" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E220),
@@ -32458,7 +32417,7 @@
       <c r="Q220" s="116"/>
       <c r="R220" s="50"/>
     </row>
-    <row r="221" spans="1:18" ht="22.5">
+    <row r="221" spans="1:18" ht="22">
       <c r="A221" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A221" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E221),
@@ -32493,7 +32452,7 @@
       <c r="Q221" s="116"/>
       <c r="R221" s="50"/>
     </row>
-    <row r="222" spans="1:18" ht="22.5">
+    <row r="222" spans="1:18" ht="22">
       <c r="A222" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A222" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E222),
@@ -32528,7 +32487,7 @@
       <c r="Q222" s="116"/>
       <c r="R222" s="50"/>
     </row>
-    <row r="223" spans="1:18" ht="33.75">
+    <row r="223" spans="1:18" ht="33">
       <c r="A223" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A223" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E223),
@@ -32563,7 +32522,7 @@
       <c r="Q223" s="116"/>
       <c r="R223" s="50"/>
     </row>
-    <row r="224" spans="1:18" ht="22.5">
+    <row r="224" spans="1:18" ht="22">
       <c r="A224" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A224" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E224),
@@ -32598,7 +32557,7 @@
       <c r="Q224" s="116"/>
       <c r="R224" s="50"/>
     </row>
-    <row r="225" spans="1:18" ht="45">
+    <row r="225" spans="1:18" ht="44">
       <c r="A225" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A225" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E225),
@@ -32635,7 +32594,7 @@
       <c r="Q225" s="116"/>
       <c r="R225" s="50"/>
     </row>
-    <row r="226" spans="1:18" ht="45">
+    <row r="226" spans="1:18" ht="44">
       <c r="A226" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A226" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E226),
@@ -32670,7 +32629,7 @@
       <c r="Q226" s="116"/>
       <c r="R226" s="50"/>
     </row>
-    <row r="227" spans="1:18" ht="33.75">
+    <row r="227" spans="1:18" ht="33">
       <c r="A227" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A227" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E227),
@@ -32705,7 +32664,7 @@
       <c r="Q227" s="116"/>
       <c r="R227" s="50"/>
     </row>
-    <row r="228" spans="1:18" ht="33.75">
+    <row r="228" spans="1:18" ht="33">
       <c r="A228" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A228" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E228),
@@ -32725,7 +32684,7 @@
         <v>188</v>
       </c>
       <c r="F228" s="115" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G228" s="48" t="s">
         <v>330</v>
@@ -32742,7 +32701,7 @@
       <c r="Q228" s="116"/>
       <c r="R228" s="50"/>
     </row>
-    <row r="229" spans="1:18" ht="22.5">
+    <row r="229" spans="1:18" ht="22">
       <c r="A229" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A229" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E229),
@@ -32779,7 +32738,7 @@
       <c r="Q229" s="116"/>
       <c r="R229" s="50"/>
     </row>
-    <row r="230" spans="1:18" ht="22.5">
+    <row r="230" spans="1:18" ht="22">
       <c r="A230" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A230" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E230),
@@ -32799,10 +32758,10 @@
         <v>230</v>
       </c>
       <c r="D230" s="113" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E230" s="115" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F230" s="115" t="s">
         <v>384</v>
@@ -32822,7 +32781,7 @@
       <c r="Q230" s="116"/>
       <c r="R230" s="50"/>
     </row>
-    <row r="231" spans="1:18" ht="22.5">
+    <row r="231" spans="1:18" ht="22">
       <c r="A231" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A231" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E231),
@@ -32894,7 +32853,7 @@
       <c r="Q232" s="116"/>
       <c r="R232" s="50"/>
     </row>
-    <row r="233" spans="1:18" ht="22.5">
+    <row r="233" spans="1:18" ht="22">
       <c r="A233" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A233" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E233),
@@ -32964,7 +32923,7 @@
       <c r="Q234" s="116"/>
       <c r="R234" s="50"/>
     </row>
-    <row r="235" spans="1:18" ht="33.75">
+    <row r="235" spans="1:18" ht="33">
       <c r="A235" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A235" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E235),
@@ -32999,7 +32958,7 @@
       <c r="Q235" s="116"/>
       <c r="R235" s="50"/>
     </row>
-    <row r="236" spans="1:18" ht="33.75">
+    <row r="236" spans="1:18" ht="33">
       <c r="A236" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A236" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E236),
@@ -33036,7 +32995,7 @@
       <c r="Q236" s="116"/>
       <c r="R236" s="50"/>
     </row>
-    <row r="237" spans="1:18" ht="22.5">
+    <row r="237" spans="1:18" ht="22">
       <c r="A237" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A237" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E237),
@@ -33071,7 +33030,7 @@
       <c r="Q237" s="116"/>
       <c r="R237" s="50"/>
     </row>
-    <row r="238" spans="1:18" ht="33.75">
+    <row r="238" spans="1:18" ht="33">
       <c r="A238" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A238" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E238),
@@ -33106,7 +33065,7 @@
       <c r="Q238" s="116"/>
       <c r="R238" s="50"/>
     </row>
-    <row r="239" spans="1:18" ht="45">
+    <row r="239" spans="1:18" ht="44">
       <c r="A239" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A239" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E239),
@@ -33141,7 +33100,7 @@
       <c r="Q239" s="116"/>
       <c r="R239" s="50"/>
     </row>
-    <row r="240" spans="1:18" ht="33.75">
+    <row r="240" spans="1:18" ht="33">
       <c r="A240" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A240" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E240),
@@ -33176,7 +33135,7 @@
       <c r="Q240" s="116"/>
       <c r="R240" s="50"/>
     </row>
-    <row r="241" spans="1:18" ht="33.75">
+    <row r="241" spans="1:18" ht="33">
       <c r="A241" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A241" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E241),
@@ -33193,7 +33152,7 @@
       <c r="C241" s="118"/>
       <c r="D241" s="118"/>
       <c r="E241" s="118" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F241" s="115" t="s">
         <v>396</v>
@@ -33213,7 +33172,7 @@
       <c r="Q241" s="116"/>
       <c r="R241" s="50"/>
     </row>
-    <row r="242" spans="1:18" ht="33.75">
+    <row r="242" spans="1:18" ht="33">
       <c r="A242" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A242" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E242),
@@ -33228,7 +33187,7 @@
       </c>
       <c r="B242" s="118"/>
       <c r="C242" s="118" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D242" s="118" t="s">
         <v>251</v>
@@ -33254,7 +33213,7 @@
       <c r="Q242" s="116"/>
       <c r="R242" s="50"/>
     </row>
-    <row r="243" spans="1:18" ht="22.5">
+    <row r="243" spans="1:18" ht="22">
       <c r="A243" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A243" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E243),
@@ -33274,10 +33233,10 @@
         <v>399</v>
       </c>
       <c r="D243" s="113" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E243" s="121" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F243" s="115" t="s">
         <v>400</v>
@@ -33297,7 +33256,7 @@
       <c r="Q243" s="116"/>
       <c r="R243" s="50"/>
     </row>
-    <row r="244" spans="1:18" ht="22.5">
+    <row r="244" spans="1:18" ht="22">
       <c r="A244" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A244" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E244),
@@ -33332,7 +33291,7 @@
       <c r="Q244" s="116"/>
       <c r="R244" s="50"/>
     </row>
-    <row r="245" spans="1:18" ht="33.75">
+    <row r="245" spans="1:18" ht="33">
       <c r="A245" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A245" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E245),
@@ -33348,10 +33307,10 @@
       <c r="B245" s="114"/>
       <c r="C245" s="114"/>
       <c r="D245" s="114" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E245" s="119" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F245" s="115" t="s">
         <v>402</v>
@@ -33371,7 +33330,7 @@
       <c r="Q245" s="116"/>
       <c r="R245" s="50"/>
     </row>
-    <row r="246" spans="1:18" ht="33.75">
+    <row r="246" spans="1:18" ht="33">
       <c r="A246" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A246" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E246),
@@ -33406,7 +33365,7 @@
       <c r="Q246" s="116"/>
       <c r="R246" s="50"/>
     </row>
-    <row r="247" spans="1:18" ht="33.75">
+    <row r="247" spans="1:18" ht="33">
       <c r="A247" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A247" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E247),
@@ -33447,7 +33406,7 @@
       <c r="Q247" s="116"/>
       <c r="R247" s="50"/>
     </row>
-    <row r="248" spans="1:18" ht="33.75">
+    <row r="248" spans="1:18" ht="33">
       <c r="A248" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A248" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E248),
@@ -33484,7 +33443,7 @@
       <c r="Q248" s="116"/>
       <c r="R248" s="50"/>
     </row>
-    <row r="249" spans="1:18" ht="33.75">
+    <row r="249" spans="1:18" ht="33">
       <c r="A249" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A249" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E249),
@@ -33521,7 +33480,7 @@
       <c r="Q249" s="116"/>
       <c r="R249" s="50"/>
     </row>
-    <row r="250" spans="1:18" ht="33.75">
+    <row r="250" spans="1:18" ht="33">
       <c r="A250" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A250" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E250),
@@ -33558,7 +33517,7 @@
       <c r="Q250" s="116"/>
       <c r="R250" s="50"/>
     </row>
-    <row r="251" spans="1:18" ht="22.5">
+    <row r="251" spans="1:18" ht="22">
       <c r="A251" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A251" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E251),
@@ -33577,7 +33536,7 @@
         <v>286</v>
       </c>
       <c r="E251" s="127" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F251" s="115" t="s">
         <v>409</v>
@@ -33597,7 +33556,7 @@
       <c r="Q251" s="116"/>
       <c r="R251" s="50"/>
     </row>
-    <row r="252" spans="1:18" ht="22.5">
+    <row r="252" spans="1:18" ht="22">
       <c r="A252" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A252" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E252),
@@ -33632,7 +33591,7 @@
       <c r="Q252" s="116"/>
       <c r="R252" s="50"/>
     </row>
-    <row r="253" spans="1:18" ht="33.75">
+    <row r="253" spans="1:18" ht="33">
       <c r="A253" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A253" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E253),
@@ -33669,7 +33628,7 @@
       <c r="Q253" s="116"/>
       <c r="R253" s="50"/>
     </row>
-    <row r="254" spans="1:18" ht="33.75">
+    <row r="254" spans="1:18" ht="33">
       <c r="A254" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A254" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E254),
@@ -33704,7 +33663,7 @@
       <c r="Q254" s="116"/>
       <c r="R254" s="50"/>
     </row>
-    <row r="255" spans="1:18" ht="33.75">
+    <row r="255" spans="1:18" ht="33">
       <c r="A255" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A255" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E255),
@@ -33722,7 +33681,7 @@
       <c r="D255" s="119"/>
       <c r="E255" s="119"/>
       <c r="F255" s="115" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G255" s="50" t="s">
         <v>385</v>
@@ -33739,7 +33698,7 @@
       <c r="Q255" s="116"/>
       <c r="R255" s="50"/>
     </row>
-    <row r="256" spans="1:18" ht="33.75">
+    <row r="256" spans="1:18" ht="33">
       <c r="A256" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A256" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E256),
@@ -33774,7 +33733,7 @@
       <c r="Q256" s="116"/>
       <c r="R256" s="50"/>
     </row>
-    <row r="257" spans="1:18" ht="33.75">
+    <row r="257" spans="1:18" ht="33">
       <c r="A257" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A257" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E257),
@@ -33809,7 +33768,7 @@
       <c r="Q257" s="116"/>
       <c r="R257" s="50"/>
     </row>
-    <row r="258" spans="1:18" ht="22.5">
+    <row r="258" spans="1:18" ht="22">
       <c r="A258" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A258" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E258),
@@ -33844,7 +33803,7 @@
       <c r="Q258" s="116"/>
       <c r="R258" s="50"/>
     </row>
-    <row r="259" spans="1:18" ht="22.5">
+    <row r="259" spans="1:18" ht="22">
       <c r="A259" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A259" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E259),
@@ -33879,7 +33838,7 @@
       <c r="Q259" s="116"/>
       <c r="R259" s="50"/>
     </row>
-    <row r="260" spans="1:18" ht="33.75">
+    <row r="260" spans="1:18" ht="33">
       <c r="A260" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A260" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E260),
@@ -33914,7 +33873,7 @@
       <c r="Q260" s="116"/>
       <c r="R260" s="50"/>
     </row>
-    <row r="261" spans="1:18" ht="33.75">
+    <row r="261" spans="1:18" ht="33">
       <c r="A261" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A261" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E261),
@@ -33949,7 +33908,7 @@
       <c r="Q261" s="116"/>
       <c r="R261" s="50"/>
     </row>
-    <row r="262" spans="1:18" ht="33.75">
+    <row r="262" spans="1:18" ht="33">
       <c r="A262" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A262" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E262),
@@ -33984,7 +33943,7 @@
       <c r="Q262" s="116"/>
       <c r="R262" s="50"/>
     </row>
-    <row r="263" spans="1:18" ht="33.75">
+    <row r="263" spans="1:18" ht="33">
       <c r="A263" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A263" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E263),
@@ -34091,7 +34050,7 @@
       <c r="Q265" s="116"/>
       <c r="R265" s="50"/>
     </row>
-    <row r="266" spans="1:18" ht="22.5">
+    <row r="266" spans="1:18" ht="22">
       <c r="A266" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A266" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E266),
@@ -34196,7 +34155,7 @@
       <c r="Q268" s="116"/>
       <c r="R268" s="50"/>
     </row>
-    <row r="269" spans="1:18" ht="33.75">
+    <row r="269" spans="1:18" ht="33">
       <c r="A269" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A269" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E269),
@@ -34231,7 +34190,7 @@
       <c r="Q269" s="116"/>
       <c r="R269" s="50"/>
     </row>
-    <row r="270" spans="1:18" ht="22.5">
+    <row r="270" spans="1:18" ht="22">
       <c r="A270" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A270" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E270),
@@ -34268,7 +34227,7 @@
       <c r="Q270" s="116"/>
       <c r="R270" s="50"/>
     </row>
-    <row r="271" spans="1:18" ht="33.75">
+    <row r="271" spans="1:18" ht="33">
       <c r="A271" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A271" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E271),
@@ -34303,7 +34262,7 @@
       <c r="Q271" s="116"/>
       <c r="R271" s="50"/>
     </row>
-    <row r="272" spans="1:18" ht="33.75">
+    <row r="272" spans="1:18" ht="33">
       <c r="A272" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A272" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E272),
@@ -34338,7 +34297,7 @@
       <c r="Q272" s="116"/>
       <c r="R272" s="50"/>
     </row>
-    <row r="273" spans="1:18" ht="45">
+    <row r="273" spans="1:18" ht="44">
       <c r="A273" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A273" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E273),
@@ -34373,7 +34332,7 @@
       <c r="Q273" s="116"/>
       <c r="R273" s="50"/>
     </row>
-    <row r="274" spans="1:18" ht="22.5">
+    <row r="274" spans="1:18" ht="22">
       <c r="A274" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A274" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E274),
@@ -34408,7 +34367,7 @@
       <c r="Q274" s="116"/>
       <c r="R274" s="50"/>
     </row>
-    <row r="275" spans="1:18" ht="33.75">
+    <row r="275" spans="1:18" ht="33">
       <c r="A275" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A275" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E275),
@@ -34443,7 +34402,7 @@
       <c r="Q275" s="116"/>
       <c r="R275" s="50"/>
     </row>
-    <row r="276" spans="1:18" ht="45">
+    <row r="276" spans="1:18" ht="44">
       <c r="A276" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A276" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E276),
@@ -34478,7 +34437,7 @@
       <c r="Q276" s="116"/>
       <c r="R276" s="50"/>
     </row>
-    <row r="277" spans="1:18" ht="22.5">
+    <row r="277" spans="1:18" ht="22">
       <c r="A277" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A277" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E277),
@@ -34513,7 +34472,7 @@
       <c r="Q277" s="116"/>
       <c r="R277" s="50"/>
     </row>
-    <row r="278" spans="1:18" ht="22.5">
+    <row r="278" spans="1:18" ht="22">
       <c r="A278" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A278" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E278),
@@ -34550,7 +34509,7 @@
       <c r="Q278" s="116"/>
       <c r="R278" s="50"/>
     </row>
-    <row r="279" spans="1:18" ht="22.5">
+    <row r="279" spans="1:18" ht="22">
       <c r="A279" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A279" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E279),
@@ -34570,10 +34529,10 @@
         <v>438</v>
       </c>
       <c r="D279" s="113" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E279" s="121" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F279" s="115" t="s">
         <v>439</v>
@@ -34593,7 +34552,7 @@
       <c r="Q279" s="116"/>
       <c r="R279" s="50"/>
     </row>
-    <row r="280" spans="1:18" ht="22.5">
+    <row r="280" spans="1:18" ht="22">
       <c r="A280" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A280" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E280),
@@ -34628,7 +34587,7 @@
       <c r="Q280" s="116"/>
       <c r="R280" s="50"/>
     </row>
-    <row r="281" spans="1:18" ht="22.5">
+    <row r="281" spans="1:18" ht="22">
       <c r="A281" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A281" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E281),
@@ -34663,7 +34622,7 @@
       <c r="Q281" s="116"/>
       <c r="R281" s="50"/>
     </row>
-    <row r="282" spans="1:18" ht="22.5">
+    <row r="282" spans="1:18" ht="22">
       <c r="A282" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A282" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E282),
@@ -34698,7 +34657,7 @@
       <c r="Q282" s="116"/>
       <c r="R282" s="50"/>
     </row>
-    <row r="283" spans="1:18" ht="22.5">
+    <row r="283" spans="1:18" ht="22">
       <c r="A283" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A283" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E283),
@@ -34739,7 +34698,7 @@
       <c r="Q283" s="116"/>
       <c r="R283" s="50"/>
     </row>
-    <row r="284" spans="1:18" ht="22.5">
+    <row r="284" spans="1:18" ht="22">
       <c r="A284" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A284" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E284),
@@ -34776,7 +34735,7 @@
       <c r="Q284" s="116"/>
       <c r="R284" s="50"/>
     </row>
-    <row r="285" spans="1:18" ht="22.5">
+    <row r="285" spans="1:18" ht="22">
       <c r="A285" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A285" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E285),
@@ -34813,7 +34772,7 @@
       <c r="Q285" s="116"/>
       <c r="R285" s="50"/>
     </row>
-    <row r="286" spans="1:18" ht="22.5">
+    <row r="286" spans="1:18" ht="22">
       <c r="A286" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A286" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E286),
@@ -34850,7 +34809,7 @@
       <c r="Q286" s="116"/>
       <c r="R286" s="50"/>
     </row>
-    <row r="287" spans="1:18" ht="22.5">
+    <row r="287" spans="1:18" ht="22">
       <c r="A287" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A287" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E287),
@@ -34889,7 +34848,7 @@
       <c r="Q287" s="116"/>
       <c r="R287" s="50"/>
     </row>
-    <row r="288" spans="1:18" ht="22.5">
+    <row r="288" spans="1:18" ht="22">
       <c r="A288" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A288" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E288),
@@ -34924,7 +34883,7 @@
       <c r="Q288" s="116"/>
       <c r="R288" s="50"/>
     </row>
-    <row r="289" spans="1:18" ht="33.75">
+    <row r="289" spans="1:18" ht="33">
       <c r="A289" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A289" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E289),
@@ -34959,7 +34918,7 @@
       <c r="Q289" s="116"/>
       <c r="R289" s="50"/>
     </row>
-    <row r="290" spans="1:18" ht="33.75">
+    <row r="290" spans="1:18" ht="33">
       <c r="A290" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A290" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E290),
@@ -34977,7 +34936,7 @@
       <c r="D290" s="119"/>
       <c r="E290" s="119"/>
       <c r="F290" s="115" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G290" s="48" t="s">
         <v>440</v>
@@ -34994,7 +34953,7 @@
       <c r="Q290" s="116"/>
       <c r="R290" s="50"/>
     </row>
-    <row r="291" spans="1:18" ht="33.75">
+    <row r="291" spans="1:18" ht="33">
       <c r="A291" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A291" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E291),
@@ -35012,7 +34971,7 @@
       <c r="D291" s="119"/>
       <c r="E291" s="119"/>
       <c r="F291" s="115" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G291" s="48" t="s">
         <v>440</v>
@@ -35029,7 +34988,7 @@
       <c r="Q291" s="116"/>
       <c r="R291" s="50"/>
     </row>
-    <row r="292" spans="1:18" ht="33.75">
+    <row r="292" spans="1:18" ht="33">
       <c r="A292" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A292" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E292),
@@ -35047,7 +35006,7 @@
       <c r="D292" s="119"/>
       <c r="E292" s="119"/>
       <c r="F292" s="115" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G292" s="48" t="s">
         <v>440</v>
@@ -35064,7 +35023,7 @@
       <c r="Q292" s="116"/>
       <c r="R292" s="50"/>
     </row>
-    <row r="293" spans="1:18" ht="33.75">
+    <row r="293" spans="1:18" ht="33">
       <c r="A293" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A293" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E293),
@@ -35082,7 +35041,7 @@
       <c r="D293" s="119"/>
       <c r="E293" s="119"/>
       <c r="F293" s="115" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G293" s="48" t="s">
         <v>440</v>
@@ -35099,7 +35058,7 @@
       <c r="Q293" s="116"/>
       <c r="R293" s="50"/>
     </row>
-    <row r="294" spans="1:18" ht="22.5">
+    <row r="294" spans="1:18" ht="22">
       <c r="A294" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A294" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E294),
@@ -35134,7 +35093,7 @@
       <c r="Q294" s="116"/>
       <c r="R294" s="50"/>
     </row>
-    <row r="295" spans="1:18" ht="22.5">
+    <row r="295" spans="1:18" ht="22">
       <c r="A295" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A295" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E295),
@@ -35169,7 +35128,7 @@
       <c r="Q295" s="116"/>
       <c r="R295" s="50"/>
     </row>
-    <row r="296" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="296" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A296" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A296" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E296),
@@ -35183,7 +35142,7 @@
         <v>101-1-1</v>
       </c>
       <c r="B296" s="88" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C296" s="156" t="s">
         <v>230</v>
@@ -35195,10 +35154,10 @@
         <v>86</v>
       </c>
       <c r="F296" s="113" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G296" s="138" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H296" s="83"/>
       <c r="I296" s="83"/>
@@ -35212,7 +35171,7 @@
       <c r="Q296" s="140"/>
       <c r="R296" s="185"/>
     </row>
-    <row r="297" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="297" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A297" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A297" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E297),
@@ -35228,26 +35187,26 @@
       <c r="B297" s="90"/>
       <c r="C297" s="160"/>
       <c r="D297" s="156" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E297" s="169" t="s">
         <v>86</v>
       </c>
       <c r="F297" s="162" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G297" s="157"/>
       <c r="H297" s="158" t="s">
         <v>29</v>
       </c>
       <c r="I297" s="158" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J297" s="159" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K297" s="163" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L297" s="163" t="s">
         <v>173</v>
@@ -35261,7 +35220,7 @@
       <c r="Q297" s="166"/>
       <c r="R297" s="174"/>
     </row>
-    <row r="298" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="298" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A298" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A298" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E298),
@@ -35283,13 +35242,13 @@
       <c r="H298" s="173"/>
       <c r="I298" s="173"/>
       <c r="J298" s="180" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="K298" s="163" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L298" s="163" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M298" s="165">
         <v>1</v>
@@ -35300,7 +35259,7 @@
       <c r="Q298" s="166"/>
       <c r="R298" s="174"/>
     </row>
-    <row r="299" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="299" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A299" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A299" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E299),
@@ -35316,26 +35275,26 @@
       <c r="B299" s="90"/>
       <c r="C299" s="160"/>
       <c r="D299" s="160" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E299" s="161" t="s">
         <v>86</v>
       </c>
       <c r="F299" s="181" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G299" s="182"/>
       <c r="H299" s="158" t="s">
         <v>29</v>
       </c>
       <c r="I299" s="158" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J299" s="167" t="s">
+        <v>527</v>
+      </c>
+      <c r="K299" s="167" t="s">
         <v>528</v>
-      </c>
-      <c r="K299" s="167" t="s">
-        <v>529</v>
       </c>
       <c r="L299" s="163" t="s">
         <v>173</v>
@@ -35349,7 +35308,7 @@
       <c r="Q299" s="166"/>
       <c r="R299" s="174"/>
     </row>
-    <row r="300" spans="1:18" s="34" customFormat="1" ht="45">
+    <row r="300" spans="1:18" s="34" customFormat="1" ht="44">
       <c r="A300" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A300" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E300),
@@ -35367,23 +35326,23 @@
       <c r="D300" s="160"/>
       <c r="E300" s="161"/>
       <c r="F300" s="162" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G300" s="157"/>
       <c r="H300" s="158" t="s">
         <v>29</v>
       </c>
       <c r="I300" s="158" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J300" s="167" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K300" s="163" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L300" s="164" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M300" s="165">
         <v>1</v>
@@ -35394,7 +35353,7 @@
       <c r="Q300" s="166"/>
       <c r="R300" s="174"/>
     </row>
-    <row r="301" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="301" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A301" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A301" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E301),
@@ -35412,10 +35371,10 @@
       <c r="D301" s="160"/>
       <c r="E301" s="161"/>
       <c r="F301" s="141" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G301" s="141" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H301" s="83"/>
       <c r="I301" s="83"/>
@@ -35429,7 +35388,7 @@
       <c r="Q301" s="144"/>
       <c r="R301" s="175"/>
     </row>
-    <row r="302" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="302" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A302" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A302" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E302),
@@ -35445,16 +35404,16 @@
       <c r="B302" s="90"/>
       <c r="C302" s="168"/>
       <c r="D302" s="134" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E302" s="145" t="s">
         <v>86</v>
       </c>
       <c r="F302" s="141" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G302" s="138" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H302" s="48"/>
       <c r="I302" s="48"/>
@@ -35468,7 +35427,7 @@
       <c r="Q302" s="144"/>
       <c r="R302" s="175"/>
     </row>
-    <row r="303" spans="1:18" s="34" customFormat="1" ht="45">
+    <row r="303" spans="1:18" s="34" customFormat="1" ht="44">
       <c r="A303" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A303" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E303),
@@ -35485,13 +35444,13 @@
       <c r="C303" s="160"/>
       <c r="D303" s="135"/>
       <c r="E303" s="116" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F303" s="141" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G303" s="138" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H303" s="83"/>
       <c r="I303" s="83"/>
@@ -35505,7 +35464,7 @@
       <c r="Q303" s="144"/>
       <c r="R303" s="175"/>
     </row>
-    <row r="304" spans="1:18" s="34" customFormat="1" ht="45">
+    <row r="304" spans="1:18" s="34" customFormat="1" ht="44">
       <c r="A304" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A304" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E304),
@@ -35527,23 +35486,23 @@
         <v>86</v>
       </c>
       <c r="F304" s="162" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G304" s="162"/>
       <c r="H304" s="158" t="s">
         <v>29</v>
       </c>
       <c r="I304" s="158" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="J304" s="159" t="s">
+        <v>517</v>
+      </c>
+      <c r="K304" s="163" t="s">
+        <v>524</v>
+      </c>
+      <c r="L304" s="164" t="s">
         <v>518</v>
-      </c>
-      <c r="K304" s="163" t="s">
-        <v>525</v>
-      </c>
-      <c r="L304" s="164" t="s">
-        <v>519</v>
       </c>
       <c r="M304" s="165">
         <v>1</v>
@@ -35554,7 +35513,7 @@
       <c r="Q304" s="166"/>
       <c r="R304" s="174"/>
     </row>
-    <row r="305" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="305" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A305" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A305" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E305),
@@ -35572,10 +35531,10 @@
       <c r="D305" s="160"/>
       <c r="E305" s="161"/>
       <c r="F305" s="141" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G305" s="138" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H305" s="48"/>
       <c r="I305" s="48"/>
@@ -35589,7 +35548,7 @@
       <c r="Q305" s="144"/>
       <c r="R305" s="175"/>
     </row>
-    <row r="306" spans="1:18" s="34" customFormat="1" ht="45">
+    <row r="306" spans="1:18" s="34" customFormat="1" ht="44">
       <c r="A306" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A306" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E306),
@@ -35607,10 +35566,10 @@
       <c r="D306" s="168"/>
       <c r="E306" s="160"/>
       <c r="F306" s="138" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G306" s="138" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H306" s="48"/>
       <c r="I306" s="48"/>
@@ -35624,7 +35583,7 @@
       <c r="Q306" s="147"/>
       <c r="R306" s="176"/>
     </row>
-    <row r="307" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="307" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A307" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A307" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E307),
@@ -35642,10 +35601,10 @@
       <c r="D307" s="168"/>
       <c r="E307" s="160"/>
       <c r="F307" s="138" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G307" s="138" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H307" s="48"/>
       <c r="I307" s="48"/>
@@ -35659,7 +35618,7 @@
       <c r="Q307" s="147"/>
       <c r="R307" s="176"/>
     </row>
-    <row r="308" spans="1:18" s="34" customFormat="1" ht="45">
+    <row r="308" spans="1:18" s="34" customFormat="1" ht="44">
       <c r="A308" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A308" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E308),
@@ -35677,10 +35636,10 @@
       <c r="D308" s="168"/>
       <c r="E308" s="160"/>
       <c r="F308" s="138" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G308" s="138" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H308" s="83"/>
       <c r="I308" s="83"/>
@@ -35694,7 +35653,7 @@
       <c r="Q308" s="147"/>
       <c r="R308" s="176"/>
     </row>
-    <row r="309" spans="1:18" s="34" customFormat="1" ht="33.75">
+    <row r="309" spans="1:18" s="34" customFormat="1" ht="33">
       <c r="A309" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A309" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E309),
@@ -35712,10 +35671,10 @@
       <c r="D309" s="168"/>
       <c r="E309" s="160"/>
       <c r="F309" s="138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G309" s="138" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H309" s="83"/>
       <c r="I309" s="83"/>
@@ -35729,7 +35688,7 @@
       <c r="Q309" s="147"/>
       <c r="R309" s="176"/>
     </row>
-    <row r="310" spans="1:18" s="34" customFormat="1" ht="45">
+    <row r="310" spans="1:18" s="34" customFormat="1" ht="44">
       <c r="A310" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A310" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E310),
@@ -35747,10 +35706,10 @@
       <c r="D310" s="168"/>
       <c r="E310" s="160"/>
       <c r="F310" s="138" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G310" s="138" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H310" s="83"/>
       <c r="I310" s="83"/>
@@ -35764,7 +35723,7 @@
       <c r="Q310" s="147"/>
       <c r="R310" s="176"/>
     </row>
-    <row r="311" spans="1:18" s="34" customFormat="1" ht="22.5">
+    <row r="311" spans="1:18" s="34" customFormat="1" ht="22">
       <c r="A311" s="44" t="str" cm="1">
         <f t="array" aca="1" ref="A311" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E311),
@@ -35782,10 +35741,10 @@
       <c r="D311" s="91"/>
       <c r="E311" s="92"/>
       <c r="F311" s="177" t="s">
+        <v>514</v>
+      </c>
+      <c r="G311" s="177" t="s">
         <v>515</v>
-      </c>
-      <c r="G311" s="177" t="s">
-        <v>516</v>
       </c>
       <c r="H311" s="48"/>
       <c r="I311" s="48"/>
@@ -35818,20 +35777,20 @@
     <oddFooter>&amp;C&amp;"MS　明朝,標準"&amp;9- &amp;P -</oddFooter>
   </headerFooter>
   <rowBreaks count="9" manualBreakCount="9">
-    <brk id="41" max="17" man="1"/>
-    <brk id="84" max="17" man="1"/>
-    <brk id="125" max="17" man="1"/>
-    <brk id="161" max="17" man="1"/>
-    <brk id="196" max="17" man="1"/>
-    <brk id="229" max="17" man="1"/>
-    <brk id="250" max="17" man="1"/>
-    <brk id="278" max="17" man="1"/>
-    <brk id="295" max="17" man="1"/>
+    <brk id="41" max="16383" man="1"/>
+    <brk id="84" max="16383" man="1"/>
+    <brk id="125" max="16383" man="1"/>
+    <brk id="161" max="16383" man="1"/>
+    <brk id="196" max="16383" man="1"/>
+    <brk id="229" max="16383" man="1"/>
+    <brk id="250" max="16383" man="1"/>
+    <brk id="278" max="16383" man="1"/>
+    <brk id="295" max="16383" man="1"/>
   </rowBreaks>
   <colBreaks count="3" manualBreakCount="3">
-    <brk id="1" max="310" man="1"/>
-    <brk id="5" max="310" man="1"/>
-    <brk id="6" max="310" man="1"/>
+    <brk id="1" max="1048575" man="1"/>
+    <brk id="5" max="1048575" man="1"/>
+    <brk id="6" max="1048575" man="1"/>
   </colBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -35843,19 +35802,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="10.625" style="28" customWidth="1"/>
+    <col min="1" max="1" width="8.58203125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="10.58203125" style="28" customWidth="1"/>
     <col min="3" max="3" width="12.25" style="28" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.25" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.125" style="28" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="21.08203125" style="28" customWidth="1" outlineLevel="1"/>
     <col min="6" max="6" width="15.5" style="28" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.25" style="28" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.75" style="28" customWidth="1"/>
-    <col min="9" max="9" width="24.875" style="28" customWidth="1"/>
-    <col min="10" max="10" width="20.625" style="28" customWidth="1"/>
-    <col min="11" max="13" width="8.625" style="28" customWidth="1"/>
+    <col min="9" max="9" width="24.83203125" style="28" customWidth="1"/>
+    <col min="10" max="10" width="20.58203125" style="28" customWidth="1"/>
+    <col min="11" max="13" width="8.58203125" style="28" customWidth="1"/>
     <col min="14" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
@@ -35898,7 +35857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="12" thickBot="1">
+    <row r="8" spans="1:15" ht="11.5" thickBot="1">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
@@ -35977,7 +35936,7 @@
         <v>17</v>
       </c>
       <c r="E11" s="115" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F11" s="152" t="s">
         <v>0</v>
@@ -36004,7 +35963,7 @@
         <v>24</v>
       </c>
       <c r="E12" s="115" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F12" s="152" t="s">
         <v>0</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
@@ -3,27 +3,27 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7B0858-41A2-464C-80C7-AE5C0E209F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EEB028-8F01-4586-ACA0-5D240F2A471B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
-    <sheet name="【リクエストID】_クラス単体テスト" sheetId="23" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体テスト" sheetId="24" r:id="rId4"/>
-    <sheet name="取引単体テスト" sheetId="17" r:id="rId5"/>
+    <sheet name="XxxAction_クラス単体" sheetId="23" r:id="rId3"/>
+    <sheet name="RAxxxxxxxx_リクエスト単体" sheetId="24" r:id="rId4"/>
+    <sheet name="取引単体" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【リクエストID】_クラス単体テスト!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体テスト!$A$10:$R$311</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【リクエストID】_クラス単体テスト!$A$1:$R$296</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAxxxxxxxx_リクエスト単体!$A$10:$R$311</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$296</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$O$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【リクエストID】_クラス単体テスト!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体テスト!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">RAxxxxxxxx_リクエスト単体!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1693" uniqueCount="541">
   <si>
     <t>システム機能設計書</t>
     <rPh sb="4" eb="6">
@@ -7015,6 +7015,10 @@
   <si>
     <t>単体テスト仕様書(Webサービス)
 サンプル取引/RMXXXXXXXX</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リクエストID：RAxxxxxxxx</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -24713,7 +24717,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>66</v>
+        <v>540</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>21</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC27A36-B468-4050-B1F8-D32528008925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CB1AAD-329F-42D9-8645-412CB1A2F21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7010,7 +7010,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>リクエストID：RAxxxxxxxx</t>
+    <t>テストターゲット名：RAxxxxxxxx</t>
+    <rPh sb="8" eb="9">
+      <t>メイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8288,108 +8291,6 @@
     <xf numFmtId="31" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="11" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8496,6 +8397,108 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12674,57 +12677,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="206" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="243" t="s">
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="209" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="244"/>
-      <c r="G1" s="244"/>
-      <c r="H1" s="244"/>
-      <c r="I1" s="244"/>
-      <c r="J1" s="244"/>
-      <c r="K1" s="244"/>
-      <c r="L1" s="244"/>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="249" t="s">
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="215" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="250"/>
-      <c r="Q1" s="250"/>
-      <c r="R1" s="251"/>
-      <c r="S1" s="258" t="s">
+      <c r="P1" s="216"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="224" t="s">
         <v>537</v>
       </c>
-      <c r="T1" s="259"/>
-      <c r="U1" s="259"/>
-      <c r="V1" s="259"/>
-      <c r="W1" s="259"/>
-      <c r="X1" s="259"/>
-      <c r="Y1" s="259"/>
-      <c r="Z1" s="260"/>
-      <c r="AA1" s="240" t="s">
+      <c r="T1" s="225"/>
+      <c r="U1" s="225"/>
+      <c r="V1" s="225"/>
+      <c r="W1" s="225"/>
+      <c r="X1" s="225"/>
+      <c r="Y1" s="225"/>
+      <c r="Z1" s="226"/>
+      <c r="AA1" s="206" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="242"/>
-      <c r="AC1" s="267" t="str">
+      <c r="AB1" s="208"/>
+      <c r="AC1" s="233" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="268"/>
-      <c r="AE1" s="268"/>
-      <c r="AF1" s="269"/>
-      <c r="AG1" s="234">
+      <c r="AD1" s="234"/>
+      <c r="AE1" s="234"/>
+      <c r="AF1" s="235"/>
+      <c r="AG1" s="200">
         <f>IF(D8="","",D8)</f>
         <v>44011</v>
       </c>
-      <c r="AH1" s="235"/>
-      <c r="AI1" s="236"/>
+      <c r="AH1" s="201"/>
+      <c r="AI1" s="202"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -12732,53 +12735,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="240" t="s">
+      <c r="A2" s="206" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="241"/>
-      <c r="C2" s="241"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="243" t="s">
+      <c r="B2" s="207"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="209" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="244"/>
-      <c r="I2" s="244"/>
-      <c r="J2" s="244"/>
-      <c r="K2" s="244"/>
-      <c r="L2" s="244"/>
-      <c r="M2" s="244"/>
-      <c r="N2" s="245"/>
-      <c r="O2" s="252"/>
-      <c r="P2" s="253"/>
-      <c r="Q2" s="253"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
-      <c r="X2" s="262"/>
-      <c r="Y2" s="262"/>
-      <c r="Z2" s="263"/>
-      <c r="AA2" s="240" t="s">
+      <c r="F2" s="210"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="210"/>
+      <c r="J2" s="210"/>
+      <c r="K2" s="210"/>
+      <c r="L2" s="210"/>
+      <c r="M2" s="210"/>
+      <c r="N2" s="211"/>
+      <c r="O2" s="218"/>
+      <c r="P2" s="219"/>
+      <c r="Q2" s="219"/>
+      <c r="R2" s="220"/>
+      <c r="S2" s="227"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="229"/>
+      <c r="AA2" s="206" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="246" t="str">
+      <c r="AB2" s="208"/>
+      <c r="AC2" s="212" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="247"/>
-      <c r="AE2" s="247"/>
-      <c r="AF2" s="248"/>
-      <c r="AG2" s="234">
+      <c r="AD2" s="213"/>
+      <c r="AE2" s="213"/>
+      <c r="AF2" s="214"/>
+      <c r="AG2" s="200">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44858</v>
       </c>
-      <c r="AH2" s="235"/>
-      <c r="AI2" s="236"/>
+      <c r="AH2" s="201"/>
+      <c r="AI2" s="202"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -12786,45 +12789,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="240" t="s">
+      <c r="A3" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="241"/>
-      <c r="C3" s="241"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="243" t="s">
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="209" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="244"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="244"/>
-      <c r="I3" s="244"/>
-      <c r="J3" s="244"/>
-      <c r="K3" s="244"/>
-      <c r="L3" s="244"/>
-      <c r="M3" s="244"/>
-      <c r="N3" s="245"/>
-      <c r="O3" s="255"/>
-      <c r="P3" s="256"/>
-      <c r="Q3" s="256"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="264"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="266"/>
-      <c r="AA3" s="240"/>
-      <c r="AB3" s="242"/>
-      <c r="AC3" s="267"/>
-      <c r="AD3" s="268"/>
-      <c r="AE3" s="268"/>
-      <c r="AF3" s="269"/>
-      <c r="AG3" s="234"/>
-      <c r="AH3" s="235"/>
-      <c r="AI3" s="236"/>
+      <c r="F3" s="210"/>
+      <c r="G3" s="210"/>
+      <c r="H3" s="210"/>
+      <c r="I3" s="210"/>
+      <c r="J3" s="210"/>
+      <c r="K3" s="210"/>
+      <c r="L3" s="210"/>
+      <c r="M3" s="210"/>
+      <c r="N3" s="211"/>
+      <c r="O3" s="221"/>
+      <c r="P3" s="222"/>
+      <c r="Q3" s="222"/>
+      <c r="R3" s="223"/>
+      <c r="S3" s="230"/>
+      <c r="T3" s="231"/>
+      <c r="U3" s="231"/>
+      <c r="V3" s="231"/>
+      <c r="W3" s="231"/>
+      <c r="X3" s="231"/>
+      <c r="Y3" s="231"/>
+      <c r="Z3" s="232"/>
+      <c r="AA3" s="206"/>
+      <c r="AB3" s="208"/>
+      <c r="AC3" s="233"/>
+      <c r="AD3" s="234"/>
+      <c r="AE3" s="234"/>
+      <c r="AF3" s="235"/>
+      <c r="AG3" s="200"/>
+      <c r="AH3" s="201"/>
+      <c r="AI3" s="202"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -12861,97 +12864,97 @@
       <c r="A7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="237" t="s">
+      <c r="B7" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="238"/>
-      <c r="D7" s="237" t="s">
+      <c r="C7" s="204"/>
+      <c r="D7" s="203" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="239"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="237" t="s">
+      <c r="E7" s="205"/>
+      <c r="F7" s="204"/>
+      <c r="G7" s="203" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="239"/>
-      <c r="I7" s="238"/>
-      <c r="J7" s="237" t="s">
+      <c r="H7" s="205"/>
+      <c r="I7" s="204"/>
+      <c r="J7" s="203" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="239"/>
-      <c r="L7" s="239"/>
-      <c r="M7" s="239"/>
-      <c r="N7" s="239"/>
-      <c r="O7" s="239"/>
-      <c r="P7" s="238"/>
-      <c r="Q7" s="237" t="s">
+      <c r="K7" s="205"/>
+      <c r="L7" s="205"/>
+      <c r="M7" s="205"/>
+      <c r="N7" s="205"/>
+      <c r="O7" s="205"/>
+      <c r="P7" s="204"/>
+      <c r="Q7" s="203" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="239"/>
-      <c r="S7" s="239"/>
-      <c r="T7" s="239"/>
-      <c r="U7" s="239"/>
-      <c r="V7" s="239"/>
-      <c r="W7" s="239"/>
-      <c r="X7" s="239"/>
-      <c r="Y7" s="239"/>
-      <c r="Z7" s="239"/>
-      <c r="AA7" s="239"/>
-      <c r="AB7" s="239"/>
-      <c r="AC7" s="239"/>
-      <c r="AD7" s="239"/>
-      <c r="AE7" s="238"/>
-      <c r="AF7" s="237" t="s">
+      <c r="R7" s="205"/>
+      <c r="S7" s="205"/>
+      <c r="T7" s="205"/>
+      <c r="U7" s="205"/>
+      <c r="V7" s="205"/>
+      <c r="W7" s="205"/>
+      <c r="X7" s="205"/>
+      <c r="Y7" s="205"/>
+      <c r="Z7" s="205"/>
+      <c r="AA7" s="205"/>
+      <c r="AB7" s="205"/>
+      <c r="AC7" s="205"/>
+      <c r="AD7" s="205"/>
+      <c r="AE7" s="204"/>
+      <c r="AF7" s="203" t="s">
         <v>43</v>
       </c>
-      <c r="AG7" s="239"/>
-      <c r="AH7" s="239"/>
-      <c r="AI7" s="238"/>
+      <c r="AG7" s="205"/>
+      <c r="AH7" s="205"/>
+      <c r="AI7" s="204"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="225" t="s">
+      <c r="B8" s="248" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="226"/>
-      <c r="D8" s="227">
+      <c r="C8" s="249"/>
+      <c r="D8" s="250">
         <v>44011</v>
       </c>
-      <c r="E8" s="228"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="225" t="s">
+      <c r="E8" s="251"/>
+      <c r="F8" s="252"/>
+      <c r="G8" s="248" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="230"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="231" t="s">
+      <c r="H8" s="253"/>
+      <c r="I8" s="249"/>
+      <c r="J8" s="254" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="232"/>
-      <c r="L8" s="232"/>
-      <c r="M8" s="232"/>
-      <c r="N8" s="232"/>
-      <c r="O8" s="232"/>
-      <c r="P8" s="233"/>
-      <c r="Q8" s="231" t="s">
+      <c r="K8" s="255"/>
+      <c r="L8" s="255"/>
+      <c r="M8" s="255"/>
+      <c r="N8" s="255"/>
+      <c r="O8" s="255"/>
+      <c r="P8" s="256"/>
+      <c r="Q8" s="254" t="s">
         <v>52</v>
       </c>
-      <c r="R8" s="232"/>
-      <c r="S8" s="232"/>
-      <c r="T8" s="232"/>
-      <c r="U8" s="232"/>
-      <c r="V8" s="232"/>
-      <c r="W8" s="232"/>
-      <c r="X8" s="232"/>
-      <c r="Y8" s="232"/>
-      <c r="Z8" s="232"/>
-      <c r="AA8" s="232"/>
-      <c r="AB8" s="232"/>
-      <c r="AC8" s="232"/>
-      <c r="AD8" s="232"/>
-      <c r="AE8" s="233"/>
+      <c r="R8" s="255"/>
+      <c r="S8" s="255"/>
+      <c r="T8" s="255"/>
+      <c r="U8" s="255"/>
+      <c r="V8" s="255"/>
+      <c r="W8" s="255"/>
+      <c r="X8" s="255"/>
+      <c r="Y8" s="255"/>
+      <c r="Z8" s="255"/>
+      <c r="AA8" s="255"/>
+      <c r="AB8" s="255"/>
+      <c r="AC8" s="255"/>
+      <c r="AD8" s="255"/>
+      <c r="AE8" s="256"/>
       <c r="AF8" s="25" t="s">
         <v>53</v>
       </c>
@@ -12963,946 +12966,1101 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="213" t="s">
+      <c r="B9" s="236" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="214"/>
-      <c r="D9" s="215">
+      <c r="C9" s="237"/>
+      <c r="D9" s="238">
         <v>44858</v>
       </c>
-      <c r="E9" s="216"/>
-      <c r="F9" s="217"/>
-      <c r="G9" s="215" t="s">
+      <c r="E9" s="239"/>
+      <c r="F9" s="240"/>
+      <c r="G9" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="218"/>
-      <c r="I9" s="214"/>
-      <c r="J9" s="219" t="s">
+      <c r="H9" s="241"/>
+      <c r="I9" s="237"/>
+      <c r="J9" s="242" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="220"/>
-      <c r="L9" s="220"/>
-      <c r="M9" s="220"/>
-      <c r="N9" s="220"/>
-      <c r="O9" s="220"/>
-      <c r="P9" s="221"/>
-      <c r="Q9" s="219" t="s">
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
+      <c r="M9" s="243"/>
+      <c r="N9" s="243"/>
+      <c r="O9" s="243"/>
+      <c r="P9" s="244"/>
+      <c r="Q9" s="242" t="s">
         <v>61</v>
       </c>
-      <c r="R9" s="222"/>
-      <c r="S9" s="222"/>
-      <c r="T9" s="222"/>
-      <c r="U9" s="222"/>
-      <c r="V9" s="222"/>
-      <c r="W9" s="222"/>
-      <c r="X9" s="222"/>
-      <c r="Y9" s="222"/>
-      <c r="Z9" s="222"/>
-      <c r="AA9" s="222"/>
-      <c r="AB9" s="222"/>
-      <c r="AC9" s="222"/>
-      <c r="AD9" s="222"/>
-      <c r="AE9" s="223"/>
-      <c r="AF9" s="224" t="s">
+      <c r="R9" s="245"/>
+      <c r="S9" s="245"/>
+      <c r="T9" s="245"/>
+      <c r="U9" s="245"/>
+      <c r="V9" s="245"/>
+      <c r="W9" s="245"/>
+      <c r="X9" s="245"/>
+      <c r="Y9" s="245"/>
+      <c r="Z9" s="245"/>
+      <c r="AA9" s="245"/>
+      <c r="AB9" s="245"/>
+      <c r="AC9" s="245"/>
+      <c r="AD9" s="245"/>
+      <c r="AE9" s="246"/>
+      <c r="AF9" s="247" t="s">
         <v>53</v>
       </c>
-      <c r="AG9" s="220"/>
-      <c r="AH9" s="220"/>
-      <c r="AI9" s="221"/>
+      <c r="AG9" s="243"/>
+      <c r="AH9" s="243"/>
+      <c r="AI9" s="244"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="201"/>
-      <c r="D10" s="202"/>
-      <c r="E10" s="203"/>
-      <c r="F10" s="204"/>
-      <c r="G10" s="200"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="201"/>
-      <c r="J10" s="206"/>
-      <c r="K10" s="207"/>
-      <c r="L10" s="207"/>
-      <c r="M10" s="207"/>
-      <c r="N10" s="207"/>
-      <c r="O10" s="207"/>
-      <c r="P10" s="208"/>
-      <c r="Q10" s="209"/>
-      <c r="R10" s="210"/>
-      <c r="S10" s="210"/>
-      <c r="T10" s="210"/>
-      <c r="U10" s="210"/>
-      <c r="V10" s="210"/>
-      <c r="W10" s="210"/>
-      <c r="X10" s="210"/>
-      <c r="Y10" s="210"/>
-      <c r="Z10" s="210"/>
-      <c r="AA10" s="210"/>
-      <c r="AB10" s="210"/>
-      <c r="AC10" s="210"/>
-      <c r="AD10" s="210"/>
-      <c r="AE10" s="211"/>
-      <c r="AF10" s="206"/>
-      <c r="AG10" s="207"/>
-      <c r="AH10" s="207"/>
-      <c r="AI10" s="208"/>
+      <c r="B10" s="257"/>
+      <c r="C10" s="258"/>
+      <c r="D10" s="259"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="257"/>
+      <c r="H10" s="262"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="263"/>
+      <c r="K10" s="264"/>
+      <c r="L10" s="264"/>
+      <c r="M10" s="264"/>
+      <c r="N10" s="264"/>
+      <c r="O10" s="264"/>
+      <c r="P10" s="265"/>
+      <c r="Q10" s="266"/>
+      <c r="R10" s="267"/>
+      <c r="S10" s="267"/>
+      <c r="T10" s="267"/>
+      <c r="U10" s="267"/>
+      <c r="V10" s="267"/>
+      <c r="W10" s="267"/>
+      <c r="X10" s="267"/>
+      <c r="Y10" s="267"/>
+      <c r="Z10" s="267"/>
+      <c r="AA10" s="267"/>
+      <c r="AB10" s="267"/>
+      <c r="AC10" s="267"/>
+      <c r="AD10" s="267"/>
+      <c r="AE10" s="268"/>
+      <c r="AF10" s="263"/>
+      <c r="AG10" s="264"/>
+      <c r="AH10" s="264"/>
+      <c r="AI10" s="265"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="200"/>
-      <c r="C11" s="201"/>
-      <c r="D11" s="202"/>
-      <c r="E11" s="203"/>
-      <c r="F11" s="204"/>
-      <c r="G11" s="200"/>
-      <c r="H11" s="205"/>
-      <c r="I11" s="201"/>
-      <c r="J11" s="206"/>
-      <c r="K11" s="207"/>
-      <c r="L11" s="207"/>
-      <c r="M11" s="207"/>
-      <c r="N11" s="207"/>
-      <c r="O11" s="207"/>
-      <c r="P11" s="208"/>
-      <c r="Q11" s="209"/>
-      <c r="R11" s="210"/>
-      <c r="S11" s="210"/>
-      <c r="T11" s="210"/>
-      <c r="U11" s="210"/>
-      <c r="V11" s="210"/>
-      <c r="W11" s="210"/>
-      <c r="X11" s="210"/>
-      <c r="Y11" s="210"/>
-      <c r="Z11" s="210"/>
-      <c r="AA11" s="210"/>
-      <c r="AB11" s="210"/>
-      <c r="AC11" s="210"/>
-      <c r="AD11" s="210"/>
-      <c r="AE11" s="211"/>
-      <c r="AF11" s="206"/>
-      <c r="AG11" s="207"/>
-      <c r="AH11" s="207"/>
-      <c r="AI11" s="208"/>
+      <c r="B11" s="257"/>
+      <c r="C11" s="258"/>
+      <c r="D11" s="259"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="261"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="263"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
+      <c r="M11" s="264"/>
+      <c r="N11" s="264"/>
+      <c r="O11" s="264"/>
+      <c r="P11" s="265"/>
+      <c r="Q11" s="266"/>
+      <c r="R11" s="267"/>
+      <c r="S11" s="267"/>
+      <c r="T11" s="267"/>
+      <c r="U11" s="267"/>
+      <c r="V11" s="267"/>
+      <c r="W11" s="267"/>
+      <c r="X11" s="267"/>
+      <c r="Y11" s="267"/>
+      <c r="Z11" s="267"/>
+      <c r="AA11" s="267"/>
+      <c r="AB11" s="267"/>
+      <c r="AC11" s="267"/>
+      <c r="AD11" s="267"/>
+      <c r="AE11" s="268"/>
+      <c r="AF11" s="263"/>
+      <c r="AG11" s="264"/>
+      <c r="AH11" s="264"/>
+      <c r="AI11" s="265"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="200"/>
-      <c r="C12" s="201"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="204"/>
-      <c r="G12" s="200"/>
-      <c r="H12" s="205"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="206"/>
-      <c r="K12" s="207"/>
-      <c r="L12" s="207"/>
-      <c r="M12" s="207"/>
-      <c r="N12" s="207"/>
-      <c r="O12" s="207"/>
-      <c r="P12" s="208"/>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210"/>
-      <c r="S12" s="210"/>
-      <c r="T12" s="210"/>
-      <c r="U12" s="210"/>
-      <c r="V12" s="210"/>
-      <c r="W12" s="210"/>
-      <c r="X12" s="210"/>
-      <c r="Y12" s="210"/>
-      <c r="Z12" s="210"/>
-      <c r="AA12" s="210"/>
-      <c r="AB12" s="210"/>
-      <c r="AC12" s="210"/>
-      <c r="AD12" s="210"/>
-      <c r="AE12" s="211"/>
-      <c r="AF12" s="206"/>
-      <c r="AG12" s="207"/>
-      <c r="AH12" s="207"/>
-      <c r="AI12" s="208"/>
+      <c r="B12" s="257"/>
+      <c r="C12" s="258"/>
+      <c r="D12" s="259"/>
+      <c r="E12" s="260"/>
+      <c r="F12" s="261"/>
+      <c r="G12" s="257"/>
+      <c r="H12" s="262"/>
+      <c r="I12" s="258"/>
+      <c r="J12" s="263"/>
+      <c r="K12" s="264"/>
+      <c r="L12" s="264"/>
+      <c r="M12" s="264"/>
+      <c r="N12" s="264"/>
+      <c r="O12" s="264"/>
+      <c r="P12" s="265"/>
+      <c r="Q12" s="266"/>
+      <c r="R12" s="267"/>
+      <c r="S12" s="267"/>
+      <c r="T12" s="267"/>
+      <c r="U12" s="267"/>
+      <c r="V12" s="267"/>
+      <c r="W12" s="267"/>
+      <c r="X12" s="267"/>
+      <c r="Y12" s="267"/>
+      <c r="Z12" s="267"/>
+      <c r="AA12" s="267"/>
+      <c r="AB12" s="267"/>
+      <c r="AC12" s="267"/>
+      <c r="AD12" s="267"/>
+      <c r="AE12" s="268"/>
+      <c r="AF12" s="263"/>
+      <c r="AG12" s="264"/>
+      <c r="AH12" s="264"/>
+      <c r="AI12" s="265"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="200"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="202"/>
-      <c r="E13" s="203"/>
-      <c r="F13" s="204"/>
-      <c r="G13" s="200"/>
-      <c r="H13" s="205"/>
-      <c r="I13" s="201"/>
-      <c r="J13" s="206"/>
-      <c r="K13" s="207"/>
-      <c r="L13" s="207"/>
-      <c r="M13" s="207"/>
-      <c r="N13" s="207"/>
-      <c r="O13" s="207"/>
-      <c r="P13" s="208"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
-      <c r="S13" s="210"/>
-      <c r="T13" s="210"/>
-      <c r="U13" s="210"/>
-      <c r="V13" s="210"/>
-      <c r="W13" s="210"/>
-      <c r="X13" s="210"/>
-      <c r="Y13" s="210"/>
-      <c r="Z13" s="210"/>
-      <c r="AA13" s="210"/>
-      <c r="AB13" s="210"/>
-      <c r="AC13" s="210"/>
-      <c r="AD13" s="210"/>
-      <c r="AE13" s="211"/>
-      <c r="AF13" s="206"/>
-      <c r="AG13" s="207"/>
-      <c r="AH13" s="207"/>
-      <c r="AI13" s="208"/>
+      <c r="B13" s="257"/>
+      <c r="C13" s="258"/>
+      <c r="D13" s="259"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="261"/>
+      <c r="G13" s="257"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="263"/>
+      <c r="K13" s="264"/>
+      <c r="L13" s="264"/>
+      <c r="M13" s="264"/>
+      <c r="N13" s="264"/>
+      <c r="O13" s="264"/>
+      <c r="P13" s="265"/>
+      <c r="Q13" s="266"/>
+      <c r="R13" s="267"/>
+      <c r="S13" s="267"/>
+      <c r="T13" s="267"/>
+      <c r="U13" s="267"/>
+      <c r="V13" s="267"/>
+      <c r="W13" s="267"/>
+      <c r="X13" s="267"/>
+      <c r="Y13" s="267"/>
+      <c r="Z13" s="267"/>
+      <c r="AA13" s="267"/>
+      <c r="AB13" s="267"/>
+      <c r="AC13" s="267"/>
+      <c r="AD13" s="267"/>
+      <c r="AE13" s="268"/>
+      <c r="AF13" s="263"/>
+      <c r="AG13" s="264"/>
+      <c r="AH13" s="264"/>
+      <c r="AI13" s="265"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="200"/>
-      <c r="H14" s="205"/>
-      <c r="I14" s="201"/>
-      <c r="J14" s="206"/>
-      <c r="K14" s="207"/>
-      <c r="L14" s="207"/>
-      <c r="M14" s="207"/>
-      <c r="N14" s="207"/>
-      <c r="O14" s="207"/>
-      <c r="P14" s="208"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
-      <c r="S14" s="210"/>
-      <c r="T14" s="210"/>
-      <c r="U14" s="210"/>
-      <c r="V14" s="210"/>
-      <c r="W14" s="210"/>
-      <c r="X14" s="210"/>
-      <c r="Y14" s="210"/>
-      <c r="Z14" s="210"/>
-      <c r="AA14" s="210"/>
-      <c r="AB14" s="210"/>
-      <c r="AC14" s="210"/>
-      <c r="AD14" s="210"/>
-      <c r="AE14" s="211"/>
-      <c r="AF14" s="206"/>
-      <c r="AG14" s="207"/>
-      <c r="AH14" s="207"/>
-      <c r="AI14" s="208"/>
+      <c r="B14" s="257"/>
+      <c r="C14" s="258"/>
+      <c r="D14" s="259"/>
+      <c r="E14" s="260"/>
+      <c r="F14" s="261"/>
+      <c r="G14" s="257"/>
+      <c r="H14" s="262"/>
+      <c r="I14" s="258"/>
+      <c r="J14" s="263"/>
+      <c r="K14" s="264"/>
+      <c r="L14" s="264"/>
+      <c r="M14" s="264"/>
+      <c r="N14" s="264"/>
+      <c r="O14" s="264"/>
+      <c r="P14" s="265"/>
+      <c r="Q14" s="266"/>
+      <c r="R14" s="267"/>
+      <c r="S14" s="267"/>
+      <c r="T14" s="267"/>
+      <c r="U14" s="267"/>
+      <c r="V14" s="267"/>
+      <c r="W14" s="267"/>
+      <c r="X14" s="267"/>
+      <c r="Y14" s="267"/>
+      <c r="Z14" s="267"/>
+      <c r="AA14" s="267"/>
+      <c r="AB14" s="267"/>
+      <c r="AC14" s="267"/>
+      <c r="AD14" s="267"/>
+      <c r="AE14" s="268"/>
+      <c r="AF14" s="263"/>
+      <c r="AG14" s="264"/>
+      <c r="AH14" s="264"/>
+      <c r="AI14" s="265"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="203"/>
-      <c r="F15" s="204"/>
-      <c r="G15" s="200"/>
-      <c r="H15" s="205"/>
-      <c r="I15" s="201"/>
-      <c r="J15" s="206"/>
-      <c r="K15" s="207"/>
-      <c r="L15" s="207"/>
-      <c r="M15" s="207"/>
-      <c r="N15" s="207"/>
-      <c r="O15" s="207"/>
-      <c r="P15" s="208"/>
-      <c r="Q15" s="209"/>
-      <c r="R15" s="210"/>
-      <c r="S15" s="210"/>
-      <c r="T15" s="210"/>
-      <c r="U15" s="210"/>
-      <c r="V15" s="210"/>
-      <c r="W15" s="210"/>
-      <c r="X15" s="210"/>
-      <c r="Y15" s="210"/>
-      <c r="Z15" s="210"/>
-      <c r="AA15" s="210"/>
-      <c r="AB15" s="210"/>
-      <c r="AC15" s="210"/>
-      <c r="AD15" s="210"/>
-      <c r="AE15" s="211"/>
-      <c r="AF15" s="206"/>
-      <c r="AG15" s="207"/>
-      <c r="AH15" s="207"/>
-      <c r="AI15" s="208"/>
+      <c r="B15" s="257"/>
+      <c r="C15" s="258"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="260"/>
+      <c r="F15" s="261"/>
+      <c r="G15" s="257"/>
+      <c r="H15" s="262"/>
+      <c r="I15" s="258"/>
+      <c r="J15" s="263"/>
+      <c r="K15" s="264"/>
+      <c r="L15" s="264"/>
+      <c r="M15" s="264"/>
+      <c r="N15" s="264"/>
+      <c r="O15" s="264"/>
+      <c r="P15" s="265"/>
+      <c r="Q15" s="266"/>
+      <c r="R15" s="267"/>
+      <c r="S15" s="267"/>
+      <c r="T15" s="267"/>
+      <c r="U15" s="267"/>
+      <c r="V15" s="267"/>
+      <c r="W15" s="267"/>
+      <c r="X15" s="267"/>
+      <c r="Y15" s="267"/>
+      <c r="Z15" s="267"/>
+      <c r="AA15" s="267"/>
+      <c r="AB15" s="267"/>
+      <c r="AC15" s="267"/>
+      <c r="AD15" s="267"/>
+      <c r="AE15" s="268"/>
+      <c r="AF15" s="263"/>
+      <c r="AG15" s="264"/>
+      <c r="AH15" s="264"/>
+      <c r="AI15" s="265"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="202"/>
-      <c r="E16" s="203"/>
-      <c r="F16" s="204"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="205"/>
-      <c r="I16" s="201"/>
-      <c r="J16" s="206"/>
-      <c r="K16" s="207"/>
-      <c r="L16" s="207"/>
-      <c r="M16" s="207"/>
-      <c r="N16" s="207"/>
-      <c r="O16" s="207"/>
-      <c r="P16" s="208"/>
-      <c r="Q16" s="209"/>
-      <c r="R16" s="210"/>
-      <c r="S16" s="210"/>
-      <c r="T16" s="210"/>
-      <c r="U16" s="210"/>
-      <c r="V16" s="210"/>
-      <c r="W16" s="210"/>
-      <c r="X16" s="210"/>
-      <c r="Y16" s="210"/>
-      <c r="Z16" s="210"/>
-      <c r="AA16" s="210"/>
-      <c r="AB16" s="210"/>
-      <c r="AC16" s="210"/>
-      <c r="AD16" s="210"/>
-      <c r="AE16" s="211"/>
-      <c r="AF16" s="206"/>
-      <c r="AG16" s="207"/>
-      <c r="AH16" s="207"/>
-      <c r="AI16" s="208"/>
+      <c r="B16" s="257"/>
+      <c r="C16" s="258"/>
+      <c r="D16" s="259"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="261"/>
+      <c r="G16" s="257"/>
+      <c r="H16" s="262"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="263"/>
+      <c r="K16" s="264"/>
+      <c r="L16" s="264"/>
+      <c r="M16" s="264"/>
+      <c r="N16" s="264"/>
+      <c r="O16" s="264"/>
+      <c r="P16" s="265"/>
+      <c r="Q16" s="266"/>
+      <c r="R16" s="267"/>
+      <c r="S16" s="267"/>
+      <c r="T16" s="267"/>
+      <c r="U16" s="267"/>
+      <c r="V16" s="267"/>
+      <c r="W16" s="267"/>
+      <c r="X16" s="267"/>
+      <c r="Y16" s="267"/>
+      <c r="Z16" s="267"/>
+      <c r="AA16" s="267"/>
+      <c r="AB16" s="267"/>
+      <c r="AC16" s="267"/>
+      <c r="AD16" s="267"/>
+      <c r="AE16" s="268"/>
+      <c r="AF16" s="263"/>
+      <c r="AG16" s="264"/>
+      <c r="AH16" s="264"/>
+      <c r="AI16" s="265"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="200"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="202"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="204"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="205"/>
-      <c r="I17" s="201"/>
-      <c r="J17" s="206"/>
-      <c r="K17" s="207"/>
-      <c r="L17" s="207"/>
-      <c r="M17" s="207"/>
-      <c r="N17" s="207"/>
-      <c r="O17" s="207"/>
-      <c r="P17" s="208"/>
-      <c r="Q17" s="209"/>
-      <c r="R17" s="210"/>
-      <c r="S17" s="210"/>
-      <c r="T17" s="210"/>
-      <c r="U17" s="210"/>
-      <c r="V17" s="210"/>
-      <c r="W17" s="210"/>
-      <c r="X17" s="210"/>
-      <c r="Y17" s="210"/>
-      <c r="Z17" s="210"/>
-      <c r="AA17" s="210"/>
-      <c r="AB17" s="210"/>
-      <c r="AC17" s="210"/>
-      <c r="AD17" s="210"/>
-      <c r="AE17" s="211"/>
-      <c r="AF17" s="206"/>
-      <c r="AG17" s="207"/>
-      <c r="AH17" s="207"/>
-      <c r="AI17" s="208"/>
+      <c r="B17" s="257"/>
+      <c r="C17" s="258"/>
+      <c r="D17" s="259"/>
+      <c r="E17" s="260"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="262"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="263"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
+      <c r="M17" s="264"/>
+      <c r="N17" s="264"/>
+      <c r="O17" s="264"/>
+      <c r="P17" s="265"/>
+      <c r="Q17" s="266"/>
+      <c r="R17" s="267"/>
+      <c r="S17" s="267"/>
+      <c r="T17" s="267"/>
+      <c r="U17" s="267"/>
+      <c r="V17" s="267"/>
+      <c r="W17" s="267"/>
+      <c r="X17" s="267"/>
+      <c r="Y17" s="267"/>
+      <c r="Z17" s="267"/>
+      <c r="AA17" s="267"/>
+      <c r="AB17" s="267"/>
+      <c r="AC17" s="267"/>
+      <c r="AD17" s="267"/>
+      <c r="AE17" s="268"/>
+      <c r="AF17" s="263"/>
+      <c r="AG17" s="264"/>
+      <c r="AH17" s="264"/>
+      <c r="AI17" s="265"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="200"/>
-      <c r="C18" s="201"/>
-      <c r="D18" s="202"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="204"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="205"/>
-      <c r="I18" s="201"/>
-      <c r="J18" s="206"/>
-      <c r="K18" s="207"/>
-      <c r="L18" s="207"/>
-      <c r="M18" s="207"/>
-      <c r="N18" s="207"/>
-      <c r="O18" s="207"/>
-      <c r="P18" s="208"/>
-      <c r="Q18" s="209"/>
-      <c r="R18" s="210"/>
-      <c r="S18" s="210"/>
-      <c r="T18" s="210"/>
-      <c r="U18" s="210"/>
-      <c r="V18" s="210"/>
-      <c r="W18" s="210"/>
-      <c r="X18" s="210"/>
-      <c r="Y18" s="210"/>
-      <c r="Z18" s="210"/>
-      <c r="AA18" s="210"/>
-      <c r="AB18" s="210"/>
-      <c r="AC18" s="210"/>
-      <c r="AD18" s="210"/>
-      <c r="AE18" s="211"/>
-      <c r="AF18" s="206"/>
-      <c r="AG18" s="207"/>
-      <c r="AH18" s="207"/>
-      <c r="AI18" s="208"/>
+      <c r="B18" s="257"/>
+      <c r="C18" s="258"/>
+      <c r="D18" s="259"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="261"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="263"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
+      <c r="M18" s="264"/>
+      <c r="N18" s="264"/>
+      <c r="O18" s="264"/>
+      <c r="P18" s="265"/>
+      <c r="Q18" s="266"/>
+      <c r="R18" s="267"/>
+      <c r="S18" s="267"/>
+      <c r="T18" s="267"/>
+      <c r="U18" s="267"/>
+      <c r="V18" s="267"/>
+      <c r="W18" s="267"/>
+      <c r="X18" s="267"/>
+      <c r="Y18" s="267"/>
+      <c r="Z18" s="267"/>
+      <c r="AA18" s="267"/>
+      <c r="AB18" s="267"/>
+      <c r="AC18" s="267"/>
+      <c r="AD18" s="267"/>
+      <c r="AE18" s="268"/>
+      <c r="AF18" s="263"/>
+      <c r="AG18" s="264"/>
+      <c r="AH18" s="264"/>
+      <c r="AI18" s="265"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="200"/>
-      <c r="C19" s="201"/>
-      <c r="D19" s="202"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="204"/>
-      <c r="G19" s="200"/>
-      <c r="H19" s="205"/>
-      <c r="I19" s="201"/>
-      <c r="J19" s="206"/>
-      <c r="K19" s="207"/>
-      <c r="L19" s="207"/>
-      <c r="M19" s="207"/>
-      <c r="N19" s="207"/>
-      <c r="O19" s="207"/>
-      <c r="P19" s="208"/>
-      <c r="Q19" s="209"/>
-      <c r="R19" s="210"/>
-      <c r="S19" s="210"/>
-      <c r="T19" s="210"/>
-      <c r="U19" s="210"/>
-      <c r="V19" s="210"/>
-      <c r="W19" s="210"/>
-      <c r="X19" s="210"/>
-      <c r="Y19" s="210"/>
-      <c r="Z19" s="210"/>
-      <c r="AA19" s="210"/>
-      <c r="AB19" s="210"/>
-      <c r="AC19" s="210"/>
-      <c r="AD19" s="210"/>
-      <c r="AE19" s="211"/>
-      <c r="AF19" s="206"/>
-      <c r="AG19" s="207"/>
-      <c r="AH19" s="207"/>
-      <c r="AI19" s="208"/>
+      <c r="B19" s="257"/>
+      <c r="C19" s="258"/>
+      <c r="D19" s="259"/>
+      <c r="E19" s="260"/>
+      <c r="F19" s="261"/>
+      <c r="G19" s="257"/>
+      <c r="H19" s="262"/>
+      <c r="I19" s="258"/>
+      <c r="J19" s="263"/>
+      <c r="K19" s="264"/>
+      <c r="L19" s="264"/>
+      <c r="M19" s="264"/>
+      <c r="N19" s="264"/>
+      <c r="O19" s="264"/>
+      <c r="P19" s="265"/>
+      <c r="Q19" s="266"/>
+      <c r="R19" s="267"/>
+      <c r="S19" s="267"/>
+      <c r="T19" s="267"/>
+      <c r="U19" s="267"/>
+      <c r="V19" s="267"/>
+      <c r="W19" s="267"/>
+      <c r="X19" s="267"/>
+      <c r="Y19" s="267"/>
+      <c r="Z19" s="267"/>
+      <c r="AA19" s="267"/>
+      <c r="AB19" s="267"/>
+      <c r="AC19" s="267"/>
+      <c r="AD19" s="267"/>
+      <c r="AE19" s="268"/>
+      <c r="AF19" s="263"/>
+      <c r="AG19" s="264"/>
+      <c r="AH19" s="264"/>
+      <c r="AI19" s="265"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="200"/>
-      <c r="C20" s="201"/>
-      <c r="D20" s="202"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="204"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="205"/>
-      <c r="I20" s="201"/>
-      <c r="J20" s="206"/>
-      <c r="K20" s="207"/>
-      <c r="L20" s="207"/>
-      <c r="M20" s="207"/>
-      <c r="N20" s="207"/>
-      <c r="O20" s="207"/>
-      <c r="P20" s="208"/>
-      <c r="Q20" s="209"/>
-      <c r="R20" s="210"/>
-      <c r="S20" s="210"/>
-      <c r="T20" s="210"/>
-      <c r="U20" s="210"/>
-      <c r="V20" s="210"/>
-      <c r="W20" s="210"/>
-      <c r="X20" s="210"/>
-      <c r="Y20" s="210"/>
-      <c r="Z20" s="210"/>
-      <c r="AA20" s="210"/>
-      <c r="AB20" s="210"/>
-      <c r="AC20" s="210"/>
-      <c r="AD20" s="210"/>
-      <c r="AE20" s="211"/>
-      <c r="AF20" s="206"/>
-      <c r="AG20" s="207"/>
-      <c r="AH20" s="207"/>
-      <c r="AI20" s="208"/>
+      <c r="B20" s="257"/>
+      <c r="C20" s="258"/>
+      <c r="D20" s="259"/>
+      <c r="E20" s="260"/>
+      <c r="F20" s="261"/>
+      <c r="G20" s="257"/>
+      <c r="H20" s="262"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="263"/>
+      <c r="K20" s="264"/>
+      <c r="L20" s="264"/>
+      <c r="M20" s="264"/>
+      <c r="N20" s="264"/>
+      <c r="O20" s="264"/>
+      <c r="P20" s="265"/>
+      <c r="Q20" s="266"/>
+      <c r="R20" s="267"/>
+      <c r="S20" s="267"/>
+      <c r="T20" s="267"/>
+      <c r="U20" s="267"/>
+      <c r="V20" s="267"/>
+      <c r="W20" s="267"/>
+      <c r="X20" s="267"/>
+      <c r="Y20" s="267"/>
+      <c r="Z20" s="267"/>
+      <c r="AA20" s="267"/>
+      <c r="AB20" s="267"/>
+      <c r="AC20" s="267"/>
+      <c r="AD20" s="267"/>
+      <c r="AE20" s="268"/>
+      <c r="AF20" s="263"/>
+      <c r="AG20" s="264"/>
+      <c r="AH20" s="264"/>
+      <c r="AI20" s="265"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="200"/>
-      <c r="C21" s="201"/>
-      <c r="D21" s="202"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="204"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="205"/>
-      <c r="I21" s="201"/>
-      <c r="J21" s="206"/>
-      <c r="K21" s="207"/>
-      <c r="L21" s="207"/>
-      <c r="M21" s="207"/>
-      <c r="N21" s="207"/>
-      <c r="O21" s="207"/>
-      <c r="P21" s="208"/>
-      <c r="Q21" s="209"/>
-      <c r="R21" s="210"/>
-      <c r="S21" s="210"/>
-      <c r="T21" s="210"/>
-      <c r="U21" s="210"/>
-      <c r="V21" s="210"/>
-      <c r="W21" s="210"/>
-      <c r="X21" s="210"/>
-      <c r="Y21" s="210"/>
-      <c r="Z21" s="210"/>
-      <c r="AA21" s="210"/>
-      <c r="AB21" s="210"/>
-      <c r="AC21" s="210"/>
-      <c r="AD21" s="210"/>
-      <c r="AE21" s="211"/>
-      <c r="AF21" s="206"/>
-      <c r="AG21" s="207"/>
-      <c r="AH21" s="207"/>
-      <c r="AI21" s="208"/>
+      <c r="B21" s="257"/>
+      <c r="C21" s="258"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="261"/>
+      <c r="G21" s="257"/>
+      <c r="H21" s="262"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="263"/>
+      <c r="K21" s="264"/>
+      <c r="L21" s="264"/>
+      <c r="M21" s="264"/>
+      <c r="N21" s="264"/>
+      <c r="O21" s="264"/>
+      <c r="P21" s="265"/>
+      <c r="Q21" s="266"/>
+      <c r="R21" s="267"/>
+      <c r="S21" s="267"/>
+      <c r="T21" s="267"/>
+      <c r="U21" s="267"/>
+      <c r="V21" s="267"/>
+      <c r="W21" s="267"/>
+      <c r="X21" s="267"/>
+      <c r="Y21" s="267"/>
+      <c r="Z21" s="267"/>
+      <c r="AA21" s="267"/>
+      <c r="AB21" s="267"/>
+      <c r="AC21" s="267"/>
+      <c r="AD21" s="267"/>
+      <c r="AE21" s="268"/>
+      <c r="AF21" s="263"/>
+      <c r="AG21" s="264"/>
+      <c r="AH21" s="264"/>
+      <c r="AI21" s="265"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="200"/>
-      <c r="C22" s="201"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="204"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="205"/>
-      <c r="I22" s="201"/>
-      <c r="J22" s="206"/>
-      <c r="K22" s="207"/>
-      <c r="L22" s="207"/>
-      <c r="M22" s="207"/>
-      <c r="N22" s="207"/>
-      <c r="O22" s="207"/>
-      <c r="P22" s="208"/>
-      <c r="Q22" s="209"/>
-      <c r="R22" s="210"/>
-      <c r="S22" s="210"/>
-      <c r="T22" s="210"/>
-      <c r="U22" s="210"/>
-      <c r="V22" s="210"/>
-      <c r="W22" s="210"/>
-      <c r="X22" s="210"/>
-      <c r="Y22" s="210"/>
-      <c r="Z22" s="210"/>
-      <c r="AA22" s="210"/>
-      <c r="AB22" s="210"/>
-      <c r="AC22" s="210"/>
-      <c r="AD22" s="210"/>
-      <c r="AE22" s="211"/>
-      <c r="AF22" s="206"/>
-      <c r="AG22" s="207"/>
-      <c r="AH22" s="207"/>
-      <c r="AI22" s="208"/>
+      <c r="B22" s="257"/>
+      <c r="C22" s="258"/>
+      <c r="D22" s="259"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="261"/>
+      <c r="G22" s="257"/>
+      <c r="H22" s="262"/>
+      <c r="I22" s="258"/>
+      <c r="J22" s="263"/>
+      <c r="K22" s="264"/>
+      <c r="L22" s="264"/>
+      <c r="M22" s="264"/>
+      <c r="N22" s="264"/>
+      <c r="O22" s="264"/>
+      <c r="P22" s="265"/>
+      <c r="Q22" s="266"/>
+      <c r="R22" s="267"/>
+      <c r="S22" s="267"/>
+      <c r="T22" s="267"/>
+      <c r="U22" s="267"/>
+      <c r="V22" s="267"/>
+      <c r="W22" s="267"/>
+      <c r="X22" s="267"/>
+      <c r="Y22" s="267"/>
+      <c r="Z22" s="267"/>
+      <c r="AA22" s="267"/>
+      <c r="AB22" s="267"/>
+      <c r="AC22" s="267"/>
+      <c r="AD22" s="267"/>
+      <c r="AE22" s="268"/>
+      <c r="AF22" s="263"/>
+      <c r="AG22" s="264"/>
+      <c r="AH22" s="264"/>
+      <c r="AI22" s="265"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="200"/>
-      <c r="C23" s="201"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="203"/>
-      <c r="F23" s="204"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="205"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="206"/>
-      <c r="K23" s="207"/>
-      <c r="L23" s="207"/>
-      <c r="M23" s="207"/>
-      <c r="N23" s="207"/>
-      <c r="O23" s="207"/>
-      <c r="P23" s="208"/>
-      <c r="Q23" s="209"/>
-      <c r="R23" s="210"/>
-      <c r="S23" s="210"/>
-      <c r="T23" s="210"/>
-      <c r="U23" s="210"/>
-      <c r="V23" s="210"/>
-      <c r="W23" s="210"/>
-      <c r="X23" s="210"/>
-      <c r="Y23" s="210"/>
-      <c r="Z23" s="210"/>
-      <c r="AA23" s="210"/>
-      <c r="AB23" s="210"/>
-      <c r="AC23" s="210"/>
-      <c r="AD23" s="210"/>
-      <c r="AE23" s="211"/>
-      <c r="AF23" s="206"/>
-      <c r="AG23" s="207"/>
-      <c r="AH23" s="207"/>
-      <c r="AI23" s="208"/>
+      <c r="B23" s="257"/>
+      <c r="C23" s="258"/>
+      <c r="D23" s="259"/>
+      <c r="E23" s="260"/>
+      <c r="F23" s="261"/>
+      <c r="G23" s="257"/>
+      <c r="H23" s="262"/>
+      <c r="I23" s="258"/>
+      <c r="J23" s="263"/>
+      <c r="K23" s="264"/>
+      <c r="L23" s="264"/>
+      <c r="M23" s="264"/>
+      <c r="N23" s="264"/>
+      <c r="O23" s="264"/>
+      <c r="P23" s="265"/>
+      <c r="Q23" s="266"/>
+      <c r="R23" s="267"/>
+      <c r="S23" s="267"/>
+      <c r="T23" s="267"/>
+      <c r="U23" s="267"/>
+      <c r="V23" s="267"/>
+      <c r="W23" s="267"/>
+      <c r="X23" s="267"/>
+      <c r="Y23" s="267"/>
+      <c r="Z23" s="267"/>
+      <c r="AA23" s="267"/>
+      <c r="AB23" s="267"/>
+      <c r="AC23" s="267"/>
+      <c r="AD23" s="267"/>
+      <c r="AE23" s="268"/>
+      <c r="AF23" s="263"/>
+      <c r="AG23" s="264"/>
+      <c r="AH23" s="264"/>
+      <c r="AI23" s="265"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="200"/>
-      <c r="C24" s="201"/>
-      <c r="D24" s="202"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="204"/>
-      <c r="G24" s="200"/>
-      <c r="H24" s="205"/>
-      <c r="I24" s="201"/>
-      <c r="J24" s="206"/>
-      <c r="K24" s="207"/>
-      <c r="L24" s="207"/>
-      <c r="M24" s="207"/>
-      <c r="N24" s="207"/>
-      <c r="O24" s="207"/>
-      <c r="P24" s="208"/>
-      <c r="Q24" s="209"/>
-      <c r="R24" s="210"/>
-      <c r="S24" s="210"/>
-      <c r="T24" s="210"/>
-      <c r="U24" s="210"/>
-      <c r="V24" s="210"/>
-      <c r="W24" s="210"/>
-      <c r="X24" s="210"/>
-      <c r="Y24" s="210"/>
-      <c r="Z24" s="210"/>
-      <c r="AA24" s="210"/>
-      <c r="AB24" s="210"/>
-      <c r="AC24" s="210"/>
-      <c r="AD24" s="210"/>
-      <c r="AE24" s="211"/>
-      <c r="AF24" s="206"/>
-      <c r="AG24" s="207"/>
-      <c r="AH24" s="207"/>
-      <c r="AI24" s="208"/>
+      <c r="B24" s="257"/>
+      <c r="C24" s="258"/>
+      <c r="D24" s="259"/>
+      <c r="E24" s="260"/>
+      <c r="F24" s="261"/>
+      <c r="G24" s="257"/>
+      <c r="H24" s="262"/>
+      <c r="I24" s="258"/>
+      <c r="J24" s="263"/>
+      <c r="K24" s="264"/>
+      <c r="L24" s="264"/>
+      <c r="M24" s="264"/>
+      <c r="N24" s="264"/>
+      <c r="O24" s="264"/>
+      <c r="P24" s="265"/>
+      <c r="Q24" s="266"/>
+      <c r="R24" s="267"/>
+      <c r="S24" s="267"/>
+      <c r="T24" s="267"/>
+      <c r="U24" s="267"/>
+      <c r="V24" s="267"/>
+      <c r="W24" s="267"/>
+      <c r="X24" s="267"/>
+      <c r="Y24" s="267"/>
+      <c r="Z24" s="267"/>
+      <c r="AA24" s="267"/>
+      <c r="AB24" s="267"/>
+      <c r="AC24" s="267"/>
+      <c r="AD24" s="267"/>
+      <c r="AE24" s="268"/>
+      <c r="AF24" s="263"/>
+      <c r="AG24" s="264"/>
+      <c r="AH24" s="264"/>
+      <c r="AI24" s="265"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="200"/>
-      <c r="C25" s="201"/>
-      <c r="D25" s="202"/>
-      <c r="E25" s="203"/>
-      <c r="F25" s="204"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="205"/>
-      <c r="I25" s="201"/>
-      <c r="J25" s="206"/>
-      <c r="K25" s="207"/>
-      <c r="L25" s="207"/>
-      <c r="M25" s="207"/>
-      <c r="N25" s="207"/>
-      <c r="O25" s="207"/>
-      <c r="P25" s="208"/>
-      <c r="Q25" s="209"/>
-      <c r="R25" s="210"/>
-      <c r="S25" s="210"/>
-      <c r="T25" s="210"/>
-      <c r="U25" s="210"/>
-      <c r="V25" s="210"/>
-      <c r="W25" s="210"/>
-      <c r="X25" s="210"/>
-      <c r="Y25" s="210"/>
-      <c r="Z25" s="210"/>
-      <c r="AA25" s="210"/>
-      <c r="AB25" s="210"/>
-      <c r="AC25" s="210"/>
-      <c r="AD25" s="210"/>
-      <c r="AE25" s="211"/>
-      <c r="AF25" s="206"/>
-      <c r="AG25" s="207"/>
-      <c r="AH25" s="207"/>
-      <c r="AI25" s="208"/>
+      <c r="B25" s="257"/>
+      <c r="C25" s="258"/>
+      <c r="D25" s="259"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="261"/>
+      <c r="G25" s="257"/>
+      <c r="H25" s="262"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="263"/>
+      <c r="K25" s="264"/>
+      <c r="L25" s="264"/>
+      <c r="M25" s="264"/>
+      <c r="N25" s="264"/>
+      <c r="O25" s="264"/>
+      <c r="P25" s="265"/>
+      <c r="Q25" s="266"/>
+      <c r="R25" s="267"/>
+      <c r="S25" s="267"/>
+      <c r="T25" s="267"/>
+      <c r="U25" s="267"/>
+      <c r="V25" s="267"/>
+      <c r="W25" s="267"/>
+      <c r="X25" s="267"/>
+      <c r="Y25" s="267"/>
+      <c r="Z25" s="267"/>
+      <c r="AA25" s="267"/>
+      <c r="AB25" s="267"/>
+      <c r="AC25" s="267"/>
+      <c r="AD25" s="267"/>
+      <c r="AE25" s="268"/>
+      <c r="AF25" s="263"/>
+      <c r="AG25" s="264"/>
+      <c r="AH25" s="264"/>
+      <c r="AI25" s="265"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="200"/>
-      <c r="C26" s="201"/>
-      <c r="D26" s="202"/>
-      <c r="E26" s="203"/>
-      <c r="F26" s="204"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="205"/>
-      <c r="I26" s="201"/>
-      <c r="J26" s="206"/>
-      <c r="K26" s="207"/>
-      <c r="L26" s="207"/>
-      <c r="M26" s="207"/>
-      <c r="N26" s="207"/>
-      <c r="O26" s="207"/>
-      <c r="P26" s="208"/>
-      <c r="Q26" s="209"/>
-      <c r="R26" s="210"/>
-      <c r="S26" s="210"/>
-      <c r="T26" s="210"/>
-      <c r="U26" s="210"/>
-      <c r="V26" s="210"/>
-      <c r="W26" s="210"/>
-      <c r="X26" s="210"/>
-      <c r="Y26" s="210"/>
-      <c r="Z26" s="210"/>
-      <c r="AA26" s="210"/>
-      <c r="AB26" s="210"/>
-      <c r="AC26" s="210"/>
-      <c r="AD26" s="210"/>
-      <c r="AE26" s="211"/>
-      <c r="AF26" s="206"/>
-      <c r="AG26" s="207"/>
-      <c r="AH26" s="207"/>
-      <c r="AI26" s="208"/>
+      <c r="B26" s="257"/>
+      <c r="C26" s="258"/>
+      <c r="D26" s="259"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="261"/>
+      <c r="G26" s="257"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="263"/>
+      <c r="K26" s="264"/>
+      <c r="L26" s="264"/>
+      <c r="M26" s="264"/>
+      <c r="N26" s="264"/>
+      <c r="O26" s="264"/>
+      <c r="P26" s="265"/>
+      <c r="Q26" s="266"/>
+      <c r="R26" s="267"/>
+      <c r="S26" s="267"/>
+      <c r="T26" s="267"/>
+      <c r="U26" s="267"/>
+      <c r="V26" s="267"/>
+      <c r="W26" s="267"/>
+      <c r="X26" s="267"/>
+      <c r="Y26" s="267"/>
+      <c r="Z26" s="267"/>
+      <c r="AA26" s="267"/>
+      <c r="AB26" s="267"/>
+      <c r="AC26" s="267"/>
+      <c r="AD26" s="267"/>
+      <c r="AE26" s="268"/>
+      <c r="AF26" s="263"/>
+      <c r="AG26" s="264"/>
+      <c r="AH26" s="264"/>
+      <c r="AI26" s="265"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="200"/>
-      <c r="C27" s="201"/>
-      <c r="D27" s="202"/>
-      <c r="E27" s="203"/>
-      <c r="F27" s="204"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="205"/>
-      <c r="I27" s="201"/>
-      <c r="J27" s="206"/>
-      <c r="K27" s="207"/>
-      <c r="L27" s="207"/>
-      <c r="M27" s="207"/>
-      <c r="N27" s="207"/>
-      <c r="O27" s="207"/>
-      <c r="P27" s="208"/>
-      <c r="Q27" s="209"/>
-      <c r="R27" s="210"/>
-      <c r="S27" s="210"/>
-      <c r="T27" s="210"/>
-      <c r="U27" s="210"/>
-      <c r="V27" s="210"/>
-      <c r="W27" s="210"/>
-      <c r="X27" s="210"/>
-      <c r="Y27" s="210"/>
-      <c r="Z27" s="210"/>
-      <c r="AA27" s="210"/>
-      <c r="AB27" s="210"/>
-      <c r="AC27" s="210"/>
-      <c r="AD27" s="210"/>
-      <c r="AE27" s="211"/>
-      <c r="AF27" s="206"/>
-      <c r="AG27" s="207"/>
-      <c r="AH27" s="207"/>
-      <c r="AI27" s="208"/>
+      <c r="B27" s="257"/>
+      <c r="C27" s="258"/>
+      <c r="D27" s="259"/>
+      <c r="E27" s="260"/>
+      <c r="F27" s="261"/>
+      <c r="G27" s="257"/>
+      <c r="H27" s="262"/>
+      <c r="I27" s="258"/>
+      <c r="J27" s="263"/>
+      <c r="K27" s="264"/>
+      <c r="L27" s="264"/>
+      <c r="M27" s="264"/>
+      <c r="N27" s="264"/>
+      <c r="O27" s="264"/>
+      <c r="P27" s="265"/>
+      <c r="Q27" s="266"/>
+      <c r="R27" s="267"/>
+      <c r="S27" s="267"/>
+      <c r="T27" s="267"/>
+      <c r="U27" s="267"/>
+      <c r="V27" s="267"/>
+      <c r="W27" s="267"/>
+      <c r="X27" s="267"/>
+      <c r="Y27" s="267"/>
+      <c r="Z27" s="267"/>
+      <c r="AA27" s="267"/>
+      <c r="AB27" s="267"/>
+      <c r="AC27" s="267"/>
+      <c r="AD27" s="267"/>
+      <c r="AE27" s="268"/>
+      <c r="AF27" s="263"/>
+      <c r="AG27" s="264"/>
+      <c r="AH27" s="264"/>
+      <c r="AI27" s="265"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="200"/>
-      <c r="C28" s="201"/>
-      <c r="D28" s="202"/>
-      <c r="E28" s="203"/>
-      <c r="F28" s="204"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="205"/>
-      <c r="I28" s="201"/>
-      <c r="J28" s="206"/>
-      <c r="K28" s="207"/>
-      <c r="L28" s="207"/>
-      <c r="M28" s="207"/>
-      <c r="N28" s="207"/>
-      <c r="O28" s="207"/>
-      <c r="P28" s="208"/>
-      <c r="Q28" s="209"/>
-      <c r="R28" s="210"/>
-      <c r="S28" s="210"/>
-      <c r="T28" s="210"/>
-      <c r="U28" s="210"/>
-      <c r="V28" s="210"/>
-      <c r="W28" s="210"/>
-      <c r="X28" s="210"/>
-      <c r="Y28" s="210"/>
-      <c r="Z28" s="210"/>
-      <c r="AA28" s="210"/>
-      <c r="AB28" s="210"/>
-      <c r="AC28" s="210"/>
-      <c r="AD28" s="210"/>
-      <c r="AE28" s="211"/>
-      <c r="AF28" s="206"/>
-      <c r="AG28" s="207"/>
-      <c r="AH28" s="207"/>
-      <c r="AI28" s="208"/>
+      <c r="B28" s="257"/>
+      <c r="C28" s="258"/>
+      <c r="D28" s="259"/>
+      <c r="E28" s="260"/>
+      <c r="F28" s="261"/>
+      <c r="G28" s="257"/>
+      <c r="H28" s="262"/>
+      <c r="I28" s="258"/>
+      <c r="J28" s="263"/>
+      <c r="K28" s="264"/>
+      <c r="L28" s="264"/>
+      <c r="M28" s="264"/>
+      <c r="N28" s="264"/>
+      <c r="O28" s="264"/>
+      <c r="P28" s="265"/>
+      <c r="Q28" s="266"/>
+      <c r="R28" s="267"/>
+      <c r="S28" s="267"/>
+      <c r="T28" s="267"/>
+      <c r="U28" s="267"/>
+      <c r="V28" s="267"/>
+      <c r="W28" s="267"/>
+      <c r="X28" s="267"/>
+      <c r="Y28" s="267"/>
+      <c r="Z28" s="267"/>
+      <c r="AA28" s="267"/>
+      <c r="AB28" s="267"/>
+      <c r="AC28" s="267"/>
+      <c r="AD28" s="267"/>
+      <c r="AE28" s="268"/>
+      <c r="AF28" s="263"/>
+      <c r="AG28" s="264"/>
+      <c r="AH28" s="264"/>
+      <c r="AI28" s="265"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="200"/>
-      <c r="C29" s="201"/>
-      <c r="D29" s="202"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="204"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="205"/>
-      <c r="I29" s="201"/>
-      <c r="J29" s="206"/>
-      <c r="K29" s="207"/>
-      <c r="L29" s="207"/>
-      <c r="M29" s="207"/>
-      <c r="N29" s="207"/>
-      <c r="O29" s="207"/>
-      <c r="P29" s="208"/>
-      <c r="Q29" s="209"/>
-      <c r="R29" s="210"/>
-      <c r="S29" s="210"/>
-      <c r="T29" s="210"/>
-      <c r="U29" s="210"/>
-      <c r="V29" s="210"/>
-      <c r="W29" s="210"/>
-      <c r="X29" s="210"/>
-      <c r="Y29" s="210"/>
-      <c r="Z29" s="210"/>
-      <c r="AA29" s="210"/>
-      <c r="AB29" s="210"/>
-      <c r="AC29" s="210"/>
-      <c r="AD29" s="210"/>
-      <c r="AE29" s="211"/>
-      <c r="AF29" s="206"/>
-      <c r="AG29" s="207"/>
-      <c r="AH29" s="207"/>
-      <c r="AI29" s="208"/>
+      <c r="B29" s="257"/>
+      <c r="C29" s="258"/>
+      <c r="D29" s="259"/>
+      <c r="E29" s="260"/>
+      <c r="F29" s="261"/>
+      <c r="G29" s="257"/>
+      <c r="H29" s="262"/>
+      <c r="I29" s="258"/>
+      <c r="J29" s="263"/>
+      <c r="K29" s="264"/>
+      <c r="L29" s="264"/>
+      <c r="M29" s="264"/>
+      <c r="N29" s="264"/>
+      <c r="O29" s="264"/>
+      <c r="P29" s="265"/>
+      <c r="Q29" s="266"/>
+      <c r="R29" s="267"/>
+      <c r="S29" s="267"/>
+      <c r="T29" s="267"/>
+      <c r="U29" s="267"/>
+      <c r="V29" s="267"/>
+      <c r="W29" s="267"/>
+      <c r="X29" s="267"/>
+      <c r="Y29" s="267"/>
+      <c r="Z29" s="267"/>
+      <c r="AA29" s="267"/>
+      <c r="AB29" s="267"/>
+      <c r="AC29" s="267"/>
+      <c r="AD29" s="267"/>
+      <c r="AE29" s="268"/>
+      <c r="AF29" s="263"/>
+      <c r="AG29" s="264"/>
+      <c r="AH29" s="264"/>
+      <c r="AI29" s="265"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="200"/>
-      <c r="C30" s="201"/>
-      <c r="D30" s="202"/>
-      <c r="E30" s="203"/>
-      <c r="F30" s="204"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="205"/>
-      <c r="I30" s="201"/>
-      <c r="J30" s="206"/>
-      <c r="K30" s="207"/>
-      <c r="L30" s="207"/>
-      <c r="M30" s="207"/>
-      <c r="N30" s="207"/>
-      <c r="O30" s="207"/>
-      <c r="P30" s="208"/>
-      <c r="Q30" s="209"/>
-      <c r="R30" s="210"/>
-      <c r="S30" s="210"/>
-      <c r="T30" s="210"/>
-      <c r="U30" s="210"/>
-      <c r="V30" s="210"/>
-      <c r="W30" s="210"/>
-      <c r="X30" s="210"/>
-      <c r="Y30" s="210"/>
-      <c r="Z30" s="210"/>
-      <c r="AA30" s="210"/>
-      <c r="AB30" s="210"/>
-      <c r="AC30" s="210"/>
-      <c r="AD30" s="210"/>
-      <c r="AE30" s="211"/>
-      <c r="AF30" s="206"/>
-      <c r="AG30" s="207"/>
-      <c r="AH30" s="207"/>
-      <c r="AI30" s="208"/>
+      <c r="B30" s="257"/>
+      <c r="C30" s="258"/>
+      <c r="D30" s="259"/>
+      <c r="E30" s="260"/>
+      <c r="F30" s="261"/>
+      <c r="G30" s="257"/>
+      <c r="H30" s="262"/>
+      <c r="I30" s="258"/>
+      <c r="J30" s="263"/>
+      <c r="K30" s="264"/>
+      <c r="L30" s="264"/>
+      <c r="M30" s="264"/>
+      <c r="N30" s="264"/>
+      <c r="O30" s="264"/>
+      <c r="P30" s="265"/>
+      <c r="Q30" s="266"/>
+      <c r="R30" s="267"/>
+      <c r="S30" s="267"/>
+      <c r="T30" s="267"/>
+      <c r="U30" s="267"/>
+      <c r="V30" s="267"/>
+      <c r="W30" s="267"/>
+      <c r="X30" s="267"/>
+      <c r="Y30" s="267"/>
+      <c r="Z30" s="267"/>
+      <c r="AA30" s="267"/>
+      <c r="AB30" s="267"/>
+      <c r="AC30" s="267"/>
+      <c r="AD30" s="267"/>
+      <c r="AE30" s="268"/>
+      <c r="AF30" s="263"/>
+      <c r="AG30" s="264"/>
+      <c r="AH30" s="264"/>
+      <c r="AI30" s="265"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="200"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="202"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="204"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="205"/>
-      <c r="I31" s="201"/>
-      <c r="J31" s="206"/>
-      <c r="K31" s="207"/>
-      <c r="L31" s="207"/>
-      <c r="M31" s="207"/>
-      <c r="N31" s="207"/>
-      <c r="O31" s="207"/>
-      <c r="P31" s="208"/>
-      <c r="Q31" s="209"/>
-      <c r="R31" s="210"/>
-      <c r="S31" s="210"/>
-      <c r="T31" s="210"/>
-      <c r="U31" s="210"/>
-      <c r="V31" s="210"/>
-      <c r="W31" s="210"/>
-      <c r="X31" s="210"/>
-      <c r="Y31" s="210"/>
-      <c r="Z31" s="210"/>
-      <c r="AA31" s="210"/>
-      <c r="AB31" s="210"/>
-      <c r="AC31" s="210"/>
-      <c r="AD31" s="210"/>
-      <c r="AE31" s="211"/>
-      <c r="AF31" s="206"/>
-      <c r="AG31" s="207"/>
-      <c r="AH31" s="207"/>
-      <c r="AI31" s="208"/>
+      <c r="B31" s="257"/>
+      <c r="C31" s="258"/>
+      <c r="D31" s="259"/>
+      <c r="E31" s="260"/>
+      <c r="F31" s="261"/>
+      <c r="G31" s="257"/>
+      <c r="H31" s="262"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="263"/>
+      <c r="K31" s="264"/>
+      <c r="L31" s="264"/>
+      <c r="M31" s="264"/>
+      <c r="N31" s="264"/>
+      <c r="O31" s="264"/>
+      <c r="P31" s="265"/>
+      <c r="Q31" s="266"/>
+      <c r="R31" s="267"/>
+      <c r="S31" s="267"/>
+      <c r="T31" s="267"/>
+      <c r="U31" s="267"/>
+      <c r="V31" s="267"/>
+      <c r="W31" s="267"/>
+      <c r="X31" s="267"/>
+      <c r="Y31" s="267"/>
+      <c r="Z31" s="267"/>
+      <c r="AA31" s="267"/>
+      <c r="AB31" s="267"/>
+      <c r="AC31" s="267"/>
+      <c r="AD31" s="267"/>
+      <c r="AE31" s="268"/>
+      <c r="AF31" s="263"/>
+      <c r="AG31" s="264"/>
+      <c r="AH31" s="264"/>
+      <c r="AI31" s="265"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="200"/>
-      <c r="C32" s="201"/>
-      <c r="D32" s="202"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="204"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="205"/>
-      <c r="I32" s="201"/>
-      <c r="J32" s="206"/>
-      <c r="K32" s="212"/>
-      <c r="L32" s="207"/>
-      <c r="M32" s="207"/>
-      <c r="N32" s="207"/>
-      <c r="O32" s="207"/>
-      <c r="P32" s="208"/>
-      <c r="Q32" s="209"/>
-      <c r="R32" s="210"/>
-      <c r="S32" s="210"/>
-      <c r="T32" s="210"/>
-      <c r="U32" s="210"/>
-      <c r="V32" s="210"/>
-      <c r="W32" s="210"/>
-      <c r="X32" s="210"/>
-      <c r="Y32" s="210"/>
-      <c r="Z32" s="210"/>
-      <c r="AA32" s="210"/>
-      <c r="AB32" s="210"/>
-      <c r="AC32" s="210"/>
-      <c r="AD32" s="210"/>
-      <c r="AE32" s="211"/>
-      <c r="AF32" s="206"/>
-      <c r="AG32" s="207"/>
-      <c r="AH32" s="207"/>
-      <c r="AI32" s="208"/>
+      <c r="B32" s="257"/>
+      <c r="C32" s="258"/>
+      <c r="D32" s="259"/>
+      <c r="E32" s="260"/>
+      <c r="F32" s="261"/>
+      <c r="G32" s="257"/>
+      <c r="H32" s="262"/>
+      <c r="I32" s="258"/>
+      <c r="J32" s="263"/>
+      <c r="K32" s="269"/>
+      <c r="L32" s="264"/>
+      <c r="M32" s="264"/>
+      <c r="N32" s="264"/>
+      <c r="O32" s="264"/>
+      <c r="P32" s="265"/>
+      <c r="Q32" s="266"/>
+      <c r="R32" s="267"/>
+      <c r="S32" s="267"/>
+      <c r="T32" s="267"/>
+      <c r="U32" s="267"/>
+      <c r="V32" s="267"/>
+      <c r="W32" s="267"/>
+      <c r="X32" s="267"/>
+      <c r="Y32" s="267"/>
+      <c r="Z32" s="267"/>
+      <c r="AA32" s="267"/>
+      <c r="AB32" s="267"/>
+      <c r="AC32" s="267"/>
+      <c r="AD32" s="267"/>
+      <c r="AE32" s="268"/>
+      <c r="AF32" s="263"/>
+      <c r="AG32" s="264"/>
+      <c r="AH32" s="264"/>
+      <c r="AI32" s="265"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="200"/>
-      <c r="C33" s="201"/>
-      <c r="D33" s="202"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="204"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="205"/>
-      <c r="I33" s="201"/>
-      <c r="J33" s="206"/>
-      <c r="K33" s="207"/>
-      <c r="L33" s="207"/>
-      <c r="M33" s="207"/>
-      <c r="N33" s="207"/>
-      <c r="O33" s="207"/>
-      <c r="P33" s="208"/>
-      <c r="Q33" s="209"/>
-      <c r="R33" s="210"/>
-      <c r="S33" s="210"/>
-      <c r="T33" s="210"/>
-      <c r="U33" s="210"/>
-      <c r="V33" s="210"/>
-      <c r="W33" s="210"/>
-      <c r="X33" s="210"/>
-      <c r="Y33" s="210"/>
-      <c r="Z33" s="210"/>
-      <c r="AA33" s="210"/>
-      <c r="AB33" s="210"/>
-      <c r="AC33" s="210"/>
-      <c r="AD33" s="210"/>
-      <c r="AE33" s="211"/>
-      <c r="AF33" s="206"/>
-      <c r="AG33" s="207"/>
-      <c r="AH33" s="207"/>
-      <c r="AI33" s="208"/>
+      <c r="B33" s="257"/>
+      <c r="C33" s="258"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="261"/>
+      <c r="G33" s="257"/>
+      <c r="H33" s="262"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="263"/>
+      <c r="K33" s="264"/>
+      <c r="L33" s="264"/>
+      <c r="M33" s="264"/>
+      <c r="N33" s="264"/>
+      <c r="O33" s="264"/>
+      <c r="P33" s="265"/>
+      <c r="Q33" s="266"/>
+      <c r="R33" s="267"/>
+      <c r="S33" s="267"/>
+      <c r="T33" s="267"/>
+      <c r="U33" s="267"/>
+      <c r="V33" s="267"/>
+      <c r="W33" s="267"/>
+      <c r="X33" s="267"/>
+      <c r="Y33" s="267"/>
+      <c r="Z33" s="267"/>
+      <c r="AA33" s="267"/>
+      <c r="AB33" s="267"/>
+      <c r="AC33" s="267"/>
+      <c r="AD33" s="267"/>
+      <c r="AE33" s="268"/>
+      <c r="AF33" s="263"/>
+      <c r="AG33" s="264"/>
+      <c r="AH33" s="264"/>
+      <c r="AI33" s="265"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -13926,161 +14084,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CB1AAD-329F-42D9-8645-412CB1A2F21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B253EB-1387-4543-8699-3224C1281692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="538">
   <si>
     <t>システム機能設計書</t>
     <rPh sb="4" eb="6">
@@ -6200,34 +6200,6 @@
       <t>ニュウリョク</t>
     </rPh>
     <rPh sb="19" eb="21">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>数値項目に有効範囲の下限値＋1が入力された場合、エラーとなること。</t>
-    <rPh sb="0" eb="2">
-      <t>スウチ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ユウコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カゲン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
       <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="20"/>
@@ -12702,7 +12674,7 @@
       <c r="Q1" s="216"/>
       <c r="R1" s="217"/>
       <c r="S1" s="224" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="T1" s="225"/>
       <c r="U1" s="225"/>
@@ -15396,13 +15368,13 @@
         <v>57</v>
       </c>
       <c r="I42" s="169" t="s">
+        <v>530</v>
+      </c>
+      <c r="J42" s="37" t="s">
         <v>531</v>
       </c>
-      <c r="J42" s="37" t="s">
-        <v>532</v>
-      </c>
       <c r="K42" s="37" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="L42" s="189" t="s">
         <v>171</v>
@@ -15437,7 +15409,7 @@
         <v>131</v>
       </c>
       <c r="G43" s="48" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H43" s="48"/>
       <c r="I43" s="48"/>
@@ -15616,7 +15588,7 @@
         <v>138</v>
       </c>
       <c r="G48" s="48" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H48" s="48"/>
       <c r="I48" s="48"/>
@@ -15651,7 +15623,7 @@
         <v>139</v>
       </c>
       <c r="G49" s="48" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H49" s="48"/>
       <c r="I49" s="48"/>
@@ -16694,13 +16666,13 @@
         <v>57</v>
       </c>
       <c r="I78" s="169" t="s">
+        <v>530</v>
+      </c>
+      <c r="J78" s="37" t="s">
+        <v>532</v>
+      </c>
+      <c r="K78" s="37" t="s">
         <v>531</v>
-      </c>
-      <c r="J78" s="37" t="s">
-        <v>533</v>
-      </c>
-      <c r="K78" s="37" t="s">
-        <v>532</v>
       </c>
       <c r="L78" s="189" t="s">
         <v>171</v>
@@ -16739,16 +16711,16 @@
         <v>57</v>
       </c>
       <c r="I79" s="169" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J79" s="37" t="s">
+        <v>533</v>
+      </c>
+      <c r="K79" s="37" t="s">
         <v>534</v>
       </c>
-      <c r="K79" s="37" t="s">
-        <v>535</v>
-      </c>
       <c r="L79" s="189" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M79" s="189" t="s">
         <v>30</v>
@@ -16782,7 +16754,7 @@
         <v>182</v>
       </c>
       <c r="G80" s="48" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H80" s="48"/>
       <c r="I80" s="48"/>
@@ -24709,7 +24681,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>21</v>
@@ -25287,8 +25259,8 @@
       <c r="C24" s="117"/>
       <c r="D24" s="120"/>
       <c r="E24" s="118"/>
-      <c r="F24" s="115" t="s">
-        <v>458</v>
+      <c r="F24" s="46" t="s">
+        <v>99</v>
       </c>
       <c r="G24" s="50" t="s">
         <v>456</v>
@@ -25612,7 +25584,7 @@
       <c r="C33" s="117"/>
       <c r="D33" s="119"/>
       <c r="E33" s="119" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F33" s="115" t="s">
         <v>113</v>
@@ -25687,7 +25659,7 @@
         <v>115</v>
       </c>
       <c r="F35" s="115" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G35" s="50" t="s">
         <v>456</v>
@@ -25722,10 +25694,10 @@
         <v>117</v>
       </c>
       <c r="D36" s="121" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E36" s="113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F36" s="118" t="s">
         <v>119</v>
@@ -25763,7 +25735,7 @@
       <c r="D37" s="119"/>
       <c r="E37" s="114"/>
       <c r="F37" s="115" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G37" s="50" t="s">
         <v>456</v>
@@ -25872,7 +25844,7 @@
         <v>84</v>
       </c>
       <c r="F40" s="115" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G40" s="50" t="s">
         <v>456</v>
@@ -25907,7 +25879,7 @@
       <c r="D41" s="120"/>
       <c r="E41" s="118"/>
       <c r="F41" s="115" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="G41" s="50" t="s">
         <v>456</v>
@@ -26482,7 +26454,7 @@
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="115" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F57" s="115" t="s">
         <v>150</v>
@@ -26558,10 +26530,10 @@
         <v>153</v>
       </c>
       <c r="E59" s="119" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F59" s="115" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G59" s="50" t="s">
         <v>155</v>
@@ -26596,7 +26568,7 @@
       <c r="D60" s="114"/>
       <c r="E60" s="119"/>
       <c r="F60" s="113" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G60" s="50" t="s">
         <v>155</v>
@@ -26631,7 +26603,7 @@
       <c r="D61" s="114"/>
       <c r="E61" s="119"/>
       <c r="F61" s="115" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G61" s="50" t="s">
         <v>155</v>
@@ -26666,7 +26638,7 @@
       <c r="D62" s="114"/>
       <c r="E62" s="119"/>
       <c r="F62" s="115" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G62" s="50" t="s">
         <v>155</v>
@@ -27494,7 +27466,7 @@
         <v>58</v>
       </c>
       <c r="E85" s="115" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F85" s="115" t="s">
         <v>191</v>
@@ -27568,7 +27540,7 @@
       <c r="C87" s="118"/>
       <c r="D87" s="118"/>
       <c r="E87" s="118" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F87" s="115" t="s">
         <v>194</v>
@@ -27609,13 +27581,13 @@
         <v>58</v>
       </c>
       <c r="E88" s="119" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F88" s="113" t="s">
         <v>196</v>
       </c>
       <c r="G88" s="50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H88" s="48"/>
       <c r="I88" s="48"/>
@@ -27650,7 +27622,7 @@
         <v>197</v>
       </c>
       <c r="G89" s="50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H89" s="53"/>
       <c r="I89" s="53"/>
@@ -27687,7 +27659,7 @@
         <v>198</v>
       </c>
       <c r="G90" s="50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H90" s="53"/>
       <c r="I90" s="53"/>
@@ -27724,7 +27696,7 @@
         <v>199</v>
       </c>
       <c r="G91" s="50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H91" s="53"/>
       <c r="I91" s="53"/>
@@ -27759,7 +27731,7 @@
         <v>200</v>
       </c>
       <c r="G92" s="50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H92" s="53"/>
       <c r="I92" s="53"/>
@@ -27790,13 +27762,13 @@
       <c r="C93" s="118"/>
       <c r="D93" s="118"/>
       <c r="E93" s="118" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F93" s="115" t="s">
         <v>201</v>
       </c>
       <c r="G93" s="50" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H93" s="53"/>
       <c r="I93" s="53"/>
@@ -27837,7 +27809,7 @@
         <v>204</v>
       </c>
       <c r="G94" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H94" s="53"/>
       <c r="I94" s="53"/>
@@ -27872,7 +27844,7 @@
         <v>205</v>
       </c>
       <c r="G95" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H95" s="53"/>
       <c r="I95" s="53"/>
@@ -27907,7 +27879,7 @@
         <v>206</v>
       </c>
       <c r="G96" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H96" s="53"/>
       <c r="I96" s="53"/>
@@ -27942,7 +27914,7 @@
         <v>207</v>
       </c>
       <c r="G97" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H97" s="53"/>
       <c r="I97" s="53"/>
@@ -27977,7 +27949,7 @@
         <v>208</v>
       </c>
       <c r="G98" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H98" s="53"/>
       <c r="I98" s="53"/>
@@ -28014,7 +27986,7 @@
         <v>210</v>
       </c>
       <c r="G99" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H99" s="53"/>
       <c r="I99" s="53"/>
@@ -28049,7 +28021,7 @@
         <v>211</v>
       </c>
       <c r="G100" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H100" s="53"/>
       <c r="I100" s="53"/>
@@ -28084,7 +28056,7 @@
         <v>212</v>
       </c>
       <c r="G101" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H101" s="53"/>
       <c r="I101" s="53"/>
@@ -28119,7 +28091,7 @@
         <v>213</v>
       </c>
       <c r="G102" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H102" s="53"/>
       <c r="I102" s="53"/>
@@ -28154,7 +28126,7 @@
         <v>214</v>
       </c>
       <c r="G103" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H103" s="53"/>
       <c r="I103" s="53"/>
@@ -28185,13 +28157,13 @@
       <c r="C104" s="118"/>
       <c r="D104" s="114"/>
       <c r="E104" s="120" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F104" s="115" t="s">
         <v>215</v>
       </c>
       <c r="G104" s="50" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H104" s="53"/>
       <c r="I104" s="53"/>
@@ -28339,7 +28311,7 @@
       </c>
       <c r="B108" s="114"/>
       <c r="C108" s="115" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D108" s="115" t="s">
         <v>84</v>
@@ -28380,7 +28352,7 @@
       </c>
       <c r="B109" s="114"/>
       <c r="C109" s="114" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D109" s="114" t="s">
         <v>84</v>
@@ -28461,10 +28433,10 @@
         <v>228</v>
       </c>
       <c r="D111" s="113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E111" s="129" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F111" s="115" t="s">
         <v>229</v>
@@ -28498,7 +28470,7 @@
         <v>43-2-1</v>
       </c>
       <c r="B112" s="271" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C112" s="119"/>
       <c r="D112" s="114"/>
@@ -28962,7 +28934,7 @@
       <c r="C125" s="119"/>
       <c r="D125" s="118"/>
       <c r="E125" s="118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F125" s="115" t="s">
         <v>247</v>
@@ -28998,10 +28970,10 @@
       <c r="B126" s="114"/>
       <c r="C126" s="120"/>
       <c r="D126" s="118" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E126" s="118" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F126" s="115" t="s">
         <v>248</v>
@@ -29079,7 +29051,7 @@
       <c r="C128" s="114"/>
       <c r="D128" s="114"/>
       <c r="E128" s="119" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F128" s="115" t="s">
         <v>253</v>
@@ -29189,10 +29161,10 @@
         <v>228</v>
       </c>
       <c r="D131" s="113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E131" s="129" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F131" s="115" t="s">
         <v>257</v>
@@ -29407,10 +29379,10 @@
       <c r="B137" s="114"/>
       <c r="C137" s="120"/>
       <c r="D137" s="118" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E137" s="118" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F137" s="115" t="s">
         <v>266</v>
@@ -29599,7 +29571,7 @@
       <c r="C142" s="119"/>
       <c r="D142" s="114"/>
       <c r="E142" s="115" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F142" s="115" t="s">
         <v>276</v>
@@ -29636,7 +29608,7 @@
       <c r="C143" s="119"/>
       <c r="D143" s="114"/>
       <c r="E143" s="127" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F143" s="115" t="s">
         <v>278</v>
@@ -29850,7 +29822,7 @@
         <v>284</v>
       </c>
       <c r="E149" s="113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F149" s="115" t="s">
         <v>285</v>
@@ -29995,7 +29967,7 @@
       <c r="D153" s="114"/>
       <c r="E153" s="127"/>
       <c r="F153" s="115" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G153" s="48" t="s">
         <v>258</v>
@@ -30030,7 +30002,7 @@
       <c r="D154" s="114"/>
       <c r="E154" s="127"/>
       <c r="F154" s="115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G154" s="48" t="s">
         <v>258</v>
@@ -31028,7 +31000,7 @@
       <c r="B182" s="118"/>
       <c r="C182" s="120"/>
       <c r="D182" s="120" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E182" s="120" t="s">
         <v>84</v>
@@ -31071,7 +31043,7 @@
         <v>228</v>
       </c>
       <c r="D183" s="113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E183" s="115" t="s">
         <v>326</v>
@@ -31254,10 +31226,10 @@
       <c r="B188" s="114"/>
       <c r="C188" s="118"/>
       <c r="D188" s="118" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E188" s="118" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F188" s="115" t="s">
         <v>334</v>
@@ -31295,7 +31267,7 @@
         <v>335</v>
       </c>
       <c r="D189" s="114" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E189" s="119" t="s">
         <v>337</v>
@@ -31548,7 +31520,7 @@
         <v>345</v>
       </c>
       <c r="F196" s="115" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G196" s="48" t="s">
         <v>328</v>
@@ -31797,7 +31769,7 @@
       <c r="D203" s="114"/>
       <c r="E203" s="119"/>
       <c r="F203" s="115" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G203" s="48" t="s">
         <v>328</v>
@@ -32040,7 +32012,7 @@
       <c r="B210" s="114"/>
       <c r="C210" s="117"/>
       <c r="D210" s="113" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E210" s="121" t="s">
         <v>160</v>
@@ -32291,7 +32263,7 @@
       <c r="D217" s="114"/>
       <c r="E217" s="119"/>
       <c r="F217" s="115" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G217" s="48" t="s">
         <v>328</v>
@@ -32326,7 +32298,7 @@
       <c r="D218" s="114"/>
       <c r="E218" s="119"/>
       <c r="F218" s="115" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G218" s="48" t="s">
         <v>328</v>
@@ -32680,7 +32652,7 @@
         <v>186</v>
       </c>
       <c r="F228" s="115" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G228" s="48" t="s">
         <v>328</v>
@@ -32754,10 +32726,10 @@
         <v>228</v>
       </c>
       <c r="D230" s="113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E230" s="115" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F230" s="115" t="s">
         <v>382</v>
@@ -33148,7 +33120,7 @@
       <c r="C241" s="118"/>
       <c r="D241" s="118"/>
       <c r="E241" s="118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F241" s="115" t="s">
         <v>394</v>
@@ -33229,10 +33201,10 @@
         <v>397</v>
       </c>
       <c r="D243" s="113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E243" s="121" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F243" s="115" t="s">
         <v>398</v>
@@ -33303,10 +33275,10 @@
       <c r="B245" s="114"/>
       <c r="C245" s="114"/>
       <c r="D245" s="114" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E245" s="119" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F245" s="115" t="s">
         <v>400</v>
@@ -33532,7 +33504,7 @@
         <v>284</v>
       </c>
       <c r="E251" s="127" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F251" s="115" t="s">
         <v>407</v>
@@ -33677,7 +33649,7 @@
       <c r="D255" s="119"/>
       <c r="E255" s="119"/>
       <c r="F255" s="115" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G255" s="50" t="s">
         <v>383</v>
@@ -34525,10 +34497,10 @@
         <v>436</v>
       </c>
       <c r="D279" s="113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E279" s="121" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F279" s="115" t="s">
         <v>437</v>
@@ -34932,7 +34904,7 @@
       <c r="D290" s="119"/>
       <c r="E290" s="119"/>
       <c r="F290" s="115" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G290" s="48" t="s">
         <v>438</v>
@@ -34967,7 +34939,7 @@
       <c r="D291" s="119"/>
       <c r="E291" s="119"/>
       <c r="F291" s="115" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G291" s="48" t="s">
         <v>438</v>
@@ -35002,7 +34974,7 @@
       <c r="D292" s="119"/>
       <c r="E292" s="119"/>
       <c r="F292" s="115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G292" s="48" t="s">
         <v>438</v>
@@ -35037,7 +35009,7 @@
       <c r="D293" s="119"/>
       <c r="E293" s="119"/>
       <c r="F293" s="115" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G293" s="48" t="s">
         <v>438</v>
@@ -35138,7 +35110,7 @@
         <v>101-1-1</v>
       </c>
       <c r="B296" s="88" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C296" s="155" t="s">
         <v>228</v>
@@ -35150,7 +35122,7 @@
         <v>84</v>
       </c>
       <c r="F296" s="113" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G296" s="138" t="s">
         <v>456</v>
@@ -35183,26 +35155,26 @@
       <c r="B297" s="90"/>
       <c r="C297" s="159"/>
       <c r="D297" s="155" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E297" s="168" t="s">
         <v>84</v>
       </c>
       <c r="F297" s="161" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G297" s="156"/>
       <c r="H297" s="157" t="s">
         <v>29</v>
       </c>
       <c r="I297" s="157" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J297" s="158" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K297" s="162" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="L297" s="162" t="s">
         <v>171</v>
@@ -35238,13 +35210,13 @@
       <c r="H298" s="172"/>
       <c r="I298" s="172"/>
       <c r="J298" s="179" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="K298" s="162" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L298" s="162" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="M298" s="164">
         <v>1</v>
@@ -35271,26 +35243,26 @@
       <c r="B299" s="90"/>
       <c r="C299" s="159"/>
       <c r="D299" s="159" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E299" s="160" t="s">
         <v>84</v>
       </c>
       <c r="F299" s="180" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G299" s="181"/>
       <c r="H299" s="157" t="s">
         <v>29</v>
       </c>
       <c r="I299" s="157" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J299" s="166" t="s">
+        <v>524</v>
+      </c>
+      <c r="K299" s="166" t="s">
         <v>525</v>
-      </c>
-      <c r="K299" s="166" t="s">
-        <v>526</v>
       </c>
       <c r="L299" s="162" t="s">
         <v>171</v>
@@ -35322,23 +35294,23 @@
       <c r="D300" s="159"/>
       <c r="E300" s="160"/>
       <c r="F300" s="161" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G300" s="156"/>
       <c r="H300" s="157" t="s">
         <v>29</v>
       </c>
       <c r="I300" s="157" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J300" s="166" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="K300" s="162" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L300" s="163" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M300" s="164">
         <v>1</v>
@@ -35367,10 +35339,10 @@
       <c r="D301" s="159"/>
       <c r="E301" s="160"/>
       <c r="F301" s="141" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G301" s="141" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H301" s="83"/>
       <c r="I301" s="83"/>
@@ -35400,16 +35372,16 @@
       <c r="B302" s="90"/>
       <c r="C302" s="167"/>
       <c r="D302" s="134" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E302" s="145" t="s">
         <v>84</v>
       </c>
       <c r="F302" s="141" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G302" s="138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H302" s="48"/>
       <c r="I302" s="48"/>
@@ -35440,13 +35412,13 @@
       <c r="C303" s="159"/>
       <c r="D303" s="135"/>
       <c r="E303" s="116" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F303" s="141" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G303" s="138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H303" s="83"/>
       <c r="I303" s="83"/>
@@ -35482,23 +35454,23 @@
         <v>84</v>
       </c>
       <c r="F304" s="161" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G304" s="161"/>
       <c r="H304" s="157" t="s">
         <v>29</v>
       </c>
       <c r="I304" s="157" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="J304" s="158" t="s">
+        <v>514</v>
+      </c>
+      <c r="K304" s="162" t="s">
+        <v>521</v>
+      </c>
+      <c r="L304" s="163" t="s">
         <v>515</v>
-      </c>
-      <c r="K304" s="162" t="s">
-        <v>522</v>
-      </c>
-      <c r="L304" s="163" t="s">
-        <v>516</v>
       </c>
       <c r="M304" s="164">
         <v>1</v>
@@ -35527,10 +35499,10 @@
       <c r="D305" s="159"/>
       <c r="E305" s="160"/>
       <c r="F305" s="141" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G305" s="138" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H305" s="48"/>
       <c r="I305" s="48"/>
@@ -35562,10 +35534,10 @@
       <c r="D306" s="167"/>
       <c r="E306" s="159"/>
       <c r="F306" s="138" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G306" s="138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H306" s="48"/>
       <c r="I306" s="48"/>
@@ -35597,10 +35569,10 @@
       <c r="D307" s="167"/>
       <c r="E307" s="159"/>
       <c r="F307" s="138" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G307" s="138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H307" s="48"/>
       <c r="I307" s="48"/>
@@ -35632,10 +35604,10 @@
       <c r="D308" s="167"/>
       <c r="E308" s="159"/>
       <c r="F308" s="138" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G308" s="138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H308" s="83"/>
       <c r="I308" s="83"/>
@@ -35667,10 +35639,10 @@
       <c r="D309" s="167"/>
       <c r="E309" s="159"/>
       <c r="F309" s="138" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G309" s="138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H309" s="83"/>
       <c r="I309" s="83"/>
@@ -35702,10 +35674,10 @@
       <c r="D310" s="167"/>
       <c r="E310" s="159"/>
       <c r="F310" s="138" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G310" s="138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H310" s="83"/>
       <c r="I310" s="83"/>
@@ -35737,10 +35709,10 @@
       <c r="D311" s="91"/>
       <c r="E311" s="92"/>
       <c r="F311" s="176" t="s">
+        <v>511</v>
+      </c>
+      <c r="G311" s="176" t="s">
         <v>512</v>
-      </c>
-      <c r="G311" s="176" t="s">
-        <v>513</v>
       </c>
       <c r="H311" s="48"/>
       <c r="I311" s="48"/>
@@ -35942,7 +35914,7 @@
         <v>17</v>
       </c>
       <c r="E11" s="115" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F11" s="152" t="s">
         <v>0</v>
@@ -35979,7 +35951,7 @@
         <v>24</v>
       </c>
       <c r="E12" s="115" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F12" s="152" t="s">
         <v>0</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B253EB-1387-4543-8699-3224C1281692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0014AA43-3ACE-4BB4-93AF-95EB1A9AE53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8263,6 +8263,108 @@
     <xf numFmtId="31" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="11" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8369,108 +8471,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12649,57 +12649,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="240" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="209" t="s">
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="243" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="215" t="s">
+      <c r="F1" s="244"/>
+      <c r="G1" s="244"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="244"/>
+      <c r="L1" s="244"/>
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="249" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="216"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="224" t="s">
+      <c r="P1" s="250"/>
+      <c r="Q1" s="250"/>
+      <c r="R1" s="251"/>
+      <c r="S1" s="258" t="s">
         <v>536</v>
       </c>
-      <c r="T1" s="225"/>
-      <c r="U1" s="225"/>
-      <c r="V1" s="225"/>
-      <c r="W1" s="225"/>
-      <c r="X1" s="225"/>
-      <c r="Y1" s="225"/>
-      <c r="Z1" s="226"/>
-      <c r="AA1" s="206" t="s">
+      <c r="T1" s="259"/>
+      <c r="U1" s="259"/>
+      <c r="V1" s="259"/>
+      <c r="W1" s="259"/>
+      <c r="X1" s="259"/>
+      <c r="Y1" s="259"/>
+      <c r="Z1" s="260"/>
+      <c r="AA1" s="240" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="208"/>
-      <c r="AC1" s="233" t="str">
+      <c r="AB1" s="242"/>
+      <c r="AC1" s="267" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="234"/>
-      <c r="AE1" s="234"/>
-      <c r="AF1" s="235"/>
-      <c r="AG1" s="200">
+      <c r="AD1" s="268"/>
+      <c r="AE1" s="268"/>
+      <c r="AF1" s="269"/>
+      <c r="AG1" s="234">
         <f>IF(D8="","",D8)</f>
         <v>44011</v>
       </c>
-      <c r="AH1" s="201"/>
-      <c r="AI1" s="202"/>
+      <c r="AH1" s="235"/>
+      <c r="AI1" s="236"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -12707,53 +12707,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="206" t="s">
+      <c r="A2" s="240" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="209" t="s">
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="243" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="M2" s="210"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="218"/>
-      <c r="P2" s="219"/>
-      <c r="Q2" s="219"/>
-      <c r="R2" s="220"/>
-      <c r="S2" s="227"/>
-      <c r="T2" s="228"/>
-      <c r="U2" s="228"/>
-      <c r="V2" s="228"/>
-      <c r="W2" s="228"/>
-      <c r="X2" s="228"/>
-      <c r="Y2" s="228"/>
-      <c r="Z2" s="229"/>
-      <c r="AA2" s="206" t="s">
+      <c r="F2" s="244"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="244"/>
+      <c r="I2" s="244"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
+      <c r="M2" s="244"/>
+      <c r="N2" s="245"/>
+      <c r="O2" s="252"/>
+      <c r="P2" s="253"/>
+      <c r="Q2" s="253"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="261"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="263"/>
+      <c r="AA2" s="240" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="208"/>
-      <c r="AC2" s="212" t="str">
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="246" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="213"/>
-      <c r="AE2" s="213"/>
-      <c r="AF2" s="214"/>
-      <c r="AG2" s="200">
+      <c r="AD2" s="247"/>
+      <c r="AE2" s="247"/>
+      <c r="AF2" s="248"/>
+      <c r="AG2" s="234">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44858</v>
       </c>
-      <c r="AH2" s="201"/>
-      <c r="AI2" s="202"/>
+      <c r="AH2" s="235"/>
+      <c r="AI2" s="236"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -12761,45 +12761,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="206" t="s">
+      <c r="A3" s="240" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="209" t="s">
+      <c r="B3" s="241"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="210"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
-      <c r="M3" s="210"/>
-      <c r="N3" s="211"/>
-      <c r="O3" s="221"/>
-      <c r="P3" s="222"/>
-      <c r="Q3" s="222"/>
-      <c r="R3" s="223"/>
-      <c r="S3" s="230"/>
-      <c r="T3" s="231"/>
-      <c r="U3" s="231"/>
-      <c r="V3" s="231"/>
-      <c r="W3" s="231"/>
-      <c r="X3" s="231"/>
-      <c r="Y3" s="231"/>
-      <c r="Z3" s="232"/>
-      <c r="AA3" s="206"/>
-      <c r="AB3" s="208"/>
-      <c r="AC3" s="233"/>
-      <c r="AD3" s="234"/>
-      <c r="AE3" s="234"/>
-      <c r="AF3" s="235"/>
-      <c r="AG3" s="200"/>
-      <c r="AH3" s="201"/>
-      <c r="AI3" s="202"/>
+      <c r="F3" s="244"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="244"/>
+      <c r="I3" s="244"/>
+      <c r="J3" s="244"/>
+      <c r="K3" s="244"/>
+      <c r="L3" s="244"/>
+      <c r="M3" s="244"/>
+      <c r="N3" s="245"/>
+      <c r="O3" s="255"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="257"/>
+      <c r="S3" s="264"/>
+      <c r="T3" s="265"/>
+      <c r="U3" s="265"/>
+      <c r="V3" s="265"/>
+      <c r="W3" s="265"/>
+      <c r="X3" s="265"/>
+      <c r="Y3" s="265"/>
+      <c r="Z3" s="266"/>
+      <c r="AA3" s="240"/>
+      <c r="AB3" s="242"/>
+      <c r="AC3" s="267"/>
+      <c r="AD3" s="268"/>
+      <c r="AE3" s="268"/>
+      <c r="AF3" s="269"/>
+      <c r="AG3" s="234"/>
+      <c r="AH3" s="235"/>
+      <c r="AI3" s="236"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -12836,97 +12836,97 @@
       <c r="A7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="203" t="s">
+      <c r="B7" s="237" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="204"/>
-      <c r="D7" s="203" t="s">
+      <c r="C7" s="238"/>
+      <c r="D7" s="237" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="205"/>
-      <c r="F7" s="204"/>
-      <c r="G7" s="203" t="s">
+      <c r="E7" s="239"/>
+      <c r="F7" s="238"/>
+      <c r="G7" s="237" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="205"/>
-      <c r="I7" s="204"/>
-      <c r="J7" s="203" t="s">
+      <c r="H7" s="239"/>
+      <c r="I7" s="238"/>
+      <c r="J7" s="237" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="205"/>
-      <c r="L7" s="205"/>
-      <c r="M7" s="205"/>
-      <c r="N7" s="205"/>
-      <c r="O7" s="205"/>
-      <c r="P7" s="204"/>
-      <c r="Q7" s="203" t="s">
+      <c r="K7" s="239"/>
+      <c r="L7" s="239"/>
+      <c r="M7" s="239"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="238"/>
+      <c r="Q7" s="237" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="205"/>
-      <c r="S7" s="205"/>
-      <c r="T7" s="205"/>
-      <c r="U7" s="205"/>
-      <c r="V7" s="205"/>
-      <c r="W7" s="205"/>
-      <c r="X7" s="205"/>
-      <c r="Y7" s="205"/>
-      <c r="Z7" s="205"/>
-      <c r="AA7" s="205"/>
-      <c r="AB7" s="205"/>
-      <c r="AC7" s="205"/>
-      <c r="AD7" s="205"/>
-      <c r="AE7" s="204"/>
-      <c r="AF7" s="203" t="s">
+      <c r="R7" s="239"/>
+      <c r="S7" s="239"/>
+      <c r="T7" s="239"/>
+      <c r="U7" s="239"/>
+      <c r="V7" s="239"/>
+      <c r="W7" s="239"/>
+      <c r="X7" s="239"/>
+      <c r="Y7" s="239"/>
+      <c r="Z7" s="239"/>
+      <c r="AA7" s="239"/>
+      <c r="AB7" s="239"/>
+      <c r="AC7" s="239"/>
+      <c r="AD7" s="239"/>
+      <c r="AE7" s="238"/>
+      <c r="AF7" s="237" t="s">
         <v>43</v>
       </c>
-      <c r="AG7" s="205"/>
-      <c r="AH7" s="205"/>
-      <c r="AI7" s="204"/>
+      <c r="AG7" s="239"/>
+      <c r="AH7" s="239"/>
+      <c r="AI7" s="238"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="248" t="s">
+      <c r="B8" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="249"/>
-      <c r="D8" s="250">
+      <c r="C8" s="226"/>
+      <c r="D8" s="227">
         <v>44011</v>
       </c>
-      <c r="E8" s="251"/>
-      <c r="F8" s="252"/>
-      <c r="G8" s="248" t="s">
+      <c r="E8" s="228"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="225" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="253"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="254" t="s">
+      <c r="H8" s="230"/>
+      <c r="I8" s="226"/>
+      <c r="J8" s="231" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="255"/>
-      <c r="L8" s="255"/>
-      <c r="M8" s="255"/>
-      <c r="N8" s="255"/>
-      <c r="O8" s="255"/>
-      <c r="P8" s="256"/>
-      <c r="Q8" s="254" t="s">
+      <c r="K8" s="232"/>
+      <c r="L8" s="232"/>
+      <c r="M8" s="232"/>
+      <c r="N8" s="232"/>
+      <c r="O8" s="232"/>
+      <c r="P8" s="233"/>
+      <c r="Q8" s="231" t="s">
         <v>52</v>
       </c>
-      <c r="R8" s="255"/>
-      <c r="S8" s="255"/>
-      <c r="T8" s="255"/>
-      <c r="U8" s="255"/>
-      <c r="V8" s="255"/>
-      <c r="W8" s="255"/>
-      <c r="X8" s="255"/>
-      <c r="Y8" s="255"/>
-      <c r="Z8" s="255"/>
-      <c r="AA8" s="255"/>
-      <c r="AB8" s="255"/>
-      <c r="AC8" s="255"/>
-      <c r="AD8" s="255"/>
-      <c r="AE8" s="256"/>
+      <c r="R8" s="232"/>
+      <c r="S8" s="232"/>
+      <c r="T8" s="232"/>
+      <c r="U8" s="232"/>
+      <c r="V8" s="232"/>
+      <c r="W8" s="232"/>
+      <c r="X8" s="232"/>
+      <c r="Y8" s="232"/>
+      <c r="Z8" s="232"/>
+      <c r="AA8" s="232"/>
+      <c r="AB8" s="232"/>
+      <c r="AC8" s="232"/>
+      <c r="AD8" s="232"/>
+      <c r="AE8" s="233"/>
       <c r="AF8" s="25" t="s">
         <v>53</v>
       </c>
@@ -12938,1101 +12938,946 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="236" t="s">
+      <c r="B9" s="213" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="237"/>
-      <c r="D9" s="238">
+      <c r="C9" s="214"/>
+      <c r="D9" s="215">
         <v>44858</v>
       </c>
-      <c r="E9" s="239"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="238" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="217"/>
+      <c r="G9" s="215" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="241"/>
-      <c r="I9" s="237"/>
-      <c r="J9" s="242" t="s">
+      <c r="H9" s="218"/>
+      <c r="I9" s="214"/>
+      <c r="J9" s="219" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="243"/>
-      <c r="L9" s="243"/>
-      <c r="M9" s="243"/>
-      <c r="N9" s="243"/>
-      <c r="O9" s="243"/>
-      <c r="P9" s="244"/>
-      <c r="Q9" s="242" t="s">
+      <c r="K9" s="220"/>
+      <c r="L9" s="220"/>
+      <c r="M9" s="220"/>
+      <c r="N9" s="220"/>
+      <c r="O9" s="220"/>
+      <c r="P9" s="221"/>
+      <c r="Q9" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="R9" s="245"/>
-      <c r="S9" s="245"/>
-      <c r="T9" s="245"/>
-      <c r="U9" s="245"/>
-      <c r="V9" s="245"/>
-      <c r="W9" s="245"/>
-      <c r="X9" s="245"/>
-      <c r="Y9" s="245"/>
-      <c r="Z9" s="245"/>
-      <c r="AA9" s="245"/>
-      <c r="AB9" s="245"/>
-      <c r="AC9" s="245"/>
-      <c r="AD9" s="245"/>
-      <c r="AE9" s="246"/>
-      <c r="AF9" s="247" t="s">
+      <c r="R9" s="222"/>
+      <c r="S9" s="222"/>
+      <c r="T9" s="222"/>
+      <c r="U9" s="222"/>
+      <c r="V9" s="222"/>
+      <c r="W9" s="222"/>
+      <c r="X9" s="222"/>
+      <c r="Y9" s="222"/>
+      <c r="Z9" s="222"/>
+      <c r="AA9" s="222"/>
+      <c r="AB9" s="222"/>
+      <c r="AC9" s="222"/>
+      <c r="AD9" s="222"/>
+      <c r="AE9" s="223"/>
+      <c r="AF9" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AG9" s="243"/>
-      <c r="AH9" s="243"/>
-      <c r="AI9" s="244"/>
+      <c r="AG9" s="220"/>
+      <c r="AH9" s="220"/>
+      <c r="AI9" s="221"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="257"/>
-      <c r="C10" s="258"/>
-      <c r="D10" s="259"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="261"/>
-      <c r="G10" s="257"/>
-      <c r="H10" s="262"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="263"/>
-      <c r="K10" s="264"/>
-      <c r="L10" s="264"/>
-      <c r="M10" s="264"/>
-      <c r="N10" s="264"/>
-      <c r="O10" s="264"/>
-      <c r="P10" s="265"/>
-      <c r="Q10" s="266"/>
-      <c r="R10" s="267"/>
-      <c r="S10" s="267"/>
-      <c r="T10" s="267"/>
-      <c r="U10" s="267"/>
-      <c r="V10" s="267"/>
-      <c r="W10" s="267"/>
-      <c r="X10" s="267"/>
-      <c r="Y10" s="267"/>
-      <c r="Z10" s="267"/>
-      <c r="AA10" s="267"/>
-      <c r="AB10" s="267"/>
-      <c r="AC10" s="267"/>
-      <c r="AD10" s="267"/>
-      <c r="AE10" s="268"/>
-      <c r="AF10" s="263"/>
-      <c r="AG10" s="264"/>
-      <c r="AH10" s="264"/>
-      <c r="AI10" s="265"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="201"/>
+      <c r="D10" s="202"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="204"/>
+      <c r="G10" s="200"/>
+      <c r="H10" s="205"/>
+      <c r="I10" s="201"/>
+      <c r="J10" s="206"/>
+      <c r="K10" s="207"/>
+      <c r="L10" s="207"/>
+      <c r="M10" s="207"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
+      <c r="P10" s="208"/>
+      <c r="Q10" s="209"/>
+      <c r="R10" s="210"/>
+      <c r="S10" s="210"/>
+      <c r="T10" s="210"/>
+      <c r="U10" s="210"/>
+      <c r="V10" s="210"/>
+      <c r="W10" s="210"/>
+      <c r="X10" s="210"/>
+      <c r="Y10" s="210"/>
+      <c r="Z10" s="210"/>
+      <c r="AA10" s="210"/>
+      <c r="AB10" s="210"/>
+      <c r="AC10" s="210"/>
+      <c r="AD10" s="210"/>
+      <c r="AE10" s="211"/>
+      <c r="AF10" s="206"/>
+      <c r="AG10" s="207"/>
+      <c r="AH10" s="207"/>
+      <c r="AI10" s="208"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="257"/>
-      <c r="C11" s="258"/>
-      <c r="D11" s="259"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="261"/>
-      <c r="G11" s="257"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="263"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
-      <c r="M11" s="264"/>
-      <c r="N11" s="264"/>
-      <c r="O11" s="264"/>
-      <c r="P11" s="265"/>
-      <c r="Q11" s="266"/>
-      <c r="R11" s="267"/>
-      <c r="S11" s="267"/>
-      <c r="T11" s="267"/>
-      <c r="U11" s="267"/>
-      <c r="V11" s="267"/>
-      <c r="W11" s="267"/>
-      <c r="X11" s="267"/>
-      <c r="Y11" s="267"/>
-      <c r="Z11" s="267"/>
-      <c r="AA11" s="267"/>
-      <c r="AB11" s="267"/>
-      <c r="AC11" s="267"/>
-      <c r="AD11" s="267"/>
-      <c r="AE11" s="268"/>
-      <c r="AF11" s="263"/>
-      <c r="AG11" s="264"/>
-      <c r="AH11" s="264"/>
-      <c r="AI11" s="265"/>
+      <c r="B11" s="200"/>
+      <c r="C11" s="201"/>
+      <c r="D11" s="202"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="204"/>
+      <c r="G11" s="200"/>
+      <c r="H11" s="205"/>
+      <c r="I11" s="201"/>
+      <c r="J11" s="206"/>
+      <c r="K11" s="207"/>
+      <c r="L11" s="207"/>
+      <c r="M11" s="207"/>
+      <c r="N11" s="207"/>
+      <c r="O11" s="207"/>
+      <c r="P11" s="208"/>
+      <c r="Q11" s="209"/>
+      <c r="R11" s="210"/>
+      <c r="S11" s="210"/>
+      <c r="T11" s="210"/>
+      <c r="U11" s="210"/>
+      <c r="V11" s="210"/>
+      <c r="W11" s="210"/>
+      <c r="X11" s="210"/>
+      <c r="Y11" s="210"/>
+      <c r="Z11" s="210"/>
+      <c r="AA11" s="210"/>
+      <c r="AB11" s="210"/>
+      <c r="AC11" s="210"/>
+      <c r="AD11" s="210"/>
+      <c r="AE11" s="211"/>
+      <c r="AF11" s="206"/>
+      <c r="AG11" s="207"/>
+      <c r="AH11" s="207"/>
+      <c r="AI11" s="208"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="257"/>
-      <c r="C12" s="258"/>
-      <c r="D12" s="259"/>
-      <c r="E12" s="260"/>
-      <c r="F12" s="261"/>
-      <c r="G12" s="257"/>
-      <c r="H12" s="262"/>
-      <c r="I12" s="258"/>
-      <c r="J12" s="263"/>
-      <c r="K12" s="264"/>
-      <c r="L12" s="264"/>
-      <c r="M12" s="264"/>
-      <c r="N12" s="264"/>
-      <c r="O12" s="264"/>
-      <c r="P12" s="265"/>
-      <c r="Q12" s="266"/>
-      <c r="R12" s="267"/>
-      <c r="S12" s="267"/>
-      <c r="T12" s="267"/>
-      <c r="U12" s="267"/>
-      <c r="V12" s="267"/>
-      <c r="W12" s="267"/>
-      <c r="X12" s="267"/>
-      <c r="Y12" s="267"/>
-      <c r="Z12" s="267"/>
-      <c r="AA12" s="267"/>
-      <c r="AB12" s="267"/>
-      <c r="AC12" s="267"/>
-      <c r="AD12" s="267"/>
-      <c r="AE12" s="268"/>
-      <c r="AF12" s="263"/>
-      <c r="AG12" s="264"/>
-      <c r="AH12" s="264"/>
-      <c r="AI12" s="265"/>
+      <c r="B12" s="200"/>
+      <c r="C12" s="201"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="204"/>
+      <c r="G12" s="200"/>
+      <c r="H12" s="205"/>
+      <c r="I12" s="201"/>
+      <c r="J12" s="206"/>
+      <c r="K12" s="207"/>
+      <c r="L12" s="207"/>
+      <c r="M12" s="207"/>
+      <c r="N12" s="207"/>
+      <c r="O12" s="207"/>
+      <c r="P12" s="208"/>
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210"/>
+      <c r="S12" s="210"/>
+      <c r="T12" s="210"/>
+      <c r="U12" s="210"/>
+      <c r="V12" s="210"/>
+      <c r="W12" s="210"/>
+      <c r="X12" s="210"/>
+      <c r="Y12" s="210"/>
+      <c r="Z12" s="210"/>
+      <c r="AA12" s="210"/>
+      <c r="AB12" s="210"/>
+      <c r="AC12" s="210"/>
+      <c r="AD12" s="210"/>
+      <c r="AE12" s="211"/>
+      <c r="AF12" s="206"/>
+      <c r="AG12" s="207"/>
+      <c r="AH12" s="207"/>
+      <c r="AI12" s="208"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="257"/>
-      <c r="C13" s="258"/>
-      <c r="D13" s="259"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="261"/>
-      <c r="G13" s="257"/>
-      <c r="H13" s="262"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="263"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="264"/>
-      <c r="M13" s="264"/>
-      <c r="N13" s="264"/>
-      <c r="O13" s="264"/>
-      <c r="P13" s="265"/>
-      <c r="Q13" s="266"/>
-      <c r="R13" s="267"/>
-      <c r="S13" s="267"/>
-      <c r="T13" s="267"/>
-      <c r="U13" s="267"/>
-      <c r="V13" s="267"/>
-      <c r="W13" s="267"/>
-      <c r="X13" s="267"/>
-      <c r="Y13" s="267"/>
-      <c r="Z13" s="267"/>
-      <c r="AA13" s="267"/>
-      <c r="AB13" s="267"/>
-      <c r="AC13" s="267"/>
-      <c r="AD13" s="267"/>
-      <c r="AE13" s="268"/>
-      <c r="AF13" s="263"/>
-      <c r="AG13" s="264"/>
-      <c r="AH13" s="264"/>
-      <c r="AI13" s="265"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="204"/>
+      <c r="G13" s="200"/>
+      <c r="H13" s="205"/>
+      <c r="I13" s="201"/>
+      <c r="J13" s="206"/>
+      <c r="K13" s="207"/>
+      <c r="L13" s="207"/>
+      <c r="M13" s="207"/>
+      <c r="N13" s="207"/>
+      <c r="O13" s="207"/>
+      <c r="P13" s="208"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
+      <c r="S13" s="210"/>
+      <c r="T13" s="210"/>
+      <c r="U13" s="210"/>
+      <c r="V13" s="210"/>
+      <c r="W13" s="210"/>
+      <c r="X13" s="210"/>
+      <c r="Y13" s="210"/>
+      <c r="Z13" s="210"/>
+      <c r="AA13" s="210"/>
+      <c r="AB13" s="210"/>
+      <c r="AC13" s="210"/>
+      <c r="AD13" s="210"/>
+      <c r="AE13" s="211"/>
+      <c r="AF13" s="206"/>
+      <c r="AG13" s="207"/>
+      <c r="AH13" s="207"/>
+      <c r="AI13" s="208"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="257"/>
-      <c r="C14" s="258"/>
-      <c r="D14" s="259"/>
-      <c r="E14" s="260"/>
-      <c r="F14" s="261"/>
-      <c r="G14" s="257"/>
-      <c r="H14" s="262"/>
-      <c r="I14" s="258"/>
-      <c r="J14" s="263"/>
-      <c r="K14" s="264"/>
-      <c r="L14" s="264"/>
-      <c r="M14" s="264"/>
-      <c r="N14" s="264"/>
-      <c r="O14" s="264"/>
-      <c r="P14" s="265"/>
-      <c r="Q14" s="266"/>
-      <c r="R14" s="267"/>
-      <c r="S14" s="267"/>
-      <c r="T14" s="267"/>
-      <c r="U14" s="267"/>
-      <c r="V14" s="267"/>
-      <c r="W14" s="267"/>
-      <c r="X14" s="267"/>
-      <c r="Y14" s="267"/>
-      <c r="Z14" s="267"/>
-      <c r="AA14" s="267"/>
-      <c r="AB14" s="267"/>
-      <c r="AC14" s="267"/>
-      <c r="AD14" s="267"/>
-      <c r="AE14" s="268"/>
-      <c r="AF14" s="263"/>
-      <c r="AG14" s="264"/>
-      <c r="AH14" s="264"/>
-      <c r="AI14" s="265"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="204"/>
+      <c r="G14" s="200"/>
+      <c r="H14" s="205"/>
+      <c r="I14" s="201"/>
+      <c r="J14" s="206"/>
+      <c r="K14" s="207"/>
+      <c r="L14" s="207"/>
+      <c r="M14" s="207"/>
+      <c r="N14" s="207"/>
+      <c r="O14" s="207"/>
+      <c r="P14" s="208"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
+      <c r="S14" s="210"/>
+      <c r="T14" s="210"/>
+      <c r="U14" s="210"/>
+      <c r="V14" s="210"/>
+      <c r="W14" s="210"/>
+      <c r="X14" s="210"/>
+      <c r="Y14" s="210"/>
+      <c r="Z14" s="210"/>
+      <c r="AA14" s="210"/>
+      <c r="AB14" s="210"/>
+      <c r="AC14" s="210"/>
+      <c r="AD14" s="210"/>
+      <c r="AE14" s="211"/>
+      <c r="AF14" s="206"/>
+      <c r="AG14" s="207"/>
+      <c r="AH14" s="207"/>
+      <c r="AI14" s="208"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="257"/>
-      <c r="C15" s="258"/>
-      <c r="D15" s="259"/>
-      <c r="E15" s="260"/>
-      <c r="F15" s="261"/>
-      <c r="G15" s="257"/>
-      <c r="H15" s="262"/>
-      <c r="I15" s="258"/>
-      <c r="J15" s="263"/>
-      <c r="K15" s="264"/>
-      <c r="L15" s="264"/>
-      <c r="M15" s="264"/>
-      <c r="N15" s="264"/>
-      <c r="O15" s="264"/>
-      <c r="P15" s="265"/>
-      <c r="Q15" s="266"/>
-      <c r="R15" s="267"/>
-      <c r="S15" s="267"/>
-      <c r="T15" s="267"/>
-      <c r="U15" s="267"/>
-      <c r="V15" s="267"/>
-      <c r="W15" s="267"/>
-      <c r="X15" s="267"/>
-      <c r="Y15" s="267"/>
-      <c r="Z15" s="267"/>
-      <c r="AA15" s="267"/>
-      <c r="AB15" s="267"/>
-      <c r="AC15" s="267"/>
-      <c r="AD15" s="267"/>
-      <c r="AE15" s="268"/>
-      <c r="AF15" s="263"/>
-      <c r="AG15" s="264"/>
-      <c r="AH15" s="264"/>
-      <c r="AI15" s="265"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="204"/>
+      <c r="G15" s="200"/>
+      <c r="H15" s="205"/>
+      <c r="I15" s="201"/>
+      <c r="J15" s="206"/>
+      <c r="K15" s="207"/>
+      <c r="L15" s="207"/>
+      <c r="M15" s="207"/>
+      <c r="N15" s="207"/>
+      <c r="O15" s="207"/>
+      <c r="P15" s="208"/>
+      <c r="Q15" s="209"/>
+      <c r="R15" s="210"/>
+      <c r="S15" s="210"/>
+      <c r="T15" s="210"/>
+      <c r="U15" s="210"/>
+      <c r="V15" s="210"/>
+      <c r="W15" s="210"/>
+      <c r="X15" s="210"/>
+      <c r="Y15" s="210"/>
+      <c r="Z15" s="210"/>
+      <c r="AA15" s="210"/>
+      <c r="AB15" s="210"/>
+      <c r="AC15" s="210"/>
+      <c r="AD15" s="210"/>
+      <c r="AE15" s="211"/>
+      <c r="AF15" s="206"/>
+      <c r="AG15" s="207"/>
+      <c r="AH15" s="207"/>
+      <c r="AI15" s="208"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="257"/>
-      <c r="C16" s="258"/>
-      <c r="D16" s="259"/>
-      <c r="E16" s="260"/>
-      <c r="F16" s="261"/>
-      <c r="G16" s="257"/>
-      <c r="H16" s="262"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="263"/>
-      <c r="K16" s="264"/>
-      <c r="L16" s="264"/>
-      <c r="M16" s="264"/>
-      <c r="N16" s="264"/>
-      <c r="O16" s="264"/>
-      <c r="P16" s="265"/>
-      <c r="Q16" s="266"/>
-      <c r="R16" s="267"/>
-      <c r="S16" s="267"/>
-      <c r="T16" s="267"/>
-      <c r="U16" s="267"/>
-      <c r="V16" s="267"/>
-      <c r="W16" s="267"/>
-      <c r="X16" s="267"/>
-      <c r="Y16" s="267"/>
-      <c r="Z16" s="267"/>
-      <c r="AA16" s="267"/>
-      <c r="AB16" s="267"/>
-      <c r="AC16" s="267"/>
-      <c r="AD16" s="267"/>
-      <c r="AE16" s="268"/>
-      <c r="AF16" s="263"/>
-      <c r="AG16" s="264"/>
-      <c r="AH16" s="264"/>
-      <c r="AI16" s="265"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="204"/>
+      <c r="G16" s="200"/>
+      <c r="H16" s="205"/>
+      <c r="I16" s="201"/>
+      <c r="J16" s="206"/>
+      <c r="K16" s="207"/>
+      <c r="L16" s="207"/>
+      <c r="M16" s="207"/>
+      <c r="N16" s="207"/>
+      <c r="O16" s="207"/>
+      <c r="P16" s="208"/>
+      <c r="Q16" s="209"/>
+      <c r="R16" s="210"/>
+      <c r="S16" s="210"/>
+      <c r="T16" s="210"/>
+      <c r="U16" s="210"/>
+      <c r="V16" s="210"/>
+      <c r="W16" s="210"/>
+      <c r="X16" s="210"/>
+      <c r="Y16" s="210"/>
+      <c r="Z16" s="210"/>
+      <c r="AA16" s="210"/>
+      <c r="AB16" s="210"/>
+      <c r="AC16" s="210"/>
+      <c r="AD16" s="210"/>
+      <c r="AE16" s="211"/>
+      <c r="AF16" s="206"/>
+      <c r="AG16" s="207"/>
+      <c r="AH16" s="207"/>
+      <c r="AI16" s="208"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="257"/>
-      <c r="C17" s="258"/>
-      <c r="D17" s="259"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="261"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="262"/>
-      <c r="I17" s="258"/>
-      <c r="J17" s="263"/>
-      <c r="K17" s="264"/>
-      <c r="L17" s="264"/>
-      <c r="M17" s="264"/>
-      <c r="N17" s="264"/>
-      <c r="O17" s="264"/>
-      <c r="P17" s="265"/>
-      <c r="Q17" s="266"/>
-      <c r="R17" s="267"/>
-      <c r="S17" s="267"/>
-      <c r="T17" s="267"/>
-      <c r="U17" s="267"/>
-      <c r="V17" s="267"/>
-      <c r="W17" s="267"/>
-      <c r="X17" s="267"/>
-      <c r="Y17" s="267"/>
-      <c r="Z17" s="267"/>
-      <c r="AA17" s="267"/>
-      <c r="AB17" s="267"/>
-      <c r="AC17" s="267"/>
-      <c r="AD17" s="267"/>
-      <c r="AE17" s="268"/>
-      <c r="AF17" s="263"/>
-      <c r="AG17" s="264"/>
-      <c r="AH17" s="264"/>
-      <c r="AI17" s="265"/>
+      <c r="B17" s="200"/>
+      <c r="C17" s="201"/>
+      <c r="D17" s="202"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="204"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="205"/>
+      <c r="I17" s="201"/>
+      <c r="J17" s="206"/>
+      <c r="K17" s="207"/>
+      <c r="L17" s="207"/>
+      <c r="M17" s="207"/>
+      <c r="N17" s="207"/>
+      <c r="O17" s="207"/>
+      <c r="P17" s="208"/>
+      <c r="Q17" s="209"/>
+      <c r="R17" s="210"/>
+      <c r="S17" s="210"/>
+      <c r="T17" s="210"/>
+      <c r="U17" s="210"/>
+      <c r="V17" s="210"/>
+      <c r="W17" s="210"/>
+      <c r="X17" s="210"/>
+      <c r="Y17" s="210"/>
+      <c r="Z17" s="210"/>
+      <c r="AA17" s="210"/>
+      <c r="AB17" s="210"/>
+      <c r="AC17" s="210"/>
+      <c r="AD17" s="210"/>
+      <c r="AE17" s="211"/>
+      <c r="AF17" s="206"/>
+      <c r="AG17" s="207"/>
+      <c r="AH17" s="207"/>
+      <c r="AI17" s="208"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="257"/>
-      <c r="C18" s="258"/>
-      <c r="D18" s="259"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="261"/>
-      <c r="G18" s="257"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="263"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
-      <c r="M18" s="264"/>
-      <c r="N18" s="264"/>
-      <c r="O18" s="264"/>
-      <c r="P18" s="265"/>
-      <c r="Q18" s="266"/>
-      <c r="R18" s="267"/>
-      <c r="S18" s="267"/>
-      <c r="T18" s="267"/>
-      <c r="U18" s="267"/>
-      <c r="V18" s="267"/>
-      <c r="W18" s="267"/>
-      <c r="X18" s="267"/>
-      <c r="Y18" s="267"/>
-      <c r="Z18" s="267"/>
-      <c r="AA18" s="267"/>
-      <c r="AB18" s="267"/>
-      <c r="AC18" s="267"/>
-      <c r="AD18" s="267"/>
-      <c r="AE18" s="268"/>
-      <c r="AF18" s="263"/>
-      <c r="AG18" s="264"/>
-      <c r="AH18" s="264"/>
-      <c r="AI18" s="265"/>
+      <c r="B18" s="200"/>
+      <c r="C18" s="201"/>
+      <c r="D18" s="202"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="204"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="205"/>
+      <c r="I18" s="201"/>
+      <c r="J18" s="206"/>
+      <c r="K18" s="207"/>
+      <c r="L18" s="207"/>
+      <c r="M18" s="207"/>
+      <c r="N18" s="207"/>
+      <c r="O18" s="207"/>
+      <c r="P18" s="208"/>
+      <c r="Q18" s="209"/>
+      <c r="R18" s="210"/>
+      <c r="S18" s="210"/>
+      <c r="T18" s="210"/>
+      <c r="U18" s="210"/>
+      <c r="V18" s="210"/>
+      <c r="W18" s="210"/>
+      <c r="X18" s="210"/>
+      <c r="Y18" s="210"/>
+      <c r="Z18" s="210"/>
+      <c r="AA18" s="210"/>
+      <c r="AB18" s="210"/>
+      <c r="AC18" s="210"/>
+      <c r="AD18" s="210"/>
+      <c r="AE18" s="211"/>
+      <c r="AF18" s="206"/>
+      <c r="AG18" s="207"/>
+      <c r="AH18" s="207"/>
+      <c r="AI18" s="208"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="257"/>
-      <c r="C19" s="258"/>
-      <c r="D19" s="259"/>
-      <c r="E19" s="260"/>
-      <c r="F19" s="261"/>
-      <c r="G19" s="257"/>
-      <c r="H19" s="262"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="263"/>
-      <c r="K19" s="264"/>
-      <c r="L19" s="264"/>
-      <c r="M19" s="264"/>
-      <c r="N19" s="264"/>
-      <c r="O19" s="264"/>
-      <c r="P19" s="265"/>
-      <c r="Q19" s="266"/>
-      <c r="R19" s="267"/>
-      <c r="S19" s="267"/>
-      <c r="T19" s="267"/>
-      <c r="U19" s="267"/>
-      <c r="V19" s="267"/>
-      <c r="W19" s="267"/>
-      <c r="X19" s="267"/>
-      <c r="Y19" s="267"/>
-      <c r="Z19" s="267"/>
-      <c r="AA19" s="267"/>
-      <c r="AB19" s="267"/>
-      <c r="AC19" s="267"/>
-      <c r="AD19" s="267"/>
-      <c r="AE19" s="268"/>
-      <c r="AF19" s="263"/>
-      <c r="AG19" s="264"/>
-      <c r="AH19" s="264"/>
-      <c r="AI19" s="265"/>
+      <c r="B19" s="200"/>
+      <c r="C19" s="201"/>
+      <c r="D19" s="202"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="204"/>
+      <c r="G19" s="200"/>
+      <c r="H19" s="205"/>
+      <c r="I19" s="201"/>
+      <c r="J19" s="206"/>
+      <c r="K19" s="207"/>
+      <c r="L19" s="207"/>
+      <c r="M19" s="207"/>
+      <c r="N19" s="207"/>
+      <c r="O19" s="207"/>
+      <c r="P19" s="208"/>
+      <c r="Q19" s="209"/>
+      <c r="R19" s="210"/>
+      <c r="S19" s="210"/>
+      <c r="T19" s="210"/>
+      <c r="U19" s="210"/>
+      <c r="V19" s="210"/>
+      <c r="W19" s="210"/>
+      <c r="X19" s="210"/>
+      <c r="Y19" s="210"/>
+      <c r="Z19" s="210"/>
+      <c r="AA19" s="210"/>
+      <c r="AB19" s="210"/>
+      <c r="AC19" s="210"/>
+      <c r="AD19" s="210"/>
+      <c r="AE19" s="211"/>
+      <c r="AF19" s="206"/>
+      <c r="AG19" s="207"/>
+      <c r="AH19" s="207"/>
+      <c r="AI19" s="208"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="257"/>
-      <c r="C20" s="258"/>
-      <c r="D20" s="259"/>
-      <c r="E20" s="260"/>
-      <c r="F20" s="261"/>
-      <c r="G20" s="257"/>
-      <c r="H20" s="262"/>
-      <c r="I20" s="258"/>
-      <c r="J20" s="263"/>
-      <c r="K20" s="264"/>
-      <c r="L20" s="264"/>
-      <c r="M20" s="264"/>
-      <c r="N20" s="264"/>
-      <c r="O20" s="264"/>
-      <c r="P20" s="265"/>
-      <c r="Q20" s="266"/>
-      <c r="R20" s="267"/>
-      <c r="S20" s="267"/>
-      <c r="T20" s="267"/>
-      <c r="U20" s="267"/>
-      <c r="V20" s="267"/>
-      <c r="W20" s="267"/>
-      <c r="X20" s="267"/>
-      <c r="Y20" s="267"/>
-      <c r="Z20" s="267"/>
-      <c r="AA20" s="267"/>
-      <c r="AB20" s="267"/>
-      <c r="AC20" s="267"/>
-      <c r="AD20" s="267"/>
-      <c r="AE20" s="268"/>
-      <c r="AF20" s="263"/>
-      <c r="AG20" s="264"/>
-      <c r="AH20" s="264"/>
-      <c r="AI20" s="265"/>
+      <c r="B20" s="200"/>
+      <c r="C20" s="201"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="204"/>
+      <c r="G20" s="200"/>
+      <c r="H20" s="205"/>
+      <c r="I20" s="201"/>
+      <c r="J20" s="206"/>
+      <c r="K20" s="207"/>
+      <c r="L20" s="207"/>
+      <c r="M20" s="207"/>
+      <c r="N20" s="207"/>
+      <c r="O20" s="207"/>
+      <c r="P20" s="208"/>
+      <c r="Q20" s="209"/>
+      <c r="R20" s="210"/>
+      <c r="S20" s="210"/>
+      <c r="T20" s="210"/>
+      <c r="U20" s="210"/>
+      <c r="V20" s="210"/>
+      <c r="W20" s="210"/>
+      <c r="X20" s="210"/>
+      <c r="Y20" s="210"/>
+      <c r="Z20" s="210"/>
+      <c r="AA20" s="210"/>
+      <c r="AB20" s="210"/>
+      <c r="AC20" s="210"/>
+      <c r="AD20" s="210"/>
+      <c r="AE20" s="211"/>
+      <c r="AF20" s="206"/>
+      <c r="AG20" s="207"/>
+      <c r="AH20" s="207"/>
+      <c r="AI20" s="208"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="257"/>
-      <c r="C21" s="258"/>
-      <c r="D21" s="259"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="261"/>
-      <c r="G21" s="257"/>
-      <c r="H21" s="262"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="263"/>
-      <c r="K21" s="264"/>
-      <c r="L21" s="264"/>
-      <c r="M21" s="264"/>
-      <c r="N21" s="264"/>
-      <c r="O21" s="264"/>
-      <c r="P21" s="265"/>
-      <c r="Q21" s="266"/>
-      <c r="R21" s="267"/>
-      <c r="S21" s="267"/>
-      <c r="T21" s="267"/>
-      <c r="U21" s="267"/>
-      <c r="V21" s="267"/>
-      <c r="W21" s="267"/>
-      <c r="X21" s="267"/>
-      <c r="Y21" s="267"/>
-      <c r="Z21" s="267"/>
-      <c r="AA21" s="267"/>
-      <c r="AB21" s="267"/>
-      <c r="AC21" s="267"/>
-      <c r="AD21" s="267"/>
-      <c r="AE21" s="268"/>
-      <c r="AF21" s="263"/>
-      <c r="AG21" s="264"/>
-      <c r="AH21" s="264"/>
-      <c r="AI21" s="265"/>
+      <c r="B21" s="200"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="204"/>
+      <c r="G21" s="200"/>
+      <c r="H21" s="205"/>
+      <c r="I21" s="201"/>
+      <c r="J21" s="206"/>
+      <c r="K21" s="207"/>
+      <c r="L21" s="207"/>
+      <c r="M21" s="207"/>
+      <c r="N21" s="207"/>
+      <c r="O21" s="207"/>
+      <c r="P21" s="208"/>
+      <c r="Q21" s="209"/>
+      <c r="R21" s="210"/>
+      <c r="S21" s="210"/>
+      <c r="T21" s="210"/>
+      <c r="U21" s="210"/>
+      <c r="V21" s="210"/>
+      <c r="W21" s="210"/>
+      <c r="X21" s="210"/>
+      <c r="Y21" s="210"/>
+      <c r="Z21" s="210"/>
+      <c r="AA21" s="210"/>
+      <c r="AB21" s="210"/>
+      <c r="AC21" s="210"/>
+      <c r="AD21" s="210"/>
+      <c r="AE21" s="211"/>
+      <c r="AF21" s="206"/>
+      <c r="AG21" s="207"/>
+      <c r="AH21" s="207"/>
+      <c r="AI21" s="208"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="257"/>
-      <c r="C22" s="258"/>
-      <c r="D22" s="259"/>
-      <c r="E22" s="260"/>
-      <c r="F22" s="261"/>
-      <c r="G22" s="257"/>
-      <c r="H22" s="262"/>
-      <c r="I22" s="258"/>
-      <c r="J22" s="263"/>
-      <c r="K22" s="264"/>
-      <c r="L22" s="264"/>
-      <c r="M22" s="264"/>
-      <c r="N22" s="264"/>
-      <c r="O22" s="264"/>
-      <c r="P22" s="265"/>
-      <c r="Q22" s="266"/>
-      <c r="R22" s="267"/>
-      <c r="S22" s="267"/>
-      <c r="T22" s="267"/>
-      <c r="U22" s="267"/>
-      <c r="V22" s="267"/>
-      <c r="W22" s="267"/>
-      <c r="X22" s="267"/>
-      <c r="Y22" s="267"/>
-      <c r="Z22" s="267"/>
-      <c r="AA22" s="267"/>
-      <c r="AB22" s="267"/>
-      <c r="AC22" s="267"/>
-      <c r="AD22" s="267"/>
-      <c r="AE22" s="268"/>
-      <c r="AF22" s="263"/>
-      <c r="AG22" s="264"/>
-      <c r="AH22" s="264"/>
-      <c r="AI22" s="265"/>
+      <c r="B22" s="200"/>
+      <c r="C22" s="201"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="204"/>
+      <c r="G22" s="200"/>
+      <c r="H22" s="205"/>
+      <c r="I22" s="201"/>
+      <c r="J22" s="206"/>
+      <c r="K22" s="207"/>
+      <c r="L22" s="207"/>
+      <c r="M22" s="207"/>
+      <c r="N22" s="207"/>
+      <c r="O22" s="207"/>
+      <c r="P22" s="208"/>
+      <c r="Q22" s="209"/>
+      <c r="R22" s="210"/>
+      <c r="S22" s="210"/>
+      <c r="T22" s="210"/>
+      <c r="U22" s="210"/>
+      <c r="V22" s="210"/>
+      <c r="W22" s="210"/>
+      <c r="X22" s="210"/>
+      <c r="Y22" s="210"/>
+      <c r="Z22" s="210"/>
+      <c r="AA22" s="210"/>
+      <c r="AB22" s="210"/>
+      <c r="AC22" s="210"/>
+      <c r="AD22" s="210"/>
+      <c r="AE22" s="211"/>
+      <c r="AF22" s="206"/>
+      <c r="AG22" s="207"/>
+      <c r="AH22" s="207"/>
+      <c r="AI22" s="208"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="257"/>
-      <c r="C23" s="258"/>
-      <c r="D23" s="259"/>
-      <c r="E23" s="260"/>
-      <c r="F23" s="261"/>
-      <c r="G23" s="257"/>
-      <c r="H23" s="262"/>
-      <c r="I23" s="258"/>
-      <c r="J23" s="263"/>
-      <c r="K23" s="264"/>
-      <c r="L23" s="264"/>
-      <c r="M23" s="264"/>
-      <c r="N23" s="264"/>
-      <c r="O23" s="264"/>
-      <c r="P23" s="265"/>
-      <c r="Q23" s="266"/>
-      <c r="R23" s="267"/>
-      <c r="S23" s="267"/>
-      <c r="T23" s="267"/>
-      <c r="U23" s="267"/>
-      <c r="V23" s="267"/>
-      <c r="W23" s="267"/>
-      <c r="X23" s="267"/>
-      <c r="Y23" s="267"/>
-      <c r="Z23" s="267"/>
-      <c r="AA23" s="267"/>
-      <c r="AB23" s="267"/>
-      <c r="AC23" s="267"/>
-      <c r="AD23" s="267"/>
-      <c r="AE23" s="268"/>
-      <c r="AF23" s="263"/>
-      <c r="AG23" s="264"/>
-      <c r="AH23" s="264"/>
-      <c r="AI23" s="265"/>
+      <c r="B23" s="200"/>
+      <c r="C23" s="201"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="204"/>
+      <c r="G23" s="200"/>
+      <c r="H23" s="205"/>
+      <c r="I23" s="201"/>
+      <c r="J23" s="206"/>
+      <c r="K23" s="207"/>
+      <c r="L23" s="207"/>
+      <c r="M23" s="207"/>
+      <c r="N23" s="207"/>
+      <c r="O23" s="207"/>
+      <c r="P23" s="208"/>
+      <c r="Q23" s="209"/>
+      <c r="R23" s="210"/>
+      <c r="S23" s="210"/>
+      <c r="T23" s="210"/>
+      <c r="U23" s="210"/>
+      <c r="V23" s="210"/>
+      <c r="W23" s="210"/>
+      <c r="X23" s="210"/>
+      <c r="Y23" s="210"/>
+      <c r="Z23" s="210"/>
+      <c r="AA23" s="210"/>
+      <c r="AB23" s="210"/>
+      <c r="AC23" s="210"/>
+      <c r="AD23" s="210"/>
+      <c r="AE23" s="211"/>
+      <c r="AF23" s="206"/>
+      <c r="AG23" s="207"/>
+      <c r="AH23" s="207"/>
+      <c r="AI23" s="208"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="257"/>
-      <c r="C24" s="258"/>
-      <c r="D24" s="259"/>
-      <c r="E24" s="260"/>
-      <c r="F24" s="261"/>
-      <c r="G24" s="257"/>
-      <c r="H24" s="262"/>
-      <c r="I24" s="258"/>
-      <c r="J24" s="263"/>
-      <c r="K24" s="264"/>
-      <c r="L24" s="264"/>
-      <c r="M24" s="264"/>
-      <c r="N24" s="264"/>
-      <c r="O24" s="264"/>
-      <c r="P24" s="265"/>
-      <c r="Q24" s="266"/>
-      <c r="R24" s="267"/>
-      <c r="S24" s="267"/>
-      <c r="T24" s="267"/>
-      <c r="U24" s="267"/>
-      <c r="V24" s="267"/>
-      <c r="W24" s="267"/>
-      <c r="X24" s="267"/>
-      <c r="Y24" s="267"/>
-      <c r="Z24" s="267"/>
-      <c r="AA24" s="267"/>
-      <c r="AB24" s="267"/>
-      <c r="AC24" s="267"/>
-      <c r="AD24" s="267"/>
-      <c r="AE24" s="268"/>
-      <c r="AF24" s="263"/>
-      <c r="AG24" s="264"/>
-      <c r="AH24" s="264"/>
-      <c r="AI24" s="265"/>
+      <c r="B24" s="200"/>
+      <c r="C24" s="201"/>
+      <c r="D24" s="202"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="204"/>
+      <c r="G24" s="200"/>
+      <c r="H24" s="205"/>
+      <c r="I24" s="201"/>
+      <c r="J24" s="206"/>
+      <c r="K24" s="207"/>
+      <c r="L24" s="207"/>
+      <c r="M24" s="207"/>
+      <c r="N24" s="207"/>
+      <c r="O24" s="207"/>
+      <c r="P24" s="208"/>
+      <c r="Q24" s="209"/>
+      <c r="R24" s="210"/>
+      <c r="S24" s="210"/>
+      <c r="T24" s="210"/>
+      <c r="U24" s="210"/>
+      <c r="V24" s="210"/>
+      <c r="W24" s="210"/>
+      <c r="X24" s="210"/>
+      <c r="Y24" s="210"/>
+      <c r="Z24" s="210"/>
+      <c r="AA24" s="210"/>
+      <c r="AB24" s="210"/>
+      <c r="AC24" s="210"/>
+      <c r="AD24" s="210"/>
+      <c r="AE24" s="211"/>
+      <c r="AF24" s="206"/>
+      <c r="AG24" s="207"/>
+      <c r="AH24" s="207"/>
+      <c r="AI24" s="208"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="257"/>
-      <c r="C25" s="258"/>
-      <c r="D25" s="259"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="261"/>
-      <c r="G25" s="257"/>
-      <c r="H25" s="262"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="263"/>
-      <c r="K25" s="264"/>
-      <c r="L25" s="264"/>
-      <c r="M25" s="264"/>
-      <c r="N25" s="264"/>
-      <c r="O25" s="264"/>
-      <c r="P25" s="265"/>
-      <c r="Q25" s="266"/>
-      <c r="R25" s="267"/>
-      <c r="S25" s="267"/>
-      <c r="T25" s="267"/>
-      <c r="U25" s="267"/>
-      <c r="V25" s="267"/>
-      <c r="W25" s="267"/>
-      <c r="X25" s="267"/>
-      <c r="Y25" s="267"/>
-      <c r="Z25" s="267"/>
-      <c r="AA25" s="267"/>
-      <c r="AB25" s="267"/>
-      <c r="AC25" s="267"/>
-      <c r="AD25" s="267"/>
-      <c r="AE25" s="268"/>
-      <c r="AF25" s="263"/>
-      <c r="AG25" s="264"/>
-      <c r="AH25" s="264"/>
-      <c r="AI25" s="265"/>
+      <c r="B25" s="200"/>
+      <c r="C25" s="201"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="204"/>
+      <c r="G25" s="200"/>
+      <c r="H25" s="205"/>
+      <c r="I25" s="201"/>
+      <c r="J25" s="206"/>
+      <c r="K25" s="207"/>
+      <c r="L25" s="207"/>
+      <c r="M25" s="207"/>
+      <c r="N25" s="207"/>
+      <c r="O25" s="207"/>
+      <c r="P25" s="208"/>
+      <c r="Q25" s="209"/>
+      <c r="R25" s="210"/>
+      <c r="S25" s="210"/>
+      <c r="T25" s="210"/>
+      <c r="U25" s="210"/>
+      <c r="V25" s="210"/>
+      <c r="W25" s="210"/>
+      <c r="X25" s="210"/>
+      <c r="Y25" s="210"/>
+      <c r="Z25" s="210"/>
+      <c r="AA25" s="210"/>
+      <c r="AB25" s="210"/>
+      <c r="AC25" s="210"/>
+      <c r="AD25" s="210"/>
+      <c r="AE25" s="211"/>
+      <c r="AF25" s="206"/>
+      <c r="AG25" s="207"/>
+      <c r="AH25" s="207"/>
+      <c r="AI25" s="208"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="257"/>
-      <c r="C26" s="258"/>
-      <c r="D26" s="259"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="261"/>
-      <c r="G26" s="257"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="263"/>
-      <c r="K26" s="264"/>
-      <c r="L26" s="264"/>
-      <c r="M26" s="264"/>
-      <c r="N26" s="264"/>
-      <c r="O26" s="264"/>
-      <c r="P26" s="265"/>
-      <c r="Q26" s="266"/>
-      <c r="R26" s="267"/>
-      <c r="S26" s="267"/>
-      <c r="T26" s="267"/>
-      <c r="U26" s="267"/>
-      <c r="V26" s="267"/>
-      <c r="W26" s="267"/>
-      <c r="X26" s="267"/>
-      <c r="Y26" s="267"/>
-      <c r="Z26" s="267"/>
-      <c r="AA26" s="267"/>
-      <c r="AB26" s="267"/>
-      <c r="AC26" s="267"/>
-      <c r="AD26" s="267"/>
-      <c r="AE26" s="268"/>
-      <c r="AF26" s="263"/>
-      <c r="AG26" s="264"/>
-      <c r="AH26" s="264"/>
-      <c r="AI26" s="265"/>
+      <c r="B26" s="200"/>
+      <c r="C26" s="201"/>
+      <c r="D26" s="202"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="204"/>
+      <c r="G26" s="200"/>
+      <c r="H26" s="205"/>
+      <c r="I26" s="201"/>
+      <c r="J26" s="206"/>
+      <c r="K26" s="207"/>
+      <c r="L26" s="207"/>
+      <c r="M26" s="207"/>
+      <c r="N26" s="207"/>
+      <c r="O26" s="207"/>
+      <c r="P26" s="208"/>
+      <c r="Q26" s="209"/>
+      <c r="R26" s="210"/>
+      <c r="S26" s="210"/>
+      <c r="T26" s="210"/>
+      <c r="U26" s="210"/>
+      <c r="V26" s="210"/>
+      <c r="W26" s="210"/>
+      <c r="X26" s="210"/>
+      <c r="Y26" s="210"/>
+      <c r="Z26" s="210"/>
+      <c r="AA26" s="210"/>
+      <c r="AB26" s="210"/>
+      <c r="AC26" s="210"/>
+      <c r="AD26" s="210"/>
+      <c r="AE26" s="211"/>
+      <c r="AF26" s="206"/>
+      <c r="AG26" s="207"/>
+      <c r="AH26" s="207"/>
+      <c r="AI26" s="208"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="257"/>
-      <c r="C27" s="258"/>
-      <c r="D27" s="259"/>
-      <c r="E27" s="260"/>
-      <c r="F27" s="261"/>
-      <c r="G27" s="257"/>
-      <c r="H27" s="262"/>
-      <c r="I27" s="258"/>
-      <c r="J27" s="263"/>
-      <c r="K27" s="264"/>
-      <c r="L27" s="264"/>
-      <c r="M27" s="264"/>
-      <c r="N27" s="264"/>
-      <c r="O27" s="264"/>
-      <c r="P27" s="265"/>
-      <c r="Q27" s="266"/>
-      <c r="R27" s="267"/>
-      <c r="S27" s="267"/>
-      <c r="T27" s="267"/>
-      <c r="U27" s="267"/>
-      <c r="V27" s="267"/>
-      <c r="W27" s="267"/>
-      <c r="X27" s="267"/>
-      <c r="Y27" s="267"/>
-      <c r="Z27" s="267"/>
-      <c r="AA27" s="267"/>
-      <c r="AB27" s="267"/>
-      <c r="AC27" s="267"/>
-      <c r="AD27" s="267"/>
-      <c r="AE27" s="268"/>
-      <c r="AF27" s="263"/>
-      <c r="AG27" s="264"/>
-      <c r="AH27" s="264"/>
-      <c r="AI27" s="265"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="201"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="204"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="205"/>
+      <c r="I27" s="201"/>
+      <c r="J27" s="206"/>
+      <c r="K27" s="207"/>
+      <c r="L27" s="207"/>
+      <c r="M27" s="207"/>
+      <c r="N27" s="207"/>
+      <c r="O27" s="207"/>
+      <c r="P27" s="208"/>
+      <c r="Q27" s="209"/>
+      <c r="R27" s="210"/>
+      <c r="S27" s="210"/>
+      <c r="T27" s="210"/>
+      <c r="U27" s="210"/>
+      <c r="V27" s="210"/>
+      <c r="W27" s="210"/>
+      <c r="X27" s="210"/>
+      <c r="Y27" s="210"/>
+      <c r="Z27" s="210"/>
+      <c r="AA27" s="210"/>
+      <c r="AB27" s="210"/>
+      <c r="AC27" s="210"/>
+      <c r="AD27" s="210"/>
+      <c r="AE27" s="211"/>
+      <c r="AF27" s="206"/>
+      <c r="AG27" s="207"/>
+      <c r="AH27" s="207"/>
+      <c r="AI27" s="208"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="257"/>
-      <c r="C28" s="258"/>
-      <c r="D28" s="259"/>
-      <c r="E28" s="260"/>
-      <c r="F28" s="261"/>
-      <c r="G28" s="257"/>
-      <c r="H28" s="262"/>
-      <c r="I28" s="258"/>
-      <c r="J28" s="263"/>
-      <c r="K28" s="264"/>
-      <c r="L28" s="264"/>
-      <c r="M28" s="264"/>
-      <c r="N28" s="264"/>
-      <c r="O28" s="264"/>
-      <c r="P28" s="265"/>
-      <c r="Q28" s="266"/>
-      <c r="R28" s="267"/>
-      <c r="S28" s="267"/>
-      <c r="T28" s="267"/>
-      <c r="U28" s="267"/>
-      <c r="V28" s="267"/>
-      <c r="W28" s="267"/>
-      <c r="X28" s="267"/>
-      <c r="Y28" s="267"/>
-      <c r="Z28" s="267"/>
-      <c r="AA28" s="267"/>
-      <c r="AB28" s="267"/>
-      <c r="AC28" s="267"/>
-      <c r="AD28" s="267"/>
-      <c r="AE28" s="268"/>
-      <c r="AF28" s="263"/>
-      <c r="AG28" s="264"/>
-      <c r="AH28" s="264"/>
-      <c r="AI28" s="265"/>
+      <c r="B28" s="200"/>
+      <c r="C28" s="201"/>
+      <c r="D28" s="202"/>
+      <c r="E28" s="203"/>
+      <c r="F28" s="204"/>
+      <c r="G28" s="200"/>
+      <c r="H28" s="205"/>
+      <c r="I28" s="201"/>
+      <c r="J28" s="206"/>
+      <c r="K28" s="207"/>
+      <c r="L28" s="207"/>
+      <c r="M28" s="207"/>
+      <c r="N28" s="207"/>
+      <c r="O28" s="207"/>
+      <c r="P28" s="208"/>
+      <c r="Q28" s="209"/>
+      <c r="R28" s="210"/>
+      <c r="S28" s="210"/>
+      <c r="T28" s="210"/>
+      <c r="U28" s="210"/>
+      <c r="V28" s="210"/>
+      <c r="W28" s="210"/>
+      <c r="X28" s="210"/>
+      <c r="Y28" s="210"/>
+      <c r="Z28" s="210"/>
+      <c r="AA28" s="210"/>
+      <c r="AB28" s="210"/>
+      <c r="AC28" s="210"/>
+      <c r="AD28" s="210"/>
+      <c r="AE28" s="211"/>
+      <c r="AF28" s="206"/>
+      <c r="AG28" s="207"/>
+      <c r="AH28" s="207"/>
+      <c r="AI28" s="208"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="257"/>
-      <c r="C29" s="258"/>
-      <c r="D29" s="259"/>
-      <c r="E29" s="260"/>
-      <c r="F29" s="261"/>
-      <c r="G29" s="257"/>
-      <c r="H29" s="262"/>
-      <c r="I29" s="258"/>
-      <c r="J29" s="263"/>
-      <c r="K29" s="264"/>
-      <c r="L29" s="264"/>
-      <c r="M29" s="264"/>
-      <c r="N29" s="264"/>
-      <c r="O29" s="264"/>
-      <c r="P29" s="265"/>
-      <c r="Q29" s="266"/>
-      <c r="R29" s="267"/>
-      <c r="S29" s="267"/>
-      <c r="T29" s="267"/>
-      <c r="U29" s="267"/>
-      <c r="V29" s="267"/>
-      <c r="W29" s="267"/>
-      <c r="X29" s="267"/>
-      <c r="Y29" s="267"/>
-      <c r="Z29" s="267"/>
-      <c r="AA29" s="267"/>
-      <c r="AB29" s="267"/>
-      <c r="AC29" s="267"/>
-      <c r="AD29" s="267"/>
-      <c r="AE29" s="268"/>
-      <c r="AF29" s="263"/>
-      <c r="AG29" s="264"/>
-      <c r="AH29" s="264"/>
-      <c r="AI29" s="265"/>
+      <c r="B29" s="200"/>
+      <c r="C29" s="201"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="204"/>
+      <c r="G29" s="200"/>
+      <c r="H29" s="205"/>
+      <c r="I29" s="201"/>
+      <c r="J29" s="206"/>
+      <c r="K29" s="207"/>
+      <c r="L29" s="207"/>
+      <c r="M29" s="207"/>
+      <c r="N29" s="207"/>
+      <c r="O29" s="207"/>
+      <c r="P29" s="208"/>
+      <c r="Q29" s="209"/>
+      <c r="R29" s="210"/>
+      <c r="S29" s="210"/>
+      <c r="T29" s="210"/>
+      <c r="U29" s="210"/>
+      <c r="V29" s="210"/>
+      <c r="W29" s="210"/>
+      <c r="X29" s="210"/>
+      <c r="Y29" s="210"/>
+      <c r="Z29" s="210"/>
+      <c r="AA29" s="210"/>
+      <c r="AB29" s="210"/>
+      <c r="AC29" s="210"/>
+      <c r="AD29" s="210"/>
+      <c r="AE29" s="211"/>
+      <c r="AF29" s="206"/>
+      <c r="AG29" s="207"/>
+      <c r="AH29" s="207"/>
+      <c r="AI29" s="208"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="257"/>
-      <c r="C30" s="258"/>
-      <c r="D30" s="259"/>
-      <c r="E30" s="260"/>
-      <c r="F30" s="261"/>
-      <c r="G30" s="257"/>
-      <c r="H30" s="262"/>
-      <c r="I30" s="258"/>
-      <c r="J30" s="263"/>
-      <c r="K30" s="264"/>
-      <c r="L30" s="264"/>
-      <c r="M30" s="264"/>
-      <c r="N30" s="264"/>
-      <c r="O30" s="264"/>
-      <c r="P30" s="265"/>
-      <c r="Q30" s="266"/>
-      <c r="R30" s="267"/>
-      <c r="S30" s="267"/>
-      <c r="T30" s="267"/>
-      <c r="U30" s="267"/>
-      <c r="V30" s="267"/>
-      <c r="W30" s="267"/>
-      <c r="X30" s="267"/>
-      <c r="Y30" s="267"/>
-      <c r="Z30" s="267"/>
-      <c r="AA30" s="267"/>
-      <c r="AB30" s="267"/>
-      <c r="AC30" s="267"/>
-      <c r="AD30" s="267"/>
-      <c r="AE30" s="268"/>
-      <c r="AF30" s="263"/>
-      <c r="AG30" s="264"/>
-      <c r="AH30" s="264"/>
-      <c r="AI30" s="265"/>
+      <c r="B30" s="200"/>
+      <c r="C30" s="201"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="204"/>
+      <c r="G30" s="200"/>
+      <c r="H30" s="205"/>
+      <c r="I30" s="201"/>
+      <c r="J30" s="206"/>
+      <c r="K30" s="207"/>
+      <c r="L30" s="207"/>
+      <c r="M30" s="207"/>
+      <c r="N30" s="207"/>
+      <c r="O30" s="207"/>
+      <c r="P30" s="208"/>
+      <c r="Q30" s="209"/>
+      <c r="R30" s="210"/>
+      <c r="S30" s="210"/>
+      <c r="T30" s="210"/>
+      <c r="U30" s="210"/>
+      <c r="V30" s="210"/>
+      <c r="W30" s="210"/>
+      <c r="X30" s="210"/>
+      <c r="Y30" s="210"/>
+      <c r="Z30" s="210"/>
+      <c r="AA30" s="210"/>
+      <c r="AB30" s="210"/>
+      <c r="AC30" s="210"/>
+      <c r="AD30" s="210"/>
+      <c r="AE30" s="211"/>
+      <c r="AF30" s="206"/>
+      <c r="AG30" s="207"/>
+      <c r="AH30" s="207"/>
+      <c r="AI30" s="208"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="257"/>
-      <c r="C31" s="258"/>
-      <c r="D31" s="259"/>
-      <c r="E31" s="260"/>
-      <c r="F31" s="261"/>
-      <c r="G31" s="257"/>
-      <c r="H31" s="262"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="263"/>
-      <c r="K31" s="264"/>
-      <c r="L31" s="264"/>
-      <c r="M31" s="264"/>
-      <c r="N31" s="264"/>
-      <c r="O31" s="264"/>
-      <c r="P31" s="265"/>
-      <c r="Q31" s="266"/>
-      <c r="R31" s="267"/>
-      <c r="S31" s="267"/>
-      <c r="T31" s="267"/>
-      <c r="U31" s="267"/>
-      <c r="V31" s="267"/>
-      <c r="W31" s="267"/>
-      <c r="X31" s="267"/>
-      <c r="Y31" s="267"/>
-      <c r="Z31" s="267"/>
-      <c r="AA31" s="267"/>
-      <c r="AB31" s="267"/>
-      <c r="AC31" s="267"/>
-      <c r="AD31" s="267"/>
-      <c r="AE31" s="268"/>
-      <c r="AF31" s="263"/>
-      <c r="AG31" s="264"/>
-      <c r="AH31" s="264"/>
-      <c r="AI31" s="265"/>
+      <c r="B31" s="200"/>
+      <c r="C31" s="201"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="204"/>
+      <c r="G31" s="200"/>
+      <c r="H31" s="205"/>
+      <c r="I31" s="201"/>
+      <c r="J31" s="206"/>
+      <c r="K31" s="207"/>
+      <c r="L31" s="207"/>
+      <c r="M31" s="207"/>
+      <c r="N31" s="207"/>
+      <c r="O31" s="207"/>
+      <c r="P31" s="208"/>
+      <c r="Q31" s="209"/>
+      <c r="R31" s="210"/>
+      <c r="S31" s="210"/>
+      <c r="T31" s="210"/>
+      <c r="U31" s="210"/>
+      <c r="V31" s="210"/>
+      <c r="W31" s="210"/>
+      <c r="X31" s="210"/>
+      <c r="Y31" s="210"/>
+      <c r="Z31" s="210"/>
+      <c r="AA31" s="210"/>
+      <c r="AB31" s="210"/>
+      <c r="AC31" s="210"/>
+      <c r="AD31" s="210"/>
+      <c r="AE31" s="211"/>
+      <c r="AF31" s="206"/>
+      <c r="AG31" s="207"/>
+      <c r="AH31" s="207"/>
+      <c r="AI31" s="208"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="257"/>
-      <c r="C32" s="258"/>
-      <c r="D32" s="259"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="261"/>
-      <c r="G32" s="257"/>
-      <c r="H32" s="262"/>
-      <c r="I32" s="258"/>
-      <c r="J32" s="263"/>
-      <c r="K32" s="269"/>
-      <c r="L32" s="264"/>
-      <c r="M32" s="264"/>
-      <c r="N32" s="264"/>
-      <c r="O32" s="264"/>
-      <c r="P32" s="265"/>
-      <c r="Q32" s="266"/>
-      <c r="R32" s="267"/>
-      <c r="S32" s="267"/>
-      <c r="T32" s="267"/>
-      <c r="U32" s="267"/>
-      <c r="V32" s="267"/>
-      <c r="W32" s="267"/>
-      <c r="X32" s="267"/>
-      <c r="Y32" s="267"/>
-      <c r="Z32" s="267"/>
-      <c r="AA32" s="267"/>
-      <c r="AB32" s="267"/>
-      <c r="AC32" s="267"/>
-      <c r="AD32" s="267"/>
-      <c r="AE32" s="268"/>
-      <c r="AF32" s="263"/>
-      <c r="AG32" s="264"/>
-      <c r="AH32" s="264"/>
-      <c r="AI32" s="265"/>
+      <c r="B32" s="200"/>
+      <c r="C32" s="201"/>
+      <c r="D32" s="202"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="204"/>
+      <c r="G32" s="200"/>
+      <c r="H32" s="205"/>
+      <c r="I32" s="201"/>
+      <c r="J32" s="206"/>
+      <c r="K32" s="212"/>
+      <c r="L32" s="207"/>
+      <c r="M32" s="207"/>
+      <c r="N32" s="207"/>
+      <c r="O32" s="207"/>
+      <c r="P32" s="208"/>
+      <c r="Q32" s="209"/>
+      <c r="R32" s="210"/>
+      <c r="S32" s="210"/>
+      <c r="T32" s="210"/>
+      <c r="U32" s="210"/>
+      <c r="V32" s="210"/>
+      <c r="W32" s="210"/>
+      <c r="X32" s="210"/>
+      <c r="Y32" s="210"/>
+      <c r="Z32" s="210"/>
+      <c r="AA32" s="210"/>
+      <c r="AB32" s="210"/>
+      <c r="AC32" s="210"/>
+      <c r="AD32" s="210"/>
+      <c r="AE32" s="211"/>
+      <c r="AF32" s="206"/>
+      <c r="AG32" s="207"/>
+      <c r="AH32" s="207"/>
+      <c r="AI32" s="208"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="257"/>
-      <c r="C33" s="258"/>
-      <c r="D33" s="259"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="261"/>
-      <c r="G33" s="257"/>
-      <c r="H33" s="262"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="263"/>
-      <c r="K33" s="264"/>
-      <c r="L33" s="264"/>
-      <c r="M33" s="264"/>
-      <c r="N33" s="264"/>
-      <c r="O33" s="264"/>
-      <c r="P33" s="265"/>
-      <c r="Q33" s="266"/>
-      <c r="R33" s="267"/>
-      <c r="S33" s="267"/>
-      <c r="T33" s="267"/>
-      <c r="U33" s="267"/>
-      <c r="V33" s="267"/>
-      <c r="W33" s="267"/>
-      <c r="X33" s="267"/>
-      <c r="Y33" s="267"/>
-      <c r="Z33" s="267"/>
-      <c r="AA33" s="267"/>
-      <c r="AB33" s="267"/>
-      <c r="AC33" s="267"/>
-      <c r="AD33" s="267"/>
-      <c r="AE33" s="268"/>
-      <c r="AF33" s="263"/>
-      <c r="AG33" s="264"/>
-      <c r="AH33" s="264"/>
-      <c r="AI33" s="265"/>
+      <c r="B33" s="200"/>
+      <c r="C33" s="201"/>
+      <c r="D33" s="202"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="204"/>
+      <c r="G33" s="200"/>
+      <c r="H33" s="205"/>
+      <c r="I33" s="201"/>
+      <c r="J33" s="206"/>
+      <c r="K33" s="207"/>
+      <c r="L33" s="207"/>
+      <c r="M33" s="207"/>
+      <c r="N33" s="207"/>
+      <c r="O33" s="207"/>
+      <c r="P33" s="208"/>
+      <c r="Q33" s="209"/>
+      <c r="R33" s="210"/>
+      <c r="S33" s="210"/>
+      <c r="T33" s="210"/>
+      <c r="U33" s="210"/>
+      <c r="V33" s="210"/>
+      <c r="W33" s="210"/>
+      <c r="X33" s="210"/>
+      <c r="Y33" s="210"/>
+      <c r="Z33" s="210"/>
+      <c r="AA33" s="210"/>
+      <c r="AB33" s="210"/>
+      <c r="AC33" s="210"/>
+      <c r="AD33" s="210"/>
+      <c r="AE33" s="211"/>
+      <c r="AF33" s="206"/>
+      <c r="AG33" s="207"/>
+      <c r="AH33" s="207"/>
+      <c r="AI33" s="208"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -14056,6 +13901,161 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -35897,7 +35897,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C11)&gt;0)*ROW($C$11:C11),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D11),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H11),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -35938,7 +35938,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C12)&gt;0)*ROW($C$11:C12),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D12),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H12),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0014AA43-3ACE-4BB4-93AF-95EB1A9AE53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1959350-7755-46C6-8251-1CA889009C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,18 +11,18 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="XxxAction_クラス単体" sheetId="23" r:id="rId3"/>
-    <sheet name="RAxxxxxxxx_リクエスト単体" sheetId="24" r:id="rId4"/>
+    <sheet name="XxxAction_リクエスト単体" sheetId="24" r:id="rId4"/>
     <sheet name="取引単体" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RAxxxxxxxx_リクエスト単体!$A$10:$R$311</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XxxAction_リクエスト単体!$A$10:$R$311</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$296</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$O$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">RAxxxxxxxx_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">XxxAction_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1691" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1692" uniqueCount="538">
   <si>
     <t>システム機能設計書</t>
     <rPh sb="4" eb="6">
@@ -6982,10 +6982,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>テストターゲット名：RAxxxxxxxx</t>
-    <rPh sb="8" eb="9">
-      <t>メイ</t>
-    </rPh>
+    <t>リクエストID：XXX</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8263,108 +8260,6 @@
     <xf numFmtId="31" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="11" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8471,6 +8366,108 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12649,57 +12646,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="206" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="243" t="s">
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="209" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="244"/>
-      <c r="G1" s="244"/>
-      <c r="H1" s="244"/>
-      <c r="I1" s="244"/>
-      <c r="J1" s="244"/>
-      <c r="K1" s="244"/>
-      <c r="L1" s="244"/>
-      <c r="M1" s="244"/>
-      <c r="N1" s="245"/>
-      <c r="O1" s="249" t="s">
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="210"/>
+      <c r="N1" s="211"/>
+      <c r="O1" s="215" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="250"/>
-      <c r="Q1" s="250"/>
-      <c r="R1" s="251"/>
-      <c r="S1" s="258" t="s">
+      <c r="P1" s="216"/>
+      <c r="Q1" s="216"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="224" t="s">
         <v>536</v>
       </c>
-      <c r="T1" s="259"/>
-      <c r="U1" s="259"/>
-      <c r="V1" s="259"/>
-      <c r="W1" s="259"/>
-      <c r="X1" s="259"/>
-      <c r="Y1" s="259"/>
-      <c r="Z1" s="260"/>
-      <c r="AA1" s="240" t="s">
+      <c r="T1" s="225"/>
+      <c r="U1" s="225"/>
+      <c r="V1" s="225"/>
+      <c r="W1" s="225"/>
+      <c r="X1" s="225"/>
+      <c r="Y1" s="225"/>
+      <c r="Z1" s="226"/>
+      <c r="AA1" s="206" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="242"/>
-      <c r="AC1" s="267" t="str">
+      <c r="AB1" s="208"/>
+      <c r="AC1" s="233" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="268"/>
-      <c r="AE1" s="268"/>
-      <c r="AF1" s="269"/>
-      <c r="AG1" s="234">
+      <c r="AD1" s="234"/>
+      <c r="AE1" s="234"/>
+      <c r="AF1" s="235"/>
+      <c r="AG1" s="200">
         <f>IF(D8="","",D8)</f>
         <v>44011</v>
       </c>
-      <c r="AH1" s="235"/>
-      <c r="AI1" s="236"/>
+      <c r="AH1" s="201"/>
+      <c r="AI1" s="202"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -12707,53 +12704,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="240" t="s">
+      <c r="A2" s="206" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="241"/>
-      <c r="C2" s="241"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="243" t="s">
+      <c r="B2" s="207"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="208"/>
+      <c r="E2" s="209" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="244"/>
-      <c r="I2" s="244"/>
-      <c r="J2" s="244"/>
-      <c r="K2" s="244"/>
-      <c r="L2" s="244"/>
-      <c r="M2" s="244"/>
-      <c r="N2" s="245"/>
-      <c r="O2" s="252"/>
-      <c r="P2" s="253"/>
-      <c r="Q2" s="253"/>
-      <c r="R2" s="254"/>
-      <c r="S2" s="261"/>
-      <c r="T2" s="262"/>
-      <c r="U2" s="262"/>
-      <c r="V2" s="262"/>
-      <c r="W2" s="262"/>
-      <c r="X2" s="262"/>
-      <c r="Y2" s="262"/>
-      <c r="Z2" s="263"/>
-      <c r="AA2" s="240" t="s">
+      <c r="F2" s="210"/>
+      <c r="G2" s="210"/>
+      <c r="H2" s="210"/>
+      <c r="I2" s="210"/>
+      <c r="J2" s="210"/>
+      <c r="K2" s="210"/>
+      <c r="L2" s="210"/>
+      <c r="M2" s="210"/>
+      <c r="N2" s="211"/>
+      <c r="O2" s="218"/>
+      <c r="P2" s="219"/>
+      <c r="Q2" s="219"/>
+      <c r="R2" s="220"/>
+      <c r="S2" s="227"/>
+      <c r="T2" s="228"/>
+      <c r="U2" s="228"/>
+      <c r="V2" s="228"/>
+      <c r="W2" s="228"/>
+      <c r="X2" s="228"/>
+      <c r="Y2" s="228"/>
+      <c r="Z2" s="229"/>
+      <c r="AA2" s="206" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="246" t="str">
+      <c r="AB2" s="208"/>
+      <c r="AC2" s="212" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="247"/>
-      <c r="AE2" s="247"/>
-      <c r="AF2" s="248"/>
-      <c r="AG2" s="234">
+      <c r="AD2" s="213"/>
+      <c r="AE2" s="213"/>
+      <c r="AF2" s="214"/>
+      <c r="AG2" s="200">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44858</v>
       </c>
-      <c r="AH2" s="235"/>
-      <c r="AI2" s="236"/>
+      <c r="AH2" s="201"/>
+      <c r="AI2" s="202"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -12761,45 +12758,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="240" t="s">
+      <c r="A3" s="206" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="241"/>
-      <c r="C3" s="241"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="243" t="s">
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="209" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="244"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="244"/>
-      <c r="I3" s="244"/>
-      <c r="J3" s="244"/>
-      <c r="K3" s="244"/>
-      <c r="L3" s="244"/>
-      <c r="M3" s="244"/>
-      <c r="N3" s="245"/>
-      <c r="O3" s="255"/>
-      <c r="P3" s="256"/>
-      <c r="Q3" s="256"/>
-      <c r="R3" s="257"/>
-      <c r="S3" s="264"/>
-      <c r="T3" s="265"/>
-      <c r="U3" s="265"/>
-      <c r="V3" s="265"/>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="266"/>
-      <c r="AA3" s="240"/>
-      <c r="AB3" s="242"/>
-      <c r="AC3" s="267"/>
-      <c r="AD3" s="268"/>
-      <c r="AE3" s="268"/>
-      <c r="AF3" s="269"/>
-      <c r="AG3" s="234"/>
-      <c r="AH3" s="235"/>
-      <c r="AI3" s="236"/>
+      <c r="F3" s="210"/>
+      <c r="G3" s="210"/>
+      <c r="H3" s="210"/>
+      <c r="I3" s="210"/>
+      <c r="J3" s="210"/>
+      <c r="K3" s="210"/>
+      <c r="L3" s="210"/>
+      <c r="M3" s="210"/>
+      <c r="N3" s="211"/>
+      <c r="O3" s="221"/>
+      <c r="P3" s="222"/>
+      <c r="Q3" s="222"/>
+      <c r="R3" s="223"/>
+      <c r="S3" s="230"/>
+      <c r="T3" s="231"/>
+      <c r="U3" s="231"/>
+      <c r="V3" s="231"/>
+      <c r="W3" s="231"/>
+      <c r="X3" s="231"/>
+      <c r="Y3" s="231"/>
+      <c r="Z3" s="232"/>
+      <c r="AA3" s="206"/>
+      <c r="AB3" s="208"/>
+      <c r="AC3" s="233"/>
+      <c r="AD3" s="234"/>
+      <c r="AE3" s="234"/>
+      <c r="AF3" s="235"/>
+      <c r="AG3" s="200"/>
+      <c r="AH3" s="201"/>
+      <c r="AI3" s="202"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -12836,97 +12833,97 @@
       <c r="A7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="237" t="s">
+      <c r="B7" s="203" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="238"/>
-      <c r="D7" s="237" t="s">
+      <c r="C7" s="204"/>
+      <c r="D7" s="203" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="239"/>
-      <c r="F7" s="238"/>
-      <c r="G7" s="237" t="s">
+      <c r="E7" s="205"/>
+      <c r="F7" s="204"/>
+      <c r="G7" s="203" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="239"/>
-      <c r="I7" s="238"/>
-      <c r="J7" s="237" t="s">
+      <c r="H7" s="205"/>
+      <c r="I7" s="204"/>
+      <c r="J7" s="203" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="239"/>
-      <c r="L7" s="239"/>
-      <c r="M7" s="239"/>
-      <c r="N7" s="239"/>
-      <c r="O7" s="239"/>
-      <c r="P7" s="238"/>
-      <c r="Q7" s="237" t="s">
+      <c r="K7" s="205"/>
+      <c r="L7" s="205"/>
+      <c r="M7" s="205"/>
+      <c r="N7" s="205"/>
+      <c r="O7" s="205"/>
+      <c r="P7" s="204"/>
+      <c r="Q7" s="203" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="239"/>
-      <c r="S7" s="239"/>
-      <c r="T7" s="239"/>
-      <c r="U7" s="239"/>
-      <c r="V7" s="239"/>
-      <c r="W7" s="239"/>
-      <c r="X7" s="239"/>
-      <c r="Y7" s="239"/>
-      <c r="Z7" s="239"/>
-      <c r="AA7" s="239"/>
-      <c r="AB7" s="239"/>
-      <c r="AC7" s="239"/>
-      <c r="AD7" s="239"/>
-      <c r="AE7" s="238"/>
-      <c r="AF7" s="237" t="s">
+      <c r="R7" s="205"/>
+      <c r="S7" s="205"/>
+      <c r="T7" s="205"/>
+      <c r="U7" s="205"/>
+      <c r="V7" s="205"/>
+      <c r="W7" s="205"/>
+      <c r="X7" s="205"/>
+      <c r="Y7" s="205"/>
+      <c r="Z7" s="205"/>
+      <c r="AA7" s="205"/>
+      <c r="AB7" s="205"/>
+      <c r="AC7" s="205"/>
+      <c r="AD7" s="205"/>
+      <c r="AE7" s="204"/>
+      <c r="AF7" s="203" t="s">
         <v>43</v>
       </c>
-      <c r="AG7" s="239"/>
-      <c r="AH7" s="239"/>
-      <c r="AI7" s="238"/>
+      <c r="AG7" s="205"/>
+      <c r="AH7" s="205"/>
+      <c r="AI7" s="204"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="225" t="s">
+      <c r="B8" s="248" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="226"/>
-      <c r="D8" s="227">
+      <c r="C8" s="249"/>
+      <c r="D8" s="250">
         <v>44011</v>
       </c>
-      <c r="E8" s="228"/>
-      <c r="F8" s="229"/>
-      <c r="G8" s="225" t="s">
+      <c r="E8" s="251"/>
+      <c r="F8" s="252"/>
+      <c r="G8" s="248" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="230"/>
-      <c r="I8" s="226"/>
-      <c r="J8" s="231" t="s">
+      <c r="H8" s="253"/>
+      <c r="I8" s="249"/>
+      <c r="J8" s="254" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="232"/>
-      <c r="L8" s="232"/>
-      <c r="M8" s="232"/>
-      <c r="N8" s="232"/>
-      <c r="O8" s="232"/>
-      <c r="P8" s="233"/>
-      <c r="Q8" s="231" t="s">
+      <c r="K8" s="255"/>
+      <c r="L8" s="255"/>
+      <c r="M8" s="255"/>
+      <c r="N8" s="255"/>
+      <c r="O8" s="255"/>
+      <c r="P8" s="256"/>
+      <c r="Q8" s="254" t="s">
         <v>52</v>
       </c>
-      <c r="R8" s="232"/>
-      <c r="S8" s="232"/>
-      <c r="T8" s="232"/>
-      <c r="U8" s="232"/>
-      <c r="V8" s="232"/>
-      <c r="W8" s="232"/>
-      <c r="X8" s="232"/>
-      <c r="Y8" s="232"/>
-      <c r="Z8" s="232"/>
-      <c r="AA8" s="232"/>
-      <c r="AB8" s="232"/>
-      <c r="AC8" s="232"/>
-      <c r="AD8" s="232"/>
-      <c r="AE8" s="233"/>
+      <c r="R8" s="255"/>
+      <c r="S8" s="255"/>
+      <c r="T8" s="255"/>
+      <c r="U8" s="255"/>
+      <c r="V8" s="255"/>
+      <c r="W8" s="255"/>
+      <c r="X8" s="255"/>
+      <c r="Y8" s="255"/>
+      <c r="Z8" s="255"/>
+      <c r="AA8" s="255"/>
+      <c r="AB8" s="255"/>
+      <c r="AC8" s="255"/>
+      <c r="AD8" s="255"/>
+      <c r="AE8" s="256"/>
       <c r="AF8" s="25" t="s">
         <v>53</v>
       </c>
@@ -12938,946 +12935,1101 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="213" t="s">
+      <c r="B9" s="236" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="214"/>
-      <c r="D9" s="215">
+      <c r="C9" s="237"/>
+      <c r="D9" s="238">
         <v>44858</v>
       </c>
-      <c r="E9" s="216"/>
-      <c r="F9" s="217"/>
-      <c r="G9" s="215" t="s">
+      <c r="E9" s="239"/>
+      <c r="F9" s="240"/>
+      <c r="G9" s="238" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="218"/>
-      <c r="I9" s="214"/>
-      <c r="J9" s="219" t="s">
+      <c r="H9" s="241"/>
+      <c r="I9" s="237"/>
+      <c r="J9" s="242" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="220"/>
-      <c r="L9" s="220"/>
-      <c r="M9" s="220"/>
-      <c r="N9" s="220"/>
-      <c r="O9" s="220"/>
-      <c r="P9" s="221"/>
-      <c r="Q9" s="219" t="s">
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
+      <c r="M9" s="243"/>
+      <c r="N9" s="243"/>
+      <c r="O9" s="243"/>
+      <c r="P9" s="244"/>
+      <c r="Q9" s="242" t="s">
         <v>61</v>
       </c>
-      <c r="R9" s="222"/>
-      <c r="S9" s="222"/>
-      <c r="T9" s="222"/>
-      <c r="U9" s="222"/>
-      <c r="V9" s="222"/>
-      <c r="W9" s="222"/>
-      <c r="X9" s="222"/>
-      <c r="Y9" s="222"/>
-      <c r="Z9" s="222"/>
-      <c r="AA9" s="222"/>
-      <c r="AB9" s="222"/>
-      <c r="AC9" s="222"/>
-      <c r="AD9" s="222"/>
-      <c r="AE9" s="223"/>
-      <c r="AF9" s="224" t="s">
+      <c r="R9" s="245"/>
+      <c r="S9" s="245"/>
+      <c r="T9" s="245"/>
+      <c r="U9" s="245"/>
+      <c r="V9" s="245"/>
+      <c r="W9" s="245"/>
+      <c r="X9" s="245"/>
+      <c r="Y9" s="245"/>
+      <c r="Z9" s="245"/>
+      <c r="AA9" s="245"/>
+      <c r="AB9" s="245"/>
+      <c r="AC9" s="245"/>
+      <c r="AD9" s="245"/>
+      <c r="AE9" s="246"/>
+      <c r="AF9" s="247" t="s">
         <v>53</v>
       </c>
-      <c r="AG9" s="220"/>
-      <c r="AH9" s="220"/>
-      <c r="AI9" s="221"/>
+      <c r="AG9" s="243"/>
+      <c r="AH9" s="243"/>
+      <c r="AI9" s="244"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="201"/>
-      <c r="D10" s="202"/>
-      <c r="E10" s="203"/>
-      <c r="F10" s="204"/>
-      <c r="G10" s="200"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="201"/>
-      <c r="J10" s="206"/>
-      <c r="K10" s="207"/>
-      <c r="L10" s="207"/>
-      <c r="M10" s="207"/>
-      <c r="N10" s="207"/>
-      <c r="O10" s="207"/>
-      <c r="P10" s="208"/>
-      <c r="Q10" s="209"/>
-      <c r="R10" s="210"/>
-      <c r="S10" s="210"/>
-      <c r="T10" s="210"/>
-      <c r="U10" s="210"/>
-      <c r="V10" s="210"/>
-      <c r="W10" s="210"/>
-      <c r="X10" s="210"/>
-      <c r="Y10" s="210"/>
-      <c r="Z10" s="210"/>
-      <c r="AA10" s="210"/>
-      <c r="AB10" s="210"/>
-      <c r="AC10" s="210"/>
-      <c r="AD10" s="210"/>
-      <c r="AE10" s="211"/>
-      <c r="AF10" s="206"/>
-      <c r="AG10" s="207"/>
-      <c r="AH10" s="207"/>
-      <c r="AI10" s="208"/>
+      <c r="B10" s="257"/>
+      <c r="C10" s="258"/>
+      <c r="D10" s="259"/>
+      <c r="E10" s="260"/>
+      <c r="F10" s="261"/>
+      <c r="G10" s="257"/>
+      <c r="H10" s="262"/>
+      <c r="I10" s="258"/>
+      <c r="J10" s="263"/>
+      <c r="K10" s="264"/>
+      <c r="L10" s="264"/>
+      <c r="M10" s="264"/>
+      <c r="N10" s="264"/>
+      <c r="O10" s="264"/>
+      <c r="P10" s="265"/>
+      <c r="Q10" s="266"/>
+      <c r="R10" s="267"/>
+      <c r="S10" s="267"/>
+      <c r="T10" s="267"/>
+      <c r="U10" s="267"/>
+      <c r="V10" s="267"/>
+      <c r="W10" s="267"/>
+      <c r="X10" s="267"/>
+      <c r="Y10" s="267"/>
+      <c r="Z10" s="267"/>
+      <c r="AA10" s="267"/>
+      <c r="AB10" s="267"/>
+      <c r="AC10" s="267"/>
+      <c r="AD10" s="267"/>
+      <c r="AE10" s="268"/>
+      <c r="AF10" s="263"/>
+      <c r="AG10" s="264"/>
+      <c r="AH10" s="264"/>
+      <c r="AI10" s="265"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="200"/>
-      <c r="C11" s="201"/>
-      <c r="D11" s="202"/>
-      <c r="E11" s="203"/>
-      <c r="F11" s="204"/>
-      <c r="G11" s="200"/>
-      <c r="H11" s="205"/>
-      <c r="I11" s="201"/>
-      <c r="J11" s="206"/>
-      <c r="K11" s="207"/>
-      <c r="L11" s="207"/>
-      <c r="M11" s="207"/>
-      <c r="N11" s="207"/>
-      <c r="O11" s="207"/>
-      <c r="P11" s="208"/>
-      <c r="Q11" s="209"/>
-      <c r="R11" s="210"/>
-      <c r="S11" s="210"/>
-      <c r="T11" s="210"/>
-      <c r="U11" s="210"/>
-      <c r="V11" s="210"/>
-      <c r="W11" s="210"/>
-      <c r="X11" s="210"/>
-      <c r="Y11" s="210"/>
-      <c r="Z11" s="210"/>
-      <c r="AA11" s="210"/>
-      <c r="AB11" s="210"/>
-      <c r="AC11" s="210"/>
-      <c r="AD11" s="210"/>
-      <c r="AE11" s="211"/>
-      <c r="AF11" s="206"/>
-      <c r="AG11" s="207"/>
-      <c r="AH11" s="207"/>
-      <c r="AI11" s="208"/>
+      <c r="B11" s="257"/>
+      <c r="C11" s="258"/>
+      <c r="D11" s="259"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="261"/>
+      <c r="G11" s="257"/>
+      <c r="H11" s="262"/>
+      <c r="I11" s="258"/>
+      <c r="J11" s="263"/>
+      <c r="K11" s="264"/>
+      <c r="L11" s="264"/>
+      <c r="M11" s="264"/>
+      <c r="N11" s="264"/>
+      <c r="O11" s="264"/>
+      <c r="P11" s="265"/>
+      <c r="Q11" s="266"/>
+      <c r="R11" s="267"/>
+      <c r="S11" s="267"/>
+      <c r="T11" s="267"/>
+      <c r="U11" s="267"/>
+      <c r="V11" s="267"/>
+      <c r="W11" s="267"/>
+      <c r="X11" s="267"/>
+      <c r="Y11" s="267"/>
+      <c r="Z11" s="267"/>
+      <c r="AA11" s="267"/>
+      <c r="AB11" s="267"/>
+      <c r="AC11" s="267"/>
+      <c r="AD11" s="267"/>
+      <c r="AE11" s="268"/>
+      <c r="AF11" s="263"/>
+      <c r="AG11" s="264"/>
+      <c r="AH11" s="264"/>
+      <c r="AI11" s="265"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="200"/>
-      <c r="C12" s="201"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="204"/>
-      <c r="G12" s="200"/>
-      <c r="H12" s="205"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="206"/>
-      <c r="K12" s="207"/>
-      <c r="L12" s="207"/>
-      <c r="M12" s="207"/>
-      <c r="N12" s="207"/>
-      <c r="O12" s="207"/>
-      <c r="P12" s="208"/>
-      <c r="Q12" s="209"/>
-      <c r="R12" s="210"/>
-      <c r="S12" s="210"/>
-      <c r="T12" s="210"/>
-      <c r="U12" s="210"/>
-      <c r="V12" s="210"/>
-      <c r="W12" s="210"/>
-      <c r="X12" s="210"/>
-      <c r="Y12" s="210"/>
-      <c r="Z12" s="210"/>
-      <c r="AA12" s="210"/>
-      <c r="AB12" s="210"/>
-      <c r="AC12" s="210"/>
-      <c r="AD12" s="210"/>
-      <c r="AE12" s="211"/>
-      <c r="AF12" s="206"/>
-      <c r="AG12" s="207"/>
-      <c r="AH12" s="207"/>
-      <c r="AI12" s="208"/>
+      <c r="B12" s="257"/>
+      <c r="C12" s="258"/>
+      <c r="D12" s="259"/>
+      <c r="E12" s="260"/>
+      <c r="F12" s="261"/>
+      <c r="G12" s="257"/>
+      <c r="H12" s="262"/>
+      <c r="I12" s="258"/>
+      <c r="J12" s="263"/>
+      <c r="K12" s="264"/>
+      <c r="L12" s="264"/>
+      <c r="M12" s="264"/>
+      <c r="N12" s="264"/>
+      <c r="O12" s="264"/>
+      <c r="P12" s="265"/>
+      <c r="Q12" s="266"/>
+      <c r="R12" s="267"/>
+      <c r="S12" s="267"/>
+      <c r="T12" s="267"/>
+      <c r="U12" s="267"/>
+      <c r="V12" s="267"/>
+      <c r="W12" s="267"/>
+      <c r="X12" s="267"/>
+      <c r="Y12" s="267"/>
+      <c r="Z12" s="267"/>
+      <c r="AA12" s="267"/>
+      <c r="AB12" s="267"/>
+      <c r="AC12" s="267"/>
+      <c r="AD12" s="267"/>
+      <c r="AE12" s="268"/>
+      <c r="AF12" s="263"/>
+      <c r="AG12" s="264"/>
+      <c r="AH12" s="264"/>
+      <c r="AI12" s="265"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="200"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="202"/>
-      <c r="E13" s="203"/>
-      <c r="F13" s="204"/>
-      <c r="G13" s="200"/>
-      <c r="H13" s="205"/>
-      <c r="I13" s="201"/>
-      <c r="J13" s="206"/>
-      <c r="K13" s="207"/>
-      <c r="L13" s="207"/>
-      <c r="M13" s="207"/>
-      <c r="N13" s="207"/>
-      <c r="O13" s="207"/>
-      <c r="P13" s="208"/>
-      <c r="Q13" s="209"/>
-      <c r="R13" s="210"/>
-      <c r="S13" s="210"/>
-      <c r="T13" s="210"/>
-      <c r="U13" s="210"/>
-      <c r="V13" s="210"/>
-      <c r="W13" s="210"/>
-      <c r="X13" s="210"/>
-      <c r="Y13" s="210"/>
-      <c r="Z13" s="210"/>
-      <c r="AA13" s="210"/>
-      <c r="AB13" s="210"/>
-      <c r="AC13" s="210"/>
-      <c r="AD13" s="210"/>
-      <c r="AE13" s="211"/>
-      <c r="AF13" s="206"/>
-      <c r="AG13" s="207"/>
-      <c r="AH13" s="207"/>
-      <c r="AI13" s="208"/>
+      <c r="B13" s="257"/>
+      <c r="C13" s="258"/>
+      <c r="D13" s="259"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="261"/>
+      <c r="G13" s="257"/>
+      <c r="H13" s="262"/>
+      <c r="I13" s="258"/>
+      <c r="J13" s="263"/>
+      <c r="K13" s="264"/>
+      <c r="L13" s="264"/>
+      <c r="M13" s="264"/>
+      <c r="N13" s="264"/>
+      <c r="O13" s="264"/>
+      <c r="P13" s="265"/>
+      <c r="Q13" s="266"/>
+      <c r="R13" s="267"/>
+      <c r="S13" s="267"/>
+      <c r="T13" s="267"/>
+      <c r="U13" s="267"/>
+      <c r="V13" s="267"/>
+      <c r="W13" s="267"/>
+      <c r="X13" s="267"/>
+      <c r="Y13" s="267"/>
+      <c r="Z13" s="267"/>
+      <c r="AA13" s="267"/>
+      <c r="AB13" s="267"/>
+      <c r="AC13" s="267"/>
+      <c r="AD13" s="267"/>
+      <c r="AE13" s="268"/>
+      <c r="AF13" s="263"/>
+      <c r="AG13" s="264"/>
+      <c r="AH13" s="264"/>
+      <c r="AI13" s="265"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="200"/>
-      <c r="H14" s="205"/>
-      <c r="I14" s="201"/>
-      <c r="J14" s="206"/>
-      <c r="K14" s="207"/>
-      <c r="L14" s="207"/>
-      <c r="M14" s="207"/>
-      <c r="N14" s="207"/>
-      <c r="O14" s="207"/>
-      <c r="P14" s="208"/>
-      <c r="Q14" s="209"/>
-      <c r="R14" s="210"/>
-      <c r="S14" s="210"/>
-      <c r="T14" s="210"/>
-      <c r="U14" s="210"/>
-      <c r="V14" s="210"/>
-      <c r="W14" s="210"/>
-      <c r="X14" s="210"/>
-      <c r="Y14" s="210"/>
-      <c r="Z14" s="210"/>
-      <c r="AA14" s="210"/>
-      <c r="AB14" s="210"/>
-      <c r="AC14" s="210"/>
-      <c r="AD14" s="210"/>
-      <c r="AE14" s="211"/>
-      <c r="AF14" s="206"/>
-      <c r="AG14" s="207"/>
-      <c r="AH14" s="207"/>
-      <c r="AI14" s="208"/>
+      <c r="B14" s="257"/>
+      <c r="C14" s="258"/>
+      <c r="D14" s="259"/>
+      <c r="E14" s="260"/>
+      <c r="F14" s="261"/>
+      <c r="G14" s="257"/>
+      <c r="H14" s="262"/>
+      <c r="I14" s="258"/>
+      <c r="J14" s="263"/>
+      <c r="K14" s="264"/>
+      <c r="L14" s="264"/>
+      <c r="M14" s="264"/>
+      <c r="N14" s="264"/>
+      <c r="O14" s="264"/>
+      <c r="P14" s="265"/>
+      <c r="Q14" s="266"/>
+      <c r="R14" s="267"/>
+      <c r="S14" s="267"/>
+      <c r="T14" s="267"/>
+      <c r="U14" s="267"/>
+      <c r="V14" s="267"/>
+      <c r="W14" s="267"/>
+      <c r="X14" s="267"/>
+      <c r="Y14" s="267"/>
+      <c r="Z14" s="267"/>
+      <c r="AA14" s="267"/>
+      <c r="AB14" s="267"/>
+      <c r="AC14" s="267"/>
+      <c r="AD14" s="267"/>
+      <c r="AE14" s="268"/>
+      <c r="AF14" s="263"/>
+      <c r="AG14" s="264"/>
+      <c r="AH14" s="264"/>
+      <c r="AI14" s="265"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="203"/>
-      <c r="F15" s="204"/>
-      <c r="G15" s="200"/>
-      <c r="H15" s="205"/>
-      <c r="I15" s="201"/>
-      <c r="J15" s="206"/>
-      <c r="K15" s="207"/>
-      <c r="L15" s="207"/>
-      <c r="M15" s="207"/>
-      <c r="N15" s="207"/>
-      <c r="O15" s="207"/>
-      <c r="P15" s="208"/>
-      <c r="Q15" s="209"/>
-      <c r="R15" s="210"/>
-      <c r="S15" s="210"/>
-      <c r="T15" s="210"/>
-      <c r="U15" s="210"/>
-      <c r="V15" s="210"/>
-      <c r="W15" s="210"/>
-      <c r="X15" s="210"/>
-      <c r="Y15" s="210"/>
-      <c r="Z15" s="210"/>
-      <c r="AA15" s="210"/>
-      <c r="AB15" s="210"/>
-      <c r="AC15" s="210"/>
-      <c r="AD15" s="210"/>
-      <c r="AE15" s="211"/>
-      <c r="AF15" s="206"/>
-      <c r="AG15" s="207"/>
-      <c r="AH15" s="207"/>
-      <c r="AI15" s="208"/>
+      <c r="B15" s="257"/>
+      <c r="C15" s="258"/>
+      <c r="D15" s="259"/>
+      <c r="E15" s="260"/>
+      <c r="F15" s="261"/>
+      <c r="G15" s="257"/>
+      <c r="H15" s="262"/>
+      <c r="I15" s="258"/>
+      <c r="J15" s="263"/>
+      <c r="K15" s="264"/>
+      <c r="L15" s="264"/>
+      <c r="M15" s="264"/>
+      <c r="N15" s="264"/>
+      <c r="O15" s="264"/>
+      <c r="P15" s="265"/>
+      <c r="Q15" s="266"/>
+      <c r="R15" s="267"/>
+      <c r="S15" s="267"/>
+      <c r="T15" s="267"/>
+      <c r="U15" s="267"/>
+      <c r="V15" s="267"/>
+      <c r="W15" s="267"/>
+      <c r="X15" s="267"/>
+      <c r="Y15" s="267"/>
+      <c r="Z15" s="267"/>
+      <c r="AA15" s="267"/>
+      <c r="AB15" s="267"/>
+      <c r="AC15" s="267"/>
+      <c r="AD15" s="267"/>
+      <c r="AE15" s="268"/>
+      <c r="AF15" s="263"/>
+      <c r="AG15" s="264"/>
+      <c r="AH15" s="264"/>
+      <c r="AI15" s="265"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="202"/>
-      <c r="E16" s="203"/>
-      <c r="F16" s="204"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="205"/>
-      <c r="I16" s="201"/>
-      <c r="J16" s="206"/>
-      <c r="K16" s="207"/>
-      <c r="L16" s="207"/>
-      <c r="M16" s="207"/>
-      <c r="N16" s="207"/>
-      <c r="O16" s="207"/>
-      <c r="P16" s="208"/>
-      <c r="Q16" s="209"/>
-      <c r="R16" s="210"/>
-      <c r="S16" s="210"/>
-      <c r="T16" s="210"/>
-      <c r="U16" s="210"/>
-      <c r="V16" s="210"/>
-      <c r="W16" s="210"/>
-      <c r="X16" s="210"/>
-      <c r="Y16" s="210"/>
-      <c r="Z16" s="210"/>
-      <c r="AA16" s="210"/>
-      <c r="AB16" s="210"/>
-      <c r="AC16" s="210"/>
-      <c r="AD16" s="210"/>
-      <c r="AE16" s="211"/>
-      <c r="AF16" s="206"/>
-      <c r="AG16" s="207"/>
-      <c r="AH16" s="207"/>
-      <c r="AI16" s="208"/>
+      <c r="B16" s="257"/>
+      <c r="C16" s="258"/>
+      <c r="D16" s="259"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="261"/>
+      <c r="G16" s="257"/>
+      <c r="H16" s="262"/>
+      <c r="I16" s="258"/>
+      <c r="J16" s="263"/>
+      <c r="K16" s="264"/>
+      <c r="L16" s="264"/>
+      <c r="M16" s="264"/>
+      <c r="N16" s="264"/>
+      <c r="O16" s="264"/>
+      <c r="P16" s="265"/>
+      <c r="Q16" s="266"/>
+      <c r="R16" s="267"/>
+      <c r="S16" s="267"/>
+      <c r="T16" s="267"/>
+      <c r="U16" s="267"/>
+      <c r="V16" s="267"/>
+      <c r="W16" s="267"/>
+      <c r="X16" s="267"/>
+      <c r="Y16" s="267"/>
+      <c r="Z16" s="267"/>
+      <c r="AA16" s="267"/>
+      <c r="AB16" s="267"/>
+      <c r="AC16" s="267"/>
+      <c r="AD16" s="267"/>
+      <c r="AE16" s="268"/>
+      <c r="AF16" s="263"/>
+      <c r="AG16" s="264"/>
+      <c r="AH16" s="264"/>
+      <c r="AI16" s="265"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="200"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="202"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="204"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="205"/>
-      <c r="I17" s="201"/>
-      <c r="J17" s="206"/>
-      <c r="K17" s="207"/>
-      <c r="L17" s="207"/>
-      <c r="M17" s="207"/>
-      <c r="N17" s="207"/>
-      <c r="O17" s="207"/>
-      <c r="P17" s="208"/>
-      <c r="Q17" s="209"/>
-      <c r="R17" s="210"/>
-      <c r="S17" s="210"/>
-      <c r="T17" s="210"/>
-      <c r="U17" s="210"/>
-      <c r="V17" s="210"/>
-      <c r="W17" s="210"/>
-      <c r="X17" s="210"/>
-      <c r="Y17" s="210"/>
-      <c r="Z17" s="210"/>
-      <c r="AA17" s="210"/>
-      <c r="AB17" s="210"/>
-      <c r="AC17" s="210"/>
-      <c r="AD17" s="210"/>
-      <c r="AE17" s="211"/>
-      <c r="AF17" s="206"/>
-      <c r="AG17" s="207"/>
-      <c r="AH17" s="207"/>
-      <c r="AI17" s="208"/>
+      <c r="B17" s="257"/>
+      <c r="C17" s="258"/>
+      <c r="D17" s="259"/>
+      <c r="E17" s="260"/>
+      <c r="F17" s="261"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="262"/>
+      <c r="I17" s="258"/>
+      <c r="J17" s="263"/>
+      <c r="K17" s="264"/>
+      <c r="L17" s="264"/>
+      <c r="M17" s="264"/>
+      <c r="N17" s="264"/>
+      <c r="O17" s="264"/>
+      <c r="P17" s="265"/>
+      <c r="Q17" s="266"/>
+      <c r="R17" s="267"/>
+      <c r="S17" s="267"/>
+      <c r="T17" s="267"/>
+      <c r="U17" s="267"/>
+      <c r="V17" s="267"/>
+      <c r="W17" s="267"/>
+      <c r="X17" s="267"/>
+      <c r="Y17" s="267"/>
+      <c r="Z17" s="267"/>
+      <c r="AA17" s="267"/>
+      <c r="AB17" s="267"/>
+      <c r="AC17" s="267"/>
+      <c r="AD17" s="267"/>
+      <c r="AE17" s="268"/>
+      <c r="AF17" s="263"/>
+      <c r="AG17" s="264"/>
+      <c r="AH17" s="264"/>
+      <c r="AI17" s="265"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="200"/>
-      <c r="C18" s="201"/>
-      <c r="D18" s="202"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="204"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="205"/>
-      <c r="I18" s="201"/>
-      <c r="J18" s="206"/>
-      <c r="K18" s="207"/>
-      <c r="L18" s="207"/>
-      <c r="M18" s="207"/>
-      <c r="N18" s="207"/>
-      <c r="O18" s="207"/>
-      <c r="P18" s="208"/>
-      <c r="Q18" s="209"/>
-      <c r="R18" s="210"/>
-      <c r="S18" s="210"/>
-      <c r="T18" s="210"/>
-      <c r="U18" s="210"/>
-      <c r="V18" s="210"/>
-      <c r="W18" s="210"/>
-      <c r="X18" s="210"/>
-      <c r="Y18" s="210"/>
-      <c r="Z18" s="210"/>
-      <c r="AA18" s="210"/>
-      <c r="AB18" s="210"/>
-      <c r="AC18" s="210"/>
-      <c r="AD18" s="210"/>
-      <c r="AE18" s="211"/>
-      <c r="AF18" s="206"/>
-      <c r="AG18" s="207"/>
-      <c r="AH18" s="207"/>
-      <c r="AI18" s="208"/>
+      <c r="B18" s="257"/>
+      <c r="C18" s="258"/>
+      <c r="D18" s="259"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="261"/>
+      <c r="G18" s="257"/>
+      <c r="H18" s="262"/>
+      <c r="I18" s="258"/>
+      <c r="J18" s="263"/>
+      <c r="K18" s="264"/>
+      <c r="L18" s="264"/>
+      <c r="M18" s="264"/>
+      <c r="N18" s="264"/>
+      <c r="O18" s="264"/>
+      <c r="P18" s="265"/>
+      <c r="Q18" s="266"/>
+      <c r="R18" s="267"/>
+      <c r="S18" s="267"/>
+      <c r="T18" s="267"/>
+      <c r="U18" s="267"/>
+      <c r="V18" s="267"/>
+      <c r="W18" s="267"/>
+      <c r="X18" s="267"/>
+      <c r="Y18" s="267"/>
+      <c r="Z18" s="267"/>
+      <c r="AA18" s="267"/>
+      <c r="AB18" s="267"/>
+      <c r="AC18" s="267"/>
+      <c r="AD18" s="267"/>
+      <c r="AE18" s="268"/>
+      <c r="AF18" s="263"/>
+      <c r="AG18" s="264"/>
+      <c r="AH18" s="264"/>
+      <c r="AI18" s="265"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="200"/>
-      <c r="C19" s="201"/>
-      <c r="D19" s="202"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="204"/>
-      <c r="G19" s="200"/>
-      <c r="H19" s="205"/>
-      <c r="I19" s="201"/>
-      <c r="J19" s="206"/>
-      <c r="K19" s="207"/>
-      <c r="L19" s="207"/>
-      <c r="M19" s="207"/>
-      <c r="N19" s="207"/>
-      <c r="O19" s="207"/>
-      <c r="P19" s="208"/>
-      <c r="Q19" s="209"/>
-      <c r="R19" s="210"/>
-      <c r="S19" s="210"/>
-      <c r="T19" s="210"/>
-      <c r="U19" s="210"/>
-      <c r="V19" s="210"/>
-      <c r="W19" s="210"/>
-      <c r="X19" s="210"/>
-      <c r="Y19" s="210"/>
-      <c r="Z19" s="210"/>
-      <c r="AA19" s="210"/>
-      <c r="AB19" s="210"/>
-      <c r="AC19" s="210"/>
-      <c r="AD19" s="210"/>
-      <c r="AE19" s="211"/>
-      <c r="AF19" s="206"/>
-      <c r="AG19" s="207"/>
-      <c r="AH19" s="207"/>
-      <c r="AI19" s="208"/>
+      <c r="B19" s="257"/>
+      <c r="C19" s="258"/>
+      <c r="D19" s="259"/>
+      <c r="E19" s="260"/>
+      <c r="F19" s="261"/>
+      <c r="G19" s="257"/>
+      <c r="H19" s="262"/>
+      <c r="I19" s="258"/>
+      <c r="J19" s="263"/>
+      <c r="K19" s="264"/>
+      <c r="L19" s="264"/>
+      <c r="M19" s="264"/>
+      <c r="N19" s="264"/>
+      <c r="O19" s="264"/>
+      <c r="P19" s="265"/>
+      <c r="Q19" s="266"/>
+      <c r="R19" s="267"/>
+      <c r="S19" s="267"/>
+      <c r="T19" s="267"/>
+      <c r="U19" s="267"/>
+      <c r="V19" s="267"/>
+      <c r="W19" s="267"/>
+      <c r="X19" s="267"/>
+      <c r="Y19" s="267"/>
+      <c r="Z19" s="267"/>
+      <c r="AA19" s="267"/>
+      <c r="AB19" s="267"/>
+      <c r="AC19" s="267"/>
+      <c r="AD19" s="267"/>
+      <c r="AE19" s="268"/>
+      <c r="AF19" s="263"/>
+      <c r="AG19" s="264"/>
+      <c r="AH19" s="264"/>
+      <c r="AI19" s="265"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="200"/>
-      <c r="C20" s="201"/>
-      <c r="D20" s="202"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="204"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="205"/>
-      <c r="I20" s="201"/>
-      <c r="J20" s="206"/>
-      <c r="K20" s="207"/>
-      <c r="L20" s="207"/>
-      <c r="M20" s="207"/>
-      <c r="N20" s="207"/>
-      <c r="O20" s="207"/>
-      <c r="P20" s="208"/>
-      <c r="Q20" s="209"/>
-      <c r="R20" s="210"/>
-      <c r="S20" s="210"/>
-      <c r="T20" s="210"/>
-      <c r="U20" s="210"/>
-      <c r="V20" s="210"/>
-      <c r="W20" s="210"/>
-      <c r="X20" s="210"/>
-      <c r="Y20" s="210"/>
-      <c r="Z20" s="210"/>
-      <c r="AA20" s="210"/>
-      <c r="AB20" s="210"/>
-      <c r="AC20" s="210"/>
-      <c r="AD20" s="210"/>
-      <c r="AE20" s="211"/>
-      <c r="AF20" s="206"/>
-      <c r="AG20" s="207"/>
-      <c r="AH20" s="207"/>
-      <c r="AI20" s="208"/>
+      <c r="B20" s="257"/>
+      <c r="C20" s="258"/>
+      <c r="D20" s="259"/>
+      <c r="E20" s="260"/>
+      <c r="F20" s="261"/>
+      <c r="G20" s="257"/>
+      <c r="H20" s="262"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="263"/>
+      <c r="K20" s="264"/>
+      <c r="L20" s="264"/>
+      <c r="M20" s="264"/>
+      <c r="N20" s="264"/>
+      <c r="O20" s="264"/>
+      <c r="P20" s="265"/>
+      <c r="Q20" s="266"/>
+      <c r="R20" s="267"/>
+      <c r="S20" s="267"/>
+      <c r="T20" s="267"/>
+      <c r="U20" s="267"/>
+      <c r="V20" s="267"/>
+      <c r="W20" s="267"/>
+      <c r="X20" s="267"/>
+      <c r="Y20" s="267"/>
+      <c r="Z20" s="267"/>
+      <c r="AA20" s="267"/>
+      <c r="AB20" s="267"/>
+      <c r="AC20" s="267"/>
+      <c r="AD20" s="267"/>
+      <c r="AE20" s="268"/>
+      <c r="AF20" s="263"/>
+      <c r="AG20" s="264"/>
+      <c r="AH20" s="264"/>
+      <c r="AI20" s="265"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="200"/>
-      <c r="C21" s="201"/>
-      <c r="D21" s="202"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="204"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="205"/>
-      <c r="I21" s="201"/>
-      <c r="J21" s="206"/>
-      <c r="K21" s="207"/>
-      <c r="L21" s="207"/>
-      <c r="M21" s="207"/>
-      <c r="N21" s="207"/>
-      <c r="O21" s="207"/>
-      <c r="P21" s="208"/>
-      <c r="Q21" s="209"/>
-      <c r="R21" s="210"/>
-      <c r="S21" s="210"/>
-      <c r="T21" s="210"/>
-      <c r="U21" s="210"/>
-      <c r="V21" s="210"/>
-      <c r="W21" s="210"/>
-      <c r="X21" s="210"/>
-      <c r="Y21" s="210"/>
-      <c r="Z21" s="210"/>
-      <c r="AA21" s="210"/>
-      <c r="AB21" s="210"/>
-      <c r="AC21" s="210"/>
-      <c r="AD21" s="210"/>
-      <c r="AE21" s="211"/>
-      <c r="AF21" s="206"/>
-      <c r="AG21" s="207"/>
-      <c r="AH21" s="207"/>
-      <c r="AI21" s="208"/>
+      <c r="B21" s="257"/>
+      <c r="C21" s="258"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="260"/>
+      <c r="F21" s="261"/>
+      <c r="G21" s="257"/>
+      <c r="H21" s="262"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="263"/>
+      <c r="K21" s="264"/>
+      <c r="L21" s="264"/>
+      <c r="M21" s="264"/>
+      <c r="N21" s="264"/>
+      <c r="O21" s="264"/>
+      <c r="P21" s="265"/>
+      <c r="Q21" s="266"/>
+      <c r="R21" s="267"/>
+      <c r="S21" s="267"/>
+      <c r="T21" s="267"/>
+      <c r="U21" s="267"/>
+      <c r="V21" s="267"/>
+      <c r="W21" s="267"/>
+      <c r="X21" s="267"/>
+      <c r="Y21" s="267"/>
+      <c r="Z21" s="267"/>
+      <c r="AA21" s="267"/>
+      <c r="AB21" s="267"/>
+      <c r="AC21" s="267"/>
+      <c r="AD21" s="267"/>
+      <c r="AE21" s="268"/>
+      <c r="AF21" s="263"/>
+      <c r="AG21" s="264"/>
+      <c r="AH21" s="264"/>
+      <c r="AI21" s="265"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="200"/>
-      <c r="C22" s="201"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="204"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="205"/>
-      <c r="I22" s="201"/>
-      <c r="J22" s="206"/>
-      <c r="K22" s="207"/>
-      <c r="L22" s="207"/>
-      <c r="M22" s="207"/>
-      <c r="N22" s="207"/>
-      <c r="O22" s="207"/>
-      <c r="P22" s="208"/>
-      <c r="Q22" s="209"/>
-      <c r="R22" s="210"/>
-      <c r="S22" s="210"/>
-      <c r="T22" s="210"/>
-      <c r="U22" s="210"/>
-      <c r="V22" s="210"/>
-      <c r="W22" s="210"/>
-      <c r="X22" s="210"/>
-      <c r="Y22" s="210"/>
-      <c r="Z22" s="210"/>
-      <c r="AA22" s="210"/>
-      <c r="AB22" s="210"/>
-      <c r="AC22" s="210"/>
-      <c r="AD22" s="210"/>
-      <c r="AE22" s="211"/>
-      <c r="AF22" s="206"/>
-      <c r="AG22" s="207"/>
-      <c r="AH22" s="207"/>
-      <c r="AI22" s="208"/>
+      <c r="B22" s="257"/>
+      <c r="C22" s="258"/>
+      <c r="D22" s="259"/>
+      <c r="E22" s="260"/>
+      <c r="F22" s="261"/>
+      <c r="G22" s="257"/>
+      <c r="H22" s="262"/>
+      <c r="I22" s="258"/>
+      <c r="J22" s="263"/>
+      <c r="K22" s="264"/>
+      <c r="L22" s="264"/>
+      <c r="M22" s="264"/>
+      <c r="N22" s="264"/>
+      <c r="O22" s="264"/>
+      <c r="P22" s="265"/>
+      <c r="Q22" s="266"/>
+      <c r="R22" s="267"/>
+      <c r="S22" s="267"/>
+      <c r="T22" s="267"/>
+      <c r="U22" s="267"/>
+      <c r="V22" s="267"/>
+      <c r="W22" s="267"/>
+      <c r="X22" s="267"/>
+      <c r="Y22" s="267"/>
+      <c r="Z22" s="267"/>
+      <c r="AA22" s="267"/>
+      <c r="AB22" s="267"/>
+      <c r="AC22" s="267"/>
+      <c r="AD22" s="267"/>
+      <c r="AE22" s="268"/>
+      <c r="AF22" s="263"/>
+      <c r="AG22" s="264"/>
+      <c r="AH22" s="264"/>
+      <c r="AI22" s="265"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="200"/>
-      <c r="C23" s="201"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="203"/>
-      <c r="F23" s="204"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="205"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="206"/>
-      <c r="K23" s="207"/>
-      <c r="L23" s="207"/>
-      <c r="M23" s="207"/>
-      <c r="N23" s="207"/>
-      <c r="O23" s="207"/>
-      <c r="P23" s="208"/>
-      <c r="Q23" s="209"/>
-      <c r="R23" s="210"/>
-      <c r="S23" s="210"/>
-      <c r="T23" s="210"/>
-      <c r="U23" s="210"/>
-      <c r="V23" s="210"/>
-      <c r="W23" s="210"/>
-      <c r="X23" s="210"/>
-      <c r="Y23" s="210"/>
-      <c r="Z23" s="210"/>
-      <c r="AA23" s="210"/>
-      <c r="AB23" s="210"/>
-      <c r="AC23" s="210"/>
-      <c r="AD23" s="210"/>
-      <c r="AE23" s="211"/>
-      <c r="AF23" s="206"/>
-      <c r="AG23" s="207"/>
-      <c r="AH23" s="207"/>
-      <c r="AI23" s="208"/>
+      <c r="B23" s="257"/>
+      <c r="C23" s="258"/>
+      <c r="D23" s="259"/>
+      <c r="E23" s="260"/>
+      <c r="F23" s="261"/>
+      <c r="G23" s="257"/>
+      <c r="H23" s="262"/>
+      <c r="I23" s="258"/>
+      <c r="J23" s="263"/>
+      <c r="K23" s="264"/>
+      <c r="L23" s="264"/>
+      <c r="M23" s="264"/>
+      <c r="N23" s="264"/>
+      <c r="O23" s="264"/>
+      <c r="P23" s="265"/>
+      <c r="Q23" s="266"/>
+      <c r="R23" s="267"/>
+      <c r="S23" s="267"/>
+      <c r="T23" s="267"/>
+      <c r="U23" s="267"/>
+      <c r="V23" s="267"/>
+      <c r="W23" s="267"/>
+      <c r="X23" s="267"/>
+      <c r="Y23" s="267"/>
+      <c r="Z23" s="267"/>
+      <c r="AA23" s="267"/>
+      <c r="AB23" s="267"/>
+      <c r="AC23" s="267"/>
+      <c r="AD23" s="267"/>
+      <c r="AE23" s="268"/>
+      <c r="AF23" s="263"/>
+      <c r="AG23" s="264"/>
+      <c r="AH23" s="264"/>
+      <c r="AI23" s="265"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="200"/>
-      <c r="C24" s="201"/>
-      <c r="D24" s="202"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="204"/>
-      <c r="G24" s="200"/>
-      <c r="H24" s="205"/>
-      <c r="I24" s="201"/>
-      <c r="J24" s="206"/>
-      <c r="K24" s="207"/>
-      <c r="L24" s="207"/>
-      <c r="M24" s="207"/>
-      <c r="N24" s="207"/>
-      <c r="O24" s="207"/>
-      <c r="P24" s="208"/>
-      <c r="Q24" s="209"/>
-      <c r="R24" s="210"/>
-      <c r="S24" s="210"/>
-      <c r="T24" s="210"/>
-      <c r="U24" s="210"/>
-      <c r="V24" s="210"/>
-      <c r="W24" s="210"/>
-      <c r="X24" s="210"/>
-      <c r="Y24" s="210"/>
-      <c r="Z24" s="210"/>
-      <c r="AA24" s="210"/>
-      <c r="AB24" s="210"/>
-      <c r="AC24" s="210"/>
-      <c r="AD24" s="210"/>
-      <c r="AE24" s="211"/>
-      <c r="AF24" s="206"/>
-      <c r="AG24" s="207"/>
-      <c r="AH24" s="207"/>
-      <c r="AI24" s="208"/>
+      <c r="B24" s="257"/>
+      <c r="C24" s="258"/>
+      <c r="D24" s="259"/>
+      <c r="E24" s="260"/>
+      <c r="F24" s="261"/>
+      <c r="G24" s="257"/>
+      <c r="H24" s="262"/>
+      <c r="I24" s="258"/>
+      <c r="J24" s="263"/>
+      <c r="K24" s="264"/>
+      <c r="L24" s="264"/>
+      <c r="M24" s="264"/>
+      <c r="N24" s="264"/>
+      <c r="O24" s="264"/>
+      <c r="P24" s="265"/>
+      <c r="Q24" s="266"/>
+      <c r="R24" s="267"/>
+      <c r="S24" s="267"/>
+      <c r="T24" s="267"/>
+      <c r="U24" s="267"/>
+      <c r="V24" s="267"/>
+      <c r="W24" s="267"/>
+      <c r="X24" s="267"/>
+      <c r="Y24" s="267"/>
+      <c r="Z24" s="267"/>
+      <c r="AA24" s="267"/>
+      <c r="AB24" s="267"/>
+      <c r="AC24" s="267"/>
+      <c r="AD24" s="267"/>
+      <c r="AE24" s="268"/>
+      <c r="AF24" s="263"/>
+      <c r="AG24" s="264"/>
+      <c r="AH24" s="264"/>
+      <c r="AI24" s="265"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="200"/>
-      <c r="C25" s="201"/>
-      <c r="D25" s="202"/>
-      <c r="E25" s="203"/>
-      <c r="F25" s="204"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="205"/>
-      <c r="I25" s="201"/>
-      <c r="J25" s="206"/>
-      <c r="K25" s="207"/>
-      <c r="L25" s="207"/>
-      <c r="M25" s="207"/>
-      <c r="N25" s="207"/>
-      <c r="O25" s="207"/>
-      <c r="P25" s="208"/>
-      <c r="Q25" s="209"/>
-      <c r="R25" s="210"/>
-      <c r="S25" s="210"/>
-      <c r="T25" s="210"/>
-      <c r="U25" s="210"/>
-      <c r="V25" s="210"/>
-      <c r="W25" s="210"/>
-      <c r="X25" s="210"/>
-      <c r="Y25" s="210"/>
-      <c r="Z25" s="210"/>
-      <c r="AA25" s="210"/>
-      <c r="AB25" s="210"/>
-      <c r="AC25" s="210"/>
-      <c r="AD25" s="210"/>
-      <c r="AE25" s="211"/>
-      <c r="AF25" s="206"/>
-      <c r="AG25" s="207"/>
-      <c r="AH25" s="207"/>
-      <c r="AI25" s="208"/>
+      <c r="B25" s="257"/>
+      <c r="C25" s="258"/>
+      <c r="D25" s="259"/>
+      <c r="E25" s="260"/>
+      <c r="F25" s="261"/>
+      <c r="G25" s="257"/>
+      <c r="H25" s="262"/>
+      <c r="I25" s="258"/>
+      <c r="J25" s="263"/>
+      <c r="K25" s="264"/>
+      <c r="L25" s="264"/>
+      <c r="M25" s="264"/>
+      <c r="N25" s="264"/>
+      <c r="O25" s="264"/>
+      <c r="P25" s="265"/>
+      <c r="Q25" s="266"/>
+      <c r="R25" s="267"/>
+      <c r="S25" s="267"/>
+      <c r="T25" s="267"/>
+      <c r="U25" s="267"/>
+      <c r="V25" s="267"/>
+      <c r="W25" s="267"/>
+      <c r="X25" s="267"/>
+      <c r="Y25" s="267"/>
+      <c r="Z25" s="267"/>
+      <c r="AA25" s="267"/>
+      <c r="AB25" s="267"/>
+      <c r="AC25" s="267"/>
+      <c r="AD25" s="267"/>
+      <c r="AE25" s="268"/>
+      <c r="AF25" s="263"/>
+      <c r="AG25" s="264"/>
+      <c r="AH25" s="264"/>
+      <c r="AI25" s="265"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="200"/>
-      <c r="C26" s="201"/>
-      <c r="D26" s="202"/>
-      <c r="E26" s="203"/>
-      <c r="F26" s="204"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="205"/>
-      <c r="I26" s="201"/>
-      <c r="J26" s="206"/>
-      <c r="K26" s="207"/>
-      <c r="L26" s="207"/>
-      <c r="M26" s="207"/>
-      <c r="N26" s="207"/>
-      <c r="O26" s="207"/>
-      <c r="P26" s="208"/>
-      <c r="Q26" s="209"/>
-      <c r="R26" s="210"/>
-      <c r="S26" s="210"/>
-      <c r="T26" s="210"/>
-      <c r="U26" s="210"/>
-      <c r="V26" s="210"/>
-      <c r="W26" s="210"/>
-      <c r="X26" s="210"/>
-      <c r="Y26" s="210"/>
-      <c r="Z26" s="210"/>
-      <c r="AA26" s="210"/>
-      <c r="AB26" s="210"/>
-      <c r="AC26" s="210"/>
-      <c r="AD26" s="210"/>
-      <c r="AE26" s="211"/>
-      <c r="AF26" s="206"/>
-      <c r="AG26" s="207"/>
-      <c r="AH26" s="207"/>
-      <c r="AI26" s="208"/>
+      <c r="B26" s="257"/>
+      <c r="C26" s="258"/>
+      <c r="D26" s="259"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="261"/>
+      <c r="G26" s="257"/>
+      <c r="H26" s="262"/>
+      <c r="I26" s="258"/>
+      <c r="J26" s="263"/>
+      <c r="K26" s="264"/>
+      <c r="L26" s="264"/>
+      <c r="M26" s="264"/>
+      <c r="N26" s="264"/>
+      <c r="O26" s="264"/>
+      <c r="P26" s="265"/>
+      <c r="Q26" s="266"/>
+      <c r="R26" s="267"/>
+      <c r="S26" s="267"/>
+      <c r="T26" s="267"/>
+      <c r="U26" s="267"/>
+      <c r="V26" s="267"/>
+      <c r="W26" s="267"/>
+      <c r="X26" s="267"/>
+      <c r="Y26" s="267"/>
+      <c r="Z26" s="267"/>
+      <c r="AA26" s="267"/>
+      <c r="AB26" s="267"/>
+      <c r="AC26" s="267"/>
+      <c r="AD26" s="267"/>
+      <c r="AE26" s="268"/>
+      <c r="AF26" s="263"/>
+      <c r="AG26" s="264"/>
+      <c r="AH26" s="264"/>
+      <c r="AI26" s="265"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="200"/>
-      <c r="C27" s="201"/>
-      <c r="D27" s="202"/>
-      <c r="E27" s="203"/>
-      <c r="F27" s="204"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="205"/>
-      <c r="I27" s="201"/>
-      <c r="J27" s="206"/>
-      <c r="K27" s="207"/>
-      <c r="L27" s="207"/>
-      <c r="M27" s="207"/>
-      <c r="N27" s="207"/>
-      <c r="O27" s="207"/>
-      <c r="P27" s="208"/>
-      <c r="Q27" s="209"/>
-      <c r="R27" s="210"/>
-      <c r="S27" s="210"/>
-      <c r="T27" s="210"/>
-      <c r="U27" s="210"/>
-      <c r="V27" s="210"/>
-      <c r="W27" s="210"/>
-      <c r="X27" s="210"/>
-      <c r="Y27" s="210"/>
-      <c r="Z27" s="210"/>
-      <c r="AA27" s="210"/>
-      <c r="AB27" s="210"/>
-      <c r="AC27" s="210"/>
-      <c r="AD27" s="210"/>
-      <c r="AE27" s="211"/>
-      <c r="AF27" s="206"/>
-      <c r="AG27" s="207"/>
-      <c r="AH27" s="207"/>
-      <c r="AI27" s="208"/>
+      <c r="B27" s="257"/>
+      <c r="C27" s="258"/>
+      <c r="D27" s="259"/>
+      <c r="E27" s="260"/>
+      <c r="F27" s="261"/>
+      <c r="G27" s="257"/>
+      <c r="H27" s="262"/>
+      <c r="I27" s="258"/>
+      <c r="J27" s="263"/>
+      <c r="K27" s="264"/>
+      <c r="L27" s="264"/>
+      <c r="M27" s="264"/>
+      <c r="N27" s="264"/>
+      <c r="O27" s="264"/>
+      <c r="P27" s="265"/>
+      <c r="Q27" s="266"/>
+      <c r="R27" s="267"/>
+      <c r="S27" s="267"/>
+      <c r="T27" s="267"/>
+      <c r="U27" s="267"/>
+      <c r="V27" s="267"/>
+      <c r="W27" s="267"/>
+      <c r="X27" s="267"/>
+      <c r="Y27" s="267"/>
+      <c r="Z27" s="267"/>
+      <c r="AA27" s="267"/>
+      <c r="AB27" s="267"/>
+      <c r="AC27" s="267"/>
+      <c r="AD27" s="267"/>
+      <c r="AE27" s="268"/>
+      <c r="AF27" s="263"/>
+      <c r="AG27" s="264"/>
+      <c r="AH27" s="264"/>
+      <c r="AI27" s="265"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="200"/>
-      <c r="C28" s="201"/>
-      <c r="D28" s="202"/>
-      <c r="E28" s="203"/>
-      <c r="F28" s="204"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="205"/>
-      <c r="I28" s="201"/>
-      <c r="J28" s="206"/>
-      <c r="K28" s="207"/>
-      <c r="L28" s="207"/>
-      <c r="M28" s="207"/>
-      <c r="N28" s="207"/>
-      <c r="O28" s="207"/>
-      <c r="P28" s="208"/>
-      <c r="Q28" s="209"/>
-      <c r="R28" s="210"/>
-      <c r="S28" s="210"/>
-      <c r="T28" s="210"/>
-      <c r="U28" s="210"/>
-      <c r="V28" s="210"/>
-      <c r="W28" s="210"/>
-      <c r="X28" s="210"/>
-      <c r="Y28" s="210"/>
-      <c r="Z28" s="210"/>
-      <c r="AA28" s="210"/>
-      <c r="AB28" s="210"/>
-      <c r="AC28" s="210"/>
-      <c r="AD28" s="210"/>
-      <c r="AE28" s="211"/>
-      <c r="AF28" s="206"/>
-      <c r="AG28" s="207"/>
-      <c r="AH28" s="207"/>
-      <c r="AI28" s="208"/>
+      <c r="B28" s="257"/>
+      <c r="C28" s="258"/>
+      <c r="D28" s="259"/>
+      <c r="E28" s="260"/>
+      <c r="F28" s="261"/>
+      <c r="G28" s="257"/>
+      <c r="H28" s="262"/>
+      <c r="I28" s="258"/>
+      <c r="J28" s="263"/>
+      <c r="K28" s="264"/>
+      <c r="L28" s="264"/>
+      <c r="M28" s="264"/>
+      <c r="N28" s="264"/>
+      <c r="O28" s="264"/>
+      <c r="P28" s="265"/>
+      <c r="Q28" s="266"/>
+      <c r="R28" s="267"/>
+      <c r="S28" s="267"/>
+      <c r="T28" s="267"/>
+      <c r="U28" s="267"/>
+      <c r="V28" s="267"/>
+      <c r="W28" s="267"/>
+      <c r="X28" s="267"/>
+      <c r="Y28" s="267"/>
+      <c r="Z28" s="267"/>
+      <c r="AA28" s="267"/>
+      <c r="AB28" s="267"/>
+      <c r="AC28" s="267"/>
+      <c r="AD28" s="267"/>
+      <c r="AE28" s="268"/>
+      <c r="AF28" s="263"/>
+      <c r="AG28" s="264"/>
+      <c r="AH28" s="264"/>
+      <c r="AI28" s="265"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="200"/>
-      <c r="C29" s="201"/>
-      <c r="D29" s="202"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="204"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="205"/>
-      <c r="I29" s="201"/>
-      <c r="J29" s="206"/>
-      <c r="K29" s="207"/>
-      <c r="L29" s="207"/>
-      <c r="M29" s="207"/>
-      <c r="N29" s="207"/>
-      <c r="O29" s="207"/>
-      <c r="P29" s="208"/>
-      <c r="Q29" s="209"/>
-      <c r="R29" s="210"/>
-      <c r="S29" s="210"/>
-      <c r="T29" s="210"/>
-      <c r="U29" s="210"/>
-      <c r="V29" s="210"/>
-      <c r="W29" s="210"/>
-      <c r="X29" s="210"/>
-      <c r="Y29" s="210"/>
-      <c r="Z29" s="210"/>
-      <c r="AA29" s="210"/>
-      <c r="AB29" s="210"/>
-      <c r="AC29" s="210"/>
-      <c r="AD29" s="210"/>
-      <c r="AE29" s="211"/>
-      <c r="AF29" s="206"/>
-      <c r="AG29" s="207"/>
-      <c r="AH29" s="207"/>
-      <c r="AI29" s="208"/>
+      <c r="B29" s="257"/>
+      <c r="C29" s="258"/>
+      <c r="D29" s="259"/>
+      <c r="E29" s="260"/>
+      <c r="F29" s="261"/>
+      <c r="G29" s="257"/>
+      <c r="H29" s="262"/>
+      <c r="I29" s="258"/>
+      <c r="J29" s="263"/>
+      <c r="K29" s="264"/>
+      <c r="L29" s="264"/>
+      <c r="M29" s="264"/>
+      <c r="N29" s="264"/>
+      <c r="O29" s="264"/>
+      <c r="P29" s="265"/>
+      <c r="Q29" s="266"/>
+      <c r="R29" s="267"/>
+      <c r="S29" s="267"/>
+      <c r="T29" s="267"/>
+      <c r="U29" s="267"/>
+      <c r="V29" s="267"/>
+      <c r="W29" s="267"/>
+      <c r="X29" s="267"/>
+      <c r="Y29" s="267"/>
+      <c r="Z29" s="267"/>
+      <c r="AA29" s="267"/>
+      <c r="AB29" s="267"/>
+      <c r="AC29" s="267"/>
+      <c r="AD29" s="267"/>
+      <c r="AE29" s="268"/>
+      <c r="AF29" s="263"/>
+      <c r="AG29" s="264"/>
+      <c r="AH29" s="264"/>
+      <c r="AI29" s="265"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="200"/>
-      <c r="C30" s="201"/>
-      <c r="D30" s="202"/>
-      <c r="E30" s="203"/>
-      <c r="F30" s="204"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="205"/>
-      <c r="I30" s="201"/>
-      <c r="J30" s="206"/>
-      <c r="K30" s="207"/>
-      <c r="L30" s="207"/>
-      <c r="M30" s="207"/>
-      <c r="N30" s="207"/>
-      <c r="O30" s="207"/>
-      <c r="P30" s="208"/>
-      <c r="Q30" s="209"/>
-      <c r="R30" s="210"/>
-      <c r="S30" s="210"/>
-      <c r="T30" s="210"/>
-      <c r="U30" s="210"/>
-      <c r="V30" s="210"/>
-      <c r="W30" s="210"/>
-      <c r="X30" s="210"/>
-      <c r="Y30" s="210"/>
-      <c r="Z30" s="210"/>
-      <c r="AA30" s="210"/>
-      <c r="AB30" s="210"/>
-      <c r="AC30" s="210"/>
-      <c r="AD30" s="210"/>
-      <c r="AE30" s="211"/>
-      <c r="AF30" s="206"/>
-      <c r="AG30" s="207"/>
-      <c r="AH30" s="207"/>
-      <c r="AI30" s="208"/>
+      <c r="B30" s="257"/>
+      <c r="C30" s="258"/>
+      <c r="D30" s="259"/>
+      <c r="E30" s="260"/>
+      <c r="F30" s="261"/>
+      <c r="G30" s="257"/>
+      <c r="H30" s="262"/>
+      <c r="I30" s="258"/>
+      <c r="J30" s="263"/>
+      <c r="K30" s="264"/>
+      <c r="L30" s="264"/>
+      <c r="M30" s="264"/>
+      <c r="N30" s="264"/>
+      <c r="O30" s="264"/>
+      <c r="P30" s="265"/>
+      <c r="Q30" s="266"/>
+      <c r="R30" s="267"/>
+      <c r="S30" s="267"/>
+      <c r="T30" s="267"/>
+      <c r="U30" s="267"/>
+      <c r="V30" s="267"/>
+      <c r="W30" s="267"/>
+      <c r="X30" s="267"/>
+      <c r="Y30" s="267"/>
+      <c r="Z30" s="267"/>
+      <c r="AA30" s="267"/>
+      <c r="AB30" s="267"/>
+      <c r="AC30" s="267"/>
+      <c r="AD30" s="267"/>
+      <c r="AE30" s="268"/>
+      <c r="AF30" s="263"/>
+      <c r="AG30" s="264"/>
+      <c r="AH30" s="264"/>
+      <c r="AI30" s="265"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="200"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="202"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="204"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="205"/>
-      <c r="I31" s="201"/>
-      <c r="J31" s="206"/>
-      <c r="K31" s="207"/>
-      <c r="L31" s="207"/>
-      <c r="M31" s="207"/>
-      <c r="N31" s="207"/>
-      <c r="O31" s="207"/>
-      <c r="P31" s="208"/>
-      <c r="Q31" s="209"/>
-      <c r="R31" s="210"/>
-      <c r="S31" s="210"/>
-      <c r="T31" s="210"/>
-      <c r="U31" s="210"/>
-      <c r="V31" s="210"/>
-      <c r="W31" s="210"/>
-      <c r="X31" s="210"/>
-      <c r="Y31" s="210"/>
-      <c r="Z31" s="210"/>
-      <c r="AA31" s="210"/>
-      <c r="AB31" s="210"/>
-      <c r="AC31" s="210"/>
-      <c r="AD31" s="210"/>
-      <c r="AE31" s="211"/>
-      <c r="AF31" s="206"/>
-      <c r="AG31" s="207"/>
-      <c r="AH31" s="207"/>
-      <c r="AI31" s="208"/>
+      <c r="B31" s="257"/>
+      <c r="C31" s="258"/>
+      <c r="D31" s="259"/>
+      <c r="E31" s="260"/>
+      <c r="F31" s="261"/>
+      <c r="G31" s="257"/>
+      <c r="H31" s="262"/>
+      <c r="I31" s="258"/>
+      <c r="J31" s="263"/>
+      <c r="K31" s="264"/>
+      <c r="L31" s="264"/>
+      <c r="M31" s="264"/>
+      <c r="N31" s="264"/>
+      <c r="O31" s="264"/>
+      <c r="P31" s="265"/>
+      <c r="Q31" s="266"/>
+      <c r="R31" s="267"/>
+      <c r="S31" s="267"/>
+      <c r="T31" s="267"/>
+      <c r="U31" s="267"/>
+      <c r="V31" s="267"/>
+      <c r="W31" s="267"/>
+      <c r="X31" s="267"/>
+      <c r="Y31" s="267"/>
+      <c r="Z31" s="267"/>
+      <c r="AA31" s="267"/>
+      <c r="AB31" s="267"/>
+      <c r="AC31" s="267"/>
+      <c r="AD31" s="267"/>
+      <c r="AE31" s="268"/>
+      <c r="AF31" s="263"/>
+      <c r="AG31" s="264"/>
+      <c r="AH31" s="264"/>
+      <c r="AI31" s="265"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="200"/>
-      <c r="C32" s="201"/>
-      <c r="D32" s="202"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="204"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="205"/>
-      <c r="I32" s="201"/>
-      <c r="J32" s="206"/>
-      <c r="K32" s="212"/>
-      <c r="L32" s="207"/>
-      <c r="M32" s="207"/>
-      <c r="N32" s="207"/>
-      <c r="O32" s="207"/>
-      <c r="P32" s="208"/>
-      <c r="Q32" s="209"/>
-      <c r="R32" s="210"/>
-      <c r="S32" s="210"/>
-      <c r="T32" s="210"/>
-      <c r="U32" s="210"/>
-      <c r="V32" s="210"/>
-      <c r="W32" s="210"/>
-      <c r="X32" s="210"/>
-      <c r="Y32" s="210"/>
-      <c r="Z32" s="210"/>
-      <c r="AA32" s="210"/>
-      <c r="AB32" s="210"/>
-      <c r="AC32" s="210"/>
-      <c r="AD32" s="210"/>
-      <c r="AE32" s="211"/>
-      <c r="AF32" s="206"/>
-      <c r="AG32" s="207"/>
-      <c r="AH32" s="207"/>
-      <c r="AI32" s="208"/>
+      <c r="B32" s="257"/>
+      <c r="C32" s="258"/>
+      <c r="D32" s="259"/>
+      <c r="E32" s="260"/>
+      <c r="F32" s="261"/>
+      <c r="G32" s="257"/>
+      <c r="H32" s="262"/>
+      <c r="I32" s="258"/>
+      <c r="J32" s="263"/>
+      <c r="K32" s="269"/>
+      <c r="L32" s="264"/>
+      <c r="M32" s="264"/>
+      <c r="N32" s="264"/>
+      <c r="O32" s="264"/>
+      <c r="P32" s="265"/>
+      <c r="Q32" s="266"/>
+      <c r="R32" s="267"/>
+      <c r="S32" s="267"/>
+      <c r="T32" s="267"/>
+      <c r="U32" s="267"/>
+      <c r="V32" s="267"/>
+      <c r="W32" s="267"/>
+      <c r="X32" s="267"/>
+      <c r="Y32" s="267"/>
+      <c r="Z32" s="267"/>
+      <c r="AA32" s="267"/>
+      <c r="AB32" s="267"/>
+      <c r="AC32" s="267"/>
+      <c r="AD32" s="267"/>
+      <c r="AE32" s="268"/>
+      <c r="AF32" s="263"/>
+      <c r="AG32" s="264"/>
+      <c r="AH32" s="264"/>
+      <c r="AI32" s="265"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="200"/>
-      <c r="C33" s="201"/>
-      <c r="D33" s="202"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="204"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="205"/>
-      <c r="I33" s="201"/>
-      <c r="J33" s="206"/>
-      <c r="K33" s="207"/>
-      <c r="L33" s="207"/>
-      <c r="M33" s="207"/>
-      <c r="N33" s="207"/>
-      <c r="O33" s="207"/>
-      <c r="P33" s="208"/>
-      <c r="Q33" s="209"/>
-      <c r="R33" s="210"/>
-      <c r="S33" s="210"/>
-      <c r="T33" s="210"/>
-      <c r="U33" s="210"/>
-      <c r="V33" s="210"/>
-      <c r="W33" s="210"/>
-      <c r="X33" s="210"/>
-      <c r="Y33" s="210"/>
-      <c r="Z33" s="210"/>
-      <c r="AA33" s="210"/>
-      <c r="AB33" s="210"/>
-      <c r="AC33" s="210"/>
-      <c r="AD33" s="210"/>
-      <c r="AE33" s="211"/>
-      <c r="AF33" s="206"/>
-      <c r="AG33" s="207"/>
-      <c r="AH33" s="207"/>
-      <c r="AI33" s="208"/>
+      <c r="B33" s="257"/>
+      <c r="C33" s="258"/>
+      <c r="D33" s="259"/>
+      <c r="E33" s="260"/>
+      <c r="F33" s="261"/>
+      <c r="G33" s="257"/>
+      <c r="H33" s="262"/>
+      <c r="I33" s="258"/>
+      <c r="J33" s="263"/>
+      <c r="K33" s="264"/>
+      <c r="L33" s="264"/>
+      <c r="M33" s="264"/>
+      <c r="N33" s="264"/>
+      <c r="O33" s="264"/>
+      <c r="P33" s="265"/>
+      <c r="Q33" s="266"/>
+      <c r="R33" s="267"/>
+      <c r="S33" s="267"/>
+      <c r="T33" s="267"/>
+      <c r="U33" s="267"/>
+      <c r="V33" s="267"/>
+      <c r="W33" s="267"/>
+      <c r="X33" s="267"/>
+      <c r="Y33" s="267"/>
+      <c r="Z33" s="267"/>
+      <c r="AA33" s="267"/>
+      <c r="AB33" s="267"/>
+      <c r="AC33" s="267"/>
+      <c r="AD33" s="267"/>
+      <c r="AE33" s="268"/>
+      <c r="AF33" s="263"/>
+      <c r="AG33" s="264"/>
+      <c r="AH33" s="264"/>
+      <c r="AI33" s="265"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -13901,161 +14053,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -24681,7 +24678,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>537</v>
+        <v>64</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>21</v>
@@ -24691,7 +24688,9 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="11.5" thickBot="1">
-      <c r="A8" s="30"/>
+      <c r="A8" s="30" t="s">
+        <v>537</v>
+      </c>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
       <c r="D8" s="31"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1959350-7755-46C6-8251-1CA889009C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305B9EE1-FD87-4ECC-A15F-F443E5861863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,18 +11,18 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="XxxAction_クラス単体" sheetId="23" r:id="rId3"/>
-    <sheet name="XxxAction_リクエスト単体" sheetId="24" r:id="rId4"/>
+    <sheet name="XXX_リクエスト単体" sheetId="24" r:id="rId4"/>
     <sheet name="取引単体" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XXX_リクエスト単体!$A$10:$R$311</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XxxAction_リクエスト単体!$A$10:$R$311</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$296</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$O$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">XXX_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">XxxAction_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -8260,6 +8260,108 @@
     <xf numFmtId="31" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="11" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8366,108 +8468,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="29" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="28" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12646,57 +12646,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="240" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="208"/>
-      <c r="E1" s="209" t="s">
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="243" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="210"/>
-      <c r="G1" s="210"/>
-      <c r="H1" s="210"/>
-      <c r="I1" s="210"/>
-      <c r="J1" s="210"/>
-      <c r="K1" s="210"/>
-      <c r="L1" s="210"/>
-      <c r="M1" s="210"/>
-      <c r="N1" s="211"/>
-      <c r="O1" s="215" t="s">
+      <c r="F1" s="244"/>
+      <c r="G1" s="244"/>
+      <c r="H1" s="244"/>
+      <c r="I1" s="244"/>
+      <c r="J1" s="244"/>
+      <c r="K1" s="244"/>
+      <c r="L1" s="244"/>
+      <c r="M1" s="244"/>
+      <c r="N1" s="245"/>
+      <c r="O1" s="249" t="s">
         <v>32</v>
       </c>
-      <c r="P1" s="216"/>
-      <c r="Q1" s="216"/>
-      <c r="R1" s="217"/>
-      <c r="S1" s="224" t="s">
+      <c r="P1" s="250"/>
+      <c r="Q1" s="250"/>
+      <c r="R1" s="251"/>
+      <c r="S1" s="258" t="s">
         <v>536</v>
       </c>
-      <c r="T1" s="225"/>
-      <c r="U1" s="225"/>
-      <c r="V1" s="225"/>
-      <c r="W1" s="225"/>
-      <c r="X1" s="225"/>
-      <c r="Y1" s="225"/>
-      <c r="Z1" s="226"/>
-      <c r="AA1" s="206" t="s">
+      <c r="T1" s="259"/>
+      <c r="U1" s="259"/>
+      <c r="V1" s="259"/>
+      <c r="W1" s="259"/>
+      <c r="X1" s="259"/>
+      <c r="Y1" s="259"/>
+      <c r="Z1" s="260"/>
+      <c r="AA1" s="240" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="208"/>
-      <c r="AC1" s="233" t="str">
+      <c r="AB1" s="242"/>
+      <c r="AC1" s="267" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="234"/>
-      <c r="AE1" s="234"/>
-      <c r="AF1" s="235"/>
-      <c r="AG1" s="200">
+      <c r="AD1" s="268"/>
+      <c r="AE1" s="268"/>
+      <c r="AF1" s="269"/>
+      <c r="AG1" s="234">
         <f>IF(D8="","",D8)</f>
         <v>44011</v>
       </c>
-      <c r="AH1" s="201"/>
-      <c r="AI1" s="202"/>
+      <c r="AH1" s="235"/>
+      <c r="AI1" s="236"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -12704,53 +12704,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="206" t="s">
+      <c r="A2" s="240" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="208"/>
-      <c r="E2" s="209" t="s">
+      <c r="B2" s="241"/>
+      <c r="C2" s="241"/>
+      <c r="D2" s="242"/>
+      <c r="E2" s="243" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="210"/>
-      <c r="G2" s="210"/>
-      <c r="H2" s="210"/>
-      <c r="I2" s="210"/>
-      <c r="J2" s="210"/>
-      <c r="K2" s="210"/>
-      <c r="L2" s="210"/>
-      <c r="M2" s="210"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="218"/>
-      <c r="P2" s="219"/>
-      <c r="Q2" s="219"/>
-      <c r="R2" s="220"/>
-      <c r="S2" s="227"/>
-      <c r="T2" s="228"/>
-      <c r="U2" s="228"/>
-      <c r="V2" s="228"/>
-      <c r="W2" s="228"/>
-      <c r="X2" s="228"/>
-      <c r="Y2" s="228"/>
-      <c r="Z2" s="229"/>
-      <c r="AA2" s="206" t="s">
+      <c r="F2" s="244"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="244"/>
+      <c r="I2" s="244"/>
+      <c r="J2" s="244"/>
+      <c r="K2" s="244"/>
+      <c r="L2" s="244"/>
+      <c r="M2" s="244"/>
+      <c r="N2" s="245"/>
+      <c r="O2" s="252"/>
+      <c r="P2" s="253"/>
+      <c r="Q2" s="253"/>
+      <c r="R2" s="254"/>
+      <c r="S2" s="261"/>
+      <c r="T2" s="262"/>
+      <c r="U2" s="262"/>
+      <c r="V2" s="262"/>
+      <c r="W2" s="262"/>
+      <c r="X2" s="262"/>
+      <c r="Y2" s="262"/>
+      <c r="Z2" s="263"/>
+      <c r="AA2" s="240" t="s">
         <v>35</v>
       </c>
-      <c r="AB2" s="208"/>
-      <c r="AC2" s="212" t="str">
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="246" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="213"/>
-      <c r="AE2" s="213"/>
-      <c r="AF2" s="214"/>
-      <c r="AG2" s="200">
+      <c r="AD2" s="247"/>
+      <c r="AE2" s="247"/>
+      <c r="AF2" s="248"/>
+      <c r="AG2" s="234">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44858</v>
       </c>
-      <c r="AH2" s="201"/>
-      <c r="AI2" s="202"/>
+      <c r="AH2" s="235"/>
+      <c r="AI2" s="236"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -12758,45 +12758,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="206" t="s">
+      <c r="A3" s="240" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="209" t="s">
+      <c r="B3" s="241"/>
+      <c r="C3" s="241"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="243" t="s">
         <v>46</v>
       </c>
-      <c r="F3" s="210"/>
-      <c r="G3" s="210"/>
-      <c r="H3" s="210"/>
-      <c r="I3" s="210"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="210"/>
-      <c r="L3" s="210"/>
-      <c r="M3" s="210"/>
-      <c r="N3" s="211"/>
-      <c r="O3" s="221"/>
-      <c r="P3" s="222"/>
-      <c r="Q3" s="222"/>
-      <c r="R3" s="223"/>
-      <c r="S3" s="230"/>
-      <c r="T3" s="231"/>
-      <c r="U3" s="231"/>
-      <c r="V3" s="231"/>
-      <c r="W3" s="231"/>
-      <c r="X3" s="231"/>
-      <c r="Y3" s="231"/>
-      <c r="Z3" s="232"/>
-      <c r="AA3" s="206"/>
-      <c r="AB3" s="208"/>
-      <c r="AC3" s="233"/>
-      <c r="AD3" s="234"/>
-      <c r="AE3" s="234"/>
-      <c r="AF3" s="235"/>
-      <c r="AG3" s="200"/>
-      <c r="AH3" s="201"/>
-      <c r="AI3" s="202"/>
+      <c r="F3" s="244"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="244"/>
+      <c r="I3" s="244"/>
+      <c r="J3" s="244"/>
+      <c r="K3" s="244"/>
+      <c r="L3" s="244"/>
+      <c r="M3" s="244"/>
+      <c r="N3" s="245"/>
+      <c r="O3" s="255"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="257"/>
+      <c r="S3" s="264"/>
+      <c r="T3" s="265"/>
+      <c r="U3" s="265"/>
+      <c r="V3" s="265"/>
+      <c r="W3" s="265"/>
+      <c r="X3" s="265"/>
+      <c r="Y3" s="265"/>
+      <c r="Z3" s="266"/>
+      <c r="AA3" s="240"/>
+      <c r="AB3" s="242"/>
+      <c r="AC3" s="267"/>
+      <c r="AD3" s="268"/>
+      <c r="AE3" s="268"/>
+      <c r="AF3" s="269"/>
+      <c r="AG3" s="234"/>
+      <c r="AH3" s="235"/>
+      <c r="AI3" s="236"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -12833,97 +12833,97 @@
       <c r="A7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="203" t="s">
+      <c r="B7" s="237" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="204"/>
-      <c r="D7" s="203" t="s">
+      <c r="C7" s="238"/>
+      <c r="D7" s="237" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="205"/>
-      <c r="F7" s="204"/>
-      <c r="G7" s="203" t="s">
+      <c r="E7" s="239"/>
+      <c r="F7" s="238"/>
+      <c r="G7" s="237" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="205"/>
-      <c r="I7" s="204"/>
-      <c r="J7" s="203" t="s">
+      <c r="H7" s="239"/>
+      <c r="I7" s="238"/>
+      <c r="J7" s="237" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="205"/>
-      <c r="L7" s="205"/>
-      <c r="M7" s="205"/>
-      <c r="N7" s="205"/>
-      <c r="O7" s="205"/>
-      <c r="P7" s="204"/>
-      <c r="Q7" s="203" t="s">
+      <c r="K7" s="239"/>
+      <c r="L7" s="239"/>
+      <c r="M7" s="239"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="239"/>
+      <c r="P7" s="238"/>
+      <c r="Q7" s="237" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="205"/>
-      <c r="S7" s="205"/>
-      <c r="T7" s="205"/>
-      <c r="U7" s="205"/>
-      <c r="V7" s="205"/>
-      <c r="W7" s="205"/>
-      <c r="X7" s="205"/>
-      <c r="Y7" s="205"/>
-      <c r="Z7" s="205"/>
-      <c r="AA7" s="205"/>
-      <c r="AB7" s="205"/>
-      <c r="AC7" s="205"/>
-      <c r="AD7" s="205"/>
-      <c r="AE7" s="204"/>
-      <c r="AF7" s="203" t="s">
+      <c r="R7" s="239"/>
+      <c r="S7" s="239"/>
+      <c r="T7" s="239"/>
+      <c r="U7" s="239"/>
+      <c r="V7" s="239"/>
+      <c r="W7" s="239"/>
+      <c r="X7" s="239"/>
+      <c r="Y7" s="239"/>
+      <c r="Z7" s="239"/>
+      <c r="AA7" s="239"/>
+      <c r="AB7" s="239"/>
+      <c r="AC7" s="239"/>
+      <c r="AD7" s="239"/>
+      <c r="AE7" s="238"/>
+      <c r="AF7" s="237" t="s">
         <v>43</v>
       </c>
-      <c r="AG7" s="205"/>
-      <c r="AH7" s="205"/>
-      <c r="AI7" s="204"/>
+      <c r="AG7" s="239"/>
+      <c r="AH7" s="239"/>
+      <c r="AI7" s="238"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="248" t="s">
+      <c r="B8" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="249"/>
-      <c r="D8" s="250">
+      <c r="C8" s="226"/>
+      <c r="D8" s="227">
         <v>44011</v>
       </c>
-      <c r="E8" s="251"/>
-      <c r="F8" s="252"/>
-      <c r="G8" s="248" t="s">
+      <c r="E8" s="228"/>
+      <c r="F8" s="229"/>
+      <c r="G8" s="225" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="253"/>
-      <c r="I8" s="249"/>
-      <c r="J8" s="254" t="s">
+      <c r="H8" s="230"/>
+      <c r="I8" s="226"/>
+      <c r="J8" s="231" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="255"/>
-      <c r="L8" s="255"/>
-      <c r="M8" s="255"/>
-      <c r="N8" s="255"/>
-      <c r="O8" s="255"/>
-      <c r="P8" s="256"/>
-      <c r="Q8" s="254" t="s">
+      <c r="K8" s="232"/>
+      <c r="L8" s="232"/>
+      <c r="M8" s="232"/>
+      <c r="N8" s="232"/>
+      <c r="O8" s="232"/>
+      <c r="P8" s="233"/>
+      <c r="Q8" s="231" t="s">
         <v>52</v>
       </c>
-      <c r="R8" s="255"/>
-      <c r="S8" s="255"/>
-      <c r="T8" s="255"/>
-      <c r="U8" s="255"/>
-      <c r="V8" s="255"/>
-      <c r="W8" s="255"/>
-      <c r="X8" s="255"/>
-      <c r="Y8" s="255"/>
-      <c r="Z8" s="255"/>
-      <c r="AA8" s="255"/>
-      <c r="AB8" s="255"/>
-      <c r="AC8" s="255"/>
-      <c r="AD8" s="255"/>
-      <c r="AE8" s="256"/>
+      <c r="R8" s="232"/>
+      <c r="S8" s="232"/>
+      <c r="T8" s="232"/>
+      <c r="U8" s="232"/>
+      <c r="V8" s="232"/>
+      <c r="W8" s="232"/>
+      <c r="X8" s="232"/>
+      <c r="Y8" s="232"/>
+      <c r="Z8" s="232"/>
+      <c r="AA8" s="232"/>
+      <c r="AB8" s="232"/>
+      <c r="AC8" s="232"/>
+      <c r="AD8" s="232"/>
+      <c r="AE8" s="233"/>
       <c r="AF8" s="25" t="s">
         <v>53</v>
       </c>
@@ -12935,1101 +12935,946 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="236" t="s">
+      <c r="B9" s="213" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="237"/>
-      <c r="D9" s="238">
+      <c r="C9" s="214"/>
+      <c r="D9" s="215">
         <v>44858</v>
       </c>
-      <c r="E9" s="239"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="238" t="s">
+      <c r="E9" s="216"/>
+      <c r="F9" s="217"/>
+      <c r="G9" s="215" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="241"/>
-      <c r="I9" s="237"/>
-      <c r="J9" s="242" t="s">
+      <c r="H9" s="218"/>
+      <c r="I9" s="214"/>
+      <c r="J9" s="219" t="s">
         <v>62</v>
       </c>
-      <c r="K9" s="243"/>
-      <c r="L9" s="243"/>
-      <c r="M9" s="243"/>
-      <c r="N9" s="243"/>
-      <c r="O9" s="243"/>
-      <c r="P9" s="244"/>
-      <c r="Q9" s="242" t="s">
+      <c r="K9" s="220"/>
+      <c r="L9" s="220"/>
+      <c r="M9" s="220"/>
+      <c r="N9" s="220"/>
+      <c r="O9" s="220"/>
+      <c r="P9" s="221"/>
+      <c r="Q9" s="219" t="s">
         <v>61</v>
       </c>
-      <c r="R9" s="245"/>
-      <c r="S9" s="245"/>
-      <c r="T9" s="245"/>
-      <c r="U9" s="245"/>
-      <c r="V9" s="245"/>
-      <c r="W9" s="245"/>
-      <c r="X9" s="245"/>
-      <c r="Y9" s="245"/>
-      <c r="Z9" s="245"/>
-      <c r="AA9" s="245"/>
-      <c r="AB9" s="245"/>
-      <c r="AC9" s="245"/>
-      <c r="AD9" s="245"/>
-      <c r="AE9" s="246"/>
-      <c r="AF9" s="247" t="s">
+      <c r="R9" s="222"/>
+      <c r="S9" s="222"/>
+      <c r="T9" s="222"/>
+      <c r="U9" s="222"/>
+      <c r="V9" s="222"/>
+      <c r="W9" s="222"/>
+      <c r="X9" s="222"/>
+      <c r="Y9" s="222"/>
+      <c r="Z9" s="222"/>
+      <c r="AA9" s="222"/>
+      <c r="AB9" s="222"/>
+      <c r="AC9" s="222"/>
+      <c r="AD9" s="222"/>
+      <c r="AE9" s="223"/>
+      <c r="AF9" s="224" t="s">
         <v>53</v>
       </c>
-      <c r="AG9" s="243"/>
-      <c r="AH9" s="243"/>
-      <c r="AI9" s="244"/>
+      <c r="AG9" s="220"/>
+      <c r="AH9" s="220"/>
+      <c r="AI9" s="221"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="257"/>
-      <c r="C10" s="258"/>
-      <c r="D10" s="259"/>
-      <c r="E10" s="260"/>
-      <c r="F10" s="261"/>
-      <c r="G10" s="257"/>
-      <c r="H10" s="262"/>
-      <c r="I10" s="258"/>
-      <c r="J10" s="263"/>
-      <c r="K10" s="264"/>
-      <c r="L10" s="264"/>
-      <c r="M10" s="264"/>
-      <c r="N10" s="264"/>
-      <c r="O10" s="264"/>
-      <c r="P10" s="265"/>
-      <c r="Q10" s="266"/>
-      <c r="R10" s="267"/>
-      <c r="S10" s="267"/>
-      <c r="T10" s="267"/>
-      <c r="U10" s="267"/>
-      <c r="V10" s="267"/>
-      <c r="W10" s="267"/>
-      <c r="X10" s="267"/>
-      <c r="Y10" s="267"/>
-      <c r="Z10" s="267"/>
-      <c r="AA10" s="267"/>
-      <c r="AB10" s="267"/>
-      <c r="AC10" s="267"/>
-      <c r="AD10" s="267"/>
-      <c r="AE10" s="268"/>
-      <c r="AF10" s="263"/>
-      <c r="AG10" s="264"/>
-      <c r="AH10" s="264"/>
-      <c r="AI10" s="265"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="201"/>
+      <c r="D10" s="202"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="204"/>
+      <c r="G10" s="200"/>
+      <c r="H10" s="205"/>
+      <c r="I10" s="201"/>
+      <c r="J10" s="206"/>
+      <c r="K10" s="207"/>
+      <c r="L10" s="207"/>
+      <c r="M10" s="207"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
+      <c r="P10" s="208"/>
+      <c r="Q10" s="209"/>
+      <c r="R10" s="210"/>
+      <c r="S10" s="210"/>
+      <c r="T10" s="210"/>
+      <c r="U10" s="210"/>
+      <c r="V10" s="210"/>
+      <c r="W10" s="210"/>
+      <c r="X10" s="210"/>
+      <c r="Y10" s="210"/>
+      <c r="Z10" s="210"/>
+      <c r="AA10" s="210"/>
+      <c r="AB10" s="210"/>
+      <c r="AC10" s="210"/>
+      <c r="AD10" s="210"/>
+      <c r="AE10" s="211"/>
+      <c r="AF10" s="206"/>
+      <c r="AG10" s="207"/>
+      <c r="AH10" s="207"/>
+      <c r="AI10" s="208"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="257"/>
-      <c r="C11" s="258"/>
-      <c r="D11" s="259"/>
-      <c r="E11" s="260"/>
-      <c r="F11" s="261"/>
-      <c r="G11" s="257"/>
-      <c r="H11" s="262"/>
-      <c r="I11" s="258"/>
-      <c r="J11" s="263"/>
-      <c r="K11" s="264"/>
-      <c r="L11" s="264"/>
-      <c r="M11" s="264"/>
-      <c r="N11" s="264"/>
-      <c r="O11" s="264"/>
-      <c r="P11" s="265"/>
-      <c r="Q11" s="266"/>
-      <c r="R11" s="267"/>
-      <c r="S11" s="267"/>
-      <c r="T11" s="267"/>
-      <c r="U11" s="267"/>
-      <c r="V11" s="267"/>
-      <c r="W11" s="267"/>
-      <c r="X11" s="267"/>
-      <c r="Y11" s="267"/>
-      <c r="Z11" s="267"/>
-      <c r="AA11" s="267"/>
-      <c r="AB11" s="267"/>
-      <c r="AC11" s="267"/>
-      <c r="AD11" s="267"/>
-      <c r="AE11" s="268"/>
-      <c r="AF11" s="263"/>
-      <c r="AG11" s="264"/>
-      <c r="AH11" s="264"/>
-      <c r="AI11" s="265"/>
+      <c r="B11" s="200"/>
+      <c r="C11" s="201"/>
+      <c r="D11" s="202"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="204"/>
+      <c r="G11" s="200"/>
+      <c r="H11" s="205"/>
+      <c r="I11" s="201"/>
+      <c r="J11" s="206"/>
+      <c r="K11" s="207"/>
+      <c r="L11" s="207"/>
+      <c r="M11" s="207"/>
+      <c r="N11" s="207"/>
+      <c r="O11" s="207"/>
+      <c r="P11" s="208"/>
+      <c r="Q11" s="209"/>
+      <c r="R11" s="210"/>
+      <c r="S11" s="210"/>
+      <c r="T11" s="210"/>
+      <c r="U11" s="210"/>
+      <c r="V11" s="210"/>
+      <c r="W11" s="210"/>
+      <c r="X11" s="210"/>
+      <c r="Y11" s="210"/>
+      <c r="Z11" s="210"/>
+      <c r="AA11" s="210"/>
+      <c r="AB11" s="210"/>
+      <c r="AC11" s="210"/>
+      <c r="AD11" s="210"/>
+      <c r="AE11" s="211"/>
+      <c r="AF11" s="206"/>
+      <c r="AG11" s="207"/>
+      <c r="AH11" s="207"/>
+      <c r="AI11" s="208"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="257"/>
-      <c r="C12" s="258"/>
-      <c r="D12" s="259"/>
-      <c r="E12" s="260"/>
-      <c r="F12" s="261"/>
-      <c r="G12" s="257"/>
-      <c r="H12" s="262"/>
-      <c r="I12" s="258"/>
-      <c r="J12" s="263"/>
-      <c r="K12" s="264"/>
-      <c r="L12" s="264"/>
-      <c r="M12" s="264"/>
-      <c r="N12" s="264"/>
-      <c r="O12" s="264"/>
-      <c r="P12" s="265"/>
-      <c r="Q12" s="266"/>
-      <c r="R12" s="267"/>
-      <c r="S12" s="267"/>
-      <c r="T12" s="267"/>
-      <c r="U12" s="267"/>
-      <c r="V12" s="267"/>
-      <c r="W12" s="267"/>
-      <c r="X12" s="267"/>
-      <c r="Y12" s="267"/>
-      <c r="Z12" s="267"/>
-      <c r="AA12" s="267"/>
-      <c r="AB12" s="267"/>
-      <c r="AC12" s="267"/>
-      <c r="AD12" s="267"/>
-      <c r="AE12" s="268"/>
-      <c r="AF12" s="263"/>
-      <c r="AG12" s="264"/>
-      <c r="AH12" s="264"/>
-      <c r="AI12" s="265"/>
+      <c r="B12" s="200"/>
+      <c r="C12" s="201"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="204"/>
+      <c r="G12" s="200"/>
+      <c r="H12" s="205"/>
+      <c r="I12" s="201"/>
+      <c r="J12" s="206"/>
+      <c r="K12" s="207"/>
+      <c r="L12" s="207"/>
+      <c r="M12" s="207"/>
+      <c r="N12" s="207"/>
+      <c r="O12" s="207"/>
+      <c r="P12" s="208"/>
+      <c r="Q12" s="209"/>
+      <c r="R12" s="210"/>
+      <c r="S12" s="210"/>
+      <c r="T12" s="210"/>
+      <c r="U12" s="210"/>
+      <c r="V12" s="210"/>
+      <c r="W12" s="210"/>
+      <c r="X12" s="210"/>
+      <c r="Y12" s="210"/>
+      <c r="Z12" s="210"/>
+      <c r="AA12" s="210"/>
+      <c r="AB12" s="210"/>
+      <c r="AC12" s="210"/>
+      <c r="AD12" s="210"/>
+      <c r="AE12" s="211"/>
+      <c r="AF12" s="206"/>
+      <c r="AG12" s="207"/>
+      <c r="AH12" s="207"/>
+      <c r="AI12" s="208"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="257"/>
-      <c r="C13" s="258"/>
-      <c r="D13" s="259"/>
-      <c r="E13" s="260"/>
-      <c r="F13" s="261"/>
-      <c r="G13" s="257"/>
-      <c r="H13" s="262"/>
-      <c r="I13" s="258"/>
-      <c r="J13" s="263"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="264"/>
-      <c r="M13" s="264"/>
-      <c r="N13" s="264"/>
-      <c r="O13" s="264"/>
-      <c r="P13" s="265"/>
-      <c r="Q13" s="266"/>
-      <c r="R13" s="267"/>
-      <c r="S13" s="267"/>
-      <c r="T13" s="267"/>
-      <c r="U13" s="267"/>
-      <c r="V13" s="267"/>
-      <c r="W13" s="267"/>
-      <c r="X13" s="267"/>
-      <c r="Y13" s="267"/>
-      <c r="Z13" s="267"/>
-      <c r="AA13" s="267"/>
-      <c r="AB13" s="267"/>
-      <c r="AC13" s="267"/>
-      <c r="AD13" s="267"/>
-      <c r="AE13" s="268"/>
-      <c r="AF13" s="263"/>
-      <c r="AG13" s="264"/>
-      <c r="AH13" s="264"/>
-      <c r="AI13" s="265"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="204"/>
+      <c r="G13" s="200"/>
+      <c r="H13" s="205"/>
+      <c r="I13" s="201"/>
+      <c r="J13" s="206"/>
+      <c r="K13" s="207"/>
+      <c r="L13" s="207"/>
+      <c r="M13" s="207"/>
+      <c r="N13" s="207"/>
+      <c r="O13" s="207"/>
+      <c r="P13" s="208"/>
+      <c r="Q13" s="209"/>
+      <c r="R13" s="210"/>
+      <c r="S13" s="210"/>
+      <c r="T13" s="210"/>
+      <c r="U13" s="210"/>
+      <c r="V13" s="210"/>
+      <c r="W13" s="210"/>
+      <c r="X13" s="210"/>
+      <c r="Y13" s="210"/>
+      <c r="Z13" s="210"/>
+      <c r="AA13" s="210"/>
+      <c r="AB13" s="210"/>
+      <c r="AC13" s="210"/>
+      <c r="AD13" s="210"/>
+      <c r="AE13" s="211"/>
+      <c r="AF13" s="206"/>
+      <c r="AG13" s="207"/>
+      <c r="AH13" s="207"/>
+      <c r="AI13" s="208"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="257"/>
-      <c r="C14" s="258"/>
-      <c r="D14" s="259"/>
-      <c r="E14" s="260"/>
-      <c r="F14" s="261"/>
-      <c r="G14" s="257"/>
-      <c r="H14" s="262"/>
-      <c r="I14" s="258"/>
-      <c r="J14" s="263"/>
-      <c r="K14" s="264"/>
-      <c r="L14" s="264"/>
-      <c r="M14" s="264"/>
-      <c r="N14" s="264"/>
-      <c r="O14" s="264"/>
-      <c r="P14" s="265"/>
-      <c r="Q14" s="266"/>
-      <c r="R14" s="267"/>
-      <c r="S14" s="267"/>
-      <c r="T14" s="267"/>
-      <c r="U14" s="267"/>
-      <c r="V14" s="267"/>
-      <c r="W14" s="267"/>
-      <c r="X14" s="267"/>
-      <c r="Y14" s="267"/>
-      <c r="Z14" s="267"/>
-      <c r="AA14" s="267"/>
-      <c r="AB14" s="267"/>
-      <c r="AC14" s="267"/>
-      <c r="AD14" s="267"/>
-      <c r="AE14" s="268"/>
-      <c r="AF14" s="263"/>
-      <c r="AG14" s="264"/>
-      <c r="AH14" s="264"/>
-      <c r="AI14" s="265"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="204"/>
+      <c r="G14" s="200"/>
+      <c r="H14" s="205"/>
+      <c r="I14" s="201"/>
+      <c r="J14" s="206"/>
+      <c r="K14" s="207"/>
+      <c r="L14" s="207"/>
+      <c r="M14" s="207"/>
+      <c r="N14" s="207"/>
+      <c r="O14" s="207"/>
+      <c r="P14" s="208"/>
+      <c r="Q14" s="209"/>
+      <c r="R14" s="210"/>
+      <c r="S14" s="210"/>
+      <c r="T14" s="210"/>
+      <c r="U14" s="210"/>
+      <c r="V14" s="210"/>
+      <c r="W14" s="210"/>
+      <c r="X14" s="210"/>
+      <c r="Y14" s="210"/>
+      <c r="Z14" s="210"/>
+      <c r="AA14" s="210"/>
+      <c r="AB14" s="210"/>
+      <c r="AC14" s="210"/>
+      <c r="AD14" s="210"/>
+      <c r="AE14" s="211"/>
+      <c r="AF14" s="206"/>
+      <c r="AG14" s="207"/>
+      <c r="AH14" s="207"/>
+      <c r="AI14" s="208"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="257"/>
-      <c r="C15" s="258"/>
-      <c r="D15" s="259"/>
-      <c r="E15" s="260"/>
-      <c r="F15" s="261"/>
-      <c r="G15" s="257"/>
-      <c r="H15" s="262"/>
-      <c r="I15" s="258"/>
-      <c r="J15" s="263"/>
-      <c r="K15" s="264"/>
-      <c r="L15" s="264"/>
-      <c r="M15" s="264"/>
-      <c r="N15" s="264"/>
-      <c r="O15" s="264"/>
-      <c r="P15" s="265"/>
-      <c r="Q15" s="266"/>
-      <c r="R15" s="267"/>
-      <c r="S15" s="267"/>
-      <c r="T15" s="267"/>
-      <c r="U15" s="267"/>
-      <c r="V15" s="267"/>
-      <c r="W15" s="267"/>
-      <c r="X15" s="267"/>
-      <c r="Y15" s="267"/>
-      <c r="Z15" s="267"/>
-      <c r="AA15" s="267"/>
-      <c r="AB15" s="267"/>
-      <c r="AC15" s="267"/>
-      <c r="AD15" s="267"/>
-      <c r="AE15" s="268"/>
-      <c r="AF15" s="263"/>
-      <c r="AG15" s="264"/>
-      <c r="AH15" s="264"/>
-      <c r="AI15" s="265"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="204"/>
+      <c r="G15" s="200"/>
+      <c r="H15" s="205"/>
+      <c r="I15" s="201"/>
+      <c r="J15" s="206"/>
+      <c r="K15" s="207"/>
+      <c r="L15" s="207"/>
+      <c r="M15" s="207"/>
+      <c r="N15" s="207"/>
+      <c r="O15" s="207"/>
+      <c r="P15" s="208"/>
+      <c r="Q15" s="209"/>
+      <c r="R15" s="210"/>
+      <c r="S15" s="210"/>
+      <c r="T15" s="210"/>
+      <c r="U15" s="210"/>
+      <c r="V15" s="210"/>
+      <c r="W15" s="210"/>
+      <c r="X15" s="210"/>
+      <c r="Y15" s="210"/>
+      <c r="Z15" s="210"/>
+      <c r="AA15" s="210"/>
+      <c r="AB15" s="210"/>
+      <c r="AC15" s="210"/>
+      <c r="AD15" s="210"/>
+      <c r="AE15" s="211"/>
+      <c r="AF15" s="206"/>
+      <c r="AG15" s="207"/>
+      <c r="AH15" s="207"/>
+      <c r="AI15" s="208"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="257"/>
-      <c r="C16" s="258"/>
-      <c r="D16" s="259"/>
-      <c r="E16" s="260"/>
-      <c r="F16" s="261"/>
-      <c r="G16" s="257"/>
-      <c r="H16" s="262"/>
-      <c r="I16" s="258"/>
-      <c r="J16" s="263"/>
-      <c r="K16" s="264"/>
-      <c r="L16" s="264"/>
-      <c r="M16" s="264"/>
-      <c r="N16" s="264"/>
-      <c r="O16" s="264"/>
-      <c r="P16" s="265"/>
-      <c r="Q16" s="266"/>
-      <c r="R16" s="267"/>
-      <c r="S16" s="267"/>
-      <c r="T16" s="267"/>
-      <c r="U16" s="267"/>
-      <c r="V16" s="267"/>
-      <c r="W16" s="267"/>
-      <c r="X16" s="267"/>
-      <c r="Y16" s="267"/>
-      <c r="Z16" s="267"/>
-      <c r="AA16" s="267"/>
-      <c r="AB16" s="267"/>
-      <c r="AC16" s="267"/>
-      <c r="AD16" s="267"/>
-      <c r="AE16" s="268"/>
-      <c r="AF16" s="263"/>
-      <c r="AG16" s="264"/>
-      <c r="AH16" s="264"/>
-      <c r="AI16" s="265"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="204"/>
+      <c r="G16" s="200"/>
+      <c r="H16" s="205"/>
+      <c r="I16" s="201"/>
+      <c r="J16" s="206"/>
+      <c r="K16" s="207"/>
+      <c r="L16" s="207"/>
+      <c r="M16" s="207"/>
+      <c r="N16" s="207"/>
+      <c r="O16" s="207"/>
+      <c r="P16" s="208"/>
+      <c r="Q16" s="209"/>
+      <c r="R16" s="210"/>
+      <c r="S16" s="210"/>
+      <c r="T16" s="210"/>
+      <c r="U16" s="210"/>
+      <c r="V16" s="210"/>
+      <c r="W16" s="210"/>
+      <c r="X16" s="210"/>
+      <c r="Y16" s="210"/>
+      <c r="Z16" s="210"/>
+      <c r="AA16" s="210"/>
+      <c r="AB16" s="210"/>
+      <c r="AC16" s="210"/>
+      <c r="AD16" s="210"/>
+      <c r="AE16" s="211"/>
+      <c r="AF16" s="206"/>
+      <c r="AG16" s="207"/>
+      <c r="AH16" s="207"/>
+      <c r="AI16" s="208"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="257"/>
-      <c r="C17" s="258"/>
-      <c r="D17" s="259"/>
-      <c r="E17" s="260"/>
-      <c r="F17" s="261"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="262"/>
-      <c r="I17" s="258"/>
-      <c r="J17" s="263"/>
-      <c r="K17" s="264"/>
-      <c r="L17" s="264"/>
-      <c r="M17" s="264"/>
-      <c r="N17" s="264"/>
-      <c r="O17" s="264"/>
-      <c r="P17" s="265"/>
-      <c r="Q17" s="266"/>
-      <c r="R17" s="267"/>
-      <c r="S17" s="267"/>
-      <c r="T17" s="267"/>
-      <c r="U17" s="267"/>
-      <c r="V17" s="267"/>
-      <c r="W17" s="267"/>
-      <c r="X17" s="267"/>
-      <c r="Y17" s="267"/>
-      <c r="Z17" s="267"/>
-      <c r="AA17" s="267"/>
-      <c r="AB17" s="267"/>
-      <c r="AC17" s="267"/>
-      <c r="AD17" s="267"/>
-      <c r="AE17" s="268"/>
-      <c r="AF17" s="263"/>
-      <c r="AG17" s="264"/>
-      <c r="AH17" s="264"/>
-      <c r="AI17" s="265"/>
+      <c r="B17" s="200"/>
+      <c r="C17" s="201"/>
+      <c r="D17" s="202"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="204"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="205"/>
+      <c r="I17" s="201"/>
+      <c r="J17" s="206"/>
+      <c r="K17" s="207"/>
+      <c r="L17" s="207"/>
+      <c r="M17" s="207"/>
+      <c r="N17" s="207"/>
+      <c r="O17" s="207"/>
+      <c r="P17" s="208"/>
+      <c r="Q17" s="209"/>
+      <c r="R17" s="210"/>
+      <c r="S17" s="210"/>
+      <c r="T17" s="210"/>
+      <c r="U17" s="210"/>
+      <c r="V17" s="210"/>
+      <c r="W17" s="210"/>
+      <c r="X17" s="210"/>
+      <c r="Y17" s="210"/>
+      <c r="Z17" s="210"/>
+      <c r="AA17" s="210"/>
+      <c r="AB17" s="210"/>
+      <c r="AC17" s="210"/>
+      <c r="AD17" s="210"/>
+      <c r="AE17" s="211"/>
+      <c r="AF17" s="206"/>
+      <c r="AG17" s="207"/>
+      <c r="AH17" s="207"/>
+      <c r="AI17" s="208"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="257"/>
-      <c r="C18" s="258"/>
-      <c r="D18" s="259"/>
-      <c r="E18" s="260"/>
-      <c r="F18" s="261"/>
-      <c r="G18" s="257"/>
-      <c r="H18" s="262"/>
-      <c r="I18" s="258"/>
-      <c r="J18" s="263"/>
-      <c r="K18" s="264"/>
-      <c r="L18" s="264"/>
-      <c r="M18" s="264"/>
-      <c r="N18" s="264"/>
-      <c r="O18" s="264"/>
-      <c r="P18" s="265"/>
-      <c r="Q18" s="266"/>
-      <c r="R18" s="267"/>
-      <c r="S18" s="267"/>
-      <c r="T18" s="267"/>
-      <c r="U18" s="267"/>
-      <c r="V18" s="267"/>
-      <c r="W18" s="267"/>
-      <c r="X18" s="267"/>
-      <c r="Y18" s="267"/>
-      <c r="Z18" s="267"/>
-      <c r="AA18" s="267"/>
-      <c r="AB18" s="267"/>
-      <c r="AC18" s="267"/>
-      <c r="AD18" s="267"/>
-      <c r="AE18" s="268"/>
-      <c r="AF18" s="263"/>
-      <c r="AG18" s="264"/>
-      <c r="AH18" s="264"/>
-      <c r="AI18" s="265"/>
+      <c r="B18" s="200"/>
+      <c r="C18" s="201"/>
+      <c r="D18" s="202"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="204"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="205"/>
+      <c r="I18" s="201"/>
+      <c r="J18" s="206"/>
+      <c r="K18" s="207"/>
+      <c r="L18" s="207"/>
+      <c r="M18" s="207"/>
+      <c r="N18" s="207"/>
+      <c r="O18" s="207"/>
+      <c r="P18" s="208"/>
+      <c r="Q18" s="209"/>
+      <c r="R18" s="210"/>
+      <c r="S18" s="210"/>
+      <c r="T18" s="210"/>
+      <c r="U18" s="210"/>
+      <c r="V18" s="210"/>
+      <c r="W18" s="210"/>
+      <c r="X18" s="210"/>
+      <c r="Y18" s="210"/>
+      <c r="Z18" s="210"/>
+      <c r="AA18" s="210"/>
+      <c r="AB18" s="210"/>
+      <c r="AC18" s="210"/>
+      <c r="AD18" s="210"/>
+      <c r="AE18" s="211"/>
+      <c r="AF18" s="206"/>
+      <c r="AG18" s="207"/>
+      <c r="AH18" s="207"/>
+      <c r="AI18" s="208"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="257"/>
-      <c r="C19" s="258"/>
-      <c r="D19" s="259"/>
-      <c r="E19" s="260"/>
-      <c r="F19" s="261"/>
-      <c r="G19" s="257"/>
-      <c r="H19" s="262"/>
-      <c r="I19" s="258"/>
-      <c r="J19" s="263"/>
-      <c r="K19" s="264"/>
-      <c r="L19" s="264"/>
-      <c r="M19" s="264"/>
-      <c r="N19" s="264"/>
-      <c r="O19" s="264"/>
-      <c r="P19" s="265"/>
-      <c r="Q19" s="266"/>
-      <c r="R19" s="267"/>
-      <c r="S19" s="267"/>
-      <c r="T19" s="267"/>
-      <c r="U19" s="267"/>
-      <c r="V19" s="267"/>
-      <c r="W19" s="267"/>
-      <c r="X19" s="267"/>
-      <c r="Y19" s="267"/>
-      <c r="Z19" s="267"/>
-      <c r="AA19" s="267"/>
-      <c r="AB19" s="267"/>
-      <c r="AC19" s="267"/>
-      <c r="AD19" s="267"/>
-      <c r="AE19" s="268"/>
-      <c r="AF19" s="263"/>
-      <c r="AG19" s="264"/>
-      <c r="AH19" s="264"/>
-      <c r="AI19" s="265"/>
+      <c r="B19" s="200"/>
+      <c r="C19" s="201"/>
+      <c r="D19" s="202"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="204"/>
+      <c r="G19" s="200"/>
+      <c r="H19" s="205"/>
+      <c r="I19" s="201"/>
+      <c r="J19" s="206"/>
+      <c r="K19" s="207"/>
+      <c r="L19" s="207"/>
+      <c r="M19" s="207"/>
+      <c r="N19" s="207"/>
+      <c r="O19" s="207"/>
+      <c r="P19" s="208"/>
+      <c r="Q19" s="209"/>
+      <c r="R19" s="210"/>
+      <c r="S19" s="210"/>
+      <c r="T19" s="210"/>
+      <c r="U19" s="210"/>
+      <c r="V19" s="210"/>
+      <c r="W19" s="210"/>
+      <c r="X19" s="210"/>
+      <c r="Y19" s="210"/>
+      <c r="Z19" s="210"/>
+      <c r="AA19" s="210"/>
+      <c r="AB19" s="210"/>
+      <c r="AC19" s="210"/>
+      <c r="AD19" s="210"/>
+      <c r="AE19" s="211"/>
+      <c r="AF19" s="206"/>
+      <c r="AG19" s="207"/>
+      <c r="AH19" s="207"/>
+      <c r="AI19" s="208"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="257"/>
-      <c r="C20" s="258"/>
-      <c r="D20" s="259"/>
-      <c r="E20" s="260"/>
-      <c r="F20" s="261"/>
-      <c r="G20" s="257"/>
-      <c r="H20" s="262"/>
-      <c r="I20" s="258"/>
-      <c r="J20" s="263"/>
-      <c r="K20" s="264"/>
-      <c r="L20" s="264"/>
-      <c r="M20" s="264"/>
-      <c r="N20" s="264"/>
-      <c r="O20" s="264"/>
-      <c r="P20" s="265"/>
-      <c r="Q20" s="266"/>
-      <c r="R20" s="267"/>
-      <c r="S20" s="267"/>
-      <c r="T20" s="267"/>
-      <c r="U20" s="267"/>
-      <c r="V20" s="267"/>
-      <c r="W20" s="267"/>
-      <c r="X20" s="267"/>
-      <c r="Y20" s="267"/>
-      <c r="Z20" s="267"/>
-      <c r="AA20" s="267"/>
-      <c r="AB20" s="267"/>
-      <c r="AC20" s="267"/>
-      <c r="AD20" s="267"/>
-      <c r="AE20" s="268"/>
-      <c r="AF20" s="263"/>
-      <c r="AG20" s="264"/>
-      <c r="AH20" s="264"/>
-      <c r="AI20" s="265"/>
+      <c r="B20" s="200"/>
+      <c r="C20" s="201"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="204"/>
+      <c r="G20" s="200"/>
+      <c r="H20" s="205"/>
+      <c r="I20" s="201"/>
+      <c r="J20" s="206"/>
+      <c r="K20" s="207"/>
+      <c r="L20" s="207"/>
+      <c r="M20" s="207"/>
+      <c r="N20" s="207"/>
+      <c r="O20" s="207"/>
+      <c r="P20" s="208"/>
+      <c r="Q20" s="209"/>
+      <c r="R20" s="210"/>
+      <c r="S20" s="210"/>
+      <c r="T20" s="210"/>
+      <c r="U20" s="210"/>
+      <c r="V20" s="210"/>
+      <c r="W20" s="210"/>
+      <c r="X20" s="210"/>
+      <c r="Y20" s="210"/>
+      <c r="Z20" s="210"/>
+      <c r="AA20" s="210"/>
+      <c r="AB20" s="210"/>
+      <c r="AC20" s="210"/>
+      <c r="AD20" s="210"/>
+      <c r="AE20" s="211"/>
+      <c r="AF20" s="206"/>
+      <c r="AG20" s="207"/>
+      <c r="AH20" s="207"/>
+      <c r="AI20" s="208"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="257"/>
-      <c r="C21" s="258"/>
-      <c r="D21" s="259"/>
-      <c r="E21" s="260"/>
-      <c r="F21" s="261"/>
-      <c r="G21" s="257"/>
-      <c r="H21" s="262"/>
-      <c r="I21" s="258"/>
-      <c r="J21" s="263"/>
-      <c r="K21" s="264"/>
-      <c r="L21" s="264"/>
-      <c r="M21" s="264"/>
-      <c r="N21" s="264"/>
-      <c r="O21" s="264"/>
-      <c r="P21" s="265"/>
-      <c r="Q21" s="266"/>
-      <c r="R21" s="267"/>
-      <c r="S21" s="267"/>
-      <c r="T21" s="267"/>
-      <c r="U21" s="267"/>
-      <c r="V21" s="267"/>
-      <c r="W21" s="267"/>
-      <c r="X21" s="267"/>
-      <c r="Y21" s="267"/>
-      <c r="Z21" s="267"/>
-      <c r="AA21" s="267"/>
-      <c r="AB21" s="267"/>
-      <c r="AC21" s="267"/>
-      <c r="AD21" s="267"/>
-      <c r="AE21" s="268"/>
-      <c r="AF21" s="263"/>
-      <c r="AG21" s="264"/>
-      <c r="AH21" s="264"/>
-      <c r="AI21" s="265"/>
+      <c r="B21" s="200"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="204"/>
+      <c r="G21" s="200"/>
+      <c r="H21" s="205"/>
+      <c r="I21" s="201"/>
+      <c r="J21" s="206"/>
+      <c r="K21" s="207"/>
+      <c r="L21" s="207"/>
+      <c r="M21" s="207"/>
+      <c r="N21" s="207"/>
+      <c r="O21" s="207"/>
+      <c r="P21" s="208"/>
+      <c r="Q21" s="209"/>
+      <c r="R21" s="210"/>
+      <c r="S21" s="210"/>
+      <c r="T21" s="210"/>
+      <c r="U21" s="210"/>
+      <c r="V21" s="210"/>
+      <c r="W21" s="210"/>
+      <c r="X21" s="210"/>
+      <c r="Y21" s="210"/>
+      <c r="Z21" s="210"/>
+      <c r="AA21" s="210"/>
+      <c r="AB21" s="210"/>
+      <c r="AC21" s="210"/>
+      <c r="AD21" s="210"/>
+      <c r="AE21" s="211"/>
+      <c r="AF21" s="206"/>
+      <c r="AG21" s="207"/>
+      <c r="AH21" s="207"/>
+      <c r="AI21" s="208"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="257"/>
-      <c r="C22" s="258"/>
-      <c r="D22" s="259"/>
-      <c r="E22" s="260"/>
-      <c r="F22" s="261"/>
-      <c r="G22" s="257"/>
-      <c r="H22" s="262"/>
-      <c r="I22" s="258"/>
-      <c r="J22" s="263"/>
-      <c r="K22" s="264"/>
-      <c r="L22" s="264"/>
-      <c r="M22" s="264"/>
-      <c r="N22" s="264"/>
-      <c r="O22" s="264"/>
-      <c r="P22" s="265"/>
-      <c r="Q22" s="266"/>
-      <c r="R22" s="267"/>
-      <c r="S22" s="267"/>
-      <c r="T22" s="267"/>
-      <c r="U22" s="267"/>
-      <c r="V22" s="267"/>
-      <c r="W22" s="267"/>
-      <c r="X22" s="267"/>
-      <c r="Y22" s="267"/>
-      <c r="Z22" s="267"/>
-      <c r="AA22" s="267"/>
-      <c r="AB22" s="267"/>
-      <c r="AC22" s="267"/>
-      <c r="AD22" s="267"/>
-      <c r="AE22" s="268"/>
-      <c r="AF22" s="263"/>
-      <c r="AG22" s="264"/>
-      <c r="AH22" s="264"/>
-      <c r="AI22" s="265"/>
+      <c r="B22" s="200"/>
+      <c r="C22" s="201"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="204"/>
+      <c r="G22" s="200"/>
+      <c r="H22" s="205"/>
+      <c r="I22" s="201"/>
+      <c r="J22" s="206"/>
+      <c r="K22" s="207"/>
+      <c r="L22" s="207"/>
+      <c r="M22" s="207"/>
+      <c r="N22" s="207"/>
+      <c r="O22" s="207"/>
+      <c r="P22" s="208"/>
+      <c r="Q22" s="209"/>
+      <c r="R22" s="210"/>
+      <c r="S22" s="210"/>
+      <c r="T22" s="210"/>
+      <c r="U22" s="210"/>
+      <c r="V22" s="210"/>
+      <c r="W22" s="210"/>
+      <c r="X22" s="210"/>
+      <c r="Y22" s="210"/>
+      <c r="Z22" s="210"/>
+      <c r="AA22" s="210"/>
+      <c r="AB22" s="210"/>
+      <c r="AC22" s="210"/>
+      <c r="AD22" s="210"/>
+      <c r="AE22" s="211"/>
+      <c r="AF22" s="206"/>
+      <c r="AG22" s="207"/>
+      <c r="AH22" s="207"/>
+      <c r="AI22" s="208"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="257"/>
-      <c r="C23" s="258"/>
-      <c r="D23" s="259"/>
-      <c r="E23" s="260"/>
-      <c r="F23" s="261"/>
-      <c r="G23" s="257"/>
-      <c r="H23" s="262"/>
-      <c r="I23" s="258"/>
-      <c r="J23" s="263"/>
-      <c r="K23" s="264"/>
-      <c r="L23" s="264"/>
-      <c r="M23" s="264"/>
-      <c r="N23" s="264"/>
-      <c r="O23" s="264"/>
-      <c r="P23" s="265"/>
-      <c r="Q23" s="266"/>
-      <c r="R23" s="267"/>
-      <c r="S23" s="267"/>
-      <c r="T23" s="267"/>
-      <c r="U23" s="267"/>
-      <c r="V23" s="267"/>
-      <c r="W23" s="267"/>
-      <c r="X23" s="267"/>
-      <c r="Y23" s="267"/>
-      <c r="Z23" s="267"/>
-      <c r="AA23" s="267"/>
-      <c r="AB23" s="267"/>
-      <c r="AC23" s="267"/>
-      <c r="AD23" s="267"/>
-      <c r="AE23" s="268"/>
-      <c r="AF23" s="263"/>
-      <c r="AG23" s="264"/>
-      <c r="AH23" s="264"/>
-      <c r="AI23" s="265"/>
+      <c r="B23" s="200"/>
+      <c r="C23" s="201"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="204"/>
+      <c r="G23" s="200"/>
+      <c r="H23" s="205"/>
+      <c r="I23" s="201"/>
+      <c r="J23" s="206"/>
+      <c r="K23" s="207"/>
+      <c r="L23" s="207"/>
+      <c r="M23" s="207"/>
+      <c r="N23" s="207"/>
+      <c r="O23" s="207"/>
+      <c r="P23" s="208"/>
+      <c r="Q23" s="209"/>
+      <c r="R23" s="210"/>
+      <c r="S23" s="210"/>
+      <c r="T23" s="210"/>
+      <c r="U23" s="210"/>
+      <c r="V23" s="210"/>
+      <c r="W23" s="210"/>
+      <c r="X23" s="210"/>
+      <c r="Y23" s="210"/>
+      <c r="Z23" s="210"/>
+      <c r="AA23" s="210"/>
+      <c r="AB23" s="210"/>
+      <c r="AC23" s="210"/>
+      <c r="AD23" s="210"/>
+      <c r="AE23" s="211"/>
+      <c r="AF23" s="206"/>
+      <c r="AG23" s="207"/>
+      <c r="AH23" s="207"/>
+      <c r="AI23" s="208"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="257"/>
-      <c r="C24" s="258"/>
-      <c r="D24" s="259"/>
-      <c r="E24" s="260"/>
-      <c r="F24" s="261"/>
-      <c r="G24" s="257"/>
-      <c r="H24" s="262"/>
-      <c r="I24" s="258"/>
-      <c r="J24" s="263"/>
-      <c r="K24" s="264"/>
-      <c r="L24" s="264"/>
-      <c r="M24" s="264"/>
-      <c r="N24" s="264"/>
-      <c r="O24" s="264"/>
-      <c r="P24" s="265"/>
-      <c r="Q24" s="266"/>
-      <c r="R24" s="267"/>
-      <c r="S24" s="267"/>
-      <c r="T24" s="267"/>
-      <c r="U24" s="267"/>
-      <c r="V24" s="267"/>
-      <c r="W24" s="267"/>
-      <c r="X24" s="267"/>
-      <c r="Y24" s="267"/>
-      <c r="Z24" s="267"/>
-      <c r="AA24" s="267"/>
-      <c r="AB24" s="267"/>
-      <c r="AC24" s="267"/>
-      <c r="AD24" s="267"/>
-      <c r="AE24" s="268"/>
-      <c r="AF24" s="263"/>
-      <c r="AG24" s="264"/>
-      <c r="AH24" s="264"/>
-      <c r="AI24" s="265"/>
+      <c r="B24" s="200"/>
+      <c r="C24" s="201"/>
+      <c r="D24" s="202"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="204"/>
+      <c r="G24" s="200"/>
+      <c r="H24" s="205"/>
+      <c r="I24" s="201"/>
+      <c r="J24" s="206"/>
+      <c r="K24" s="207"/>
+      <c r="L24" s="207"/>
+      <c r="M24" s="207"/>
+      <c r="N24" s="207"/>
+      <c r="O24" s="207"/>
+      <c r="P24" s="208"/>
+      <c r="Q24" s="209"/>
+      <c r="R24" s="210"/>
+      <c r="S24" s="210"/>
+      <c r="T24" s="210"/>
+      <c r="U24" s="210"/>
+      <c r="V24" s="210"/>
+      <c r="W24" s="210"/>
+      <c r="X24" s="210"/>
+      <c r="Y24" s="210"/>
+      <c r="Z24" s="210"/>
+      <c r="AA24" s="210"/>
+      <c r="AB24" s="210"/>
+      <c r="AC24" s="210"/>
+      <c r="AD24" s="210"/>
+      <c r="AE24" s="211"/>
+      <c r="AF24" s="206"/>
+      <c r="AG24" s="207"/>
+      <c r="AH24" s="207"/>
+      <c r="AI24" s="208"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="257"/>
-      <c r="C25" s="258"/>
-      <c r="D25" s="259"/>
-      <c r="E25" s="260"/>
-      <c r="F25" s="261"/>
-      <c r="G25" s="257"/>
-      <c r="H25" s="262"/>
-      <c r="I25" s="258"/>
-      <c r="J25" s="263"/>
-      <c r="K25" s="264"/>
-      <c r="L25" s="264"/>
-      <c r="M25" s="264"/>
-      <c r="N25" s="264"/>
-      <c r="O25" s="264"/>
-      <c r="P25" s="265"/>
-      <c r="Q25" s="266"/>
-      <c r="R25" s="267"/>
-      <c r="S25" s="267"/>
-      <c r="T25" s="267"/>
-      <c r="U25" s="267"/>
-      <c r="V25" s="267"/>
-      <c r="W25" s="267"/>
-      <c r="X25" s="267"/>
-      <c r="Y25" s="267"/>
-      <c r="Z25" s="267"/>
-      <c r="AA25" s="267"/>
-      <c r="AB25" s="267"/>
-      <c r="AC25" s="267"/>
-      <c r="AD25" s="267"/>
-      <c r="AE25" s="268"/>
-      <c r="AF25" s="263"/>
-      <c r="AG25" s="264"/>
-      <c r="AH25" s="264"/>
-      <c r="AI25" s="265"/>
+      <c r="B25" s="200"/>
+      <c r="C25" s="201"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="204"/>
+      <c r="G25" s="200"/>
+      <c r="H25" s="205"/>
+      <c r="I25" s="201"/>
+      <c r="J25" s="206"/>
+      <c r="K25" s="207"/>
+      <c r="L25" s="207"/>
+      <c r="M25" s="207"/>
+      <c r="N25" s="207"/>
+      <c r="O25" s="207"/>
+      <c r="P25" s="208"/>
+      <c r="Q25" s="209"/>
+      <c r="R25" s="210"/>
+      <c r="S25" s="210"/>
+      <c r="T25" s="210"/>
+      <c r="U25" s="210"/>
+      <c r="V25" s="210"/>
+      <c r="W25" s="210"/>
+      <c r="X25" s="210"/>
+      <c r="Y25" s="210"/>
+      <c r="Z25" s="210"/>
+      <c r="AA25" s="210"/>
+      <c r="AB25" s="210"/>
+      <c r="AC25" s="210"/>
+      <c r="AD25" s="210"/>
+      <c r="AE25" s="211"/>
+      <c r="AF25" s="206"/>
+      <c r="AG25" s="207"/>
+      <c r="AH25" s="207"/>
+      <c r="AI25" s="208"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="257"/>
-      <c r="C26" s="258"/>
-      <c r="D26" s="259"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="261"/>
-      <c r="G26" s="257"/>
-      <c r="H26" s="262"/>
-      <c r="I26" s="258"/>
-      <c r="J26" s="263"/>
-      <c r="K26" s="264"/>
-      <c r="L26" s="264"/>
-      <c r="M26" s="264"/>
-      <c r="N26" s="264"/>
-      <c r="O26" s="264"/>
-      <c r="P26" s="265"/>
-      <c r="Q26" s="266"/>
-      <c r="R26" s="267"/>
-      <c r="S26" s="267"/>
-      <c r="T26" s="267"/>
-      <c r="U26" s="267"/>
-      <c r="V26" s="267"/>
-      <c r="W26" s="267"/>
-      <c r="X26" s="267"/>
-      <c r="Y26" s="267"/>
-      <c r="Z26" s="267"/>
-      <c r="AA26" s="267"/>
-      <c r="AB26" s="267"/>
-      <c r="AC26" s="267"/>
-      <c r="AD26" s="267"/>
-      <c r="AE26" s="268"/>
-      <c r="AF26" s="263"/>
-      <c r="AG26" s="264"/>
-      <c r="AH26" s="264"/>
-      <c r="AI26" s="265"/>
+      <c r="B26" s="200"/>
+      <c r="C26" s="201"/>
+      <c r="D26" s="202"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="204"/>
+      <c r="G26" s="200"/>
+      <c r="H26" s="205"/>
+      <c r="I26" s="201"/>
+      <c r="J26" s="206"/>
+      <c r="K26" s="207"/>
+      <c r="L26" s="207"/>
+      <c r="M26" s="207"/>
+      <c r="N26" s="207"/>
+      <c r="O26" s="207"/>
+      <c r="P26" s="208"/>
+      <c r="Q26" s="209"/>
+      <c r="R26" s="210"/>
+      <c r="S26" s="210"/>
+      <c r="T26" s="210"/>
+      <c r="U26" s="210"/>
+      <c r="V26" s="210"/>
+      <c r="W26" s="210"/>
+      <c r="X26" s="210"/>
+      <c r="Y26" s="210"/>
+      <c r="Z26" s="210"/>
+      <c r="AA26" s="210"/>
+      <c r="AB26" s="210"/>
+      <c r="AC26" s="210"/>
+      <c r="AD26" s="210"/>
+      <c r="AE26" s="211"/>
+      <c r="AF26" s="206"/>
+      <c r="AG26" s="207"/>
+      <c r="AH26" s="207"/>
+      <c r="AI26" s="208"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="257"/>
-      <c r="C27" s="258"/>
-      <c r="D27" s="259"/>
-      <c r="E27" s="260"/>
-      <c r="F27" s="261"/>
-      <c r="G27" s="257"/>
-      <c r="H27" s="262"/>
-      <c r="I27" s="258"/>
-      <c r="J27" s="263"/>
-      <c r="K27" s="264"/>
-      <c r="L27" s="264"/>
-      <c r="M27" s="264"/>
-      <c r="N27" s="264"/>
-      <c r="O27" s="264"/>
-      <c r="P27" s="265"/>
-      <c r="Q27" s="266"/>
-      <c r="R27" s="267"/>
-      <c r="S27" s="267"/>
-      <c r="T27" s="267"/>
-      <c r="U27" s="267"/>
-      <c r="V27" s="267"/>
-      <c r="W27" s="267"/>
-      <c r="X27" s="267"/>
-      <c r="Y27" s="267"/>
-      <c r="Z27" s="267"/>
-      <c r="AA27" s="267"/>
-      <c r="AB27" s="267"/>
-      <c r="AC27" s="267"/>
-      <c r="AD27" s="267"/>
-      <c r="AE27" s="268"/>
-      <c r="AF27" s="263"/>
-      <c r="AG27" s="264"/>
-      <c r="AH27" s="264"/>
-      <c r="AI27" s="265"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="201"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="204"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="205"/>
+      <c r="I27" s="201"/>
+      <c r="J27" s="206"/>
+      <c r="K27" s="207"/>
+      <c r="L27" s="207"/>
+      <c r="M27" s="207"/>
+      <c r="N27" s="207"/>
+      <c r="O27" s="207"/>
+      <c r="P27" s="208"/>
+      <c r="Q27" s="209"/>
+      <c r="R27" s="210"/>
+      <c r="S27" s="210"/>
+      <c r="T27" s="210"/>
+      <c r="U27" s="210"/>
+      <c r="V27" s="210"/>
+      <c r="W27" s="210"/>
+      <c r="X27" s="210"/>
+      <c r="Y27" s="210"/>
+      <c r="Z27" s="210"/>
+      <c r="AA27" s="210"/>
+      <c r="AB27" s="210"/>
+      <c r="AC27" s="210"/>
+      <c r="AD27" s="210"/>
+      <c r="AE27" s="211"/>
+      <c r="AF27" s="206"/>
+      <c r="AG27" s="207"/>
+      <c r="AH27" s="207"/>
+      <c r="AI27" s="208"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="257"/>
-      <c r="C28" s="258"/>
-      <c r="D28" s="259"/>
-      <c r="E28" s="260"/>
-      <c r="F28" s="261"/>
-      <c r="G28" s="257"/>
-      <c r="H28" s="262"/>
-      <c r="I28" s="258"/>
-      <c r="J28" s="263"/>
-      <c r="K28" s="264"/>
-      <c r="L28" s="264"/>
-      <c r="M28" s="264"/>
-      <c r="N28" s="264"/>
-      <c r="O28" s="264"/>
-      <c r="P28" s="265"/>
-      <c r="Q28" s="266"/>
-      <c r="R28" s="267"/>
-      <c r="S28" s="267"/>
-      <c r="T28" s="267"/>
-      <c r="U28" s="267"/>
-      <c r="V28" s="267"/>
-      <c r="W28" s="267"/>
-      <c r="X28" s="267"/>
-      <c r="Y28" s="267"/>
-      <c r="Z28" s="267"/>
-      <c r="AA28" s="267"/>
-      <c r="AB28" s="267"/>
-      <c r="AC28" s="267"/>
-      <c r="AD28" s="267"/>
-      <c r="AE28" s="268"/>
-      <c r="AF28" s="263"/>
-      <c r="AG28" s="264"/>
-      <c r="AH28" s="264"/>
-      <c r="AI28" s="265"/>
+      <c r="B28" s="200"/>
+      <c r="C28" s="201"/>
+      <c r="D28" s="202"/>
+      <c r="E28" s="203"/>
+      <c r="F28" s="204"/>
+      <c r="G28" s="200"/>
+      <c r="H28" s="205"/>
+      <c r="I28" s="201"/>
+      <c r="J28" s="206"/>
+      <c r="K28" s="207"/>
+      <c r="L28" s="207"/>
+      <c r="M28" s="207"/>
+      <c r="N28" s="207"/>
+      <c r="O28" s="207"/>
+      <c r="P28" s="208"/>
+      <c r="Q28" s="209"/>
+      <c r="R28" s="210"/>
+      <c r="S28" s="210"/>
+      <c r="T28" s="210"/>
+      <c r="U28" s="210"/>
+      <c r="V28" s="210"/>
+      <c r="W28" s="210"/>
+      <c r="X28" s="210"/>
+      <c r="Y28" s="210"/>
+      <c r="Z28" s="210"/>
+      <c r="AA28" s="210"/>
+      <c r="AB28" s="210"/>
+      <c r="AC28" s="210"/>
+      <c r="AD28" s="210"/>
+      <c r="AE28" s="211"/>
+      <c r="AF28" s="206"/>
+      <c r="AG28" s="207"/>
+      <c r="AH28" s="207"/>
+      <c r="AI28" s="208"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="257"/>
-      <c r="C29" s="258"/>
-      <c r="D29" s="259"/>
-      <c r="E29" s="260"/>
-      <c r="F29" s="261"/>
-      <c r="G29" s="257"/>
-      <c r="H29" s="262"/>
-      <c r="I29" s="258"/>
-      <c r="J29" s="263"/>
-      <c r="K29" s="264"/>
-      <c r="L29" s="264"/>
-      <c r="M29" s="264"/>
-      <c r="N29" s="264"/>
-      <c r="O29" s="264"/>
-      <c r="P29" s="265"/>
-      <c r="Q29" s="266"/>
-      <c r="R29" s="267"/>
-      <c r="S29" s="267"/>
-      <c r="T29" s="267"/>
-      <c r="U29" s="267"/>
-      <c r="V29" s="267"/>
-      <c r="W29" s="267"/>
-      <c r="X29" s="267"/>
-      <c r="Y29" s="267"/>
-      <c r="Z29" s="267"/>
-      <c r="AA29" s="267"/>
-      <c r="AB29" s="267"/>
-      <c r="AC29" s="267"/>
-      <c r="AD29" s="267"/>
-      <c r="AE29" s="268"/>
-      <c r="AF29" s="263"/>
-      <c r="AG29" s="264"/>
-      <c r="AH29" s="264"/>
-      <c r="AI29" s="265"/>
+      <c r="B29" s="200"/>
+      <c r="C29" s="201"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="204"/>
+      <c r="G29" s="200"/>
+      <c r="H29" s="205"/>
+      <c r="I29" s="201"/>
+      <c r="J29" s="206"/>
+      <c r="K29" s="207"/>
+      <c r="L29" s="207"/>
+      <c r="M29" s="207"/>
+      <c r="N29" s="207"/>
+      <c r="O29" s="207"/>
+      <c r="P29" s="208"/>
+      <c r="Q29" s="209"/>
+      <c r="R29" s="210"/>
+      <c r="S29" s="210"/>
+      <c r="T29" s="210"/>
+      <c r="U29" s="210"/>
+      <c r="V29" s="210"/>
+      <c r="W29" s="210"/>
+      <c r="X29" s="210"/>
+      <c r="Y29" s="210"/>
+      <c r="Z29" s="210"/>
+      <c r="AA29" s="210"/>
+      <c r="AB29" s="210"/>
+      <c r="AC29" s="210"/>
+      <c r="AD29" s="210"/>
+      <c r="AE29" s="211"/>
+      <c r="AF29" s="206"/>
+      <c r="AG29" s="207"/>
+      <c r="AH29" s="207"/>
+      <c r="AI29" s="208"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="257"/>
-      <c r="C30" s="258"/>
-      <c r="D30" s="259"/>
-      <c r="E30" s="260"/>
-      <c r="F30" s="261"/>
-      <c r="G30" s="257"/>
-      <c r="H30" s="262"/>
-      <c r="I30" s="258"/>
-      <c r="J30" s="263"/>
-      <c r="K30" s="264"/>
-      <c r="L30" s="264"/>
-      <c r="M30" s="264"/>
-      <c r="N30" s="264"/>
-      <c r="O30" s="264"/>
-      <c r="P30" s="265"/>
-      <c r="Q30" s="266"/>
-      <c r="R30" s="267"/>
-      <c r="S30" s="267"/>
-      <c r="T30" s="267"/>
-      <c r="U30" s="267"/>
-      <c r="V30" s="267"/>
-      <c r="W30" s="267"/>
-      <c r="X30" s="267"/>
-      <c r="Y30" s="267"/>
-      <c r="Z30" s="267"/>
-      <c r="AA30" s="267"/>
-      <c r="AB30" s="267"/>
-      <c r="AC30" s="267"/>
-      <c r="AD30" s="267"/>
-      <c r="AE30" s="268"/>
-      <c r="AF30" s="263"/>
-      <c r="AG30" s="264"/>
-      <c r="AH30" s="264"/>
-      <c r="AI30" s="265"/>
+      <c r="B30" s="200"/>
+      <c r="C30" s="201"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="204"/>
+      <c r="G30" s="200"/>
+      <c r="H30" s="205"/>
+      <c r="I30" s="201"/>
+      <c r="J30" s="206"/>
+      <c r="K30" s="207"/>
+      <c r="L30" s="207"/>
+      <c r="M30" s="207"/>
+      <c r="N30" s="207"/>
+      <c r="O30" s="207"/>
+      <c r="P30" s="208"/>
+      <c r="Q30" s="209"/>
+      <c r="R30" s="210"/>
+      <c r="S30" s="210"/>
+      <c r="T30" s="210"/>
+      <c r="U30" s="210"/>
+      <c r="V30" s="210"/>
+      <c r="W30" s="210"/>
+      <c r="X30" s="210"/>
+      <c r="Y30" s="210"/>
+      <c r="Z30" s="210"/>
+      <c r="AA30" s="210"/>
+      <c r="AB30" s="210"/>
+      <c r="AC30" s="210"/>
+      <c r="AD30" s="210"/>
+      <c r="AE30" s="211"/>
+      <c r="AF30" s="206"/>
+      <c r="AG30" s="207"/>
+      <c r="AH30" s="207"/>
+      <c r="AI30" s="208"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="257"/>
-      <c r="C31" s="258"/>
-      <c r="D31" s="259"/>
-      <c r="E31" s="260"/>
-      <c r="F31" s="261"/>
-      <c r="G31" s="257"/>
-      <c r="H31" s="262"/>
-      <c r="I31" s="258"/>
-      <c r="J31" s="263"/>
-      <c r="K31" s="264"/>
-      <c r="L31" s="264"/>
-      <c r="M31" s="264"/>
-      <c r="N31" s="264"/>
-      <c r="O31" s="264"/>
-      <c r="P31" s="265"/>
-      <c r="Q31" s="266"/>
-      <c r="R31" s="267"/>
-      <c r="S31" s="267"/>
-      <c r="T31" s="267"/>
-      <c r="U31" s="267"/>
-      <c r="V31" s="267"/>
-      <c r="W31" s="267"/>
-      <c r="X31" s="267"/>
-      <c r="Y31" s="267"/>
-      <c r="Z31" s="267"/>
-      <c r="AA31" s="267"/>
-      <c r="AB31" s="267"/>
-      <c r="AC31" s="267"/>
-      <c r="AD31" s="267"/>
-      <c r="AE31" s="268"/>
-      <c r="AF31" s="263"/>
-      <c r="AG31" s="264"/>
-      <c r="AH31" s="264"/>
-      <c r="AI31" s="265"/>
+      <c r="B31" s="200"/>
+      <c r="C31" s="201"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="204"/>
+      <c r="G31" s="200"/>
+      <c r="H31" s="205"/>
+      <c r="I31" s="201"/>
+      <c r="J31" s="206"/>
+      <c r="K31" s="207"/>
+      <c r="L31" s="207"/>
+      <c r="M31" s="207"/>
+      <c r="N31" s="207"/>
+      <c r="O31" s="207"/>
+      <c r="P31" s="208"/>
+      <c r="Q31" s="209"/>
+      <c r="R31" s="210"/>
+      <c r="S31" s="210"/>
+      <c r="T31" s="210"/>
+      <c r="U31" s="210"/>
+      <c r="V31" s="210"/>
+      <c r="W31" s="210"/>
+      <c r="X31" s="210"/>
+      <c r="Y31" s="210"/>
+      <c r="Z31" s="210"/>
+      <c r="AA31" s="210"/>
+      <c r="AB31" s="210"/>
+      <c r="AC31" s="210"/>
+      <c r="AD31" s="210"/>
+      <c r="AE31" s="211"/>
+      <c r="AF31" s="206"/>
+      <c r="AG31" s="207"/>
+      <c r="AH31" s="207"/>
+      <c r="AI31" s="208"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="257"/>
-      <c r="C32" s="258"/>
-      <c r="D32" s="259"/>
-      <c r="E32" s="260"/>
-      <c r="F32" s="261"/>
-      <c r="G32" s="257"/>
-      <c r="H32" s="262"/>
-      <c r="I32" s="258"/>
-      <c r="J32" s="263"/>
-      <c r="K32" s="269"/>
-      <c r="L32" s="264"/>
-      <c r="M32" s="264"/>
-      <c r="N32" s="264"/>
-      <c r="O32" s="264"/>
-      <c r="P32" s="265"/>
-      <c r="Q32" s="266"/>
-      <c r="R32" s="267"/>
-      <c r="S32" s="267"/>
-      <c r="T32" s="267"/>
-      <c r="U32" s="267"/>
-      <c r="V32" s="267"/>
-      <c r="W32" s="267"/>
-      <c r="X32" s="267"/>
-      <c r="Y32" s="267"/>
-      <c r="Z32" s="267"/>
-      <c r="AA32" s="267"/>
-      <c r="AB32" s="267"/>
-      <c r="AC32" s="267"/>
-      <c r="AD32" s="267"/>
-      <c r="AE32" s="268"/>
-      <c r="AF32" s="263"/>
-      <c r="AG32" s="264"/>
-      <c r="AH32" s="264"/>
-      <c r="AI32" s="265"/>
+      <c r="B32" s="200"/>
+      <c r="C32" s="201"/>
+      <c r="D32" s="202"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="204"/>
+      <c r="G32" s="200"/>
+      <c r="H32" s="205"/>
+      <c r="I32" s="201"/>
+      <c r="J32" s="206"/>
+      <c r="K32" s="212"/>
+      <c r="L32" s="207"/>
+      <c r="M32" s="207"/>
+      <c r="N32" s="207"/>
+      <c r="O32" s="207"/>
+      <c r="P32" s="208"/>
+      <c r="Q32" s="209"/>
+      <c r="R32" s="210"/>
+      <c r="S32" s="210"/>
+      <c r="T32" s="210"/>
+      <c r="U32" s="210"/>
+      <c r="V32" s="210"/>
+      <c r="W32" s="210"/>
+      <c r="X32" s="210"/>
+      <c r="Y32" s="210"/>
+      <c r="Z32" s="210"/>
+      <c r="AA32" s="210"/>
+      <c r="AB32" s="210"/>
+      <c r="AC32" s="210"/>
+      <c r="AD32" s="210"/>
+      <c r="AE32" s="211"/>
+      <c r="AF32" s="206"/>
+      <c r="AG32" s="207"/>
+      <c r="AH32" s="207"/>
+      <c r="AI32" s="208"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="257"/>
-      <c r="C33" s="258"/>
-      <c r="D33" s="259"/>
-      <c r="E33" s="260"/>
-      <c r="F33" s="261"/>
-      <c r="G33" s="257"/>
-      <c r="H33" s="262"/>
-      <c r="I33" s="258"/>
-      <c r="J33" s="263"/>
-      <c r="K33" s="264"/>
-      <c r="L33" s="264"/>
-      <c r="M33" s="264"/>
-      <c r="N33" s="264"/>
-      <c r="O33" s="264"/>
-      <c r="P33" s="265"/>
-      <c r="Q33" s="266"/>
-      <c r="R33" s="267"/>
-      <c r="S33" s="267"/>
-      <c r="T33" s="267"/>
-      <c r="U33" s="267"/>
-      <c r="V33" s="267"/>
-      <c r="W33" s="267"/>
-      <c r="X33" s="267"/>
-      <c r="Y33" s="267"/>
-      <c r="Z33" s="267"/>
-      <c r="AA33" s="267"/>
-      <c r="AB33" s="267"/>
-      <c r="AC33" s="267"/>
-      <c r="AD33" s="267"/>
-      <c r="AE33" s="268"/>
-      <c r="AF33" s="263"/>
-      <c r="AG33" s="264"/>
-      <c r="AH33" s="264"/>
-      <c r="AI33" s="265"/>
+      <c r="B33" s="200"/>
+      <c r="C33" s="201"/>
+      <c r="D33" s="202"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="204"/>
+      <c r="G33" s="200"/>
+      <c r="H33" s="205"/>
+      <c r="I33" s="201"/>
+      <c r="J33" s="206"/>
+      <c r="K33" s="207"/>
+      <c r="L33" s="207"/>
+      <c r="M33" s="207"/>
+      <c r="N33" s="207"/>
+      <c r="O33" s="207"/>
+      <c r="P33" s="208"/>
+      <c r="Q33" s="209"/>
+      <c r="R33" s="210"/>
+      <c r="S33" s="210"/>
+      <c r="T33" s="210"/>
+      <c r="U33" s="210"/>
+      <c r="V33" s="210"/>
+      <c r="W33" s="210"/>
+      <c r="X33" s="210"/>
+      <c r="Y33" s="210"/>
+      <c r="Z33" s="210"/>
+      <c r="AA33" s="210"/>
+      <c r="AB33" s="210"/>
+      <c r="AC33" s="210"/>
+      <c r="AD33" s="210"/>
+      <c r="AE33" s="211"/>
+      <c r="AF33" s="206"/>
+      <c r="AG33" s="207"/>
+      <c r="AH33" s="207"/>
+      <c r="AI33" s="208"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -14053,6 +13898,161 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(Webサービス)_サンプル.xlsx
@@ -14211,8 +14211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -14254,8 +14254,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -14291,8 +14291,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -14330,8 +14330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -14365,8 +14365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -14400,8 +14400,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -14435,8 +14435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -14470,8 +14470,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -14509,8 +14509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -14544,8 +14544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -14579,8 +14579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -14616,8 +14616,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -14651,8 +14651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -14686,8 +14686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -14721,8 +14721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -14760,8 +14760,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -14795,8 +14795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -14834,8 +14834,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -14869,8 +14869,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -14906,8 +14906,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -14941,8 +14941,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -14976,8 +14976,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -15011,8 +15011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -15048,8 +15048,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -15083,8 +15083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -15120,8 +15120,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -15161,8 +15161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -15196,8 +15196,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -15231,8 +15231,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -15266,8 +15266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -15305,8 +15305,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -15340,8 +15340,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -15393,8 +15393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -15428,8 +15428,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -15463,8 +15463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -15500,8 +15500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -15535,8 +15535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -15570,8 +15570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -15607,8 +15607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -15642,8 +15642,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -15679,8 +15679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -15714,8 +15714,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -15749,8 +15749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -15784,8 +15784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -15819,8 +15819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -15854,8 +15854,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -15891,8 +15891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -15928,8 +15928,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -15965,8 +15965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -16004,8 +16004,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -16039,8 +16039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -16074,8 +16074,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -16109,8 +16109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -16144,8 +16144,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -16181,8 +16181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -16216,8 +16216,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -16251,8 +16251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -16286,8 +16286,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -16321,8 +16321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -16356,8 +16356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -16391,8 +16391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -16426,8 +16426,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -16463,8 +16463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -16500,8 +16500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -16535,8 +16535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -16570,8 +16570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -16605,8 +16605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -16640,8 +16640,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -16691,8 +16691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -16736,8 +16736,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -16773,8 +16773,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -16810,8 +16810,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -16845,8 +16845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -16882,8 +16882,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -16919,8 +16919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -16960,8 +16960,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -16997,8 +16997,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -17034,8 +17034,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -17075,8 +17075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -17108,8 +17108,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -17143,8 +17143,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -17180,8 +17180,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -17217,8 +17217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -17252,8 +17252,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -17289,8 +17289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -17330,8 +17330,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -17365,8 +17365,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -17400,8 +17400,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -17435,8 +17435,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -17470,8 +17470,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -17507,8 +17507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -17542,8 +17542,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -17577,8 +17577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -17612,8 +17612,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -17647,8 +17647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -17684,8 +17684,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -17727,8 +17727,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -17768,8 +17768,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -17803,8 +17803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -17844,8 +17844,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -17885,8 +17885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -17920,8 +17920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -17963,8 +17963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -18000,8 +18000,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -18035,8 +18035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -18070,8 +18070,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -18107,8 +18107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -18142,8 +18142,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -18177,8 +18177,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -18212,8 +18212,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -18247,8 +18247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -18284,8 +18284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -18319,8 +18319,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -18354,8 +18354,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -18389,8 +18389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -18424,8 +18424,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -18461,8 +18461,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -18500,8 +18500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -18541,8 +18541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -18578,8 +18578,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -18613,8 +18613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -18648,8 +18648,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -18691,8 +18691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -18728,8 +18728,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -18763,8 +18763,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -18798,8 +18798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -18835,8 +18835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -18870,8 +18870,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -18909,8 +18909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -18950,8 +18950,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -18987,8 +18987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -19024,8 +19024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -19061,8 +19061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -19098,8 +19098,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -19135,8 +19135,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -19170,8 +19170,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -19205,8 +19205,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -19240,8 +19240,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -19275,8 +19275,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -19310,8 +19310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -19349,8 +19349,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -19384,8 +19384,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -19421,8 +19421,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -19456,8 +19456,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -19491,8 +19491,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -19526,8 +19526,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -19561,8 +19561,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -19596,8 +19596,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -19631,8 +19631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -19666,8 +19666,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -19701,8 +19701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -19736,8 +19736,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -19771,8 +19771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -19808,8 +19808,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -19843,8 +19843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -19878,8 +19878,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -19913,8 +19913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -19948,8 +19948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -19983,8 +19983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -20018,8 +20018,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -20055,8 +20055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -20090,8 +20090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -20125,8 +20125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -20160,8 +20160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -20195,8 +20195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -20230,8 +20230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -20265,8 +20265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -20300,8 +20300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -20335,8 +20335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -20372,8 +20372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -20409,8 +20409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -20452,8 +20452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -20491,8 +20491,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -20530,8 +20530,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -20573,8 +20573,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -20610,8 +20610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -20645,8 +20645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -20682,8 +20682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -20717,8 +20717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -20756,8 +20756,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -20797,8 +20797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -20832,8 +20832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -20867,8 +20867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -20902,8 +20902,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -20937,8 +20937,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -20972,8 +20972,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -21007,8 +21007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -21044,8 +21044,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -21083,8 +21083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -21118,8 +21118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -21153,8 +21153,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -21188,8 +21188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -21223,8 +21223,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -21258,8 +21258,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -21293,8 +21293,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -21328,8 +21328,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -21363,8 +21363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -21398,8 +21398,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -21433,8 +21433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -21468,8 +21468,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -21503,8 +21503,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -21542,8 +21542,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -21577,8 +21577,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -21612,8 +21612,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -21647,8 +21647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -21682,8 +21682,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -21717,8 +21717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -21752,8 +21752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -21787,8 +21787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -21822,8 +21822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -21857,8 +21857,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -21892,8 +21892,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -21927,8 +21927,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -21962,8 +21962,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -21997,8 +21997,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -22032,8 +22032,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -22069,8 +22069,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -22104,8 +22104,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -22139,8 +22139,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -22176,8 +22176,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -22213,8 +22213,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -22256,8 +22256,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -22293,8 +22293,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -22328,8 +22328,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -22363,8 +22363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -22398,8 +22398,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -22433,8 +22433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -22470,8 +22470,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -22505,8 +22505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -22540,8 +22540,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -22575,8 +22575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -22610,8 +22610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -22647,8 +22647,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -22688,8 +22688,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -22731,8 +22731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -22766,8 +22766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -22805,8 +22805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -22840,8 +22840,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -22881,8 +22881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -22918,8 +22918,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -22955,8 +22955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -22992,8 +22992,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -23031,8 +23031,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -23066,8 +23066,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -23103,8 +23103,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -23138,8 +23138,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -23173,8 +23173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -23208,8 +23208,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -23243,8 +23243,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -23278,8 +23278,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -23313,8 +23313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -23348,8 +23348,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -23383,8 +23383,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -23418,8 +23418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -23453,8 +23453,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -23490,8 +23490,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -23525,8 +23525,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -23560,8 +23560,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -23595,8 +23595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -23630,8 +23630,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -23665,8 +23665,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -23702,8 +23702,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -23737,8 +23737,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -23772,8 +23772,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -23807,8 +23807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -23842,8 +23842,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -23877,8 +23877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -23912,8 +23912,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -23947,8 +23947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -23984,8 +23984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -24027,8 +24027,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -24062,8 +24062,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -24097,8 +24097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -24132,8 +24132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -24173,8 +24173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -24210,8 +24210,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -24247,8 +24247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -24284,8 +24284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -24323,8 +24323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -24358,8 +24358,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -24393,8 +24393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -24428,8 +24428,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -24463,8 +24463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -24498,8 +24498,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -24533,8 +24533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -24568,8 +24568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -24774,8 +24774,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -24817,8 +24817,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -24854,8 +24854,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -24893,8 +24893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -24928,8 +24928,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -24963,8 +24963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -24998,8 +24998,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -25033,8 +25033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -25072,8 +25072,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -25107,8 +25107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -25142,8 +25142,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -25179,8 +25179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -25214,8 +25214,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -25249,8 +25249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -25284,8 +25284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -25323,8 +25323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -25358,8 +25358,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -25397,8 +25397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -25432,8 +25432,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -25469,8 +25469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -25504,8 +25504,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -25539,8 +25539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -25574,8 +25574,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -25611,8 +25611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -25646,8 +25646,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -25683,8 +25683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -25724,8 +25724,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -25759,8 +25759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -25794,8 +25794,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -25829,8 +25829,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -25868,8 +25868,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -25903,8 +25903,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -25946,8 +25946,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -25981,8 +25981,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -26016,8 +26016,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -26053,8 +26053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -26088,8 +26088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -26123,8 +26123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -26160,8 +26160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -26195,8 +26195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -26232,8 +26232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -26267,8 +26267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -26302,8 +26302,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -26337,8 +26337,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -26372,8 +26372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -26407,8 +26407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -26444,8 +26444,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -26481,8 +26481,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -26518,8 +26518,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -26557,8 +26557,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -26592,8 +26592,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -26627,8 +26627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -26662,8 +26662,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -26697,8 +26697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -26734,8 +26734,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -26769,8 +26769,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -26804,8 +26804,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -26839,8 +26839,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -26874,8 +26874,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -26909,8 +26909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -26944,8 +26944,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -26979,8 +26979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -27016,8 +27016,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -27053,8 +27053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -27088,8 +27088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -27123,8 +27123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -27158,8 +27158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -27193,8 +27193,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -27234,8 +27234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -27269,8 +27269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -27306,8 +27306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -27343,8 +27343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -27378,8 +27378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -27415,8 +27415,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -27452,8 +27452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -27493,8 +27493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -27530,8 +27530,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -27567,8 +27567,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -27608,8 +27608,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -27643,8 +27643,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -27680,8 +27680,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -27717,8 +27717,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -27752,8 +27752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -27789,8 +27789,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -27830,8 +27830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -27865,8 +27865,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -27900,8 +27900,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -27935,8 +27935,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -27970,8 +27970,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -28007,8 +28007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -28042,8 +28042,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -28077,8 +28077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -28112,8 +28112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -28147,8 +28147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -28184,8 +28184,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -28227,8 +28227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -28268,8 +28268,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -28303,8 +28303,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -28344,8 +28344,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -28385,8 +28385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -28420,8 +28420,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -28463,8 +28463,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -28500,8 +28500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -28535,8 +28535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -28570,8 +28570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -28607,8 +28607,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -28642,8 +28642,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -28677,8 +28677,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -28712,8 +28712,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -28747,8 +28747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -28784,8 +28784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -28819,8 +28819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -28854,8 +28854,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -28889,8 +28889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -28924,8 +28924,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -28961,8 +28961,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -29000,8 +29000,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -29041,8 +29041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -29078,8 +29078,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -29113,8 +29113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -29148,8 +29148,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -29191,8 +29191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -29228,8 +29228,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -29263,8 +29263,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -29298,8 +29298,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -29335,8 +29335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -29370,8 +29370,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -29409,8 +29409,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -29450,8 +29450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -29487,8 +29487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -29524,8 +29524,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -29561,8 +29561,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -29598,8 +29598,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -29635,8 +29635,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -29670,8 +29670,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -29705,8 +29705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -29740,8 +29740,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -29775,8 +29775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -29810,8 +29810,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -29849,8 +29849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -29884,8 +29884,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -29921,8 +29921,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -29956,8 +29956,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -29991,8 +29991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -30026,8 +30026,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -30061,8 +30061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -30096,8 +30096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -30131,8 +30131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -30166,8 +30166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -30201,8 +30201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -30236,8 +30236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -30271,8 +30271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -30308,8 +30308,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -30343,8 +30343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -30378,8 +30378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -30413,8 +30413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -30448,8 +30448,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -30483,8 +30483,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -30518,8 +30518,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -30555,8 +30555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -30590,8 +30590,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -30625,8 +30625,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -30660,8 +30660,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -30695,8 +30695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -30730,8 +30730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -30765,8 +30765,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -30800,8 +30800,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -30835,8 +30835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -30872,8 +30872,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -30909,8 +30909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -30952,8 +30952,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -30991,8 +30991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -31030,8 +31030,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -31073,8 +31073,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -31110,8 +31110,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -31145,8 +31145,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -31182,8 +31182,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -31217,8 +31217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -31256,8 +31256,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -31297,8 +31297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -31332,8 +31332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -31367,8 +31367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -31402,8 +31402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -31437,8 +31437,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -31472,8 +31472,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -31507,8 +31507,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -31544,8 +31544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -31583,8 +31583,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -31618,8 +31618,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -31653,8 +31653,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -31688,8 +31688,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -31723,8 +31723,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -31758,8 +31758,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -31793,8 +31793,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -31828,8 +31828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -31863,8 +31863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -31898,8 +31898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -31933,8 +31933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -31968,8 +31968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -32003,8 +32003,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -32042,8 +32042,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -32077,8 +32077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -32112,8 +32112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -32147,8 +32147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -32182,8 +32182,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -32217,8 +32217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -32252,8 +32252,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -32287,8 +32287,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -32322,8 +32322,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -32357,8 +32357,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -32392,8 +32392,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -32427,8 +32427,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -32462,8 +32462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -32497,8 +32497,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -32532,8 +32532,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -32569,8 +32569,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -32604,8 +32604,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -32639,8 +32639,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -32676,8 +32676,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -32713,8 +32713,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -32756,8 +32756,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -32793,8 +32793,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -32828,8 +32828,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -32863,8 +32863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -32898,8 +32898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -32933,8 +32933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -32970,8 +32970,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -33005,8 +33005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -33040,8 +33040,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -33075,8 +33075,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -33110,8 +33110,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -33147,8 +33147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -33188,8 +33188,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -33231,8 +33231,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -33266,8 +33266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -33305,8 +33305,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -33340,8 +33340,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -33381,8 +33381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -33418,8 +33418,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -33455,8 +33455,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -33492,8 +33492,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -33531,8 +33531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -33566,8 +33566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -33603,8 +33603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -33638,8 +33638,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -33673,8 +33673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -33708,8 +33708,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -33743,8 +33743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -33778,8 +33778,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -33813,8 +33813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -33848,8 +33848,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -33883,8 +33883,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -33918,8 +33918,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -33953,8 +33953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -33990,8 +33990,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -34025,8 +34025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -34060,8 +34060,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -34095,8 +34095,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -34130,8 +34130,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -34165,8 +34165,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -34202,8 +34202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -34237,8 +34237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -34272,8 +34272,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -34307,8 +34307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -34342,8 +34342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -34377,8 +34377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -34412,8 +34412,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -34447,8 +34447,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -34484,8 +34484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -34527,8 +34527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -34562,8 +34562,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -34597,8 +34597,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -34632,8 +34632,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -34673,8 +34673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -34710,8 +34710,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -34747,8 +34747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -34784,8 +34784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -34823,8 +34823,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -34858,8 +34858,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -34893,8 +34893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -34928,8 +34928,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -34963,8 +34963,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -34998,8 +34998,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -35033,8 +35033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -35068,8 +35068,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -35103,8 +35103,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -35146,8 +35146,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -35195,8 +35195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-2</v>
       </c>
@@ -35234,8 +35234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -35283,8 +35283,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-2-1</v>
       </c>
@@ -35328,8 +35328,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-3-1</v>
       </c>
@@ -35363,8 +35363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -35402,8 +35402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -35439,8 +35439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -35488,8 +35488,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-2-1</v>
       </c>
@@ -35523,8 +35523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-3-1</v>
       </c>
@@ -35558,8 +35558,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-4-1</v>
       </c>
@@ -35593,8 +35593,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-5-1</v>
       </c>
@@ -35628,8 +35628,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-6-1</v>
       </c>
@@ -35663,8 +35663,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-7-1</v>
       </c>
@@ -35698,8 +35698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-8-1</v>
       </c>
@@ -35895,11 +35895,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C11),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C11)&gt;0)*ROW($C$11:C11),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D11),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -35936,11 +35936,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C12),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C12)&gt;0)*ROW($C$11:C12),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D12),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-2-1</v>
       </c>
